--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -16,7 +16,8 @@
     <sheet name="국내SCHD형_분배" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="국내SCHD형_비교" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="구성종목" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="차트데이터" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="주가_월별" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="차트데이터" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -660,7 +661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1025" uniqueCount="528">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="716">
   <si>
     <r>
       <rPr>
@@ -7449,16 +7450,42 @@
     <t xml:space="preserve">DJIA MINI e-CBOT DEC 26</t>
   </si>
   <si>
-    <t xml:space="preserve">라벨</t>
-  </si>
-  <si>
-    <t xml:space="preserve">확정 배당</t>
-  </si>
-  <si>
-    <t xml:space="preserve">예상 배당</t>
-  </si>
-  <si>
-    <t xml:space="preserve">전체 평균</t>
+    <t xml:space="preserve">월</t>
+  </si>
+  <si>
+    <t xml:space="preserve">월말 거래일</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">종가</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FFFFFFFF"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(USD)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">배당 재투자 지수</t>
+  </si>
+  <si>
+    <t xml:space="preserve">종가 전년 대비</t>
+  </si>
+  <si>
+    <t xml:space="preserve">재투자 전년 대비</t>
   </si>
   <si>
     <r>
@@ -7468,7 +7495,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">분기 차트용 표</t>
+      <t xml:space="preserve">출처</t>
     </r>
     <r>
       <rPr>
@@ -7478,7 +7505,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">. </t>
+      <t xml:space="preserve">: Yahoo Finance (</t>
     </r>
     <r>
       <rPr>
@@ -7487,7 +7514,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">예상 배당 </t>
+      <t xml:space="preserve">종가</t>
     </r>
     <r>
       <rPr>
@@ -7497,7 +7524,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">= </t>
+      <t xml:space="preserve">: </t>
     </r>
     <r>
       <rPr>
@@ -7506,7 +7533,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">올해</t>
+      <t xml:space="preserve">주식분할 반영</t>
     </r>
     <r>
       <rPr>
@@ -7516,7 +7543,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(</t>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -7525,7 +7552,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">데이터가 있는 마지막 연도</t>
+      <t xml:space="preserve">배당 미조정 </t>
     </r>
     <r>
       <rPr>
@@ -7535,6 +7562,705 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
+      <t xml:space="preserve">/ adj: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">배당 재투자 반영 수정주가</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">) · </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기준일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2026-10-02 · 3:1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분할</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2024-10-11) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">반영 가격</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2011-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2012-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2013-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2014-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2015-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2016-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2018-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2020-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2021-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2023-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">라벨</t>
+  </si>
+  <si>
+    <t xml:space="preserve">확정 배당</t>
+  </si>
+  <si>
+    <t xml:space="preserve">예상 배당</t>
+  </si>
+  <si>
+    <t xml:space="preserve">전체 평균</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">분기 차트용 표</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">예상 배당 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">= </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">올해</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">데이터가 있는 마지막 연도</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF666666"/>
+        <rFont val="맑은 고딕"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
       <t xml:space="preserve">) </t>
     </r>
     <r>
@@ -7732,7 +8458,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="21">
+  <numFmts count="23">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="0"/>
@@ -7754,6 +8480,8 @@
     <numFmt numFmtId="182" formatCode="0.00%"/>
     <numFmt numFmtId="183" formatCode="0.0000%"/>
     <numFmt numFmtId="184" formatCode="#,##0\원;\-#,##0\원;\-"/>
+    <numFmt numFmtId="185" formatCode="0.0000"/>
+    <numFmt numFmtId="186" formatCode="\$0"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -7932,7 +8660,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F2A44"/>
-        <bgColor rgb="FF003366"/>
+        <bgColor rgb="FF16232C"/>
       </patternFill>
     </fill>
     <fill>
@@ -7991,7 +8719,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="79">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8296,6 +9024,14 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="171" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="185" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -8361,7 +9097,7 @@
       <rgbColor rgb="FF4F7FAF"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF4E9E72"/>
-      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF16232C"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
       <rgbColor rgb="FF666666"/>
@@ -9117,8 +9853,8 @@
         </c:ser>
         <c:gapWidth val="40"/>
         <c:overlap val="100"/>
-        <c:axId val="68490695"/>
-        <c:axId val="86662195"/>
+        <c:axId val="46553738"/>
+        <c:axId val="28528609"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -9575,11 +10311,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="68490695"/>
-        <c:axId val="86662195"/>
+        <c:axId val="46553738"/>
+        <c:axId val="28528609"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="68490695"/>
+        <c:axId val="46553738"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9612,7 +10348,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="86662195"/>
+        <c:crossAx val="28528609"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -9620,7 +10356,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="86662195"/>
+        <c:axId val="28528609"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -9663,7 +10399,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="68490695"/>
+        <c:crossAx val="46553738"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10063,8 +10799,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="73700406"/>
-        <c:axId val="21111900"/>
+        <c:axId val="68796494"/>
+        <c:axId val="91782959"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="stacked"/>
@@ -10425,11 +11161,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="73700406"/>
-        <c:axId val="21111900"/>
+        <c:axId val="68796494"/>
+        <c:axId val="91782959"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="73700406"/>
+        <c:axId val="68796494"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10462,7 +11198,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="21111900"/>
+        <c:crossAx val="91782959"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10470,7 +11206,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="21111900"/>
+        <c:axId val="91782959"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10503,7 +11239,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="73700406"/>
+        <c:crossAx val="68796494"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10897,8 +11633,8 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="6293981"/>
-        <c:axId val="44580402"/>
+        <c:axId val="91131650"/>
+        <c:axId val="21810884"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -11086,11 +11822,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="6293981"/>
-        <c:axId val="44580402"/>
+        <c:axId val="91131650"/>
+        <c:axId val="21810884"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="6293981"/>
+        <c:axId val="91131650"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11123,7 +11859,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="44580402"/>
+        <c:crossAx val="21810884"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11131,7 +11867,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="44580402"/>
+        <c:axId val="21810884"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11174,7 +11910,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6293981"/>
+        <c:crossAx val="91131650"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11862,6 +12598,1343 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1300" b="0" u="none" strike="noStrike">
+                <a:uFillTx/>
+                <a:latin typeface="Arial"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1800" b="1" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:rPr>
+              <a:t>SCHD 월말 종가 (USD)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>주가_월별!C1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>종가(USD)</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="16232C"/>
+            </a:solidFill>
+            <a:ln w="19080">
+              <a:solidFill>
+                <a:srgbClr val="16232C"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="none"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                    <a:uFillTx/>
+                    <a:latin typeface="Arial"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:separator> </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="19080">
+                  <a:solidFill>
+                    <a:srgbClr val="000000"/>
+                  </a:solidFill>
+                </a:ln>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>주가_월별!$A$2:$A$182</c:f>
+              <c:strCache>
+                <c:ptCount val="181"/>
+                <c:pt idx="0">
+                  <c:v>2011-10</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2011-11</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2011-12</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2012-01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2012-02</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2012-03</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2012-04</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2012-05</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>2012-06</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2012-07</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2012-08</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2012-09</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2012-10</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2012-11</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2012-12</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>2013-01</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>2013-02</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2013-03</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2013-04</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>2013-05</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2013-06</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>2013-07</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>2013-08</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>2013-09</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>2013-10</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2013-11</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2013-12</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>2014-01</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2014-02</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2014-03</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>2014-04</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2014-05</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2014-06</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2014-07</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>2014-08</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>2014-09</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2014-10</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2014-11</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>2014-12</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2015-01</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>2015-02</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2015-03</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>2015-04</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>2015-05</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2015-06</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2015-07</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>2015-08</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2015-09</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2015-10</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>2015-11</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2015-12</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>2016-01</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2016-02</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>2016-03</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>2016-04</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2016-05</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2016-06</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2016-07</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2016-08</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>2016-09</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2016-10</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2016-11</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>2016-12</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2017-01</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2017-02</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>2017-03</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2017-04</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2017-05</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>2017-06</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2017-07</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2017-08</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2017-09</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2017-10</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2017-11</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2017-12</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>2018-01</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>2018-02</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2018-03</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>2018-04</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>2018-05</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>2018-06</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>2018-07</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>2018-08</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>2018-09</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2018-10</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>2018-11</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>2018-12</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>2019-01</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>2019-02</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>2019-03</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>2019-04</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>2019-05</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>2019-06</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>2019-07</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>2019-08</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>2019-09</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>2019-10</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>2019-11</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>2019-12</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>2020-01</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>2020-02</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>2020-03</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>2020-04</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>2020-05</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>2020-06</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>2020-07</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>2020-08</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>2020-09</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>2020-10</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>2020-11</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>2020-12</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>2021-01</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>2021-02</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>2021-03</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>2021-04</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>2021-05</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>2021-06</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>2021-07</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>2021-08</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>2021-09</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>2021-10</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>2021-11</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>2021-12</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>2022-01</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>2022-02</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>2022-03</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>2022-04</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>2022-05</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>2022-06</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>2022-07</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>2022-08</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>2022-09</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>2022-10</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>2022-11</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>2022-12</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>2023-01</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>2023-02</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>2023-03</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>2023-04</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>2023-05</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>2023-06</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>2023-07</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>2023-08</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>2023-09</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>2023-10</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>2023-11</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>2023-12</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>2024-01</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>2024-02</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>2024-03</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>2024-04</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>2024-05</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>2024-06</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>2024-07</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>2024-08</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>2024-09</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>2024-10</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>2024-11</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>2024-12</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>2025-01</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>2025-02</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>2025-03</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>2025-04</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>2025-05</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>2025-06</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>2025-07</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>2025-08</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>2025-09</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>2025-10</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>2025-11</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>2025-12</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>2026-01</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>2026-02</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>2026-03</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>2026-04</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>2026-05</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>2026-06</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>2026-07</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>2026-08</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>2026-09</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>2026-10</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>주가_월별!$C$2:$C$182</c:f>
+              <c:numCache>
+                <c:formatCode>\$0.00</c:formatCode>
+                <c:ptCount val="181"/>
+                <c:pt idx="0">
+                  <c:v>8.5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>8.64</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.7267</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8.87</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9.1233</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>9.2967</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>9.2867</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>8.9333</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>9.2533</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>9.48</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>9.5367</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.5833</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>9.4933</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>9.5367</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>9.4467</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>9.97</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>10.18</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>10.5967</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10.9133</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>11.0667</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>10.9</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>11.4</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>10.9967</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>11.2167</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>11.7767</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12.0767</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>12.22</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>11.6767</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>12.13</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>12.2833</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>12.5067</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>12.6733</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>12.7567</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>12.5367</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>12.9667</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>12.8533</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>13.1067</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>13.4967</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>13.2833</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>12.87</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>13.5433</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>13.1367</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>13.2367</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>13.3033</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>12.7633</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>12.8533</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>12.17</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>11.9833</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>13.0333</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>13.07</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>12.8533</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>12.56</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>12.6533</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>13.3633</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>13.34</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>13.5267</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>13.8133</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>14.2067</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>14.16</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>14.1033</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>13.8833</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>14.3367</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>14.5233</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>14.4533</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>14.9467</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>14.86</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>14.8967</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>15.1567</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>15.0333</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>15.2833</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>15.28</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>15.6</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>16.1633</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>16.8433</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>17.0567</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>17.8333</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>16.83</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>16.3433</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>16.16</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>16.45</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>16.43</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>17.1767</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>17.57</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>17.6667</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>16.6233</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>17.1833</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>15.6567</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>16.6033</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>17.2767</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>17.4267</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>17.9867</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>16.62</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>17.69</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>17.9833</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>17.75</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>18.26</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>18.5067</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>19.03</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>19.3067</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>18.9667</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>17.1933</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>14.9933</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>16.8833</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>17.5067</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>17.25</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>18.1633</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>19.0933</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>18.4333</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>18.5033</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>20.94</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>21.38</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>21.1867</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>22.47</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>24.3067</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>24.8433</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>25.6433</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>25.2067</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>25.37</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>25.9</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>24.7467</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>25.8367</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>25.3067</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>26.9433</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>26.2067</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>25.7</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>26.2967</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>25.2133</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>26.1967</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>23.8767</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>24.81</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>24.1333</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>22.1433</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>24.6267</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>26.31</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>25.18</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>25.7033</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>24.85</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>24.3867</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>24.19</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>23.1967</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>24.2067</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>25.22</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>24.8433</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>23.5867</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>22.6867</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>24.1167</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>25.3767</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>25.4133</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>25.88</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>26.8767</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>25.6633</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>26.19</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>25.92</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>27.5267</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>28.1767</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>28.1767</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>28.23</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>29.53</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>27.32</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>27.83</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>28.54</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>27.96</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>25.82</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>26.17</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>26.5</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>27.92</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>27.3</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>26.75</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>27.59</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>27.43</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>29.82</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>31.77</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>30.68</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>32.07</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>32.5</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>31.71</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>33.47</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>34.89</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>32.53</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>32.72</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:hiLowLines>
+          <c:spPr>
+            <a:ln w="0">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+        </c:hiLowLines>
+        <c:marker val="0"/>
+        <c:axId val="95167768"/>
+        <c:axId val="2628601"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="95167768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2628601"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2628601"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9360">
+              <a:solidFill>
+                <a:srgbClr val="878787"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="\$0" sourceLinked="0"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:ln w="9360">
+            <a:solidFill>
+              <a:srgbClr val="878787"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1000" b="0" u="none" strike="noStrike">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
+                <a:uFillTx/>
+                <a:latin typeface="Calibri"/>
+              </a:defRPr>
+            </a:pPr>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="95167768"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:solidFill>
+          <a:srgbClr val="FFFFFF"/>
+        </a:solidFill>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="FFFFFF"/>
+    </a:solidFill>
+    <a:ln w="9360">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -11881,6 +13954,12 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
 </cs:colorStyle>
@@ -12726,6 +14805,216 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="419">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataLabel>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointMarkerLayout>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor"/>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <xdr:twoCellAnchor editAs="oneCell">
@@ -12849,6 +15138,41 @@
       <xdr:xfrm>
         <a:off x="16590600" y="655200"/>
         <a:ext cx="5039640" cy="3599640"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>187200</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>1080</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame>
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 1"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="5545440" y="619200"/>
+        <a:ext cx="9359640" cy="3239640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -13260,6 +15584,1434 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:G61"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="E1" s="28" t="s">
+        <v>653</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>654</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="51" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B2" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="51" t="s">
+        <v>656</v>
+      </c>
+      <c r="D2" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A2,SCHD_배당!$B$2:$B$90,B2)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A2,SCHD_배당!$B$2:$B$90,B2))</f>
+        <v>0.046</v>
+      </c>
+      <c r="E2" s="34" t="str">
+        <f aca="false">IF(AND(D2="",A2=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A2)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A2)/COUNTIFS(SCHD_배당!$A$2:$A$90,A2),"")</f>
+        <v/>
+      </c>
+      <c r="F2" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="51" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B3" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" s="51" t="s">
+        <v>657</v>
+      </c>
+      <c r="D3" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A3,SCHD_배당!$B$2:$B$90,B3)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A3,SCHD_배당!$B$2:$B$90,B3))</f>
+        <v>0.0687</v>
+      </c>
+      <c r="E3" s="34" t="str">
+        <f aca="false">IF(AND(D3="",A3=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A3)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A3)/COUNTIFS(SCHD_배당!$A$2:$A$90,A3),"")</f>
+        <v/>
+      </c>
+      <c r="F3" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="51" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B4" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" s="51" t="s">
+        <v>658</v>
+      </c>
+      <c r="D4" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A4,SCHD_배당!$B$2:$B$90,B4)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A4,SCHD_배당!$B$2:$B$90,B4))</f>
+        <v>0.0693</v>
+      </c>
+      <c r="E4" s="34" t="str">
+        <f aca="false">IF(AND(D4="",A4=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A4)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A4)/COUNTIFS(SCHD_배당!$A$2:$A$90,A4),"")</f>
+        <v/>
+      </c>
+      <c r="F4" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="51" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B5" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" s="51" t="s">
+        <v>659</v>
+      </c>
+      <c r="D5" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A5,SCHD_배당!$B$2:$B$90,B5)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A5,SCHD_배당!$B$2:$B$90,B5))</f>
+        <v>0.086</v>
+      </c>
+      <c r="E5" s="34" t="str">
+        <f aca="false">IF(AND(D5="",A5=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A5)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A5)/COUNTIFS(SCHD_배당!$A$2:$A$90,A5),"")</f>
+        <v/>
+      </c>
+      <c r="F5" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="51" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B6" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="51" t="s">
+        <v>660</v>
+      </c>
+      <c r="D6" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A6,SCHD_배당!$B$2:$B$90,B6)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A6,SCHD_배당!$B$2:$B$90,B6))</f>
+        <v>0.0664</v>
+      </c>
+      <c r="E6" s="34" t="str">
+        <f aca="false">IF(AND(D6="",A6=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A6)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A6)/COUNTIFS(SCHD_배당!$A$2:$A$90,A6),"")</f>
+        <v/>
+      </c>
+      <c r="F6" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="51" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B7" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" s="51" t="s">
+        <v>661</v>
+      </c>
+      <c r="D7" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A7,SCHD_배당!$B$2:$B$90,B7)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A7,SCHD_배당!$B$2:$B$90,B7))</f>
+        <v>0.075</v>
+      </c>
+      <c r="E7" s="34" t="str">
+        <f aca="false">IF(AND(D7="",A7=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A7)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A7)/COUNTIFS(SCHD_배당!$A$2:$A$90,A7),"")</f>
+        <v/>
+      </c>
+      <c r="F7" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="51" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B8" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="51" t="s">
+        <v>662</v>
+      </c>
+      <c r="D8" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A8,SCHD_배당!$B$2:$B$90,B8)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A8,SCHD_배당!$B$2:$B$90,B8))</f>
+        <v>0.0769</v>
+      </c>
+      <c r="E8" s="34" t="str">
+        <f aca="false">IF(AND(D8="",A8=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A8)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A8)/COUNTIFS(SCHD_배당!$A$2:$A$90,A8),"")</f>
+        <v/>
+      </c>
+      <c r="F8" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="51" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B9" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="51" t="s">
+        <v>663</v>
+      </c>
+      <c r="D9" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A9,SCHD_배당!$B$2:$B$90,B9)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A9,SCHD_배당!$B$2:$B$90,B9))</f>
+        <v>0.083</v>
+      </c>
+      <c r="E9" s="34" t="str">
+        <f aca="false">IF(AND(D9="",A9=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A9)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A9)/COUNTIFS(SCHD_배당!$A$2:$A$90,A9),"")</f>
+        <v/>
+      </c>
+      <c r="F9" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="51" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B10" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" s="51" t="s">
+        <v>664</v>
+      </c>
+      <c r="D10" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A10,SCHD_배당!$B$2:$B$90,B10)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A10,SCHD_배당!$B$2:$B$90,B10))</f>
+        <v>0.0826</v>
+      </c>
+      <c r="E10" s="34" t="str">
+        <f aca="false">IF(AND(D10="",A10=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A10)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A10)/COUNTIFS(SCHD_배당!$A$2:$A$90,A10),"")</f>
+        <v/>
+      </c>
+      <c r="F10" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="51" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B11" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" s="51" t="s">
+        <v>665</v>
+      </c>
+      <c r="D11" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A11,SCHD_배당!$B$2:$B$90,B11)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A11,SCHD_배당!$B$2:$B$90,B11))</f>
+        <v>0.0898</v>
+      </c>
+      <c r="E11" s="34" t="str">
+        <f aca="false">IF(AND(D11="",A11=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A11)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A11)/COUNTIFS(SCHD_배당!$A$2:$A$90,A11),"")</f>
+        <v/>
+      </c>
+      <c r="F11" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="51" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B12" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" s="51" t="s">
+        <v>666</v>
+      </c>
+      <c r="D12" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A12,SCHD_배당!$B$2:$B$90,B12)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A12,SCHD_배당!$B$2:$B$90,B12))</f>
+        <v>0.0848</v>
+      </c>
+      <c r="E12" s="34" t="str">
+        <f aca="false">IF(AND(D12="",A12=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A12)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A12)/COUNTIFS(SCHD_배당!$A$2:$A$90,A12),"")</f>
+        <v/>
+      </c>
+      <c r="F12" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="51" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B13" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="51" t="s">
+        <v>667</v>
+      </c>
+      <c r="D13" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A13,SCHD_배당!$B$2:$B$90,B13)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A13,SCHD_배당!$B$2:$B$90,B13))</f>
+        <v>0.0918</v>
+      </c>
+      <c r="E13" s="34" t="str">
+        <f aca="false">IF(AND(D13="",A13=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A13)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A13)/COUNTIFS(SCHD_배당!$A$2:$A$90,A13),"")</f>
+        <v/>
+      </c>
+      <c r="F13" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="51" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B14" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>668</v>
+      </c>
+      <c r="D14" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A14,SCHD_배당!$B$2:$B$90,B14)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A14,SCHD_배당!$B$2:$B$90,B14))</f>
+        <v>0.09</v>
+      </c>
+      <c r="E14" s="34" t="str">
+        <f aca="false">IF(AND(D14="",A14=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A14)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A14)/COUNTIFS(SCHD_배당!$A$2:$A$90,A14),"")</f>
+        <v/>
+      </c>
+      <c r="F14" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="51" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B15" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="51" t="s">
+        <v>669</v>
+      </c>
+      <c r="D15" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A15,SCHD_배당!$B$2:$B$90,B15)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A15,SCHD_배당!$B$2:$B$90,B15))</f>
+        <v>0.1021</v>
+      </c>
+      <c r="E15" s="34" t="str">
+        <f aca="false">IF(AND(D15="",A15=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A15)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A15)/COUNTIFS(SCHD_배당!$A$2:$A$90,A15),"")</f>
+        <v/>
+      </c>
+      <c r="F15" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="51" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B16" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" s="51" t="s">
+        <v>670</v>
+      </c>
+      <c r="D16" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A16,SCHD_배당!$B$2:$B$90,B16)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A16,SCHD_배당!$B$2:$B$90,B16))</f>
+        <v>0.0996</v>
+      </c>
+      <c r="E16" s="34" t="str">
+        <f aca="false">IF(AND(D16="",A16=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A16)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A16)/COUNTIFS(SCHD_배당!$A$2:$A$90,A16),"")</f>
+        <v/>
+      </c>
+      <c r="F16" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="51" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B17" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C17" s="51" t="s">
+        <v>671</v>
+      </c>
+      <c r="D17" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A17,SCHD_배당!$B$2:$B$90,B17)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A17,SCHD_배당!$B$2:$B$90,B17))</f>
+        <v>0.0905</v>
+      </c>
+      <c r="E17" s="34" t="str">
+        <f aca="false">IF(AND(D17="",A17=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A17)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A17)/COUNTIFS(SCHD_배당!$A$2:$A$90,A17),"")</f>
+        <v/>
+      </c>
+      <c r="F17" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="51" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B18" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" s="51" t="s">
+        <v>672</v>
+      </c>
+      <c r="D18" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A18,SCHD_배당!$B$2:$B$90,B18)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A18,SCHD_배당!$B$2:$B$90,B18))</f>
+        <v>0.0994</v>
+      </c>
+      <c r="E18" s="34" t="str">
+        <f aca="false">IF(AND(D18="",A18=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A18)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A18)/COUNTIFS(SCHD_배당!$A$2:$A$90,A18),"")</f>
+        <v/>
+      </c>
+      <c r="F18" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="51" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B19" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="51" t="s">
+        <v>673</v>
+      </c>
+      <c r="D19" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A19,SCHD_배당!$B$2:$B$90,B19)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A19,SCHD_배당!$B$2:$B$90,B19))</f>
+        <v>0.1058</v>
+      </c>
+      <c r="E19" s="34" t="str">
+        <f aca="false">IF(AND(D19="",A19=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A19)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A19)/COUNTIFS(SCHD_배당!$A$2:$A$90,A19),"")</f>
+        <v/>
+      </c>
+      <c r="F19" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="51" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B20" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>674</v>
+      </c>
+      <c r="D20" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A20,SCHD_배당!$B$2:$B$90,B20)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A20,SCHD_배당!$B$2:$B$90,B20))</f>
+        <v>0.0813</v>
+      </c>
+      <c r="E20" s="34" t="str">
+        <f aca="false">IF(AND(D20="",A20=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A20)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A20)/COUNTIFS(SCHD_배당!$A$2:$A$90,A20),"")</f>
+        <v/>
+      </c>
+      <c r="F20" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="51" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B21" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C21" s="51" t="s">
+        <v>675</v>
+      </c>
+      <c r="D21" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A21,SCHD_배당!$B$2:$B$90,B21)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A21,SCHD_배당!$B$2:$B$90,B21))</f>
+        <v>0.1329</v>
+      </c>
+      <c r="E21" s="34" t="str">
+        <f aca="false">IF(AND(D21="",A21=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A21)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A21)/COUNTIFS(SCHD_배당!$A$2:$A$90,A21),"")</f>
+        <v/>
+      </c>
+      <c r="F21" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="51" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B22" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="51" t="s">
+        <v>676</v>
+      </c>
+      <c r="D22" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A22,SCHD_배당!$B$2:$B$90,B22)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A22,SCHD_배당!$B$2:$B$90,B22))</f>
+        <v>0.1086</v>
+      </c>
+      <c r="E22" s="34" t="str">
+        <f aca="false">IF(AND(D22="",A22=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A22)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A22)/COUNTIFS(SCHD_배당!$A$2:$A$90,A22),"")</f>
+        <v/>
+      </c>
+      <c r="F22" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="51" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B23" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C23" s="51" t="s">
+        <v>677</v>
+      </c>
+      <c r="D23" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A23,SCHD_배당!$B$2:$B$90,B23)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A23,SCHD_배당!$B$2:$B$90,B23))</f>
+        <v>0.1104</v>
+      </c>
+      <c r="E23" s="34" t="str">
+        <f aca="false">IF(AND(D23="",A23=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A23)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A23)/COUNTIFS(SCHD_배당!$A$2:$A$90,A23),"")</f>
+        <v/>
+      </c>
+      <c r="F23" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="51" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B24" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C24" s="51" t="s">
+        <v>678</v>
+      </c>
+      <c r="D24" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A24,SCHD_배당!$B$2:$B$90,B24)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A24,SCHD_배당!$B$2:$B$90,B24))</f>
+        <v>0.114633333333333</v>
+      </c>
+      <c r="E24" s="34" t="str">
+        <f aca="false">IF(AND(D24="",A24=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A24)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A24)/COUNTIFS(SCHD_배당!$A$2:$A$90,A24),"")</f>
+        <v/>
+      </c>
+      <c r="F24" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="51" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B25" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C25" s="51" t="s">
+        <v>679</v>
+      </c>
+      <c r="D25" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A25,SCHD_배당!$B$2:$B$90,B25)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A25,SCHD_배당!$B$2:$B$90,B25))</f>
+        <v>0.114933333333333</v>
+      </c>
+      <c r="E25" s="34" t="str">
+        <f aca="false">IF(AND(D25="",A25=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A25)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A25)/COUNTIFS(SCHD_배당!$A$2:$A$90,A25),"")</f>
+        <v/>
+      </c>
+      <c r="F25" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="51" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B26" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" s="51" t="s">
+        <v>680</v>
+      </c>
+      <c r="D26" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A26,SCHD_배당!$B$2:$B$90,B26)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A26,SCHD_배당!$B$2:$B$90,B26))</f>
+        <v>0.0871666666666667</v>
+      </c>
+      <c r="E26" s="34" t="str">
+        <f aca="false">IF(AND(D26="",A26=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A26)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A26)/COUNTIFS(SCHD_배당!$A$2:$A$90,A26),"")</f>
+        <v/>
+      </c>
+      <c r="F26" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="51" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B27" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>681</v>
+      </c>
+      <c r="D27" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A27,SCHD_배당!$B$2:$B$90,B27)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A27,SCHD_배당!$B$2:$B$90,B27))</f>
+        <v>0.1352</v>
+      </c>
+      <c r="E27" s="34" t="str">
+        <f aca="false">IF(AND(D27="",A27=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A27)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A27)/COUNTIFS(SCHD_배당!$A$2:$A$90,A27),"")</f>
+        <v/>
+      </c>
+      <c r="F27" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="51" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B28" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C28" s="51" t="s">
+        <v>682</v>
+      </c>
+      <c r="D28" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A28,SCHD_배당!$B$2:$B$90,B28)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A28,SCHD_배당!$B$2:$B$90,B28))</f>
+        <v>0.122266666666667</v>
+      </c>
+      <c r="E28" s="34" t="str">
+        <f aca="false">IF(AND(D28="",A28=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A28)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A28)/COUNTIFS(SCHD_배당!$A$2:$A$90,A28),"")</f>
+        <v/>
+      </c>
+      <c r="F28" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="51" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B29" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C29" s="51" t="s">
+        <v>683</v>
+      </c>
+      <c r="D29" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A29,SCHD_배당!$B$2:$B$90,B29)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A29,SCHD_배당!$B$2:$B$90,B29))</f>
+        <v>0.135133333333333</v>
+      </c>
+      <c r="E29" s="34" t="str">
+        <f aca="false">IF(AND(D29="",A29=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A29)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A29)/COUNTIFS(SCHD_배당!$A$2:$A$90,A29),"")</f>
+        <v/>
+      </c>
+      <c r="F29" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="51" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B30" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="51" t="s">
+        <v>684</v>
+      </c>
+      <c r="D30" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A30,SCHD_배당!$B$2:$B$90,B30)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A30,SCHD_배당!$B$2:$B$90,B30))</f>
+        <v>0.117333333333333</v>
+      </c>
+      <c r="E30" s="34" t="str">
+        <f aca="false">IF(AND(D30="",A30=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A30)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A30)/COUNTIFS(SCHD_배당!$A$2:$A$90,A30),"")</f>
+        <v/>
+      </c>
+      <c r="F30" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="51" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B31" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="51" t="s">
+        <v>685</v>
+      </c>
+      <c r="D31" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A31,SCHD_배당!$B$2:$B$90,B31)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A31,SCHD_배당!$B$2:$B$90,B31))</f>
+        <v>0.1403</v>
+      </c>
+      <c r="E31" s="34" t="str">
+        <f aca="false">IF(AND(D31="",A31=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A31)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A31)/COUNTIFS(SCHD_배당!$A$2:$A$90,A31),"")</f>
+        <v/>
+      </c>
+      <c r="F31" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="51" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B32" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>686</v>
+      </c>
+      <c r="D32" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A32,SCHD_배당!$B$2:$B$90,B32)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A32,SCHD_배당!$B$2:$B$90,B32))</f>
+        <v>0.161833333333333</v>
+      </c>
+      <c r="E32" s="34" t="str">
+        <f aca="false">IF(AND(D32="",A32=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A32)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A32)/COUNTIFS(SCHD_배당!$A$2:$A$90,A32),"")</f>
+        <v/>
+      </c>
+      <c r="F32" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="51" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B33" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C33" s="51" t="s">
+        <v>687</v>
+      </c>
+      <c r="D33" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A33,SCHD_배당!$B$2:$B$90,B33)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A33,SCHD_배당!$B$2:$B$90,B33))</f>
+        <v>0.155266666666667</v>
+      </c>
+      <c r="E33" s="34" t="str">
+        <f aca="false">IF(AND(D33="",A33=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A33)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A33)/COUNTIFS(SCHD_배당!$A$2:$A$90,A33),"")</f>
+        <v/>
+      </c>
+      <c r="F33" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="51" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B34" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" s="51" t="s">
+        <v>688</v>
+      </c>
+      <c r="D34" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A34,SCHD_배당!$B$2:$B$90,B34)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A34,SCHD_배당!$B$2:$B$90,B34))</f>
+        <v>0.1473</v>
+      </c>
+      <c r="E34" s="34" t="str">
+        <f aca="false">IF(AND(D34="",A34=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A34)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A34)/COUNTIFS(SCHD_배당!$A$2:$A$90,A34),"")</f>
+        <v/>
+      </c>
+      <c r="F34" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="51" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B35" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C35" s="51" t="s">
+        <v>689</v>
+      </c>
+      <c r="D35" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A35,SCHD_배당!$B$2:$B$90,B35)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A35,SCHD_배당!$B$2:$B$90,B35))</f>
+        <v>0.147333333333333</v>
+      </c>
+      <c r="E35" s="34" t="str">
+        <f aca="false">IF(AND(D35="",A35=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A35)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A35)/COUNTIFS(SCHD_배당!$A$2:$A$90,A35),"")</f>
+        <v/>
+      </c>
+      <c r="F35" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="51" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B36" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" s="51" t="s">
+        <v>690</v>
+      </c>
+      <c r="D36" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A36,SCHD_배당!$B$2:$B$90,B36)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A36,SCHD_배당!$B$2:$B$90,B36))</f>
+        <v>0.181</v>
+      </c>
+      <c r="E36" s="34" t="str">
+        <f aca="false">IF(AND(D36="",A36=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A36)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A36)/COUNTIFS(SCHD_배당!$A$2:$A$90,A36),"")</f>
+        <v/>
+      </c>
+      <c r="F36" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="51" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B37" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C37" s="51" t="s">
+        <v>691</v>
+      </c>
+      <c r="D37" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A37,SCHD_배당!$B$2:$B$90,B37)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A37,SCHD_배당!$B$2:$B$90,B37))</f>
+        <v>0.2005</v>
+      </c>
+      <c r="E37" s="34" t="str">
+        <f aca="false">IF(AND(D37="",A37=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A37)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A37)/COUNTIFS(SCHD_배당!$A$2:$A$90,A37),"")</f>
+        <v/>
+      </c>
+      <c r="F37" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="51" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B38" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>692</v>
+      </c>
+      <c r="D38" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A38,SCHD_배당!$B$2:$B$90,B38)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A38,SCHD_배당!$B$2:$B$90,B38))</f>
+        <v>0.167533333333333</v>
+      </c>
+      <c r="E38" s="34" t="str">
+        <f aca="false">IF(AND(D38="",A38=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A38)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A38)/COUNTIFS(SCHD_배당!$A$2:$A$90,A38),"")</f>
+        <v/>
+      </c>
+      <c r="F38" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="51" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B39" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C39" s="51" t="s">
+        <v>693</v>
+      </c>
+      <c r="D39" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A39,SCHD_배당!$B$2:$B$90,B39)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A39,SCHD_배당!$B$2:$B$90,B39))</f>
+        <v>0.179866666666667</v>
+      </c>
+      <c r="E39" s="34" t="str">
+        <f aca="false">IF(AND(D39="",A39=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A39)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A39)/COUNTIFS(SCHD_배당!$A$2:$A$90,A39),"")</f>
+        <v/>
+      </c>
+      <c r="F39" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="51" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B40" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" s="51" t="s">
+        <v>694</v>
+      </c>
+      <c r="D40" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A40,SCHD_배당!$B$2:$B$90,B40)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A40,SCHD_배당!$B$2:$B$90,B40))</f>
+        <v>0.195666666666667</v>
+      </c>
+      <c r="E40" s="34" t="str">
+        <f aca="false">IF(AND(D40="",A40=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A40)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A40)/COUNTIFS(SCHD_배당!$A$2:$A$90,A40),"")</f>
+        <v/>
+      </c>
+      <c r="F40" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="51" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B41" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C41" s="51" t="s">
+        <v>695</v>
+      </c>
+      <c r="D41" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A41,SCHD_배당!$B$2:$B$90,B41)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A41,SCHD_배당!$B$2:$B$90,B41))</f>
+        <v>0.2066</v>
+      </c>
+      <c r="E41" s="34" t="str">
+        <f aca="false">IF(AND(D41="",A41=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A41)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A41)/COUNTIFS(SCHD_배당!$A$2:$A$90,A41),"")</f>
+        <v/>
+      </c>
+      <c r="F41" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="51" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B42" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="51" t="s">
+        <v>696</v>
+      </c>
+      <c r="D42" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A42,SCHD_배당!$B$2:$B$90,B42)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A42,SCHD_배당!$B$2:$B$90,B42))</f>
+        <v>0.172533333333333</v>
+      </c>
+      <c r="E42" s="34" t="str">
+        <f aca="false">IF(AND(D42="",A42=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A42)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A42)/COUNTIFS(SCHD_배당!$A$2:$A$90,A42),"")</f>
+        <v/>
+      </c>
+      <c r="F42" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="51" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B43" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="51" t="s">
+        <v>697</v>
+      </c>
+      <c r="D43" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A43,SCHD_배당!$B$2:$B$90,B43)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A43,SCHD_배당!$B$2:$B$90,B43))</f>
+        <v>0.2346</v>
+      </c>
+      <c r="E43" s="34" t="str">
+        <f aca="false">IF(AND(D43="",A43=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A43)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A43)/COUNTIFS(SCHD_배당!$A$2:$A$90,A43),"")</f>
+        <v/>
+      </c>
+      <c r="F43" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="51" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B44" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C44" s="51" t="s">
+        <v>698</v>
+      </c>
+      <c r="D44" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A44,SCHD_배당!$B$2:$B$90,B44)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A44,SCHD_배당!$B$2:$B$90,B44))</f>
+        <v>0.212233333333333</v>
+      </c>
+      <c r="E44" s="34" t="str">
+        <f aca="false">IF(AND(D44="",A44=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A44)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A44)/COUNTIFS(SCHD_배당!$A$2:$A$90,A44),"")</f>
+        <v/>
+      </c>
+      <c r="F44" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="51" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B45" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C45" s="51" t="s">
+        <v>699</v>
+      </c>
+      <c r="D45" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A45,SCHD_배당!$B$2:$B$90,B45)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A45,SCHD_배당!$B$2:$B$90,B45))</f>
+        <v>0.234466666666667</v>
+      </c>
+      <c r="E45" s="34" t="str">
+        <f aca="false">IF(AND(D45="",A45=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A45)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A45)/COUNTIFS(SCHD_배당!$A$2:$A$90,A45),"")</f>
+        <v/>
+      </c>
+      <c r="F45" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="51" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B46" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="51" t="s">
+        <v>700</v>
+      </c>
+      <c r="D46" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A46,SCHD_배당!$B$2:$B$90,B46)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A46,SCHD_배당!$B$2:$B$90,B46))</f>
+        <v>0.198833333333333</v>
+      </c>
+      <c r="E46" s="34" t="str">
+        <f aca="false">IF(AND(D46="",A46=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A46)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A46)/COUNTIFS(SCHD_배당!$A$2:$A$90,A46),"")</f>
+        <v/>
+      </c>
+      <c r="F46" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="51" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B47" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="51" t="s">
+        <v>701</v>
+      </c>
+      <c r="D47" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A47,SCHD_배당!$B$2:$B$90,B47)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A47,SCHD_배당!$B$2:$B$90,B47))</f>
+        <v>0.221566666666667</v>
+      </c>
+      <c r="E47" s="34" t="str">
+        <f aca="false">IF(AND(D47="",A47=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A47)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A47)/COUNTIFS(SCHD_배당!$A$2:$A$90,A47),"")</f>
+        <v/>
+      </c>
+      <c r="F47" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="51" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B48" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C48" s="51" t="s">
+        <v>702</v>
+      </c>
+      <c r="D48" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A48,SCHD_배당!$B$2:$B$90,B48)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A48,SCHD_배당!$B$2:$B$90,B48))</f>
+        <v>0.218166666666667</v>
+      </c>
+      <c r="E48" s="34" t="str">
+        <f aca="false">IF(AND(D48="",A48=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A48)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A48)/COUNTIFS(SCHD_배당!$A$2:$A$90,A48),"")</f>
+        <v/>
+      </c>
+      <c r="F48" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="51" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B49" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C49" s="51" t="s">
+        <v>703</v>
+      </c>
+      <c r="D49" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A49,SCHD_배당!$B$2:$B$90,B49)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A49,SCHD_배당!$B$2:$B$90,B49))</f>
+        <v>0.247433333333333</v>
+      </c>
+      <c r="E49" s="34" t="str">
+        <f aca="false">IF(AND(D49="",A49=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A49)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A49)/COUNTIFS(SCHD_배당!$A$2:$A$90,A49),"")</f>
+        <v/>
+      </c>
+      <c r="F49" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="51" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B50" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" s="51" t="s">
+        <v>704</v>
+      </c>
+      <c r="D50" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A50,SCHD_배당!$B$2:$B$90,B50)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A50,SCHD_배당!$B$2:$B$90,B50))</f>
+        <v>0.203666666666667</v>
+      </c>
+      <c r="E50" s="34" t="str">
+        <f aca="false">IF(AND(D50="",A50=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A50)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A50)/COUNTIFS(SCHD_배당!$A$2:$A$90,A50),"")</f>
+        <v/>
+      </c>
+      <c r="F50" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="51" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B51" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" s="51" t="s">
+        <v>705</v>
+      </c>
+      <c r="D51" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A51,SCHD_배당!$B$2:$B$90,B51)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A51,SCHD_배당!$B$2:$B$90,B51))</f>
+        <v>0.2747</v>
+      </c>
+      <c r="E51" s="34" t="str">
+        <f aca="false">IF(AND(D51="",A51=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A51)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A51)/COUNTIFS(SCHD_배당!$A$2:$A$90,A51),"")</f>
+        <v/>
+      </c>
+      <c r="F51" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="51" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B52" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C52" s="51" t="s">
+        <v>706</v>
+      </c>
+      <c r="D52" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A52,SCHD_배당!$B$2:$B$90,B52)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A52,SCHD_배당!$B$2:$B$90,B52))</f>
+        <v>0.2515</v>
+      </c>
+      <c r="E52" s="34" t="str">
+        <f aca="false">IF(AND(D52="",A52=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A52)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A52)/COUNTIFS(SCHD_배당!$A$2:$A$90,A52),"")</f>
+        <v/>
+      </c>
+      <c r="F52" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="51" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B53" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C53" s="51" t="s">
+        <v>707</v>
+      </c>
+      <c r="D53" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A53,SCHD_배당!$B$2:$B$90,B53)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A53,SCHD_배당!$B$2:$B$90,B53))</f>
+        <v>0.2645</v>
+      </c>
+      <c r="E53" s="34" t="str">
+        <f aca="false">IF(AND(D53="",A53=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A53)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A53)/COUNTIFS(SCHD_배당!$A$2:$A$90,A53),"")</f>
+        <v/>
+      </c>
+      <c r="F53" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B54" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" s="51" t="s">
+        <v>708</v>
+      </c>
+      <c r="D54" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A54,SCHD_배당!$B$2:$B$90,B54)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A54,SCHD_배당!$B$2:$B$90,B54))</f>
+        <v>0.2488</v>
+      </c>
+      <c r="E54" s="34" t="str">
+        <f aca="false">IF(AND(D54="",A54=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A54)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A54)/COUNTIFS(SCHD_배당!$A$2:$A$90,A54),"")</f>
+        <v/>
+      </c>
+      <c r="F54" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B55" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C55" s="51" t="s">
+        <v>709</v>
+      </c>
+      <c r="D55" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A55,SCHD_배당!$B$2:$B$90,B55)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A55,SCHD_배당!$B$2:$B$90,B55))</f>
+        <v>0.2602</v>
+      </c>
+      <c r="E55" s="34" t="str">
+        <f aca="false">IF(AND(D55="",A55=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A55)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A55)/COUNTIFS(SCHD_배당!$A$2:$A$90,A55),"")</f>
+        <v/>
+      </c>
+      <c r="F55" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B56" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C56" s="51" t="s">
+        <v>710</v>
+      </c>
+      <c r="D56" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A56,SCHD_배당!$B$2:$B$90,B56)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A56,SCHD_배당!$B$2:$B$90,B56))</f>
+        <v>0.2604</v>
+      </c>
+      <c r="E56" s="34" t="str">
+        <f aca="false">IF(AND(D56="",A56=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A56)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A56)/COUNTIFS(SCHD_배당!$A$2:$A$90,A56),"")</f>
+        <v/>
+      </c>
+      <c r="F56" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="51" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B57" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" s="51" t="s">
+        <v>711</v>
+      </c>
+      <c r="D57" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A57,SCHD_배당!$B$2:$B$90,B57)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A57,SCHD_배당!$B$2:$B$90,B57))</f>
+        <v>0.2782</v>
+      </c>
+      <c r="E57" s="34" t="str">
+        <f aca="false">IF(AND(D57="",A57=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A57)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A57)/COUNTIFS(SCHD_배당!$A$2:$A$90,A57),"")</f>
+        <v/>
+      </c>
+      <c r="F57" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B58" s="78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" s="51" t="s">
+        <v>712</v>
+      </c>
+      <c r="D58" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A58,SCHD_배당!$B$2:$B$90,B58)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A58,SCHD_배당!$B$2:$B$90,B58))</f>
+        <v>0.2569</v>
+      </c>
+      <c r="E58" s="34" t="str">
+        <f aca="false">IF(AND(D58="",A58=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A58)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A58)/COUNTIFS(SCHD_배당!$A$2:$A$90,A58),"")</f>
+        <v/>
+      </c>
+      <c r="F58" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B59" s="78" t="n">
+        <v>2</v>
+      </c>
+      <c r="C59" s="51" t="s">
+        <v>713</v>
+      </c>
+      <c r="D59" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A59,SCHD_배당!$B$2:$B$90,B59)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A59,SCHD_배당!$B$2:$B$90,B59))</f>
+        <v>0.2525</v>
+      </c>
+      <c r="E59" s="34" t="str">
+        <f aca="false">IF(AND(D59="",A59=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A59)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A59)/COUNTIFS(SCHD_배당!$A$2:$A$90,A59),"")</f>
+        <v/>
+      </c>
+      <c r="F59" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B60" s="78" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" s="51" t="s">
+        <v>714</v>
+      </c>
+      <c r="D60" s="34" t="n">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A60,SCHD_배당!$B$2:$B$90,B60)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A60,SCHD_배당!$B$2:$B$90,B60))</f>
+        <v>0.2665</v>
+      </c>
+      <c r="E60" s="34" t="str">
+        <f aca="false">IF(AND(D60="",A60=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A60)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A60)/COUNTIFS(SCHD_배당!$A$2:$A$90,A60),"")</f>
+        <v/>
+      </c>
+      <c r="F60" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="51" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B61" s="78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C61" s="51" t="s">
+        <v>715</v>
+      </c>
+      <c r="D61" s="34" t="str">
+        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A61,SCHD_배당!$B$2:$B$90,B61)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A61,SCHD_배당!$B$2:$B$90,B61))</f>
+        <v/>
+      </c>
+      <c r="E61" s="34" t="n">
+        <f aca="false">IF(AND(D61="",A61=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A61)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A61)/COUNTIFS(SCHD_배당!$A$2:$A$90,A61),"")</f>
+        <v>0.258633333333333</v>
+      </c>
+      <c r="F61" s="34" t="n">
+        <f aca="false">AVERAGE($D$2:$D$61)</f>
+        <v>0.156075706214689</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
@@ -29717,1416 +33469,3947 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G61"/>
+  <dimension ref="A1:H182"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="28" t="s">
-        <v>45</v>
+        <v>463</v>
       </c>
       <c r="B1" s="28" t="s">
-        <v>46</v>
+        <v>464</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>466</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="51" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B2" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>468</v>
-      </c>
-      <c r="D2" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A2,SCHD_배당!$B$2:$B$90,B2)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A2,SCHD_배당!$B$2:$B$90,B2))</f>
-        <v>0.046</v>
-      </c>
-      <c r="E2" s="34" t="str">
-        <f aca="false">IF(AND(D2="",A2=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A2)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A2)/COUNTIFS(SCHD_배당!$A$2:$A$90,A2),"")</f>
-        <v/>
-      </c>
-      <c r="F2" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
-      </c>
+      <c r="A2" s="63" t="s">
+        <v>470</v>
+      </c>
+      <c r="B2" s="65" t="n">
+        <v>40847</v>
+      </c>
+      <c r="C2" s="76" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="D2" s="77" t="n">
+        <v>5.287</v>
+      </c>
+      <c r="E2" s="63"/>
+      <c r="F2" s="63"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="51" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B3" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C3" s="51" t="s">
-        <v>469</v>
-      </c>
-      <c r="D3" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A3,SCHD_배당!$B$2:$B$90,B3)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A3,SCHD_배당!$B$2:$B$90,B3))</f>
-        <v>0.0687</v>
-      </c>
-      <c r="E3" s="34" t="str">
-        <f aca="false">IF(AND(D3="",A3=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A3)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A3)/COUNTIFS(SCHD_배당!$A$2:$A$90,A3),"")</f>
-        <v/>
-      </c>
-      <c r="F3" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
-      </c>
+      <c r="A3" s="63" t="s">
+        <v>471</v>
+      </c>
+      <c r="B3" s="65" t="n">
+        <v>40877</v>
+      </c>
+      <c r="C3" s="76" t="n">
+        <v>8.64</v>
+      </c>
+      <c r="D3" s="77" t="n">
+        <v>5.3741</v>
+      </c>
+      <c r="E3" s="63"/>
+      <c r="F3" s="63"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="51" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B4" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="51" t="s">
-        <v>470</v>
-      </c>
-      <c r="D4" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A4,SCHD_배당!$B$2:$B$90,B4)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A4,SCHD_배당!$B$2:$B$90,B4))</f>
-        <v>0.0693</v>
-      </c>
-      <c r="E4" s="34" t="str">
-        <f aca="false">IF(AND(D4="",A4=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A4)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A4)/COUNTIFS(SCHD_배당!$A$2:$A$90,A4),"")</f>
-        <v/>
-      </c>
-      <c r="F4" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
-      </c>
+      <c r="A4" s="63" t="s">
+        <v>472</v>
+      </c>
+      <c r="B4" s="65" t="n">
+        <v>40907</v>
+      </c>
+      <c r="C4" s="76" t="n">
+        <v>8.7267</v>
+      </c>
+      <c r="D4" s="77" t="n">
+        <v>5.4541</v>
+      </c>
+      <c r="E4" s="63"/>
+      <c r="F4" s="63"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="51" t="n">
-        <v>2012</v>
-      </c>
-      <c r="B5" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="51" t="s">
-        <v>471</v>
-      </c>
-      <c r="D5" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A5,SCHD_배당!$B$2:$B$90,B5)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A5,SCHD_배당!$B$2:$B$90,B5))</f>
-        <v>0.086</v>
-      </c>
-      <c r="E5" s="34" t="str">
-        <f aca="false">IF(AND(D5="",A5=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A5)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A5)/COUNTIFS(SCHD_배당!$A$2:$A$90,A5),"")</f>
-        <v/>
-      </c>
-      <c r="F5" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
-      </c>
+      <c r="A5" s="63" t="s">
+        <v>473</v>
+      </c>
+      <c r="B5" s="65" t="n">
+        <v>40939</v>
+      </c>
+      <c r="C5" s="76" t="n">
+        <v>8.87</v>
+      </c>
+      <c r="D5" s="77" t="n">
+        <v>5.5437</v>
+      </c>
+      <c r="E5" s="63"/>
+      <c r="F5" s="63"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="51" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B6" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="51" t="s">
-        <v>472</v>
-      </c>
-      <c r="D6" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A6,SCHD_배당!$B$2:$B$90,B6)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A6,SCHD_배당!$B$2:$B$90,B6))</f>
-        <v>0.0664</v>
-      </c>
-      <c r="E6" s="34" t="str">
-        <f aca="false">IF(AND(D6="",A6=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A6)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A6)/COUNTIFS(SCHD_배당!$A$2:$A$90,A6),"")</f>
-        <v/>
-      </c>
-      <c r="F6" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
-      </c>
+      <c r="A6" s="63" t="s">
+        <v>474</v>
+      </c>
+      <c r="B6" s="65" t="n">
+        <v>40968</v>
+      </c>
+      <c r="C6" s="76" t="n">
+        <v>9.1233</v>
+      </c>
+      <c r="D6" s="77" t="n">
+        <v>5.702</v>
+      </c>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="51" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B7" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="51" t="s">
-        <v>473</v>
-      </c>
-      <c r="D7" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A7,SCHD_배당!$B$2:$B$90,B7)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A7,SCHD_배당!$B$2:$B$90,B7))</f>
-        <v>0.075</v>
-      </c>
-      <c r="E7" s="34" t="str">
-        <f aca="false">IF(AND(D7="",A7=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A7)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A7)/COUNTIFS(SCHD_배당!$A$2:$A$90,A7),"")</f>
-        <v/>
-      </c>
-      <c r="F7" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
-      </c>
+      <c r="A7" s="63" t="s">
+        <v>475</v>
+      </c>
+      <c r="B7" s="65" t="n">
+        <v>40998</v>
+      </c>
+      <c r="C7" s="76" t="n">
+        <v>9.2967</v>
+      </c>
+      <c r="D7" s="77" t="n">
+        <v>5.8393</v>
+      </c>
+      <c r="E7" s="63"/>
+      <c r="F7" s="63"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="51" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B8" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" s="51" t="s">
-        <v>474</v>
-      </c>
-      <c r="D8" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A8,SCHD_배당!$B$2:$B$90,B8)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A8,SCHD_배당!$B$2:$B$90,B8))</f>
-        <v>0.0769</v>
-      </c>
-      <c r="E8" s="34" t="str">
-        <f aca="false">IF(AND(D8="",A8=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A8)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A8)/COUNTIFS(SCHD_배당!$A$2:$A$90,A8),"")</f>
-        <v/>
-      </c>
-      <c r="F8" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
-      </c>
+      <c r="A8" s="63" t="s">
+        <v>476</v>
+      </c>
+      <c r="B8" s="65" t="n">
+        <v>41029</v>
+      </c>
+      <c r="C8" s="76" t="n">
+        <v>9.2867</v>
+      </c>
+      <c r="D8" s="77" t="n">
+        <v>5.833</v>
+      </c>
+      <c r="E8" s="63"/>
+      <c r="F8" s="63"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="51" t="n">
-        <v>2013</v>
-      </c>
-      <c r="B9" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" s="51" t="s">
-        <v>475</v>
-      </c>
-      <c r="D9" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A9,SCHD_배당!$B$2:$B$90,B9)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A9,SCHD_배당!$B$2:$B$90,B9))</f>
-        <v>0.083</v>
-      </c>
-      <c r="E9" s="34" t="str">
-        <f aca="false">IF(AND(D9="",A9=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A9)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A9)/COUNTIFS(SCHD_배당!$A$2:$A$90,A9),"")</f>
-        <v/>
-      </c>
-      <c r="F9" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
-      </c>
+      <c r="A9" s="63" t="s">
+        <v>477</v>
+      </c>
+      <c r="B9" s="65" t="n">
+        <v>41060</v>
+      </c>
+      <c r="C9" s="76" t="n">
+        <v>8.9333</v>
+      </c>
+      <c r="D9" s="77" t="n">
+        <v>5.6111</v>
+      </c>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="51" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B10" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C10" s="51" t="s">
-        <v>476</v>
-      </c>
-      <c r="D10" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A10,SCHD_배당!$B$2:$B$90,B10)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A10,SCHD_배당!$B$2:$B$90,B10))</f>
-        <v>0.0826</v>
-      </c>
-      <c r="E10" s="34" t="str">
-        <f aca="false">IF(AND(D10="",A10=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A10)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A10)/COUNTIFS(SCHD_배당!$A$2:$A$90,A10),"")</f>
-        <v/>
-      </c>
-      <c r="F10" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
-      </c>
+      <c r="A10" s="63" t="s">
+        <v>478</v>
+      </c>
+      <c r="B10" s="65" t="n">
+        <v>41089</v>
+      </c>
+      <c r="C10" s="76" t="n">
+        <v>9.2533</v>
+      </c>
+      <c r="D10" s="77" t="n">
+        <v>5.8558</v>
+      </c>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="51" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B11" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="51" t="s">
-        <v>477</v>
-      </c>
-      <c r="D11" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A11,SCHD_배당!$B$2:$B$90,B11)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A11,SCHD_배당!$B$2:$B$90,B11))</f>
-        <v>0.0898</v>
-      </c>
-      <c r="E11" s="34" t="str">
-        <f aca="false">IF(AND(D11="",A11=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A11)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A11)/COUNTIFS(SCHD_배당!$A$2:$A$90,A11),"")</f>
-        <v/>
-      </c>
-      <c r="F11" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
-      </c>
+      <c r="A11" s="63" t="s">
+        <v>479</v>
+      </c>
+      <c r="B11" s="65" t="n">
+        <v>41121</v>
+      </c>
+      <c r="C11" s="76" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="D11" s="77" t="n">
+        <v>5.9992</v>
+      </c>
+      <c r="E11" s="63"/>
+      <c r="F11" s="63"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="51" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B12" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="51" t="s">
-        <v>478</v>
-      </c>
-      <c r="D12" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A12,SCHD_배당!$B$2:$B$90,B12)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A12,SCHD_배당!$B$2:$B$90,B12))</f>
-        <v>0.0848</v>
-      </c>
-      <c r="E12" s="34" t="str">
-        <f aca="false">IF(AND(D12="",A12=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A12)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A12)/COUNTIFS(SCHD_배당!$A$2:$A$90,A12),"")</f>
-        <v/>
-      </c>
-      <c r="F12" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
-      </c>
+      <c r="A12" s="63" t="s">
+        <v>480</v>
+      </c>
+      <c r="B12" s="65" t="n">
+        <v>41152</v>
+      </c>
+      <c r="C12" s="76" t="n">
+        <v>9.5367</v>
+      </c>
+      <c r="D12" s="77" t="n">
+        <v>6.0351</v>
+      </c>
+      <c r="E12" s="63"/>
+      <c r="F12" s="63"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="51" t="n">
-        <v>2014</v>
-      </c>
-      <c r="B13" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>479</v>
-      </c>
-      <c r="D13" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A13,SCHD_배당!$B$2:$B$90,B13)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A13,SCHD_배당!$B$2:$B$90,B13))</f>
-        <v>0.0918</v>
-      </c>
-      <c r="E13" s="34" t="str">
-        <f aca="false">IF(AND(D13="",A13=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A13)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A13)/COUNTIFS(SCHD_배당!$A$2:$A$90,A13),"")</f>
-        <v/>
-      </c>
-      <c r="F13" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
-      </c>
+      <c r="A13" s="63" t="s">
+        <v>481</v>
+      </c>
+      <c r="B13" s="65" t="n">
+        <v>41180</v>
+      </c>
+      <c r="C13" s="76" t="n">
+        <v>9.5833</v>
+      </c>
+      <c r="D13" s="77" t="n">
+        <v>6.1081</v>
+      </c>
+      <c r="E13" s="63"/>
+      <c r="F13" s="63"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="51" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B14" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C14" s="51" t="s">
-        <v>480</v>
-      </c>
-      <c r="D14" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A14,SCHD_배당!$B$2:$B$90,B14)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A14,SCHD_배당!$B$2:$B$90,B14))</f>
-        <v>0.09</v>
-      </c>
-      <c r="E14" s="34" t="str">
-        <f aca="false">IF(AND(D14="",A14=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A14)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A14)/COUNTIFS(SCHD_배당!$A$2:$A$90,A14),"")</f>
-        <v/>
-      </c>
-      <c r="F14" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A14" s="63" t="s">
+        <v>482</v>
+      </c>
+      <c r="B14" s="65" t="n">
+        <v>41213</v>
+      </c>
+      <c r="C14" s="76" t="n">
+        <v>9.4933</v>
+      </c>
+      <c r="D14" s="77" t="n">
+        <v>6.0508</v>
+      </c>
+      <c r="E14" s="67" t="n">
+        <f aca="false">C14/C2-1</f>
+        <v>0.116858823529412</v>
+      </c>
+      <c r="F14" s="67" t="n">
+        <f aca="false">D14/D2-1</f>
+        <v>0.144467561944392</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="51" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B15" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C15" s="51" t="s">
-        <v>481</v>
-      </c>
-      <c r="D15" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A15,SCHD_배당!$B$2:$B$90,B15)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A15,SCHD_배당!$B$2:$B$90,B15))</f>
-        <v>0.1021</v>
-      </c>
-      <c r="E15" s="34" t="str">
-        <f aca="false">IF(AND(D15="",A15=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A15)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A15)/COUNTIFS(SCHD_배당!$A$2:$A$90,A15),"")</f>
-        <v/>
-      </c>
-      <c r="F15" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A15" s="63" t="s">
+        <v>483</v>
+      </c>
+      <c r="B15" s="65" t="n">
+        <v>41243</v>
+      </c>
+      <c r="C15" s="76" t="n">
+        <v>9.5367</v>
+      </c>
+      <c r="D15" s="77" t="n">
+        <v>6.0784</v>
+      </c>
+      <c r="E15" s="67" t="n">
+        <f aca="false">C15/C3-1</f>
+        <v>0.103784722222222</v>
+      </c>
+      <c r="F15" s="67" t="n">
+        <f aca="false">D15/D3-1</f>
+        <v>0.131054502149197</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="51" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B16" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C16" s="51" t="s">
-        <v>482</v>
-      </c>
-      <c r="D16" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A16,SCHD_배당!$B$2:$B$90,B16)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A16,SCHD_배당!$B$2:$B$90,B16))</f>
-        <v>0.0996</v>
-      </c>
-      <c r="E16" s="34" t="str">
-        <f aca="false">IF(AND(D16="",A16=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A16)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A16)/COUNTIFS(SCHD_배당!$A$2:$A$90,A16),"")</f>
-        <v/>
-      </c>
-      <c r="F16" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A16" s="63" t="s">
+        <v>484</v>
+      </c>
+      <c r="B16" s="65" t="n">
+        <v>41274</v>
+      </c>
+      <c r="C16" s="76" t="n">
+        <v>9.4467</v>
+      </c>
+      <c r="D16" s="77" t="n">
+        <v>6.0754</v>
+      </c>
+      <c r="E16" s="67" t="n">
+        <f aca="false">C16/C4-1</f>
+        <v>0.0825054144178212</v>
+      </c>
+      <c r="F16" s="67" t="n">
+        <f aca="false">D16/D4-1</f>
+        <v>0.113914303001412</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="51" t="n">
-        <v>2015</v>
-      </c>
-      <c r="B17" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>483</v>
-      </c>
-      <c r="D17" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A17,SCHD_배당!$B$2:$B$90,B17)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A17,SCHD_배당!$B$2:$B$90,B17))</f>
-        <v>0.0905</v>
-      </c>
-      <c r="E17" s="34" t="str">
-        <f aca="false">IF(AND(D17="",A17=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A17)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A17)/COUNTIFS(SCHD_배당!$A$2:$A$90,A17),"")</f>
-        <v/>
-      </c>
-      <c r="F17" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A17" s="63" t="s">
+        <v>485</v>
+      </c>
+      <c r="B17" s="65" t="n">
+        <v>41305</v>
+      </c>
+      <c r="C17" s="76" t="n">
+        <v>9.97</v>
+      </c>
+      <c r="D17" s="77" t="n">
+        <v>6.412</v>
+      </c>
+      <c r="E17" s="67" t="n">
+        <f aca="false">C17/C5-1</f>
+        <v>0.124013528748591</v>
+      </c>
+      <c r="F17" s="67" t="n">
+        <f aca="false">D17/D5-1</f>
+        <v>0.156628244674135</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="51" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B18" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" s="51" t="s">
-        <v>484</v>
-      </c>
-      <c r="D18" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A18,SCHD_배당!$B$2:$B$90,B18)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A18,SCHD_배당!$B$2:$B$90,B18))</f>
-        <v>0.0994</v>
-      </c>
-      <c r="E18" s="34" t="str">
-        <f aca="false">IF(AND(D18="",A18=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A18)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A18)/COUNTIFS(SCHD_배당!$A$2:$A$90,A18),"")</f>
-        <v/>
-      </c>
-      <c r="F18" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A18" s="63" t="s">
+        <v>486</v>
+      </c>
+      <c r="B18" s="65" t="n">
+        <v>41333</v>
+      </c>
+      <c r="C18" s="76" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="D18" s="77" t="n">
+        <v>6.547</v>
+      </c>
+      <c r="E18" s="67" t="n">
+        <f aca="false">C18/C6-1</f>
+        <v>0.115824317955126</v>
+      </c>
+      <c r="F18" s="67" t="n">
+        <f aca="false">D18/D6-1</f>
+        <v>0.148193616274991</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="51" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B19" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>485</v>
-      </c>
-      <c r="D19" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A19,SCHD_배당!$B$2:$B$90,B19)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A19,SCHD_배당!$B$2:$B$90,B19))</f>
-        <v>0.1058</v>
-      </c>
-      <c r="E19" s="34" t="str">
-        <f aca="false">IF(AND(D19="",A19=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A19)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A19)/COUNTIFS(SCHD_배당!$A$2:$A$90,A19),"")</f>
-        <v/>
-      </c>
-      <c r="F19" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A19" s="63" t="s">
+        <v>487</v>
+      </c>
+      <c r="B19" s="65" t="n">
+        <v>41361</v>
+      </c>
+      <c r="C19" s="76" t="n">
+        <v>10.5967</v>
+      </c>
+      <c r="D19" s="77" t="n">
+        <v>6.8585</v>
+      </c>
+      <c r="E19" s="67" t="n">
+        <f aca="false">C19/C7-1</f>
+        <v>0.139834564953156</v>
+      </c>
+      <c r="F19" s="67" t="n">
+        <f aca="false">D19/D7-1</f>
+        <v>0.174541469011697</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="51" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B20" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>486</v>
-      </c>
-      <c r="D20" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A20,SCHD_배당!$B$2:$B$90,B20)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A20,SCHD_배당!$B$2:$B$90,B20))</f>
-        <v>0.0813</v>
-      </c>
-      <c r="E20" s="34" t="str">
-        <f aca="false">IF(AND(D20="",A20=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A20)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A20)/COUNTIFS(SCHD_배당!$A$2:$A$90,A20),"")</f>
-        <v/>
-      </c>
-      <c r="F20" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A20" s="63" t="s">
+        <v>488</v>
+      </c>
+      <c r="B20" s="65" t="n">
+        <v>41394</v>
+      </c>
+      <c r="C20" s="76" t="n">
+        <v>10.9133</v>
+      </c>
+      <c r="D20" s="77" t="n">
+        <v>7.0635</v>
+      </c>
+      <c r="E20" s="67" t="n">
+        <f aca="false">C20/C8-1</f>
+        <v>0.17515371445185</v>
+      </c>
+      <c r="F20" s="67" t="n">
+        <f aca="false">D20/D8-1</f>
+        <v>0.210954911709241</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="51" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B21" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>487</v>
-      </c>
-      <c r="D21" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A21,SCHD_배당!$B$2:$B$90,B21)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A21,SCHD_배당!$B$2:$B$90,B21))</f>
-        <v>0.1329</v>
-      </c>
-      <c r="E21" s="34" t="str">
-        <f aca="false">IF(AND(D21="",A21=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A21)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A21)/COUNTIFS(SCHD_배당!$A$2:$A$90,A21),"")</f>
-        <v/>
-      </c>
-      <c r="F21" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A21" s="63" t="s">
+        <v>489</v>
+      </c>
+      <c r="B21" s="65" t="n">
+        <v>41425</v>
+      </c>
+      <c r="C21" s="76" t="n">
+        <v>11.0667</v>
+      </c>
+      <c r="D21" s="77" t="n">
+        <v>7.1627</v>
+      </c>
+      <c r="E21" s="67" t="n">
+        <f aca="false">C21/C9-1</f>
+        <v>0.238814323934045</v>
+      </c>
+      <c r="F21" s="67" t="n">
+        <f aca="false">D21/D9-1</f>
+        <v>0.276523319848158</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="51" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B22" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" s="51" t="s">
-        <v>488</v>
-      </c>
-      <c r="D22" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A22,SCHD_배당!$B$2:$B$90,B22)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A22,SCHD_배당!$B$2:$B$90,B22))</f>
-        <v>0.1086</v>
-      </c>
-      <c r="E22" s="34" t="str">
-        <f aca="false">IF(AND(D22="",A22=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A22)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A22)/COUNTIFS(SCHD_배당!$A$2:$A$90,A22),"")</f>
-        <v/>
-      </c>
-      <c r="F22" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A22" s="63" t="s">
+        <v>490</v>
+      </c>
+      <c r="B22" s="65" t="n">
+        <v>41453</v>
+      </c>
+      <c r="C22" s="76" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D22" s="77" t="n">
+        <v>7.1037</v>
+      </c>
+      <c r="E22" s="67" t="n">
+        <f aca="false">C22/C10-1</f>
+        <v>0.177958133854949</v>
+      </c>
+      <c r="F22" s="67" t="n">
+        <f aca="false">D22/D10-1</f>
+        <v>0.213104955770347</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="51" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B23" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C23" s="51" t="s">
-        <v>489</v>
-      </c>
-      <c r="D23" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A23,SCHD_배당!$B$2:$B$90,B23)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A23,SCHD_배당!$B$2:$B$90,B23))</f>
-        <v>0.1104</v>
-      </c>
-      <c r="E23" s="34" t="str">
-        <f aca="false">IF(AND(D23="",A23=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A23)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A23)/COUNTIFS(SCHD_배당!$A$2:$A$90,A23),"")</f>
-        <v/>
-      </c>
-      <c r="F23" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A23" s="63" t="s">
+        <v>491</v>
+      </c>
+      <c r="B23" s="65" t="n">
+        <v>41486</v>
+      </c>
+      <c r="C23" s="76" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="D23" s="77" t="n">
+        <v>7.4296</v>
+      </c>
+      <c r="E23" s="67" t="n">
+        <f aca="false">C23/C11-1</f>
+        <v>0.20253164556962</v>
+      </c>
+      <c r="F23" s="67" t="n">
+        <f aca="false">D23/D11-1</f>
+        <v>0.238431790905454</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="51" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B24" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C24" s="51" t="s">
-        <v>490</v>
-      </c>
-      <c r="D24" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A24,SCHD_배당!$B$2:$B$90,B24)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A24,SCHD_배당!$B$2:$B$90,B24))</f>
-        <v>0.114633333333333</v>
-      </c>
-      <c r="E24" s="34" t="str">
-        <f aca="false">IF(AND(D24="",A24=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A24)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A24)/COUNTIFS(SCHD_배당!$A$2:$A$90,A24),"")</f>
-        <v/>
-      </c>
-      <c r="F24" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A24" s="63" t="s">
+        <v>492</v>
+      </c>
+      <c r="B24" s="65" t="n">
+        <v>41516</v>
+      </c>
+      <c r="C24" s="76" t="n">
+        <v>10.9967</v>
+      </c>
+      <c r="D24" s="77" t="n">
+        <v>7.1667</v>
+      </c>
+      <c r="E24" s="67" t="n">
+        <f aca="false">C24/C12-1</f>
+        <v>0.15309278891021</v>
+      </c>
+      <c r="F24" s="67" t="n">
+        <f aca="false">D24/D12-1</f>
+        <v>0.187503106825073</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="51" t="n">
-        <v>2017</v>
-      </c>
-      <c r="B25" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C25" s="51" t="s">
-        <v>491</v>
-      </c>
-      <c r="D25" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A25,SCHD_배당!$B$2:$B$90,B25)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A25,SCHD_배당!$B$2:$B$90,B25))</f>
-        <v>0.114933333333333</v>
-      </c>
-      <c r="E25" s="34" t="str">
-        <f aca="false">IF(AND(D25="",A25=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A25)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A25)/COUNTIFS(SCHD_배당!$A$2:$A$90,A25),"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A25" s="63" t="s">
+        <v>493</v>
+      </c>
+      <c r="B25" s="65" t="n">
+        <v>41547</v>
+      </c>
+      <c r="C25" s="76" t="n">
+        <v>11.2167</v>
+      </c>
+      <c r="D25" s="77" t="n">
+        <v>7.3593</v>
+      </c>
+      <c r="E25" s="67" t="n">
+        <f aca="false">C25/C13-1</f>
+        <v>0.170442331973329</v>
+      </c>
+      <c r="F25" s="67" t="n">
+        <f aca="false">D25/D13-1</f>
+        <v>0.204842749791261</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="51" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B26" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C26" s="51" t="s">
-        <v>492</v>
-      </c>
-      <c r="D26" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A26,SCHD_배당!$B$2:$B$90,B26)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A26,SCHD_배당!$B$2:$B$90,B26))</f>
-        <v>0.0871666666666667</v>
-      </c>
-      <c r="E26" s="34" t="str">
-        <f aca="false">IF(AND(D26="",A26=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A26)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A26)/COUNTIFS(SCHD_배당!$A$2:$A$90,A26),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A26" s="63" t="s">
+        <v>494</v>
+      </c>
+      <c r="B26" s="65" t="n">
+        <v>41578</v>
+      </c>
+      <c r="C26" s="76" t="n">
+        <v>11.7767</v>
+      </c>
+      <c r="D26" s="77" t="n">
+        <v>7.7267</v>
+      </c>
+      <c r="E26" s="67" t="n">
+        <f aca="false">C26/C14-1</f>
+        <v>0.24052752994217</v>
+      </c>
+      <c r="F26" s="67" t="n">
+        <f aca="false">D26/D14-1</f>
+        <v>0.276971640113704</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="51" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B27" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" s="51" t="s">
-        <v>493</v>
-      </c>
-      <c r="D27" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A27,SCHD_배당!$B$2:$B$90,B27)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A27,SCHD_배당!$B$2:$B$90,B27))</f>
-        <v>0.1352</v>
-      </c>
-      <c r="E27" s="34" t="str">
-        <f aca="false">IF(AND(D27="",A27=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A27)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A27)/COUNTIFS(SCHD_배당!$A$2:$A$90,A27),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A27" s="63" t="s">
+        <v>495</v>
+      </c>
+      <c r="B27" s="65" t="n">
+        <v>41607</v>
+      </c>
+      <c r="C27" s="76" t="n">
+        <v>12.0767</v>
+      </c>
+      <c r="D27" s="77" t="n">
+        <v>7.9236</v>
+      </c>
+      <c r="E27" s="67" t="n">
+        <f aca="false">C27/C15-1</f>
+        <v>0.266339509473927</v>
+      </c>
+      <c r="F27" s="67" t="n">
+        <f aca="false">D27/D15-1</f>
+        <v>0.303566728086339</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="51" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B28" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>494</v>
-      </c>
-      <c r="D28" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A28,SCHD_배당!$B$2:$B$90,B28)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A28,SCHD_배당!$B$2:$B$90,B28))</f>
-        <v>0.122266666666667</v>
-      </c>
-      <c r="E28" s="34" t="str">
-        <f aca="false">IF(AND(D28="",A28=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A28)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A28)/COUNTIFS(SCHD_배당!$A$2:$A$90,A28),"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A28" s="63" t="s">
+        <v>496</v>
+      </c>
+      <c r="B28" s="65" t="n">
+        <v>41639</v>
+      </c>
+      <c r="C28" s="76" t="n">
+        <v>12.22</v>
+      </c>
+      <c r="D28" s="77" t="n">
+        <v>8.0729</v>
+      </c>
+      <c r="E28" s="67" t="n">
+        <f aca="false">C28/C16-1</f>
+        <v>0.293573417172134</v>
+      </c>
+      <c r="F28" s="67" t="n">
+        <f aca="false">D28/D16-1</f>
+        <v>0.328784935971294</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="51" t="n">
-        <v>2018</v>
-      </c>
-      <c r="B29" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C29" s="51" t="s">
-        <v>495</v>
-      </c>
-      <c r="D29" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A29,SCHD_배당!$B$2:$B$90,B29)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A29,SCHD_배당!$B$2:$B$90,B29))</f>
-        <v>0.135133333333333</v>
-      </c>
-      <c r="E29" s="34" t="str">
-        <f aca="false">IF(AND(D29="",A29=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A29)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A29)/COUNTIFS(SCHD_배당!$A$2:$A$90,A29),"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A29" s="63" t="s">
+        <v>497</v>
+      </c>
+      <c r="B29" s="65" t="n">
+        <v>41670</v>
+      </c>
+      <c r="C29" s="76" t="n">
+        <v>11.6767</v>
+      </c>
+      <c r="D29" s="77" t="n">
+        <v>7.7139</v>
+      </c>
+      <c r="E29" s="67" t="n">
+        <f aca="false">C29/C17-1</f>
+        <v>0.171183550651956</v>
+      </c>
+      <c r="F29" s="67" t="n">
+        <f aca="false">D29/D17-1</f>
+        <v>0.203041172800998</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="51" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B30" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="51" t="s">
-        <v>496</v>
-      </c>
-      <c r="D30" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A30,SCHD_배당!$B$2:$B$90,B30)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A30,SCHD_배당!$B$2:$B$90,B30))</f>
-        <v>0.117333333333333</v>
-      </c>
-      <c r="E30" s="34" t="str">
-        <f aca="false">IF(AND(D30="",A30=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A30)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A30)/COUNTIFS(SCHD_배당!$A$2:$A$90,A30),"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A30" s="63" t="s">
+        <v>498</v>
+      </c>
+      <c r="B30" s="65" t="n">
+        <v>41698</v>
+      </c>
+      <c r="C30" s="76" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="D30" s="77" t="n">
+        <v>8.0134</v>
+      </c>
+      <c r="E30" s="67" t="n">
+        <f aca="false">C30/C18-1</f>
+        <v>0.19155206286837</v>
+      </c>
+      <c r="F30" s="67" t="n">
+        <f aca="false">D30/D18-1</f>
+        <v>0.223980449060639</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="51" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B31" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C31" s="51" t="s">
-        <v>497</v>
-      </c>
-      <c r="D31" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A31,SCHD_배당!$B$2:$B$90,B31)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A31,SCHD_배당!$B$2:$B$90,B31))</f>
-        <v>0.1403</v>
-      </c>
-      <c r="E31" s="34" t="str">
-        <f aca="false">IF(AND(D31="",A31=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A31)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A31)/COUNTIFS(SCHD_배당!$A$2:$A$90,A31),"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A31" s="63" t="s">
+        <v>499</v>
+      </c>
+      <c r="B31" s="65" t="n">
+        <v>41729</v>
+      </c>
+      <c r="C31" s="76" t="n">
+        <v>12.2833</v>
+      </c>
+      <c r="D31" s="77" t="n">
+        <v>8.1702</v>
+      </c>
+      <c r="E31" s="67" t="n">
+        <f aca="false">C31/C19-1</f>
+        <v>0.159162758217181</v>
+      </c>
+      <c r="F31" s="67" t="n">
+        <f aca="false">D31/D19-1</f>
+        <v>0.191251731428155</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="51" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B32" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" s="51" t="s">
-        <v>498</v>
-      </c>
-      <c r="D32" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A32,SCHD_배당!$B$2:$B$90,B32)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A32,SCHD_배당!$B$2:$B$90,B32))</f>
-        <v>0.161833333333333</v>
-      </c>
-      <c r="E32" s="34" t="str">
-        <f aca="false">IF(AND(D32="",A32=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A32)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A32)/COUNTIFS(SCHD_배당!$A$2:$A$90,A32),"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A32" s="63" t="s">
+        <v>500</v>
+      </c>
+      <c r="B32" s="65" t="n">
+        <v>41759</v>
+      </c>
+      <c r="C32" s="76" t="n">
+        <v>12.5067</v>
+      </c>
+      <c r="D32" s="77" t="n">
+        <v>8.3187</v>
+      </c>
+      <c r="E32" s="67" t="n">
+        <f aca="false">C32/C20-1</f>
+        <v>0.146005332942373</v>
+      </c>
+      <c r="F32" s="67" t="n">
+        <f aca="false">D32/D20-1</f>
+        <v>0.177702272244638</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="51" t="n">
-        <v>2019</v>
-      </c>
-      <c r="B33" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C33" s="51" t="s">
-        <v>499</v>
-      </c>
-      <c r="D33" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A33,SCHD_배당!$B$2:$B$90,B33)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A33,SCHD_배당!$B$2:$B$90,B33))</f>
-        <v>0.155266666666667</v>
-      </c>
-      <c r="E33" s="34" t="str">
-        <f aca="false">IF(AND(D33="",A33=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A33)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A33)/COUNTIFS(SCHD_배당!$A$2:$A$90,A33),"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A33" s="63" t="s">
+        <v>501</v>
+      </c>
+      <c r="B33" s="65" t="n">
+        <v>41789</v>
+      </c>
+      <c r="C33" s="76" t="n">
+        <v>12.6733</v>
+      </c>
+      <c r="D33" s="77" t="n">
+        <v>8.4296</v>
+      </c>
+      <c r="E33" s="67" t="n">
+        <f aca="false">C33/C21-1</f>
+        <v>0.145174261523308</v>
+      </c>
+      <c r="F33" s="67" t="n">
+        <f aca="false">D33/D21-1</f>
+        <v>0.176874642243847</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="51" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B34" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" s="51" t="s">
-        <v>500</v>
-      </c>
-      <c r="D34" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A34,SCHD_배당!$B$2:$B$90,B34)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A34,SCHD_배당!$B$2:$B$90,B34))</f>
-        <v>0.1473</v>
-      </c>
-      <c r="E34" s="34" t="str">
-        <f aca="false">IF(AND(D34="",A34=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A34)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A34)/COUNTIFS(SCHD_배당!$A$2:$A$90,A34),"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A34" s="63" t="s">
+        <v>502</v>
+      </c>
+      <c r="B34" s="65" t="n">
+        <v>41820</v>
+      </c>
+      <c r="C34" s="76" t="n">
+        <v>12.7567</v>
+      </c>
+      <c r="D34" s="77" t="n">
+        <v>8.5442</v>
+      </c>
+      <c r="E34" s="67" t="n">
+        <f aca="false">C34/C22-1</f>
+        <v>0.170339449541284</v>
+      </c>
+      <c r="F34" s="67" t="n">
+        <f aca="false">D34/D22-1</f>
+        <v>0.202781648999817</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="51" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B35" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" s="51" t="s">
-        <v>501</v>
-      </c>
-      <c r="D35" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A35,SCHD_배당!$B$2:$B$90,B35)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A35,SCHD_배당!$B$2:$B$90,B35))</f>
-        <v>0.147333333333333</v>
-      </c>
-      <c r="E35" s="34" t="str">
-        <f aca="false">IF(AND(D35="",A35=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A35)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A35)/COUNTIFS(SCHD_배당!$A$2:$A$90,A35),"")</f>
-        <v/>
-      </c>
-      <c r="F35" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A35" s="63" t="s">
+        <v>503</v>
+      </c>
+      <c r="B35" s="65" t="n">
+        <v>41851</v>
+      </c>
+      <c r="C35" s="76" t="n">
+        <v>12.5367</v>
+      </c>
+      <c r="D35" s="77" t="n">
+        <v>8.3968</v>
+      </c>
+      <c r="E35" s="67" t="n">
+        <f aca="false">C35/C23-1</f>
+        <v>0.0997105263157894</v>
+      </c>
+      <c r="F35" s="67" t="n">
+        <f aca="false">D35/D23-1</f>
+        <v>0.130181974803489</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="51" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B36" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C36" s="51" t="s">
-        <v>502</v>
-      </c>
-      <c r="D36" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A36,SCHD_배당!$B$2:$B$90,B36)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A36,SCHD_배당!$B$2:$B$90,B36))</f>
-        <v>0.181</v>
-      </c>
-      <c r="E36" s="34" t="str">
-        <f aca="false">IF(AND(D36="",A36=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A36)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A36)/COUNTIFS(SCHD_배당!$A$2:$A$90,A36),"")</f>
-        <v/>
-      </c>
-      <c r="F36" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A36" s="63" t="s">
+        <v>504</v>
+      </c>
+      <c r="B36" s="65" t="n">
+        <v>41880</v>
+      </c>
+      <c r="C36" s="76" t="n">
+        <v>12.9667</v>
+      </c>
+      <c r="D36" s="77" t="n">
+        <v>8.6848</v>
+      </c>
+      <c r="E36" s="67" t="n">
+        <f aca="false">C36/C24-1</f>
+        <v>0.179144652486655</v>
+      </c>
+      <c r="F36" s="67" t="n">
+        <f aca="false">D36/D24-1</f>
+        <v>0.211826921735248</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="51" t="n">
-        <v>2020</v>
-      </c>
-      <c r="B37" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C37" s="51" t="s">
-        <v>503</v>
-      </c>
-      <c r="D37" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A37,SCHD_배당!$B$2:$B$90,B37)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A37,SCHD_배당!$B$2:$B$90,B37))</f>
-        <v>0.2005</v>
-      </c>
-      <c r="E37" s="34" t="str">
-        <f aca="false">IF(AND(D37="",A37=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A37)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A37)/COUNTIFS(SCHD_배당!$A$2:$A$90,A37),"")</f>
-        <v/>
-      </c>
-      <c r="F37" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A37" s="63" t="s">
+        <v>505</v>
+      </c>
+      <c r="B37" s="65" t="n">
+        <v>41912</v>
+      </c>
+      <c r="C37" s="76" t="n">
+        <v>12.8533</v>
+      </c>
+      <c r="D37" s="77" t="n">
+        <v>8.6648</v>
+      </c>
+      <c r="E37" s="67" t="n">
+        <f aca="false">C37/C25-1</f>
+        <v>0.14590744158264</v>
+      </c>
+      <c r="F37" s="67" t="n">
+        <f aca="false">D37/D25-1</f>
+        <v>0.177394589159295</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="51" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B38" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" s="51" t="s">
-        <v>504</v>
-      </c>
-      <c r="D38" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A38,SCHD_배당!$B$2:$B$90,B38)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A38,SCHD_배당!$B$2:$B$90,B38))</f>
-        <v>0.167533333333333</v>
-      </c>
-      <c r="E38" s="34" t="str">
-        <f aca="false">IF(AND(D38="",A38=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A38)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A38)/COUNTIFS(SCHD_배당!$A$2:$A$90,A38),"")</f>
-        <v/>
-      </c>
-      <c r="F38" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A38" s="63" t="s">
+        <v>506</v>
+      </c>
+      <c r="B38" s="65" t="n">
+        <v>41943</v>
+      </c>
+      <c r="C38" s="76" t="n">
+        <v>13.1067</v>
+      </c>
+      <c r="D38" s="77" t="n">
+        <v>8.8355</v>
+      </c>
+      <c r="E38" s="67" t="n">
+        <f aca="false">C38/C26-1</f>
+        <v>0.112934862907266</v>
+      </c>
+      <c r="F38" s="67" t="n">
+        <f aca="false">D38/D26-1</f>
+        <v>0.143502400766174</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="51" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B39" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C39" s="51" t="s">
-        <v>505</v>
-      </c>
-      <c r="D39" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A39,SCHD_배당!$B$2:$B$90,B39)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A39,SCHD_배당!$B$2:$B$90,B39))</f>
-        <v>0.179866666666667</v>
-      </c>
-      <c r="E39" s="34" t="str">
-        <f aca="false">IF(AND(D39="",A39=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A39)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A39)/COUNTIFS(SCHD_배당!$A$2:$A$90,A39),"")</f>
-        <v/>
-      </c>
-      <c r="F39" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A39" s="63" t="s">
+        <v>507</v>
+      </c>
+      <c r="B39" s="65" t="n">
+        <v>41971</v>
+      </c>
+      <c r="C39" s="76" t="n">
+        <v>13.4967</v>
+      </c>
+      <c r="D39" s="77" t="n">
+        <v>9.0985</v>
+      </c>
+      <c r="E39" s="67" t="n">
+        <f aca="false">C39/C27-1</f>
+        <v>0.117581789727326</v>
+      </c>
+      <c r="F39" s="67" t="n">
+        <f aca="false">D39/D27-1</f>
+        <v>0.148278560250391</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="51" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B40" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C40" s="51" t="s">
-        <v>506</v>
-      </c>
-      <c r="D40" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A40,SCHD_배당!$B$2:$B$90,B40)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A40,SCHD_배당!$B$2:$B$90,B40))</f>
-        <v>0.195666666666667</v>
-      </c>
-      <c r="E40" s="34" t="str">
-        <f aca="false">IF(AND(D40="",A40=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A40)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A40)/COUNTIFS(SCHD_배당!$A$2:$A$90,A40),"")</f>
-        <v/>
-      </c>
-      <c r="F40" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A40" s="63" t="s">
+        <v>508</v>
+      </c>
+      <c r="B40" s="65" t="n">
+        <v>42004</v>
+      </c>
+      <c r="C40" s="76" t="n">
+        <v>13.2833</v>
+      </c>
+      <c r="D40" s="77" t="n">
+        <v>9.0161</v>
+      </c>
+      <c r="E40" s="67" t="n">
+        <f aca="false">C40/C28-1</f>
+        <v>0.0870130932896891</v>
+      </c>
+      <c r="F40" s="67" t="n">
+        <f aca="false">D40/D28-1</f>
+        <v>0.116835337982633</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="51" t="n">
-        <v>2021</v>
-      </c>
-      <c r="B41" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C41" s="51" t="s">
-        <v>507</v>
-      </c>
-      <c r="D41" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A41,SCHD_배당!$B$2:$B$90,B41)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A41,SCHD_배당!$B$2:$B$90,B41))</f>
-        <v>0.2066</v>
-      </c>
-      <c r="E41" s="34" t="str">
-        <f aca="false">IF(AND(D41="",A41=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A41)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A41)/COUNTIFS(SCHD_배당!$A$2:$A$90,A41),"")</f>
-        <v/>
-      </c>
-      <c r="F41" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A41" s="63" t="s">
+        <v>509</v>
+      </c>
+      <c r="B41" s="65" t="n">
+        <v>42034</v>
+      </c>
+      <c r="C41" s="76" t="n">
+        <v>12.87</v>
+      </c>
+      <c r="D41" s="77" t="n">
+        <v>8.7355</v>
+      </c>
+      <c r="E41" s="67" t="n">
+        <f aca="false">C41/C29-1</f>
+        <v>0.102194969469114</v>
+      </c>
+      <c r="F41" s="67" t="n">
+        <f aca="false">D41/D29-1</f>
+        <v>0.132436251442202</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="51" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B42" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" s="51" t="s">
-        <v>508</v>
-      </c>
-      <c r="D42" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A42,SCHD_배당!$B$2:$B$90,B42)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A42,SCHD_배당!$B$2:$B$90,B42))</f>
-        <v>0.172533333333333</v>
-      </c>
-      <c r="E42" s="34" t="str">
-        <f aca="false">IF(AND(D42="",A42=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A42)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A42)/COUNTIFS(SCHD_배당!$A$2:$A$90,A42),"")</f>
-        <v/>
-      </c>
-      <c r="F42" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A42" s="63" t="s">
+        <v>510</v>
+      </c>
+      <c r="B42" s="65" t="n">
+        <v>42062</v>
+      </c>
+      <c r="C42" s="76" t="n">
+        <v>13.5433</v>
+      </c>
+      <c r="D42" s="77" t="n">
+        <v>9.1926</v>
+      </c>
+      <c r="E42" s="67" t="n">
+        <f aca="false">C42/C30-1</f>
+        <v>0.116512778235779</v>
+      </c>
+      <c r="F42" s="67" t="n">
+        <f aca="false">D42/D30-1</f>
+        <v>0.147153517857588</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="51" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B43" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C43" s="51" t="s">
-        <v>509</v>
-      </c>
-      <c r="D43" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A43,SCHD_배당!$B$2:$B$90,B43)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A43,SCHD_배당!$B$2:$B$90,B43))</f>
-        <v>0.2346</v>
-      </c>
-      <c r="E43" s="34" t="str">
-        <f aca="false">IF(AND(D43="",A43=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A43)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A43)/COUNTIFS(SCHD_배당!$A$2:$A$90,A43),"")</f>
-        <v/>
-      </c>
-      <c r="F43" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A43" s="63" t="s">
+        <v>511</v>
+      </c>
+      <c r="B43" s="65" t="n">
+        <v>42094</v>
+      </c>
+      <c r="C43" s="76" t="n">
+        <v>13.1367</v>
+      </c>
+      <c r="D43" s="77" t="n">
+        <v>8.9769</v>
+      </c>
+      <c r="E43" s="67" t="n">
+        <f aca="false">C43/C31-1</f>
+        <v>0.0694764436267126</v>
+      </c>
+      <c r="F43" s="67" t="n">
+        <f aca="false">D43/D31-1</f>
+        <v>0.0987368730263643</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="51" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B44" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C44" s="51" t="s">
-        <v>510</v>
-      </c>
-      <c r="D44" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A44,SCHD_배당!$B$2:$B$90,B44)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A44,SCHD_배당!$B$2:$B$90,B44))</f>
-        <v>0.212233333333333</v>
-      </c>
-      <c r="E44" s="34" t="str">
-        <f aca="false">IF(AND(D44="",A44=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A44)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A44)/COUNTIFS(SCHD_배당!$A$2:$A$90,A44),"")</f>
-        <v/>
-      </c>
-      <c r="F44" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A44" s="63" t="s">
+        <v>512</v>
+      </c>
+      <c r="B44" s="65" t="n">
+        <v>42124</v>
+      </c>
+      <c r="C44" s="76" t="n">
+        <v>13.2367</v>
+      </c>
+      <c r="D44" s="77" t="n">
+        <v>9.0452</v>
+      </c>
+      <c r="E44" s="67" t="n">
+        <f aca="false">C44/C32-1</f>
+        <v>0.0583687143690983</v>
+      </c>
+      <c r="F44" s="67" t="n">
+        <f aca="false">D44/D32-1</f>
+        <v>0.0873333573755515</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="51" t="n">
-        <v>2022</v>
-      </c>
-      <c r="B45" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C45" s="51" t="s">
-        <v>511</v>
-      </c>
-      <c r="D45" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A45,SCHD_배당!$B$2:$B$90,B45)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A45,SCHD_배당!$B$2:$B$90,B45))</f>
-        <v>0.234466666666667</v>
-      </c>
-      <c r="E45" s="34" t="str">
-        <f aca="false">IF(AND(D45="",A45=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A45)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A45)/COUNTIFS(SCHD_배당!$A$2:$A$90,A45),"")</f>
-        <v/>
-      </c>
-      <c r="F45" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A45" s="63" t="s">
+        <v>513</v>
+      </c>
+      <c r="B45" s="65" t="n">
+        <v>42153</v>
+      </c>
+      <c r="C45" s="76" t="n">
+        <v>13.3033</v>
+      </c>
+      <c r="D45" s="77" t="n">
+        <v>9.0908</v>
+      </c>
+      <c r="E45" s="67" t="n">
+        <f aca="false">C45/C33-1</f>
+        <v>0.0497108093393197</v>
+      </c>
+      <c r="F45" s="67" t="n">
+        <f aca="false">D45/D33-1</f>
+        <v>0.0784378855461705</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="51" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B46" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="51" t="s">
-        <v>512</v>
-      </c>
-      <c r="D46" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A46,SCHD_배당!$B$2:$B$90,B46)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A46,SCHD_배당!$B$2:$B$90,B46))</f>
-        <v>0.198833333333333</v>
-      </c>
-      <c r="E46" s="34" t="str">
-        <f aca="false">IF(AND(D46="",A46=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A46)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A46)/COUNTIFS(SCHD_배당!$A$2:$A$90,A46),"")</f>
-        <v/>
-      </c>
-      <c r="F46" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A46" s="63" t="s">
+        <v>514</v>
+      </c>
+      <c r="B46" s="65" t="n">
+        <v>42185</v>
+      </c>
+      <c r="C46" s="76" t="n">
+        <v>12.7633</v>
+      </c>
+      <c r="D46" s="77" t="n">
+        <v>8.7897</v>
+      </c>
+      <c r="E46" s="67" t="n">
+        <f aca="false">C46/C34-1</f>
+        <v>0.000517375183237023</v>
+      </c>
+      <c r="F46" s="67" t="n">
+        <f aca="false">D46/D34-1</f>
+        <v>0.0287329416446245</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="51" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B47" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C47" s="51" t="s">
-        <v>513</v>
-      </c>
-      <c r="D47" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A47,SCHD_배당!$B$2:$B$90,B47)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A47,SCHD_배당!$B$2:$B$90,B47))</f>
-        <v>0.221566666666667</v>
-      </c>
-      <c r="E47" s="34" t="str">
-        <f aca="false">IF(AND(D47="",A47=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A47)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A47)/COUNTIFS(SCHD_배당!$A$2:$A$90,A47),"")</f>
-        <v/>
-      </c>
-      <c r="F47" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A47" s="63" t="s">
+        <v>515</v>
+      </c>
+      <c r="B47" s="65" t="n">
+        <v>42216</v>
+      </c>
+      <c r="C47" s="76" t="n">
+        <v>12.8533</v>
+      </c>
+      <c r="D47" s="77" t="n">
+        <v>8.8517</v>
+      </c>
+      <c r="E47" s="67" t="n">
+        <f aca="false">C47/C35-1</f>
+        <v>0.0252538546826517</v>
+      </c>
+      <c r="F47" s="67" t="n">
+        <f aca="false">D47/D35-1</f>
+        <v>0.0541754001524388</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="51" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B48" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C48" s="51" t="s">
-        <v>514</v>
-      </c>
-      <c r="D48" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A48,SCHD_배당!$B$2:$B$90,B48)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A48,SCHD_배당!$B$2:$B$90,B48))</f>
-        <v>0.218166666666667</v>
-      </c>
-      <c r="E48" s="34" t="str">
-        <f aca="false">IF(AND(D48="",A48=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A48)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A48)/COUNTIFS(SCHD_배당!$A$2:$A$90,A48),"")</f>
-        <v/>
-      </c>
-      <c r="F48" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A48" s="63" t="s">
+        <v>516</v>
+      </c>
+      <c r="B48" s="65" t="n">
+        <v>42247</v>
+      </c>
+      <c r="C48" s="76" t="n">
+        <v>12.17</v>
+      </c>
+      <c r="D48" s="77" t="n">
+        <v>8.3811</v>
+      </c>
+      <c r="E48" s="67" t="n">
+        <f aca="false">C48/C36-1</f>
+        <v>-0.0614420014344436</v>
+      </c>
+      <c r="F48" s="67" t="n">
+        <f aca="false">D48/D36-1</f>
+        <v>-0.0349691414885777</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="51" t="n">
-        <v>2023</v>
-      </c>
-      <c r="B49" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C49" s="51" t="s">
-        <v>515</v>
-      </c>
-      <c r="D49" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A49,SCHD_배당!$B$2:$B$90,B49)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A49,SCHD_배당!$B$2:$B$90,B49))</f>
-        <v>0.247433333333333</v>
-      </c>
-      <c r="E49" s="34" t="str">
-        <f aca="false">IF(AND(D49="",A49=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A49)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A49)/COUNTIFS(SCHD_배당!$A$2:$A$90,A49),"")</f>
-        <v/>
-      </c>
-      <c r="F49" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A49" s="63" t="s">
+        <v>517</v>
+      </c>
+      <c r="B49" s="65" t="n">
+        <v>42277</v>
+      </c>
+      <c r="C49" s="76" t="n">
+        <v>11.9833</v>
+      </c>
+      <c r="D49" s="77" t="n">
+        <v>8.3211</v>
+      </c>
+      <c r="E49" s="67" t="n">
+        <f aca="false">C49/C37-1</f>
+        <v>-0.0676868975282613</v>
+      </c>
+      <c r="F49" s="67" t="n">
+        <f aca="false">D49/D37-1</f>
+        <v>-0.0396662358046349</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="51" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B50" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" s="51" t="s">
-        <v>516</v>
-      </c>
-      <c r="D50" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A50,SCHD_배당!$B$2:$B$90,B50)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A50,SCHD_배당!$B$2:$B$90,B50))</f>
-        <v>0.203666666666667</v>
-      </c>
-      <c r="E50" s="34" t="str">
-        <f aca="false">IF(AND(D50="",A50=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A50)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A50)/COUNTIFS(SCHD_배당!$A$2:$A$90,A50),"")</f>
-        <v/>
-      </c>
-      <c r="F50" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A50" s="63" t="s">
+        <v>518</v>
+      </c>
+      <c r="B50" s="65" t="n">
+        <v>42307</v>
+      </c>
+      <c r="C50" s="76" t="n">
+        <v>13.0333</v>
+      </c>
+      <c r="D50" s="77" t="n">
+        <v>9.0502</v>
+      </c>
+      <c r="E50" s="67" t="n">
+        <f aca="false">C50/C38-1</f>
+        <v>-0.00560018921620231</v>
+      </c>
+      <c r="F50" s="67" t="n">
+        <f aca="false">D50/D38-1</f>
+        <v>0.024299700073567</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="51" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B51" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C51" s="51" t="s">
-        <v>517</v>
-      </c>
-      <c r="D51" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A51,SCHD_배당!$B$2:$B$90,B51)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A51,SCHD_배당!$B$2:$B$90,B51))</f>
-        <v>0.2747</v>
-      </c>
-      <c r="E51" s="34" t="str">
-        <f aca="false">IF(AND(D51="",A51=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A51)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A51)/COUNTIFS(SCHD_배당!$A$2:$A$90,A51),"")</f>
-        <v/>
-      </c>
-      <c r="F51" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A51" s="63" t="s">
+        <v>519</v>
+      </c>
+      <c r="B51" s="65" t="n">
+        <v>42338</v>
+      </c>
+      <c r="C51" s="76" t="n">
+        <v>13.07</v>
+      </c>
+      <c r="D51" s="77" t="n">
+        <v>9.0757</v>
+      </c>
+      <c r="E51" s="67" t="n">
+        <f aca="false">C51/C39-1</f>
+        <v>-0.0316151355516534</v>
+      </c>
+      <c r="F51" s="67" t="n">
+        <f aca="false">D51/D39-1</f>
+        <v>-0.00250590756718139</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="51" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B52" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C52" s="51" t="s">
-        <v>518</v>
-      </c>
-      <c r="D52" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A52,SCHD_배당!$B$2:$B$90,B52)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A52,SCHD_배당!$B$2:$B$90,B52))</f>
-        <v>0.2515</v>
-      </c>
-      <c r="E52" s="34" t="str">
-        <f aca="false">IF(AND(D52="",A52=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A52)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A52)/COUNTIFS(SCHD_배당!$A$2:$A$90,A52),"")</f>
-        <v/>
-      </c>
-      <c r="F52" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A52" s="63" t="s">
+        <v>520</v>
+      </c>
+      <c r="B52" s="65" t="n">
+        <v>42369</v>
+      </c>
+      <c r="C52" s="76" t="n">
+        <v>12.8533</v>
+      </c>
+      <c r="D52" s="77" t="n">
+        <v>8.9894</v>
+      </c>
+      <c r="E52" s="67" t="n">
+        <f aca="false">C52/C40-1</f>
+        <v>-0.0323714739560199</v>
+      </c>
+      <c r="F52" s="67" t="n">
+        <f aca="false">D52/D40-1</f>
+        <v>-0.00296136910637634</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="51" t="n">
-        <v>2024</v>
-      </c>
-      <c r="B53" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C53" s="51" t="s">
-        <v>519</v>
-      </c>
-      <c r="D53" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A53,SCHD_배당!$B$2:$B$90,B53)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A53,SCHD_배당!$B$2:$B$90,B53))</f>
-        <v>0.2645</v>
-      </c>
-      <c r="E53" s="34" t="str">
-        <f aca="false">IF(AND(D53="",A53=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A53)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A53)/COUNTIFS(SCHD_배당!$A$2:$A$90,A53),"")</f>
-        <v/>
-      </c>
-      <c r="F53" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A53" s="63" t="s">
+        <v>521</v>
+      </c>
+      <c r="B53" s="65" t="n">
+        <v>42398</v>
+      </c>
+      <c r="C53" s="76" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="D53" s="77" t="n">
+        <v>8.7842</v>
+      </c>
+      <c r="E53" s="67" t="n">
+        <f aca="false">C53/C41-1</f>
+        <v>-0.024087024087024</v>
+      </c>
+      <c r="F53" s="67" t="n">
+        <f aca="false">D53/D41-1</f>
+        <v>0.00557495277889086</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="51" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B54" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" s="51" t="s">
-        <v>520</v>
-      </c>
-      <c r="D54" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A54,SCHD_배당!$B$2:$B$90,B54)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A54,SCHD_배당!$B$2:$B$90,B54))</f>
-        <v>0.2488</v>
-      </c>
-      <c r="E54" s="34" t="str">
-        <f aca="false">IF(AND(D54="",A54=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A54)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A54)/COUNTIFS(SCHD_배당!$A$2:$A$90,A54),"")</f>
-        <v/>
-      </c>
-      <c r="F54" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A54" s="63" t="s">
+        <v>522</v>
+      </c>
+      <c r="B54" s="65" t="n">
+        <v>42429</v>
+      </c>
+      <c r="C54" s="76" t="n">
+        <v>12.6533</v>
+      </c>
+      <c r="D54" s="77" t="n">
+        <v>8.8495</v>
+      </c>
+      <c r="E54" s="67" t="n">
+        <f aca="false">C54/C42-1</f>
+        <v>-0.0657151506649044</v>
+      </c>
+      <c r="F54" s="67" t="n">
+        <f aca="false">D54/D42-1</f>
+        <v>-0.0373234993364228</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="51" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B55" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C55" s="51" t="s">
-        <v>521</v>
-      </c>
-      <c r="D55" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A55,SCHD_배당!$B$2:$B$90,B55)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A55,SCHD_배당!$B$2:$B$90,B55))</f>
-        <v>0.2602</v>
-      </c>
-      <c r="E55" s="34" t="str">
-        <f aca="false">IF(AND(D55="",A55=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A55)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A55)/COUNTIFS(SCHD_배당!$A$2:$A$90,A55),"")</f>
-        <v/>
-      </c>
-      <c r="F55" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A55" s="63" t="s">
+        <v>523</v>
+      </c>
+      <c r="B55" s="65" t="n">
+        <v>42460</v>
+      </c>
+      <c r="C55" s="76" t="n">
+        <v>13.3633</v>
+      </c>
+      <c r="D55" s="77" t="n">
+        <v>9.4158</v>
+      </c>
+      <c r="E55" s="67" t="n">
+        <f aca="false">C55/C43-1</f>
+        <v>0.0172493853098572</v>
+      </c>
+      <c r="F55" s="67" t="n">
+        <f aca="false">D55/D43-1</f>
+        <v>0.0488921565351068</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="51" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B56" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C56" s="51" t="s">
-        <v>522</v>
-      </c>
-      <c r="D56" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A56,SCHD_배당!$B$2:$B$90,B56)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A56,SCHD_배당!$B$2:$B$90,B56))</f>
-        <v>0.2604</v>
-      </c>
-      <c r="E56" s="34" t="str">
-        <f aca="false">IF(AND(D56="",A56=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A56)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A56)/COUNTIFS(SCHD_배당!$A$2:$A$90,A56),"")</f>
-        <v/>
-      </c>
-      <c r="F56" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A56" s="63" t="s">
+        <v>524</v>
+      </c>
+      <c r="B56" s="65" t="n">
+        <v>42489</v>
+      </c>
+      <c r="C56" s="76" t="n">
+        <v>13.34</v>
+      </c>
+      <c r="D56" s="77" t="n">
+        <v>9.3993</v>
+      </c>
+      <c r="E56" s="67" t="n">
+        <f aca="false">C56/C44-1</f>
+        <v>0.00780405992430122</v>
+      </c>
+      <c r="F56" s="67" t="n">
+        <f aca="false">D56/D44-1</f>
+        <v>0.0391478353159689</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="51" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B57" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C57" s="51" t="s">
-        <v>523</v>
-      </c>
-      <c r="D57" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A57,SCHD_배당!$B$2:$B$90,B57)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A57,SCHD_배당!$B$2:$B$90,B57))</f>
-        <v>0.2782</v>
-      </c>
-      <c r="E57" s="34" t="str">
-        <f aca="false">IF(AND(D57="",A57=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A57)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A57)/COUNTIFS(SCHD_배당!$A$2:$A$90,A57),"")</f>
-        <v/>
-      </c>
-      <c r="F57" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A57" s="63" t="s">
+        <v>525</v>
+      </c>
+      <c r="B57" s="65" t="n">
+        <v>42521</v>
+      </c>
+      <c r="C57" s="76" t="n">
+        <v>13.5267</v>
+      </c>
+      <c r="D57" s="77" t="n">
+        <v>9.5309</v>
+      </c>
+      <c r="E57" s="67" t="n">
+        <f aca="false">C57/C45-1</f>
+        <v>0.016792825840205</v>
+      </c>
+      <c r="F57" s="67" t="n">
+        <f aca="false">D57/D45-1</f>
+        <v>0.0484115809389714</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B58" s="76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" s="51" t="s">
-        <v>524</v>
-      </c>
-      <c r="D58" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A58,SCHD_배당!$B$2:$B$90,B58)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A58,SCHD_배당!$B$2:$B$90,B58))</f>
-        <v>0.2569</v>
-      </c>
-      <c r="E58" s="34" t="str">
-        <f aca="false">IF(AND(D58="",A58=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A58)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A58)/COUNTIFS(SCHD_배당!$A$2:$A$90,A58),"")</f>
-        <v/>
-      </c>
-      <c r="F58" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A58" s="63" t="s">
+        <v>526</v>
+      </c>
+      <c r="B58" s="65" t="n">
+        <v>42551</v>
+      </c>
+      <c r="C58" s="76" t="n">
+        <v>13.8133</v>
+      </c>
+      <c r="D58" s="77" t="n">
+        <v>9.8089</v>
+      </c>
+      <c r="E58" s="67" t="n">
+        <f aca="false">C58/C46-1</f>
+        <v>0.0822671252732445</v>
+      </c>
+      <c r="F58" s="67" t="n">
+        <f aca="false">D58/D46-1</f>
+        <v>0.115953900588188</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B59" s="76" t="n">
-        <v>2</v>
-      </c>
-      <c r="C59" s="51" t="s">
-        <v>525</v>
-      </c>
-      <c r="D59" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A59,SCHD_배당!$B$2:$B$90,B59)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A59,SCHD_배당!$B$2:$B$90,B59))</f>
-        <v>0.2525</v>
-      </c>
-      <c r="E59" s="34" t="str">
-        <f aca="false">IF(AND(D59="",A59=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A59)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A59)/COUNTIFS(SCHD_배당!$A$2:$A$90,A59),"")</f>
-        <v/>
-      </c>
-      <c r="F59" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A59" s="63" t="s">
+        <v>527</v>
+      </c>
+      <c r="B59" s="65" t="n">
+        <v>42580</v>
+      </c>
+      <c r="C59" s="76" t="n">
+        <v>14.2067</v>
+      </c>
+      <c r="D59" s="77" t="n">
+        <v>10.0882</v>
+      </c>
+      <c r="E59" s="67" t="n">
+        <f aca="false">C59/C47-1</f>
+        <v>0.105295916223849</v>
+      </c>
+      <c r="F59" s="67" t="n">
+        <f aca="false">D59/D47-1</f>
+        <v>0.139690680886158</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B60" s="76" t="n">
-        <v>3</v>
-      </c>
-      <c r="C60" s="51" t="s">
-        <v>526</v>
-      </c>
-      <c r="D60" s="34" t="n">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A60,SCHD_배당!$B$2:$B$90,B60)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A60,SCHD_배당!$B$2:$B$90,B60))</f>
-        <v>0.2665</v>
-      </c>
-      <c r="E60" s="34" t="str">
-        <f aca="false">IF(AND(D60="",A60=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A60)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A60)/COUNTIFS(SCHD_배당!$A$2:$A$90,A60),"")</f>
-        <v/>
-      </c>
-      <c r="F60" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A60" s="63" t="s">
+        <v>528</v>
+      </c>
+      <c r="B60" s="65" t="n">
+        <v>42613</v>
+      </c>
+      <c r="C60" s="76" t="n">
+        <v>14.16</v>
+      </c>
+      <c r="D60" s="77" t="n">
+        <v>10.0551</v>
+      </c>
+      <c r="E60" s="67" t="n">
+        <f aca="false">C60/C48-1</f>
+        <v>0.163516844700082</v>
+      </c>
+      <c r="F60" s="67" t="n">
+        <f aca="false">D60/D48-1</f>
+        <v>0.199735118301893</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="51" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B61" s="76" t="n">
-        <v>4</v>
-      </c>
-      <c r="C61" s="51" t="s">
-        <v>527</v>
-      </c>
-      <c r="D61" s="34" t="str">
-        <f aca="false">IF(COUNTIFS(SCHD_배당!$A$2:$A$90,A61,SCHD_배당!$B$2:$B$90,B61)=0,"",SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A61,SCHD_배당!$B$2:$B$90,B61))</f>
-        <v/>
-      </c>
-      <c r="E61" s="34" t="n">
-        <f aca="false">IF(AND(D61="",A61=MAX(SCHD_배당!$A$2:$A$90),COUNTIFS(SCHD_배당!$A$2:$A$90,A61)&gt;0),SUMIFS(SCHD_배당!$G$2:$G$90,SCHD_배당!$A$2:$A$90,A61)/COUNTIFS(SCHD_배당!$A$2:$A$90,A61),"")</f>
-        <v>0.258633333333333</v>
-      </c>
-      <c r="F61" s="34" t="n">
-        <f aca="false">AVERAGE($D$2:$D$61)</f>
-        <v>0.156075706214689</v>
+      <c r="A61" s="63" t="s">
+        <v>529</v>
+      </c>
+      <c r="B61" s="65" t="n">
+        <v>42643</v>
+      </c>
+      <c r="C61" s="76" t="n">
+        <v>14.1033</v>
+      </c>
+      <c r="D61" s="77" t="n">
+        <v>10.0735</v>
+      </c>
+      <c r="E61" s="67" t="n">
+        <f aca="false">C61/C49-1</f>
+        <v>0.176912870411323</v>
+      </c>
+      <c r="F61" s="67" t="n">
+        <f aca="false">D61/D49-1</f>
+        <v>0.210597156625927</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="63" t="s">
+        <v>530</v>
+      </c>
+      <c r="B62" s="65" t="n">
+        <v>42674</v>
+      </c>
+      <c r="C62" s="76" t="n">
+        <v>13.8833</v>
+      </c>
+      <c r="D62" s="77" t="n">
+        <v>9.9164</v>
+      </c>
+      <c r="E62" s="67" t="n">
+        <f aca="false">C62/C50-1</f>
+        <v>0.0652175581011716</v>
+      </c>
+      <c r="F62" s="67" t="n">
+        <f aca="false">D62/D50-1</f>
+        <v>0.0957105920311152</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="63" t="s">
+        <v>531</v>
+      </c>
+      <c r="B63" s="65" t="n">
+        <v>42704</v>
+      </c>
+      <c r="C63" s="76" t="n">
+        <v>14.3367</v>
+      </c>
+      <c r="D63" s="77" t="n">
+        <v>10.2402</v>
+      </c>
+      <c r="E63" s="67" t="n">
+        <f aca="false">C63/C51-1</f>
+        <v>0.0969166029074216</v>
+      </c>
+      <c r="F63" s="67" t="n">
+        <f aca="false">D63/D51-1</f>
+        <v>0.128309662064634</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="63" t="s">
+        <v>532</v>
+      </c>
+      <c r="B64" s="65" t="n">
+        <v>42734</v>
+      </c>
+      <c r="C64" s="76" t="n">
+        <v>14.5233</v>
+      </c>
+      <c r="D64" s="77" t="n">
+        <v>10.468</v>
+      </c>
+      <c r="E64" s="67" t="n">
+        <f aca="false">C64/C52-1</f>
+        <v>0.129927722841605</v>
+      </c>
+      <c r="F64" s="67" t="n">
+        <f aca="false">D64/D52-1</f>
+        <v>0.16448261285514</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="63" t="s">
+        <v>533</v>
+      </c>
+      <c r="B65" s="65" t="n">
+        <v>42766</v>
+      </c>
+      <c r="C65" s="76" t="n">
+        <v>14.4533</v>
+      </c>
+      <c r="D65" s="77" t="n">
+        <v>10.4175</v>
+      </c>
+      <c r="E65" s="67" t="n">
+        <f aca="false">C65/C53-1</f>
+        <v>0.150740445859873</v>
+      </c>
+      <c r="F65" s="67" t="n">
+        <f aca="false">D65/D53-1</f>
+        <v>0.185936112565743</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="63" t="s">
+        <v>534</v>
+      </c>
+      <c r="B66" s="65" t="n">
+        <v>42794</v>
+      </c>
+      <c r="C66" s="76" t="n">
+        <v>14.9467</v>
+      </c>
+      <c r="D66" s="77" t="n">
+        <v>10.7731</v>
+      </c>
+      <c r="E66" s="67" t="n">
+        <f aca="false">C66/C54-1</f>
+        <v>0.181249160298104</v>
+      </c>
+      <c r="F66" s="67" t="n">
+        <f aca="false">D66/D54-1</f>
+        <v>0.217368212893384</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="63" t="s">
+        <v>535</v>
+      </c>
+      <c r="B67" s="65" t="n">
+        <v>42825</v>
+      </c>
+      <c r="C67" s="76" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="D67" s="77" t="n">
+        <v>10.7884</v>
+      </c>
+      <c r="E67" s="67" t="n">
+        <f aca="false">C67/C55-1</f>
+        <v>0.112000778250881</v>
+      </c>
+      <c r="F67" s="67" t="n">
+        <f aca="false">D67/D55-1</f>
+        <v>0.145776248433484</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="63" t="s">
+        <v>536</v>
+      </c>
+      <c r="B68" s="65" t="n">
+        <v>42853</v>
+      </c>
+      <c r="C68" s="76" t="n">
+        <v>14.8967</v>
+      </c>
+      <c r="D68" s="77" t="n">
+        <v>10.815</v>
+      </c>
+      <c r="E68" s="67" t="n">
+        <f aca="false">C68/C56-1</f>
+        <v>0.116694152923538</v>
+      </c>
+      <c r="F68" s="67" t="n">
+        <f aca="false">D68/D56-1</f>
+        <v>0.150617599182918</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="63" t="s">
+        <v>537</v>
+      </c>
+      <c r="B69" s="65" t="n">
+        <v>42886</v>
+      </c>
+      <c r="C69" s="76" t="n">
+        <v>15.1567</v>
+      </c>
+      <c r="D69" s="77" t="n">
+        <v>11.0038</v>
+      </c>
+      <c r="E69" s="67" t="n">
+        <f aca="false">C69/C57-1</f>
+        <v>0.120502413744668</v>
+      </c>
+      <c r="F69" s="67" t="n">
+        <f aca="false">D69/D57-1</f>
+        <v>0.154539445382912</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="63" t="s">
+        <v>538</v>
+      </c>
+      <c r="B70" s="65" t="n">
+        <v>42916</v>
+      </c>
+      <c r="C70" s="76" t="n">
+        <v>15.0333</v>
+      </c>
+      <c r="D70" s="77" t="n">
+        <v>10.9933</v>
+      </c>
+      <c r="E70" s="67" t="n">
+        <f aca="false">C70/C58-1</f>
+        <v>0.0883206764495088</v>
+      </c>
+      <c r="F70" s="67" t="n">
+        <f aca="false">D70/D58-1</f>
+        <v>0.120747484427408</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="63" t="s">
+        <v>539</v>
+      </c>
+      <c r="B71" s="65" t="n">
+        <v>42947</v>
+      </c>
+      <c r="C71" s="76" t="n">
+        <v>15.2833</v>
+      </c>
+      <c r="D71" s="77" t="n">
+        <v>11.1761</v>
+      </c>
+      <c r="E71" s="67" t="n">
+        <f aca="false">C71/C59-1</f>
+        <v>0.0757811455158481</v>
+      </c>
+      <c r="F71" s="67" t="n">
+        <f aca="false">D71/D59-1</f>
+        <v>0.107838861243829</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="63" t="s">
+        <v>540</v>
+      </c>
+      <c r="B72" s="65" t="n">
+        <v>42978</v>
+      </c>
+      <c r="C72" s="76" t="n">
+        <v>15.28</v>
+      </c>
+      <c r="D72" s="77" t="n">
+        <v>11.1736</v>
+      </c>
+      <c r="E72" s="67" t="n">
+        <f aca="false">C72/C60-1</f>
+        <v>0.0790960451977401</v>
+      </c>
+      <c r="F72" s="67" t="n">
+        <f aca="false">D72/D60-1</f>
+        <v>0.111237083668984</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="63" t="s">
+        <v>541</v>
+      </c>
+      <c r="B73" s="65" t="n">
+        <v>43007</v>
+      </c>
+      <c r="C73" s="76" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="D73" s="77" t="n">
+        <v>11.4919</v>
+      </c>
+      <c r="E73" s="67" t="n">
+        <f aca="false">C73/C61-1</f>
+        <v>0.106124098615218</v>
+      </c>
+      <c r="F73" s="67" t="n">
+        <f aca="false">D73/D61-1</f>
+        <v>0.140805082642577</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="63" t="s">
+        <v>542</v>
+      </c>
+      <c r="B74" s="65" t="n">
+        <v>43039</v>
+      </c>
+      <c r="C74" s="76" t="n">
+        <v>16.1633</v>
+      </c>
+      <c r="D74" s="77" t="n">
+        <v>11.9069</v>
+      </c>
+      <c r="E74" s="67" t="n">
+        <f aca="false">C74/C62-1</f>
+        <v>0.164226084576434</v>
+      </c>
+      <c r="F74" s="67" t="n">
+        <f aca="false">D74/D62-1</f>
+        <v>0.200728086805696</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="63" t="s">
+        <v>543</v>
+      </c>
+      <c r="B75" s="65" t="n">
+        <v>43069</v>
+      </c>
+      <c r="C75" s="76" t="n">
+        <v>16.8433</v>
+      </c>
+      <c r="D75" s="77" t="n">
+        <v>12.4078</v>
+      </c>
+      <c r="E75" s="67" t="n">
+        <f aca="false">C75/C63-1</f>
+        <v>0.174838003166698</v>
+      </c>
+      <c r="F75" s="67" t="n">
+        <f aca="false">D75/D63-1</f>
+        <v>0.211675553211851</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="63" t="s">
+        <v>544</v>
+      </c>
+      <c r="B76" s="65" t="n">
+        <v>43098</v>
+      </c>
+      <c r="C76" s="76" t="n">
+        <v>17.0567</v>
+      </c>
+      <c r="D76" s="77" t="n">
+        <v>12.6502</v>
+      </c>
+      <c r="E76" s="67" t="n">
+        <f aca="false">C76/C64-1</f>
+        <v>0.174436939263115</v>
+      </c>
+      <c r="F76" s="67" t="n">
+        <f aca="false">D76/D64-1</f>
+        <v>0.208463889950325</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="63" t="s">
+        <v>545</v>
+      </c>
+      <c r="B77" s="65" t="n">
+        <v>43131</v>
+      </c>
+      <c r="C77" s="76" t="n">
+        <v>17.8333</v>
+      </c>
+      <c r="D77" s="77" t="n">
+        <v>13.2263</v>
+      </c>
+      <c r="E77" s="67" t="n">
+        <f aca="false">C77/C65-1</f>
+        <v>0.233856627898127</v>
+      </c>
+      <c r="F77" s="67" t="n">
+        <f aca="false">D77/D65-1</f>
+        <v>0.269623230141589</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="63" t="s">
+        <v>546</v>
+      </c>
+      <c r="B78" s="65" t="n">
+        <v>43159</v>
+      </c>
+      <c r="C78" s="76" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="D78" s="77" t="n">
+        <v>12.4821</v>
+      </c>
+      <c r="E78" s="67" t="n">
+        <f aca="false">C78/C66-1</f>
+        <v>0.126001057089525</v>
+      </c>
+      <c r="F78" s="67" t="n">
+        <f aca="false">D78/D66-1</f>
+        <v>0.158635861544031</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="63" t="s">
+        <v>547</v>
+      </c>
+      <c r="B79" s="65" t="n">
+        <v>43188</v>
+      </c>
+      <c r="C79" s="76" t="n">
+        <v>16.3433</v>
+      </c>
+      <c r="D79" s="77" t="n">
+        <v>12.1845</v>
+      </c>
+      <c r="E79" s="67" t="n">
+        <f aca="false">C79/C67-1</f>
+        <v>0.0998183041722747</v>
+      </c>
+      <c r="F79" s="67" t="n">
+        <f aca="false">D79/D67-1</f>
+        <v>0.129407511771903</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="63" t="s">
+        <v>548</v>
+      </c>
+      <c r="B80" s="65" t="n">
+        <v>43220</v>
+      </c>
+      <c r="C80" s="76" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="D80" s="77" t="n">
+        <v>12.0478</v>
+      </c>
+      <c r="E80" s="67" t="n">
+        <f aca="false">C80/C68-1</f>
+        <v>0.0848040169970532</v>
+      </c>
+      <c r="F80" s="67" t="n">
+        <f aca="false">D80/D68-1</f>
+        <v>0.113989828941285</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="63" t="s">
+        <v>549</v>
+      </c>
+      <c r="B81" s="65" t="n">
+        <v>43251</v>
+      </c>
+      <c r="C81" s="76" t="n">
+        <v>16.45</v>
+      </c>
+      <c r="D81" s="77" t="n">
+        <v>12.264</v>
+      </c>
+      <c r="E81" s="67" t="n">
+        <f aca="false">C81/C69-1</f>
+        <v>0.0853286005528906</v>
+      </c>
+      <c r="F81" s="67" t="n">
+        <f aca="false">D81/D69-1</f>
+        <v>0.114524073501881</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="63" t="s">
+        <v>550</v>
+      </c>
+      <c r="B82" s="65" t="n">
+        <v>43280</v>
+      </c>
+      <c r="C82" s="76" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="D82" s="77" t="n">
+        <v>12.3494</v>
+      </c>
+      <c r="E82" s="67" t="n">
+        <f aca="false">C82/C70-1</f>
+        <v>0.0929070796165845</v>
+      </c>
+      <c r="F82" s="67" t="n">
+        <f aca="false">D82/D70-1</f>
+        <v>0.123356953780939</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="63" t="s">
+        <v>551</v>
+      </c>
+      <c r="B83" s="65" t="n">
+        <v>43312</v>
+      </c>
+      <c r="C83" s="76" t="n">
+        <v>17.1767</v>
+      </c>
+      <c r="D83" s="77" t="n">
+        <v>12.9106</v>
+      </c>
+      <c r="E83" s="67" t="n">
+        <f aca="false">C83/C71-1</f>
+        <v>0.123886856896089</v>
+      </c>
+      <c r="F83" s="67" t="n">
+        <f aca="false">D83/D71-1</f>
+        <v>0.155197251277279</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="63" t="s">
+        <v>552</v>
+      </c>
+      <c r="B84" s="65" t="n">
+        <v>43343</v>
+      </c>
+      <c r="C84" s="76" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="D84" s="77" t="n">
+        <v>13.2063</v>
+      </c>
+      <c r="E84" s="67" t="n">
+        <f aca="false">C84/C72-1</f>
+        <v>0.149869109947644</v>
+      </c>
+      <c r="F84" s="67" t="n">
+        <f aca="false">D84/D72-1</f>
+        <v>0.181919882580368</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="63" t="s">
+        <v>553</v>
+      </c>
+      <c r="B85" s="65" t="n">
+        <v>43371</v>
+      </c>
+      <c r="C85" s="76" t="n">
+        <v>17.6667</v>
+      </c>
+      <c r="D85" s="77" t="n">
+        <v>13.3703</v>
+      </c>
+      <c r="E85" s="67" t="n">
+        <f aca="false">C85/C73-1</f>
+        <v>0.132480769230769</v>
+      </c>
+      <c r="F85" s="67" t="n">
+        <f aca="false">D85/D73-1</f>
+        <v>0.163454259086835</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="63" t="s">
+        <v>554</v>
+      </c>
+      <c r="B86" s="65" t="n">
+        <v>43404</v>
+      </c>
+      <c r="C86" s="76" t="n">
+        <v>16.6233</v>
+      </c>
+      <c r="D86" s="77" t="n">
+        <v>12.5807</v>
+      </c>
+      <c r="E86" s="67" t="n">
+        <f aca="false">C86/C74-1</f>
+        <v>0.0284595348722105</v>
+      </c>
+      <c r="F86" s="67" t="n">
+        <f aca="false">D86/D74-1</f>
+        <v>0.0565890366090249</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="63" t="s">
+        <v>555</v>
+      </c>
+      <c r="B87" s="65" t="n">
+        <v>43434</v>
+      </c>
+      <c r="C87" s="76" t="n">
+        <v>17.1833</v>
+      </c>
+      <c r="D87" s="77" t="n">
+        <v>13.0045</v>
+      </c>
+      <c r="E87" s="67" t="n">
+        <f aca="false">C87/C75-1</f>
+        <v>0.0201860680507977</v>
+      </c>
+      <c r="F87" s="67" t="n">
+        <f aca="false">D87/D75-1</f>
+        <v>0.0480907171295475</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="63" t="s">
+        <v>556</v>
+      </c>
+      <c r="B88" s="65" t="n">
+        <v>43465</v>
+      </c>
+      <c r="C88" s="76" t="n">
+        <v>15.6567</v>
+      </c>
+      <c r="D88" s="77" t="n">
+        <v>11.9471</v>
+      </c>
+      <c r="E88" s="67" t="n">
+        <f aca="false">C88/C76-1</f>
+        <v>-0.0820791829603615</v>
+      </c>
+      <c r="F88" s="67" t="n">
+        <f aca="false">D88/D76-1</f>
+        <v>-0.0555801489304516</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="63" t="s">
+        <v>557</v>
+      </c>
+      <c r="B89" s="65" t="n">
+        <v>43496</v>
+      </c>
+      <c r="C89" s="76" t="n">
+        <v>16.6033</v>
+      </c>
+      <c r="D89" s="77" t="n">
+        <v>12.6694</v>
+      </c>
+      <c r="E89" s="67" t="n">
+        <f aca="false">C89/C77-1</f>
+        <v>-0.0689720915366198</v>
+      </c>
+      <c r="F89" s="67" t="n">
+        <f aca="false">D89/D77-1</f>
+        <v>-0.0421055019166359</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="63" t="s">
+        <v>558</v>
+      </c>
+      <c r="B90" s="65" t="n">
+        <v>43524</v>
+      </c>
+      <c r="C90" s="76" t="n">
+        <v>17.2767</v>
+      </c>
+      <c r="D90" s="77" t="n">
+        <v>13.1832</v>
+      </c>
+      <c r="E90" s="67" t="n">
+        <f aca="false">C90/C78-1</f>
+        <v>0.0265418894830662</v>
+      </c>
+      <c r="F90" s="67" t="n">
+        <f aca="false">D90/D78-1</f>
+        <v>0.056168433196337</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="63" t="s">
+        <v>559</v>
+      </c>
+      <c r="B91" s="65" t="n">
+        <v>43553</v>
+      </c>
+      <c r="C91" s="76" t="n">
+        <v>17.4267</v>
+      </c>
+      <c r="D91" s="77" t="n">
+        <v>13.3875</v>
+      </c>
+      <c r="E91" s="67" t="n">
+        <f aca="false">C91/C79-1</f>
+        <v>0.0662901617176459</v>
+      </c>
+      <c r="F91" s="67" t="n">
+        <f aca="false">D91/D79-1</f>
+        <v>0.0987319955681398</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="63" t="s">
+        <v>560</v>
+      </c>
+      <c r="B92" s="65" t="n">
+        <v>43585</v>
+      </c>
+      <c r="C92" s="76" t="n">
+        <v>17.9867</v>
+      </c>
+      <c r="D92" s="77" t="n">
+        <v>13.8177</v>
+      </c>
+      <c r="E92" s="67" t="n">
+        <f aca="false">C92/C80-1</f>
+        <v>0.113038366336634</v>
+      </c>
+      <c r="F92" s="67" t="n">
+        <f aca="false">D92/D80-1</f>
+        <v>0.146906489151546</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="63" t="s">
+        <v>561</v>
+      </c>
+      <c r="B93" s="65" t="n">
+        <v>43616</v>
+      </c>
+      <c r="C93" s="76" t="n">
+        <v>16.62</v>
+      </c>
+      <c r="D93" s="77" t="n">
+        <v>12.7678</v>
+      </c>
+      <c r="E93" s="67" t="n">
+        <f aca="false">C93/C81-1</f>
+        <v>0.0103343465045593</v>
+      </c>
+      <c r="F93" s="67" t="n">
+        <f aca="false">D93/D81-1</f>
+        <v>0.0410795825179386</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="63" t="s">
+        <v>562</v>
+      </c>
+      <c r="B94" s="65" t="n">
+        <v>43644</v>
+      </c>
+      <c r="C94" s="76" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="D94" s="77" t="n">
+        <v>13.6983</v>
+      </c>
+      <c r="E94" s="67" t="n">
+        <f aca="false">C94/C82-1</f>
+        <v>0.0766889835666464</v>
+      </c>
+      <c r="F94" s="67" t="n">
+        <f aca="false">D94/D82-1</f>
+        <v>0.109227978687224</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="63" t="s">
+        <v>563</v>
+      </c>
+      <c r="B95" s="65" t="n">
+        <v>43677</v>
+      </c>
+      <c r="C95" s="76" t="n">
+        <v>17.9833</v>
+      </c>
+      <c r="D95" s="77" t="n">
+        <v>13.9254</v>
+      </c>
+      <c r="E95" s="67" t="n">
+        <f aca="false">C95/C83-1</f>
+        <v>0.0469589618494821</v>
+      </c>
+      <c r="F95" s="67" t="n">
+        <f aca="false">D95/D83-1</f>
+        <v>0.0786020789119017</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="63" t="s">
+        <v>564</v>
+      </c>
+      <c r="B96" s="65" t="n">
+        <v>43707</v>
+      </c>
+      <c r="C96" s="76" t="n">
+        <v>17.75</v>
+      </c>
+      <c r="D96" s="77" t="n">
+        <v>13.7448</v>
+      </c>
+      <c r="E96" s="67" t="n">
+        <f aca="false">C96/C84-1</f>
+        <v>0.0102447353443369</v>
+      </c>
+      <c r="F96" s="67" t="n">
+        <f aca="false">D96/D84-1</f>
+        <v>0.0407759932759364</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="63" t="s">
+        <v>565</v>
+      </c>
+      <c r="B97" s="65" t="n">
+        <v>43738</v>
+      </c>
+      <c r="C97" s="76" t="n">
+        <v>18.26</v>
+      </c>
+      <c r="D97" s="77" t="n">
+        <v>14.2666</v>
+      </c>
+      <c r="E97" s="67" t="n">
+        <f aca="false">C97/C85-1</f>
+        <v>0.0335829555038576</v>
+      </c>
+      <c r="F97" s="67" t="n">
+        <f aca="false">D97/D85-1</f>
+        <v>0.0670366409130685</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="63" t="s">
+        <v>566</v>
+      </c>
+      <c r="B98" s="65" t="n">
+        <v>43769</v>
+      </c>
+      <c r="C98" s="76" t="n">
+        <v>18.5067</v>
+      </c>
+      <c r="D98" s="77" t="n">
+        <v>14.4594</v>
+      </c>
+      <c r="E98" s="67" t="n">
+        <f aca="false">C98/C86-1</f>
+        <v>0.113298803486672</v>
+      </c>
+      <c r="F98" s="67" t="n">
+        <f aca="false">D98/D86-1</f>
+        <v>0.149331913168584</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="63" t="s">
+        <v>567</v>
+      </c>
+      <c r="B99" s="65" t="n">
+        <v>43798</v>
+      </c>
+      <c r="C99" s="76" t="n">
+        <v>19.03</v>
+      </c>
+      <c r="D99" s="77" t="n">
+        <v>14.8682</v>
+      </c>
+      <c r="E99" s="67" t="n">
+        <f aca="false">C99/C87-1</f>
+        <v>0.107470625549225</v>
+      </c>
+      <c r="F99" s="67" t="n">
+        <f aca="false">D99/D87-1</f>
+        <v>0.143311930485601</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="63" t="s">
+        <v>568</v>
+      </c>
+      <c r="B100" s="65" t="n">
+        <v>43830</v>
+      </c>
+      <c r="C100" s="76" t="n">
+        <v>19.3067</v>
+      </c>
+      <c r="D100" s="77" t="n">
+        <v>15.2078</v>
+      </c>
+      <c r="E100" s="67" t="n">
+        <f aca="false">C100/C88-1</f>
+        <v>0.233127031877726</v>
+      </c>
+      <c r="F100" s="67" t="n">
+        <f aca="false">D100/D88-1</f>
+        <v>0.27292815829783</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="63" t="s">
+        <v>569</v>
+      </c>
+      <c r="B101" s="65" t="n">
+        <v>43861</v>
+      </c>
+      <c r="C101" s="76" t="n">
+        <v>18.9667</v>
+      </c>
+      <c r="D101" s="77" t="n">
+        <v>14.94</v>
+      </c>
+      <c r="E101" s="67" t="n">
+        <f aca="false">C101/C89-1</f>
+        <v>0.142345196436853</v>
+      </c>
+      <c r="F101" s="67" t="n">
+        <f aca="false">D101/D89-1</f>
+        <v>0.179219221115444</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="63" t="s">
+        <v>570</v>
+      </c>
+      <c r="B102" s="65" t="n">
+        <v>43889</v>
+      </c>
+      <c r="C102" s="76" t="n">
+        <v>17.1933</v>
+      </c>
+      <c r="D102" s="77" t="n">
+        <v>13.5432</v>
+      </c>
+      <c r="E102" s="67" t="n">
+        <f aca="false">C102/C90-1</f>
+        <v>-0.00482731077115428</v>
+      </c>
+      <c r="F102" s="67" t="n">
+        <f aca="false">D102/D90-1</f>
+        <v>0.0273074822501367</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="63" t="s">
+        <v>571</v>
+      </c>
+      <c r="B103" s="65" t="n">
+        <v>43921</v>
+      </c>
+      <c r="C103" s="76" t="n">
+        <v>14.9933</v>
+      </c>
+      <c r="D103" s="77" t="n">
+        <v>11.9338</v>
+      </c>
+      <c r="E103" s="67" t="n">
+        <f aca="false">C103/C91-1</f>
+        <v>-0.139636305209822</v>
+      </c>
+      <c r="F103" s="67" t="n">
+        <f aca="false">D103/D91-1</f>
+        <v>-0.108586367880485</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="63" t="s">
+        <v>572</v>
+      </c>
+      <c r="B104" s="65" t="n">
+        <v>43951</v>
+      </c>
+      <c r="C104" s="76" t="n">
+        <v>16.8833</v>
+      </c>
+      <c r="D104" s="77" t="n">
+        <v>13.4382</v>
+      </c>
+      <c r="E104" s="67" t="n">
+        <f aca="false">C104/C92-1</f>
+        <v>-0.0613453273807869</v>
+      </c>
+      <c r="F104" s="67" t="n">
+        <f aca="false">D104/D92-1</f>
+        <v>-0.0274647734427582</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="63" t="s">
+        <v>573</v>
+      </c>
+      <c r="B105" s="65" t="n">
+        <v>43980</v>
+      </c>
+      <c r="C105" s="76" t="n">
+        <v>17.5067</v>
+      </c>
+      <c r="D105" s="77" t="n">
+        <v>13.9343</v>
+      </c>
+      <c r="E105" s="67" t="n">
+        <f aca="false">C105/C93-1</f>
+        <v>0.0533513838748494</v>
+      </c>
+      <c r="F105" s="67" t="n">
+        <f aca="false">D105/D93-1</f>
+        <v>0.0913626466579991</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="63" t="s">
+        <v>574</v>
+      </c>
+      <c r="B106" s="65" t="n">
+        <v>44012</v>
+      </c>
+      <c r="C106" s="76" t="n">
+        <v>17.25</v>
+      </c>
+      <c r="D106" s="77" t="n">
+        <v>13.846</v>
+      </c>
+      <c r="E106" s="67" t="n">
+        <f aca="false">C106/C94-1</f>
+        <v>-0.024872809496891</v>
+      </c>
+      <c r="F106" s="67" t="n">
+        <f aca="false">D106/D94-1</f>
+        <v>0.0107823598548726</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="63" t="s">
+        <v>575</v>
+      </c>
+      <c r="B107" s="65" t="n">
+        <v>44043</v>
+      </c>
+      <c r="C107" s="76" t="n">
+        <v>18.1633</v>
+      </c>
+      <c r="D107" s="77" t="n">
+        <v>14.5791</v>
+      </c>
+      <c r="E107" s="67" t="n">
+        <f aca="false">C107/C95-1</f>
+        <v>0.0100092863934873</v>
+      </c>
+      <c r="F107" s="67" t="n">
+        <f aca="false">D107/D95-1</f>
+        <v>0.0469429962514543</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="63" t="s">
+        <v>576</v>
+      </c>
+      <c r="B108" s="65" t="n">
+        <v>44074</v>
+      </c>
+      <c r="C108" s="76" t="n">
+        <v>19.0933</v>
+      </c>
+      <c r="D108" s="77" t="n">
+        <v>15.3255</v>
+      </c>
+      <c r="E108" s="67" t="n">
+        <f aca="false">C108/C96-1</f>
+        <v>0.0756788732394367</v>
+      </c>
+      <c r="F108" s="67" t="n">
+        <f aca="false">D108/D96-1</f>
+        <v>0.115003492229789</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="63" t="s">
+        <v>577</v>
+      </c>
+      <c r="B109" s="65" t="n">
+        <v>44104</v>
+      </c>
+      <c r="C109" s="76" t="n">
+        <v>18.4333</v>
+      </c>
+      <c r="D109" s="77" t="n">
+        <v>14.9429</v>
+      </c>
+      <c r="E109" s="67" t="n">
+        <f aca="false">C109/C97-1</f>
+        <v>0.00949069003285863</v>
+      </c>
+      <c r="F109" s="67" t="n">
+        <f aca="false">D109/D97-1</f>
+        <v>0.0474044271234912</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="63" t="s">
+        <v>578</v>
+      </c>
+      <c r="B110" s="65" t="n">
+        <v>44134</v>
+      </c>
+      <c r="C110" s="76" t="n">
+        <v>18.5033</v>
+      </c>
+      <c r="D110" s="77" t="n">
+        <v>14.9997</v>
+      </c>
+      <c r="E110" s="67" t="n">
+        <f aca="false">C110/C98-1</f>
+        <v>-0.00018371724834787</v>
+      </c>
+      <c r="F110" s="67" t="n">
+        <f aca="false">D110/D98-1</f>
+        <v>0.037366695713515</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="63" t="s">
+        <v>579</v>
+      </c>
+      <c r="B111" s="65" t="n">
+        <v>44165</v>
+      </c>
+      <c r="C111" s="76" t="n">
+        <v>20.94</v>
+      </c>
+      <c r="D111" s="77" t="n">
+        <v>16.975</v>
+      </c>
+      <c r="E111" s="67" t="n">
+        <f aca="false">C111/C99-1</f>
+        <v>0.100367840252233</v>
+      </c>
+      <c r="F111" s="67" t="n">
+        <f aca="false">D111/D99-1</f>
+        <v>0.141698389852168</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="63" t="s">
+        <v>580</v>
+      </c>
+      <c r="B112" s="65" t="n">
+        <v>44196</v>
+      </c>
+      <c r="C112" s="76" t="n">
+        <v>21.38</v>
+      </c>
+      <c r="D112" s="77" t="n">
+        <v>17.4933</v>
+      </c>
+      <c r="E112" s="67" t="n">
+        <f aca="false">C112/C100-1</f>
+        <v>0.107387590836342</v>
+      </c>
+      <c r="F112" s="67" t="n">
+        <f aca="false">D112/D100-1</f>
+        <v>0.15028472231355</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="63" t="s">
+        <v>581</v>
+      </c>
+      <c r="B113" s="65" t="n">
+        <v>44225</v>
+      </c>
+      <c r="C113" s="76" t="n">
+        <v>21.1867</v>
+      </c>
+      <c r="D113" s="77" t="n">
+        <v>17.3351</v>
+      </c>
+      <c r="E113" s="67" t="n">
+        <f aca="false">C113/C101-1</f>
+        <v>0.117047245962661</v>
+      </c>
+      <c r="F113" s="67" t="n">
+        <f aca="false">D113/D101-1</f>
+        <v>0.160314591700134</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="63" t="s">
+        <v>582</v>
+      </c>
+      <c r="B114" s="65" t="n">
+        <v>44253</v>
+      </c>
+      <c r="C114" s="76" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="D114" s="77" t="n">
+        <v>18.3851</v>
+      </c>
+      <c r="E114" s="67" t="n">
+        <f aca="false">C114/C102-1</f>
+        <v>0.306904433703827</v>
+      </c>
+      <c r="F114" s="67" t="n">
+        <f aca="false">D114/D102-1</f>
+        <v>0.357515210585386</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="63" t="s">
+        <v>583</v>
+      </c>
+      <c r="B115" s="65" t="n">
+        <v>44286</v>
+      </c>
+      <c r="C115" s="76" t="n">
+        <v>24.3067</v>
+      </c>
+      <c r="D115" s="77" t="n">
+        <v>20.0289</v>
+      </c>
+      <c r="E115" s="67" t="n">
+        <f aca="false">C115/C103-1</f>
+        <v>0.621170789619363</v>
+      </c>
+      <c r="F115" s="67" t="n">
+        <f aca="false">D115/D103-1</f>
+        <v>0.678333808175099</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="63" t="s">
+        <v>584</v>
+      </c>
+      <c r="B116" s="65" t="n">
+        <v>44316</v>
+      </c>
+      <c r="C116" s="76" t="n">
+        <v>24.8433</v>
+      </c>
+      <c r="D116" s="77" t="n">
+        <v>20.4711</v>
+      </c>
+      <c r="E116" s="67" t="n">
+        <f aca="false">C116/C104-1</f>
+        <v>0.471471809421144</v>
+      </c>
+      <c r="F116" s="67" t="n">
+        <f aca="false">D116/D104-1</f>
+        <v>0.523351341697549</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="63" t="s">
+        <v>585</v>
+      </c>
+      <c r="B117" s="65" t="n">
+        <v>44344</v>
+      </c>
+      <c r="C117" s="76" t="n">
+        <v>25.6433</v>
+      </c>
+      <c r="D117" s="77" t="n">
+        <v>21.1303</v>
+      </c>
+      <c r="E117" s="67" t="n">
+        <f aca="false">C117/C105-1</f>
+        <v>0.464770630672828</v>
+      </c>
+      <c r="F117" s="67" t="n">
+        <f aca="false">D117/D105-1</f>
+        <v>0.51642350171878</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="63" t="s">
+        <v>586</v>
+      </c>
+      <c r="B118" s="65" t="n">
+        <v>44377</v>
+      </c>
+      <c r="C118" s="76" t="n">
+        <v>25.2067</v>
+      </c>
+      <c r="D118" s="77" t="n">
+        <v>20.9203</v>
+      </c>
+      <c r="E118" s="67" t="n">
+        <f aca="false">C118/C106-1</f>
+        <v>0.461257971014493</v>
+      </c>
+      <c r="F118" s="67" t="n">
+        <f aca="false">D118/D106-1</f>
+        <v>0.510927343637152</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="63" t="s">
+        <v>587</v>
+      </c>
+      <c r="B119" s="65" t="n">
+        <v>44407</v>
+      </c>
+      <c r="C119" s="76" t="n">
+        <v>25.37</v>
+      </c>
+      <c r="D119" s="77" t="n">
+        <v>21.0559</v>
+      </c>
+      <c r="E119" s="67" t="n">
+        <f aca="false">C119/C107-1</f>
+        <v>0.396772612906245</v>
+      </c>
+      <c r="F119" s="67" t="n">
+        <f aca="false">D119/D107-1</f>
+        <v>0.444252388693404</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="63" t="s">
+        <v>588</v>
+      </c>
+      <c r="B120" s="65" t="n">
+        <v>44439</v>
+      </c>
+      <c r="C120" s="76" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="D120" s="77" t="n">
+        <v>21.4958</v>
+      </c>
+      <c r="E120" s="67" t="n">
+        <f aca="false">C120/C108-1</f>
+        <v>0.356496781593543</v>
+      </c>
+      <c r="F120" s="67" t="n">
+        <f aca="false">D120/D108-1</f>
+        <v>0.402616554109164</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="63" t="s">
+        <v>589</v>
+      </c>
+      <c r="B121" s="65" t="n">
+        <v>44469</v>
+      </c>
+      <c r="C121" s="76" t="n">
+        <v>24.7467</v>
+      </c>
+      <c r="D121" s="77" t="n">
+        <v>20.7023</v>
+      </c>
+      <c r="E121" s="67" t="n">
+        <f aca="false">C121/C109-1</f>
+        <v>0.342499715189359</v>
+      </c>
+      <c r="F121" s="67" t="n">
+        <f aca="false">D121/D109-1</f>
+        <v>0.385427192847439</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="63" t="s">
+        <v>590</v>
+      </c>
+      <c r="B122" s="65" t="n">
+        <v>44498</v>
+      </c>
+      <c r="C122" s="76" t="n">
+        <v>25.8367</v>
+      </c>
+      <c r="D122" s="77" t="n">
+        <v>21.6141</v>
+      </c>
+      <c r="E122" s="67" t="n">
+        <f aca="false">C122/C110-1</f>
+        <v>0.396329303421552</v>
+      </c>
+      <c r="F122" s="67" t="n">
+        <f aca="false">D122/D110-1</f>
+        <v>0.440968819376387</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="63" t="s">
+        <v>591</v>
+      </c>
+      <c r="B123" s="65" t="n">
+        <v>44530</v>
+      </c>
+      <c r="C123" s="76" t="n">
+        <v>25.3067</v>
+      </c>
+      <c r="D123" s="77" t="n">
+        <v>21.1707</v>
+      </c>
+      <c r="E123" s="67" t="n">
+        <f aca="false">C123/C111-1</f>
+        <v>0.208533906399236</v>
+      </c>
+      <c r="F123" s="67" t="n">
+        <f aca="false">D123/D111-1</f>
+        <v>0.247169366715758</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="63" t="s">
+        <v>592</v>
+      </c>
+      <c r="B124" s="65" t="n">
+        <v>44561</v>
+      </c>
+      <c r="C124" s="76" t="n">
+        <v>26.9433</v>
+      </c>
+      <c r="D124" s="77" t="n">
+        <v>22.7195</v>
+      </c>
+      <c r="E124" s="67" t="n">
+        <f aca="false">C124/C112-1</f>
+        <v>0.260210477081385</v>
+      </c>
+      <c r="F124" s="67" t="n">
+        <f aca="false">D124/D112-1</f>
+        <v>0.298754380248438</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="63" t="s">
+        <v>593</v>
+      </c>
+      <c r="B125" s="65" t="n">
+        <v>44592</v>
+      </c>
+      <c r="C125" s="76" t="n">
+        <v>26.2067</v>
+      </c>
+      <c r="D125" s="77" t="n">
+        <v>22.0983</v>
+      </c>
+      <c r="E125" s="67" t="n">
+        <f aca="false">C125/C113-1</f>
+        <v>0.236941099840938</v>
+      </c>
+      <c r="F125" s="67" t="n">
+        <f aca="false">D125/D113-1</f>
+        <v>0.274771994392879</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="63" t="s">
+        <v>594</v>
+      </c>
+      <c r="B126" s="65" t="n">
+        <v>44620</v>
+      </c>
+      <c r="C126" s="76" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="D126" s="77" t="n">
+        <v>21.6711</v>
+      </c>
+      <c r="E126" s="67" t="n">
+        <f aca="false">C126/C114-1</f>
+        <v>0.143747218513574</v>
+      </c>
+      <c r="F126" s="67" t="n">
+        <f aca="false">D126/D114-1</f>
+        <v>0.178731690336196</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="63" t="s">
+        <v>595</v>
+      </c>
+      <c r="B127" s="65" t="n">
+        <v>44651</v>
+      </c>
+      <c r="C127" s="76" t="n">
+        <v>26.2967</v>
+      </c>
+      <c r="D127" s="77" t="n">
+        <v>22.3198</v>
+      </c>
+      <c r="E127" s="67" t="n">
+        <f aca="false">C127/C115-1</f>
+        <v>0.0818704307865734</v>
+      </c>
+      <c r="F127" s="67" t="n">
+        <f aca="false">D127/D115-1</f>
+        <v>0.114379721302718</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="63" t="s">
+        <v>596</v>
+      </c>
+      <c r="B128" s="65" t="n">
+        <v>44680</v>
+      </c>
+      <c r="C128" s="76" t="n">
+        <v>25.2133</v>
+      </c>
+      <c r="D128" s="77" t="n">
+        <v>21.4003</v>
+      </c>
+      <c r="E128" s="67" t="n">
+        <f aca="false">C128/C116-1</f>
+        <v>0.0148933515273737</v>
+      </c>
+      <c r="F128" s="67" t="n">
+        <f aca="false">D128/D116-1</f>
+        <v>0.0453908192525072</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="63" t="s">
+        <v>597</v>
+      </c>
+      <c r="B129" s="65" t="n">
+        <v>44712</v>
+      </c>
+      <c r="C129" s="76" t="n">
+        <v>26.1967</v>
+      </c>
+      <c r="D129" s="77" t="n">
+        <v>22.2349</v>
+      </c>
+      <c r="E129" s="67" t="n">
+        <f aca="false">C129/C117-1</f>
+        <v>0.0215806857931702</v>
+      </c>
+      <c r="F129" s="67" t="n">
+        <f aca="false">D129/D117-1</f>
+        <v>0.0522756420874291</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="63" t="s">
+        <v>598</v>
+      </c>
+      <c r="B130" s="65" t="n">
+        <v>44742</v>
+      </c>
+      <c r="C130" s="76" t="n">
+        <v>23.8767</v>
+      </c>
+      <c r="D130" s="77" t="n">
+        <v>20.4659</v>
+      </c>
+      <c r="E130" s="67" t="n">
+        <f aca="false">C130/C118-1</f>
+        <v>-0.0527637493206172</v>
+      </c>
+      <c r="F130" s="67" t="n">
+        <f aca="false">D130/D118-1</f>
+        <v>-0.021720529820318</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="63" t="s">
+        <v>599</v>
+      </c>
+      <c r="B131" s="65" t="n">
+        <v>44771</v>
+      </c>
+      <c r="C131" s="76" t="n">
+        <v>24.81</v>
+      </c>
+      <c r="D131" s="77" t="n">
+        <v>21.266</v>
+      </c>
+      <c r="E131" s="67" t="n">
+        <f aca="false">C131/C119-1</f>
+        <v>-0.0220733149389043</v>
+      </c>
+      <c r="F131" s="67" t="n">
+        <f aca="false">D131/D119-1</f>
+        <v>0.00997820088431256</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="63" t="s">
+        <v>600</v>
+      </c>
+      <c r="B132" s="65" t="n">
+        <v>44804</v>
+      </c>
+      <c r="C132" s="76" t="n">
+        <v>24.1333</v>
+      </c>
+      <c r="D132" s="77" t="n">
+        <v>20.6859</v>
+      </c>
+      <c r="E132" s="67" t="n">
+        <f aca="false">C132/C120-1</f>
+        <v>-0.0682123552123553</v>
+      </c>
+      <c r="F132" s="67" t="n">
+        <f aca="false">D132/D120-1</f>
+        <v>-0.0376771276249314</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="63" t="s">
+        <v>601</v>
+      </c>
+      <c r="B133" s="65" t="n">
+        <v>44834</v>
+      </c>
+      <c r="C133" s="76" t="n">
+        <v>22.1433</v>
+      </c>
+      <c r="D133" s="77" t="n">
+        <v>19.152</v>
+      </c>
+      <c r="E133" s="67" t="n">
+        <f aca="false">C133/C121-1</f>
+        <v>-0.10520190570864</v>
+      </c>
+      <c r="F133" s="67" t="n">
+        <f aca="false">D133/D121-1</f>
+        <v>-0.0748853992068514</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="63" t="s">
+        <v>602</v>
+      </c>
+      <c r="B134" s="65" t="n">
+        <v>44865</v>
+      </c>
+      <c r="C134" s="76" t="n">
+        <v>24.6267</v>
+      </c>
+      <c r="D134" s="77" t="n">
+        <v>21.2999</v>
+      </c>
+      <c r="E134" s="67" t="n">
+        <f aca="false">C134/C122-1</f>
+        <v>-0.0468326063313039</v>
+      </c>
+      <c r="F134" s="67" t="n">
+        <f aca="false">D134/D122-1</f>
+        <v>-0.0145368069917322</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="63" t="s">
+        <v>603</v>
+      </c>
+      <c r="B135" s="65" t="n">
+        <v>44895</v>
+      </c>
+      <c r="C135" s="76" t="n">
+        <v>26.31</v>
+      </c>
+      <c r="D135" s="77" t="n">
+        <v>22.7558</v>
+      </c>
+      <c r="E135" s="67" t="n">
+        <f aca="false">C135/C123-1</f>
+        <v>0.039645627442535</v>
+      </c>
+      <c r="F135" s="67" t="n">
+        <f aca="false">D135/D123-1</f>
+        <v>0.0748723471590453</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="63" t="s">
+        <v>604</v>
+      </c>
+      <c r="B136" s="65" t="n">
+        <v>44925</v>
+      </c>
+      <c r="C136" s="76" t="n">
+        <v>25.18</v>
+      </c>
+      <c r="D136" s="77" t="n">
+        <v>21.9799</v>
+      </c>
+      <c r="E136" s="67" t="n">
+        <f aca="false">C136/C124-1</f>
+        <v>-0.0654448415747143</v>
+      </c>
+      <c r="F136" s="67" t="n">
+        <f aca="false">D136/D124-1</f>
+        <v>-0.0325535333083914</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="63" t="s">
+        <v>605</v>
+      </c>
+      <c r="B137" s="65" t="n">
+        <v>44957</v>
+      </c>
+      <c r="C137" s="76" t="n">
+        <v>25.7033</v>
+      </c>
+      <c r="D137" s="77" t="n">
+        <v>22.4367</v>
+      </c>
+      <c r="E137" s="67" t="n">
+        <f aca="false">C137/C125-1</f>
+        <v>-0.0192088282767385</v>
+      </c>
+      <c r="F137" s="67" t="n">
+        <f aca="false">D137/D125-1</f>
+        <v>0.0153133951480431</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="63" t="s">
+        <v>606</v>
+      </c>
+      <c r="B138" s="65" t="n">
+        <v>44985</v>
+      </c>
+      <c r="C138" s="76" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="D138" s="77" t="n">
+        <v>21.6918</v>
+      </c>
+      <c r="E138" s="67" t="n">
+        <f aca="false">C138/C126-1</f>
+        <v>-0.0330739299610894</v>
+      </c>
+      <c r="F138" s="67" t="n">
+        <f aca="false">D138/D126-1</f>
+        <v>0.000955189168985404</v>
+      </c>
+    </row>
+    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="63" t="s">
+        <v>607</v>
+      </c>
+      <c r="B139" s="65" t="n">
+        <v>45016</v>
+      </c>
+      <c r="C139" s="76" t="n">
+        <v>24.3867</v>
+      </c>
+      <c r="D139" s="77" t="n">
+        <v>21.4645</v>
+      </c>
+      <c r="E139" s="67" t="n">
+        <f aca="false">C139/C127-1</f>
+        <v>-0.0726326877516951</v>
+      </c>
+      <c r="F139" s="67" t="n">
+        <f aca="false">D139/D127-1</f>
+        <v>-0.0383202358444073</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="63" t="s">
+        <v>608</v>
+      </c>
+      <c r="B140" s="65" t="n">
+        <v>45044</v>
+      </c>
+      <c r="C140" s="76" t="n">
+        <v>24.19</v>
+      </c>
+      <c r="D140" s="77" t="n">
+        <v>21.2914</v>
+      </c>
+      <c r="E140" s="67" t="n">
+        <f aca="false">C140/C128-1</f>
+        <v>-0.0405857226146518</v>
+      </c>
+      <c r="F140" s="67" t="n">
+        <f aca="false">D140/D128-1</f>
+        <v>-0.00508871370962094</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="63" t="s">
+        <v>609</v>
+      </c>
+      <c r="B141" s="65" t="n">
+        <v>45077</v>
+      </c>
+      <c r="C141" s="76" t="n">
+        <v>23.1967</v>
+      </c>
+      <c r="D141" s="77" t="n">
+        <v>20.4171</v>
+      </c>
+      <c r="E141" s="67" t="n">
+        <f aca="false">C141/C129-1</f>
+        <v>-0.11451824084713</v>
+      </c>
+      <c r="F141" s="67" t="n">
+        <f aca="false">D141/D129-1</f>
+        <v>-0.0817543591381117</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="63" t="s">
+        <v>610</v>
+      </c>
+      <c r="B142" s="65" t="n">
+        <v>45107</v>
+      </c>
+      <c r="C142" s="76" t="n">
+        <v>24.2067</v>
+      </c>
+      <c r="D142" s="77" t="n">
+        <v>21.5029</v>
+      </c>
+      <c r="E142" s="67" t="n">
+        <f aca="false">C142/C130-1</f>
+        <v>0.0138210054153214</v>
+      </c>
+      <c r="F142" s="67" t="n">
+        <f aca="false">D142/D130-1</f>
+        <v>0.0506696504917936</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="63" t="s">
+        <v>611</v>
+      </c>
+      <c r="B143" s="65" t="n">
+        <v>45138</v>
+      </c>
+      <c r="C143" s="76" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="D143" s="77" t="n">
+        <v>22.4031</v>
+      </c>
+      <c r="E143" s="67" t="n">
+        <f aca="false">C143/C131-1</f>
+        <v>0.0165255945183393</v>
+      </c>
+      <c r="F143" s="67" t="n">
+        <f aca="false">D143/D131-1</f>
+        <v>0.0534703282234552</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="63" t="s">
+        <v>612</v>
+      </c>
+      <c r="B144" s="65" t="n">
+        <v>45169</v>
+      </c>
+      <c r="C144" s="76" t="n">
+        <v>24.8433</v>
+      </c>
+      <c r="D144" s="77" t="n">
+        <v>22.0685</v>
+      </c>
+      <c r="E144" s="67" t="n">
+        <f aca="false">C144/C132-1</f>
+        <v>0.0294199301380251</v>
+      </c>
+      <c r="F144" s="67" t="n">
+        <f aca="false">D144/D132-1</f>
+        <v>0.0668377977269541</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="63" t="s">
+        <v>613</v>
+      </c>
+      <c r="B145" s="65" t="n">
+        <v>45198</v>
+      </c>
+      <c r="C145" s="76" t="n">
+        <v>23.5867</v>
+      </c>
+      <c r="D145" s="77" t="n">
+        <v>21.1408</v>
+      </c>
+      <c r="E145" s="67" t="n">
+        <f aca="false">C145/C133-1</f>
+        <v>0.0651845027615576</v>
+      </c>
+      <c r="F145" s="67" t="n">
+        <f aca="false">D145/D133-1</f>
+        <v>0.103842940685046</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="63" t="s">
+        <v>614</v>
+      </c>
+      <c r="B146" s="65" t="n">
+        <v>45230</v>
+      </c>
+      <c r="C146" s="76" t="n">
+        <v>22.6867</v>
+      </c>
+      <c r="D146" s="77" t="n">
+        <v>20.3341</v>
+      </c>
+      <c r="E146" s="67" t="n">
+        <f aca="false">C146/C134-1</f>
+        <v>-0.0787762875253283</v>
+      </c>
+      <c r="F146" s="67" t="n">
+        <f aca="false">D146/D134-1</f>
+        <v>-0.0453429358823282</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="63" t="s">
+        <v>615</v>
+      </c>
+      <c r="B147" s="65" t="n">
+        <v>45260</v>
+      </c>
+      <c r="C147" s="76" t="n">
+        <v>24.1167</v>
+      </c>
+      <c r="D147" s="77" t="n">
+        <v>21.6158</v>
+      </c>
+      <c r="E147" s="67" t="n">
+        <f aca="false">C147/C135-1</f>
+        <v>-0.0833637400228049</v>
+      </c>
+      <c r="F147" s="67" t="n">
+        <f aca="false">D147/D135-1</f>
+        <v>-0.0500971180973642</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="63" t="s">
+        <v>616</v>
+      </c>
+      <c r="B148" s="65" t="n">
+        <v>45289</v>
+      </c>
+      <c r="C148" s="76" t="n">
+        <v>25.3767</v>
+      </c>
+      <c r="D148" s="77" t="n">
+        <v>22.9787</v>
+      </c>
+      <c r="E148" s="67" t="n">
+        <f aca="false">C148/C136-1</f>
+        <v>0.00781175536139789</v>
+      </c>
+      <c r="F148" s="67" t="n">
+        <f aca="false">D148/D136-1</f>
+        <v>0.0454415170223703</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="63" t="s">
+        <v>617</v>
+      </c>
+      <c r="B149" s="65" t="n">
+        <v>45322</v>
+      </c>
+      <c r="C149" s="76" t="n">
+        <v>25.4133</v>
+      </c>
+      <c r="D149" s="77" t="n">
+        <v>23.0119</v>
+      </c>
+      <c r="E149" s="67" t="n">
+        <f aca="false">C149/C137-1</f>
+        <v>-0.0112825979543483</v>
+      </c>
+      <c r="F149" s="67" t="n">
+        <f aca="false">D149/D137-1</f>
+        <v>0.0256365686576012</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="63" t="s">
+        <v>618</v>
+      </c>
+      <c r="B150" s="65" t="n">
+        <v>45351</v>
+      </c>
+      <c r="C150" s="76" t="n">
+        <v>25.88</v>
+      </c>
+      <c r="D150" s="77" t="n">
+        <v>23.4345</v>
+      </c>
+      <c r="E150" s="67" t="n">
+        <f aca="false">C150/C138-1</f>
+        <v>0.0414486921529174</v>
+      </c>
+      <c r="F150" s="67" t="n">
+        <f aca="false">D150/D138-1</f>
+        <v>0.0803391143196968</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="63" t="s">
+        <v>619</v>
+      </c>
+      <c r="B151" s="65" t="n">
+        <v>45379</v>
+      </c>
+      <c r="C151" s="76" t="n">
+        <v>26.8767</v>
+      </c>
+      <c r="D151" s="77" t="n">
+        <v>24.5265</v>
+      </c>
+      <c r="E151" s="67" t="n">
+        <f aca="false">C151/C139-1</f>
+        <v>0.102104835832646</v>
+      </c>
+      <c r="F151" s="67" t="n">
+        <f aca="false">D151/D139-1</f>
+        <v>0.142654149875376</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="63" t="s">
+        <v>620</v>
+      </c>
+      <c r="B152" s="65" t="n">
+        <v>45412</v>
+      </c>
+      <c r="C152" s="76" t="n">
+        <v>25.6633</v>
+      </c>
+      <c r="D152" s="77" t="n">
+        <v>23.4192</v>
+      </c>
+      <c r="E152" s="67" t="n">
+        <f aca="false">C152/C140-1</f>
+        <v>0.0609053327821414</v>
+      </c>
+      <c r="F152" s="67" t="n">
+        <f aca="false">D152/D140-1</f>
+        <v>0.0999370637910142</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="63" t="s">
+        <v>621</v>
+      </c>
+      <c r="B153" s="65" t="n">
+        <v>45443</v>
+      </c>
+      <c r="C153" s="76" t="n">
+        <v>26.19</v>
+      </c>
+      <c r="D153" s="77" t="n">
+        <v>23.8998</v>
+      </c>
+      <c r="E153" s="67" t="n">
+        <f aca="false">C153/C141-1</f>
+        <v>0.12903990653843</v>
+      </c>
+      <c r="F153" s="67" t="n">
+        <f aca="false">D153/D141-1</f>
+        <v>0.170577604067179</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="63" t="s">
+        <v>622</v>
+      </c>
+      <c r="B154" s="65" t="n">
+        <v>45471</v>
+      </c>
+      <c r="C154" s="76" t="n">
+        <v>25.92</v>
+      </c>
+      <c r="D154" s="77" t="n">
+        <v>23.9041</v>
+      </c>
+      <c r="E154" s="67" t="n">
+        <f aca="false">C154/C142-1</f>
+        <v>0.0707779251199048</v>
+      </c>
+      <c r="F154" s="67" t="n">
+        <f aca="false">D154/D142-1</f>
+        <v>0.111668658646043</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="63" t="s">
+        <v>623</v>
+      </c>
+      <c r="B155" s="65" t="n">
+        <v>45504</v>
+      </c>
+      <c r="C155" s="76" t="n">
+        <v>27.5267</v>
+      </c>
+      <c r="D155" s="77" t="n">
+        <v>25.3858</v>
+      </c>
+      <c r="E155" s="67" t="n">
+        <f aca="false">C155/C143-1</f>
+        <v>0.0914631245043618</v>
+      </c>
+      <c r="F155" s="67" t="n">
+        <f aca="false">D155/D143-1</f>
+        <v>0.133137824676049</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="63" t="s">
+        <v>624</v>
+      </c>
+      <c r="B156" s="65" t="n">
+        <v>45534</v>
+      </c>
+      <c r="C156" s="76" t="n">
+        <v>28.1767</v>
+      </c>
+      <c r="D156" s="77" t="n">
+        <v>25.9853</v>
+      </c>
+      <c r="E156" s="67" t="n">
+        <f aca="false">C156/C144-1</f>
+        <v>0.134177021571208</v>
+      </c>
+      <c r="F156" s="67" t="n">
+        <f aca="false">D156/D144-1</f>
+        <v>0.177483743797721</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="63" t="s">
+        <v>625</v>
+      </c>
+      <c r="B157" s="65" t="n">
+        <v>45565</v>
+      </c>
+      <c r="C157" s="76" t="n">
+        <v>28.1767</v>
+      </c>
+      <c r="D157" s="77" t="n">
+        <v>26.218</v>
+      </c>
+      <c r="E157" s="67" t="n">
+        <f aca="false">C157/C145-1</f>
+        <v>0.194601194741104</v>
+      </c>
+      <c r="F157" s="67" t="n">
+        <f aca="false">D157/D145-1</f>
+        <v>0.240161204873988</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="63" t="s">
+        <v>626</v>
+      </c>
+      <c r="B158" s="65" t="n">
+        <v>45596</v>
+      </c>
+      <c r="C158" s="76" t="n">
+        <v>28.23</v>
+      </c>
+      <c r="D158" s="77" t="n">
+        <v>26.2676</v>
+      </c>
+      <c r="E158" s="67" t="n">
+        <f aca="false">C158/C146-1</f>
+        <v>0.244341398264181</v>
+      </c>
+      <c r="F158" s="67" t="n">
+        <f aca="false">D158/D146-1</f>
+        <v>0.291800473096916</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="63" t="s">
+        <v>627</v>
+      </c>
+      <c r="B159" s="65" t="n">
+        <v>45625</v>
+      </c>
+      <c r="C159" s="76" t="n">
+        <v>29.53</v>
+      </c>
+      <c r="D159" s="77" t="n">
+        <v>27.4772</v>
+      </c>
+      <c r="E159" s="67" t="n">
+        <f aca="false">C159/C147-1</f>
+        <v>0.22446271670668</v>
+      </c>
+      <c r="F159" s="67" t="n">
+        <f aca="false">D159/D147-1</f>
+        <v>0.271162760573284</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="63" t="s">
+        <v>628</v>
+      </c>
+      <c r="B160" s="65" t="n">
+        <v>45657</v>
+      </c>
+      <c r="C160" s="76" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="D160" s="77" t="n">
+        <v>25.658</v>
+      </c>
+      <c r="E160" s="67" t="n">
+        <f aca="false">C160/C148-1</f>
+        <v>0.0765781208746605</v>
+      </c>
+      <c r="F160" s="67" t="n">
+        <f aca="false">D160/D148-1</f>
+        <v>0.116599285425198</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="63" t="s">
+        <v>629</v>
+      </c>
+      <c r="B161" s="65" t="n">
+        <v>45688</v>
+      </c>
+      <c r="C161" s="76" t="n">
+        <v>27.83</v>
+      </c>
+      <c r="D161" s="77" t="n">
+        <v>26.1369</v>
+      </c>
+      <c r="E161" s="67" t="n">
+        <f aca="false">C161/C149-1</f>
+        <v>0.0950958749945894</v>
+      </c>
+      <c r="F161" s="67" t="n">
+        <f aca="false">D161/D149-1</f>
+        <v>0.135799303838449</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="63" t="s">
+        <v>630</v>
+      </c>
+      <c r="B162" s="65" t="n">
+        <v>45716</v>
+      </c>
+      <c r="C162" s="76" t="n">
+        <v>28.54</v>
+      </c>
+      <c r="D162" s="77" t="n">
+        <v>26.8037</v>
+      </c>
+      <c r="E162" s="67" t="n">
+        <f aca="false">C162/C150-1</f>
+        <v>0.102782071097373</v>
+      </c>
+      <c r="F162" s="67" t="n">
+        <f aca="false">D162/D150-1</f>
+        <v>0.143770936013143</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="63" t="s">
+        <v>631</v>
+      </c>
+      <c r="B163" s="65" t="n">
+        <v>45747</v>
+      </c>
+      <c r="C163" s="76" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="D163" s="77" t="n">
+        <v>26.496</v>
+      </c>
+      <c r="E163" s="67" t="n">
+        <f aca="false">C163/C151-1</f>
+        <v>0.0403062876022726</v>
+      </c>
+      <c r="F163" s="67" t="n">
+        <f aca="false">D163/D151-1</f>
+        <v>0.0803008990275824</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="63" t="s">
+        <v>632</v>
+      </c>
+      <c r="B164" s="65" t="n">
+        <v>45777</v>
+      </c>
+      <c r="C164" s="76" t="n">
+        <v>25.82</v>
+      </c>
+      <c r="D164" s="77" t="n">
+        <v>24.468</v>
+      </c>
+      <c r="E164" s="67" t="n">
+        <f aca="false">C164/C152-1</f>
+        <v>0.00610599572151682</v>
+      </c>
+      <c r="F164" s="67" t="n">
+        <f aca="false">D164/D152-1</f>
+        <v>0.0447837671654028</v>
+      </c>
+    </row>
+    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="63" t="s">
+        <v>633</v>
+      </c>
+      <c r="B165" s="65" t="n">
+        <v>45807</v>
+      </c>
+      <c r="C165" s="76" t="n">
+        <v>26.17</v>
+      </c>
+      <c r="D165" s="77" t="n">
+        <v>24.7997</v>
+      </c>
+      <c r="E165" s="67" t="n">
+        <f aca="false">C165/C153-1</f>
+        <v>-0.000763650248186365</v>
+      </c>
+      <c r="F165" s="67" t="n">
+        <f aca="false">D165/D153-1</f>
+        <v>0.037653034753429</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="63" t="s">
+        <v>634</v>
+      </c>
+      <c r="B166" s="65" t="n">
+        <v>45838</v>
+      </c>
+      <c r="C166" s="76" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D166" s="77" t="n">
+        <v>25.359</v>
+      </c>
+      <c r="E166" s="67" t="n">
+        <f aca="false">C166/C154-1</f>
+        <v>0.0223765432098764</v>
+      </c>
+      <c r="F166" s="67" t="n">
+        <f aca="false">D166/D154-1</f>
+        <v>0.0608640358766908</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="63" t="s">
+        <v>635</v>
+      </c>
+      <c r="B167" s="65" t="n">
+        <v>45869</v>
+      </c>
+      <c r="C167" s="76" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="D167" s="77" t="n">
+        <v>25.359</v>
+      </c>
+      <c r="E167" s="67" t="n">
+        <f aca="false">C167/C155-1</f>
+        <v>-0.037298332164771</v>
+      </c>
+      <c r="F167" s="67" t="n">
+        <f aca="false">D167/D155-1</f>
+        <v>-0.00105570830936974</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="63" t="s">
+        <v>636</v>
+      </c>
+      <c r="B168" s="65" t="n">
+        <v>45898</v>
+      </c>
+      <c r="C168" s="76" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="D168" s="77" t="n">
+        <v>26.7179</v>
+      </c>
+      <c r="E168" s="67" t="n">
+        <f aca="false">C168/C156-1</f>
+        <v>-0.00911036423711786</v>
+      </c>
+      <c r="F168" s="67" t="n">
+        <f aca="false">D168/D156-1</f>
+        <v>0.0281928628878636</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="63" t="s">
+        <v>637</v>
+      </c>
+      <c r="B169" s="65" t="n">
+        <v>45930</v>
+      </c>
+      <c r="C169" s="76" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="D169" s="77" t="n">
+        <v>26.3748</v>
+      </c>
+      <c r="E169" s="67" t="n">
+        <f aca="false">C169/C157-1</f>
+        <v>-0.0311143604467521</v>
+      </c>
+      <c r="F169" s="67" t="n">
+        <f aca="false">D169/D157-1</f>
+        <v>0.00598062399877941</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="63" t="s">
+        <v>638</v>
+      </c>
+      <c r="B170" s="65" t="n">
+        <v>45961</v>
+      </c>
+      <c r="C170" s="76" t="n">
+        <v>26.75</v>
+      </c>
+      <c r="D170" s="77" t="n">
+        <v>25.8435</v>
+      </c>
+      <c r="E170" s="67" t="n">
+        <f aca="false">C170/C158-1</f>
+        <v>-0.0524264966347857</v>
+      </c>
+      <c r="F170" s="67" t="n">
+        <f aca="false">D170/D158-1</f>
+        <v>-0.016145365393108</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="63" t="s">
+        <v>639</v>
+      </c>
+      <c r="B171" s="65" t="n">
+        <v>45989</v>
+      </c>
+      <c r="C171" s="76" t="n">
+        <v>27.59</v>
+      </c>
+      <c r="D171" s="77" t="n">
+        <v>26.655</v>
+      </c>
+      <c r="E171" s="67" t="n">
+        <f aca="false">C171/C159-1</f>
+        <v>-0.0656959024720624</v>
+      </c>
+      <c r="F171" s="67" t="n">
+        <f aca="false">D171/D159-1</f>
+        <v>-0.0299229906977421</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="63" t="s">
+        <v>640</v>
+      </c>
+      <c r="B172" s="65" t="n">
+        <v>46022</v>
+      </c>
+      <c r="C172" s="76" t="n">
+        <v>27.43</v>
+      </c>
+      <c r="D172" s="77" t="n">
+        <v>26.7715</v>
+      </c>
+      <c r="E172" s="67" t="n">
+        <f aca="false">C172/C160-1</f>
+        <v>0.00402635431918008</v>
+      </c>
+      <c r="F172" s="67" t="n">
+        <f aca="false">D172/D160-1</f>
+        <v>0.0433977706758126</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="63" t="s">
+        <v>641</v>
+      </c>
+      <c r="B173" s="65" t="n">
+        <v>46052</v>
+      </c>
+      <c r="C173" s="76" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="D173" s="77" t="n">
+        <v>29.1041</v>
+      </c>
+      <c r="E173" s="67" t="n">
+        <f aca="false">C173/C161-1</f>
+        <v>0.071505569529285</v>
+      </c>
+      <c r="F173" s="67" t="n">
+        <f aca="false">D173/D161-1</f>
+        <v>0.113525322436861</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="63" t="s">
+        <v>642</v>
+      </c>
+      <c r="B174" s="65" t="n">
+        <v>46080</v>
+      </c>
+      <c r="C174" s="76" t="n">
+        <v>31.77</v>
+      </c>
+      <c r="D174" s="77" t="n">
+        <v>31.0073</v>
+      </c>
+      <c r="E174" s="67" t="n">
+        <f aca="false">C174/C162-1</f>
+        <v>0.113174491941135</v>
+      </c>
+      <c r="F174" s="67" t="n">
+        <f aca="false">D174/D162-1</f>
+        <v>0.156829094490686</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="63" t="s">
+        <v>643</v>
+      </c>
+      <c r="B175" s="65" t="n">
+        <v>46112</v>
+      </c>
+      <c r="C175" s="76" t="n">
+        <v>30.68</v>
+      </c>
+      <c r="D175" s="77" t="n">
+        <v>30.1967</v>
+      </c>
+      <c r="E175" s="67" t="n">
+        <f aca="false">C175/C163-1</f>
+        <v>0.0972818311874106</v>
+      </c>
+      <c r="F175" s="67" t="n">
+        <f aca="false">D175/D163-1</f>
+        <v>0.139670138888889</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="63" t="s">
+        <v>644</v>
+      </c>
+      <c r="B176" s="65" t="n">
+        <v>46142</v>
+      </c>
+      <c r="C176" s="76" t="n">
+        <v>32.07</v>
+      </c>
+      <c r="D176" s="77" t="n">
+        <v>31.5648</v>
+      </c>
+      <c r="E176" s="67" t="n">
+        <f aca="false">C176/C164-1</f>
+        <v>0.242060418280403</v>
+      </c>
+      <c r="F176" s="67" t="n">
+        <f aca="false">D176/D164-1</f>
+        <v>0.290044139283963</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="63" t="s">
+        <v>645</v>
+      </c>
+      <c r="B177" s="65" t="n">
+        <v>46171</v>
+      </c>
+      <c r="C177" s="76" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="D177" s="77" t="n">
+        <v>31.9881</v>
+      </c>
+      <c r="E177" s="67" t="n">
+        <f aca="false">C177/C165-1</f>
+        <v>0.241880015284677</v>
+      </c>
+      <c r="F177" s="67" t="n">
+        <f aca="false">D177/D165-1</f>
+        <v>0.289858345060626</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="63" t="s">
+        <v>646</v>
+      </c>
+      <c r="B178" s="65" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C178" s="76" t="n">
+        <v>31.71</v>
+      </c>
+      <c r="D178" s="77" t="n">
+        <v>31.4591</v>
+      </c>
+      <c r="E178" s="67" t="n">
+        <f aca="false">C178/C166-1</f>
+        <v>0.196603773584906</v>
+      </c>
+      <c r="F178" s="67" t="n">
+        <f aca="false">D178/D166-1</f>
+        <v>0.240549706218699</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="63" t="s">
+        <v>647</v>
+      </c>
+      <c r="B179" s="65" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C179" s="76" t="n">
+        <v>33.47</v>
+      </c>
+      <c r="D179" s="77" t="n">
+        <v>33.2051</v>
+      </c>
+      <c r="E179" s="67" t="n">
+        <f aca="false">C179/C167-1</f>
+        <v>0.263018867924528</v>
+      </c>
+      <c r="F179" s="67" t="n">
+        <f aca="false">D179/D167-1</f>
+        <v>0.309401001616783</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="63" t="s">
+        <v>648</v>
+      </c>
+      <c r="B180" s="65" t="n">
+        <v>46265</v>
+      </c>
+      <c r="C180" s="76" t="n">
+        <v>34.89</v>
+      </c>
+      <c r="D180" s="77" t="n">
+        <v>34.6139</v>
+      </c>
+      <c r="E180" s="67" t="n">
+        <f aca="false">C180/C168-1</f>
+        <v>0.249641833810888</v>
+      </c>
+      <c r="F180" s="67" t="n">
+        <f aca="false">D180/D168-1</f>
+        <v>0.295532208743951</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="63" t="s">
+        <v>649</v>
+      </c>
+      <c r="B181" s="65" t="n">
+        <v>46295</v>
+      </c>
+      <c r="C181" s="76" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="D181" s="77" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="E181" s="67" t="n">
+        <f aca="false">C181/C169-1</f>
+        <v>0.191575091575092</v>
+      </c>
+      <c r="F181" s="67" t="n">
+        <f aca="false">D181/D169-1</f>
+        <v>0.233374281511139</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="63" t="s">
+        <v>650</v>
+      </c>
+      <c r="B182" s="65" t="n">
+        <v>46297</v>
+      </c>
+      <c r="C182" s="76" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="D182" s="77" t="n">
+        <v>32.72</v>
+      </c>
+      <c r="E182" s="67" t="n">
+        <f aca="false">C182/C170-1</f>
+        <v>0.223177570093458</v>
+      </c>
+      <c r="F182" s="67" t="n">
+        <f aca="false">D182/D170-1</f>
+        <v>0.26608238048252</v>
       </c>
     </row>
   </sheetData>
@@ -31137,5 +37420,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -3510,7 +3510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3825,6 +3825,75 @@
       <c r="B31" s="22">
         <f>INDEX(연도별!$F$2:$F$21,MATCH(B25,연도별!$A$2:$A$21,0))</f>
         <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>공식 수익률 · 다음 배당</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>30일 SEC 수익률 (Schwab 공식)</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="n">
+        <v>0.0337</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-07 기준 · 최근 30일 순투자수익(보수 차감) 연 환산</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>분배수익률 TTM (Schwab 공식)</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-31 기준 · 최근 12개월 분배금 ÷ 기준일 NAV</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>다음 배당락일 (예정)</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n">
+        <v>46365</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>2026년 4분기 · 금액 미발표 · Schwab 분배 일정 기준(변경 가능)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>다음 지급일 (예정)</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n">
+        <v>46370</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>금액 출처: Schwab 공식 · 트래커 반영 2026-10-03 · 실제 세후 입금액은 증권사 거래내역 기준</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1247,6 +1247,36 @@
 </comments>
 </file>
 
+<file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>tracker</author>
+  </authors>
+  <commentList>
+    <comment ref="C6" authorId="0" shapeId="0">
+      <text>
+        <t>총보수 0.01% + 기타비용 0.05% + 매매·중개수수료 0.0434% (KOFIA 2026-08-31)</t>
+      </text>
+    </comment>
+    <comment ref="C7" authorId="0" shapeId="0">
+      <text>
+        <t>총보수 0.01% + 기타비용 0.06% + 매매·중개수수료 0.0998% (KOFIA 2026-08-31)</t>
+      </text>
+    </comment>
+    <comment ref="C8" authorId="0" shapeId="0">
+      <text>
+        <t>총보수 0.01% + 기타비용 0.06% + 매매·중개수수료 0.0781% (KOFIA 2026-08-31)</t>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0" shapeId="0">
+      <text>
+        <t>총보수 0.0099% + 기타비용 0.08% + 매매·중개수수료 0.0934% (KOFIA 2026-08-31)</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
@@ -1666,7 +1696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C35"/>
+  <dimension ref="B2:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1886,81 +1916,93 @@
     <row r="26">
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>총보수</t>
+          <t>국내 ETF 실부담비용</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
         <is>
-          <t>KOFIA 금융투자협회 공시 2026-08-31</t>
+          <t>KOFIA 금융투자협회 전자공시 펀드별 보수비용비교 (단위 %, 실부담비용 = 총보수 + 기타비용 + 매매·중개수수료 + 판매수수료) — 기준일은 [국내SCHD형_비교] 시트 메모</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="4" t="inlineStr">
         <is>
+          <t>국내 ETF 총보수(참고)</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>KOFIA 금융투자협회 공시 2026-08-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="4" t="inlineStr">
+        <is>
           <t>구성종목·월별 비중</t>
         </is>
       </c>
-      <c r="C27" s="10" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>Schwab 공식 보유종목 CSV(SCHD_FundHoldings, 2021-09부터 공개) — 매일 자동 수집(못 받은 날은 마지막 보유 주식 수 × Yahoo 종가로 계산). [월별_비중]·[월별_섹터]는 매월 첫 거래일 기록</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="3" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
         <is>
           <t>알아둘 점</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>· 2024-10-11 SCHD 3:1 주식분할. 그 이전 배당은 공시 금액 ÷ 3 으로 환산해 지금 1주 기준으로 맞춥니다 (F열 자동).</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>· 연간 성장률은 4회 배당이 모두 확정된 해만 계산합니다. 진행 중인 해는 [연도별] 시트의 '올해 누적 vs 작년 동기'로 봅니다.</t>
+          <t>· 2024-10-11 SCHD 3:1 주식분할. 그 이전 배당은 공시 금액 ÷ 3 으로 환산해 지금 1주 기준으로 맞춥니다 (F열 자동).</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>· '평균 성장률(산술)'과 'CAGR(연평균 복리)'은 다른 숫자입니다. 글에 쓸 때 용어를 구분하세요.</t>
+          <t>· 연간 성장률은 4회 배당이 모두 확정된 해만 계산합니다. 진행 중인 해는 [연도별] 시트의 '올해 누적 vs 작년 동기'로 봅니다.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>· 진행 중인 해의 남은 분기 '예상' 값은 그해 확정 분기의 단순 평균입니다. 과거 14년 중 13년은 4분기가 1~3분기 평균보다 높았으니(보통 +8~16%) 연간 예상치는 보수적(낮게) 나올 가능성이 큽니다.</t>
+          <t>· '평균 성장률(산술)'과 'CAGR(연평균 복리)'은 다른 숫자입니다. 글에 쓸 때 용어를 구분하세요.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>· 이 파일은 GitHub에서 새 배당이 반영될 때마다 다시 만들어집니다(차트 범위도 자동). 손으로 고친 내용은 다음 생성 때 덮어써지니, 고칠 값은 data 폴더 JSON에서 고치세요.</t>
+          <t>· 진행 중인 해의 남은 분기 '예상' 값은 그해 확정 분기의 단순 평균입니다. 과거 14년 중 13년은 4분기가 1~3분기 평균보다 높았으니(보통 +8~16%) 연간 예상치는 보수적(낮게) 나올 가능성이 큽니다.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="4" t="inlineStr">
         <is>
+          <t>· 이 파일은 GitHub에서 새 배당이 반영될 때마다 다시 만들어집니다(차트 범위도 자동). 손으로 고친 내용은 다음 생성 때 덮어써지니, 고칠 값은 data 폴더 JSON에서 고치세요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="4" t="inlineStr">
+        <is>
           <t>· 국내 SCHD형 ETF 분배율은 매월 기준일 가격 대비 분배율을 12개월 합산한 값입니다(근사치).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="B30:C30"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="B34:C34"/>
+    <mergeCell ref="B36:C36"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B35:C35"/>
@@ -24071,7 +24113,7 @@
       </c>
       <c r="C5" s="23" t="inlineStr">
         <is>
-          <t>총보수
+          <t>실부담비용
 (연)</t>
         </is>
       </c>
@@ -24122,7 +24164,7 @@
         </is>
       </c>
       <c r="C6" s="51" t="n">
-        <v>0.0001</v>
+        <v>0.001034</v>
       </c>
       <c r="D6" s="33" t="inlineStr">
         <is>
@@ -24162,7 +24204,7 @@
         </is>
       </c>
       <c r="C7" s="51" t="n">
-        <v>0.0001</v>
+        <v>0.001698</v>
       </c>
       <c r="D7" s="33" t="inlineStr">
         <is>
@@ -24202,7 +24244,7 @@
         </is>
       </c>
       <c r="C8" s="51" t="n">
-        <v>0.0001</v>
+        <v>0.001481</v>
       </c>
       <c r="D8" s="33" t="inlineStr">
         <is>
@@ -24242,7 +24284,7 @@
         </is>
       </c>
       <c r="C9" s="51" t="n">
-        <v>9.899999999999999e-05</v>
+        <v>0.001834</v>
       </c>
       <c r="D9" s="33" t="inlineStr">
         <is>
@@ -24313,14 +24355,14 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>※ SCHD 행: 금액은 USD, 수익률은 최근 4회 배당 ÷ 배당락일 종가. 총보수 0.06%는 Schwab 공시.</t>
+          <t>※ SCHD 행: 금액은 USD, 수익률은 최근 4회 배당 ÷ 배당락일 종가. 0.06%는 Schwab 공시 운용보수(매매비용 별도)라 국내 ETF 실부담비용과 기준이 다릅니다.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>※ 국내 ETF 총보수: KOFIA 금융투자협회 공시 2026-08-31. 실부담비용(기타비용·매매중개수수료 포함)은 이보다 높습니다.</t>
+          <t>※ 국내 ETF 실부담비용 = 총보수 + 기타비용 + 매매·중개수수료(+판매수수료), 금융투자협회 공시 2026-08-31 기준. 셀 메모에 항목별 금액.</t>
         </is>
       </c>
     </row>
@@ -25453,6 +25495,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -17,8 +17,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="구성종목" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별_비중" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="월별_섹터" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주가_월별" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="차트데이터" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="리밸런싱" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="주가_월별" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="차트데이터" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -151,7 +152,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -263,6 +264,15 @@
     <xf numFmtId="10" fontId="5" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="168" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="179" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5096,6 +5106,674 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="60" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>SCHD 리밸런싱 기록 (직전 거래일 → 적용 후 공식 보유종목 비교)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>매년 3·6·9·12월 셋째 금요일 장 마감 후 반영 → 다음 거래일(보통 월요일) 적용. 3월은 정기 종목 교체(+비중), 나머지는 비중 재조정. 3월 적용일 파일은 새 종목 비중이 비어 있어 다음 거래일 공시로 기록.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>적용일</t>
+        </is>
+      </c>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>비교 기준
+(직전 거래일)</t>
+        </is>
+      </c>
+      <c r="D4" s="23" t="inlineStr">
+        <is>
+          <t>비중 공시일</t>
+        </is>
+      </c>
+      <c r="E4" s="23" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="G4" s="23" t="inlineStr">
+        <is>
+          <t>주식 수
+바뀐 종목</t>
+        </is>
+      </c>
+      <c r="H4" s="23" t="inlineStr">
+        <is>
+          <t>편입 종목</t>
+        </is>
+      </c>
+      <c r="I4" s="23" t="inlineStr">
+        <is>
+          <t>편출 종목</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="71" t="n">
+        <v>44550</v>
+      </c>
+      <c r="B5" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C5" s="71" t="n">
+        <v>44547</v>
+      </c>
+      <c r="D5" s="71" t="n">
+        <v>44550</v>
+      </c>
+      <c r="E5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="H5" s="72" t="inlineStr"/>
+      <c r="I5" s="72" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="73" t="n">
+        <v>44641</v>
+      </c>
+      <c r="B6" s="74" t="inlineStr">
+        <is>
+          <t>정기 종목 교체</t>
+        </is>
+      </c>
+      <c r="C6" s="73" t="n">
+        <v>44638</v>
+      </c>
+      <c r="D6" s="73" t="n">
+        <v>44642</v>
+      </c>
+      <c r="E6" s="74" t="n">
+        <v>12</v>
+      </c>
+      <c r="F6" s="74" t="n">
+        <v>13</v>
+      </c>
+      <c r="G6" s="74" t="n">
+        <v>27</v>
+      </c>
+      <c r="H6" s="75" t="inlineStr">
+        <is>
+          <t>EOG 리소시스(EOG), Lyondellbasell Industries Nv Class(LYB), Paramount Global Class B(PARA), Nrg Energy Inc(NRG), First American Financial Corp(FAF), Jefferies Financial Group Inc(JEF), H&amp;R Block Inc(HRB), Radian Group Inc(RDN), Insperity(NSP), American Eagle Outfitters Inc(AEO), Buckle(BKE), Ethan Allen Interiors(ETD)</t>
+        </is>
+      </c>
+      <c r="I6" s="75" t="inlineStr">
+        <is>
+          <t>Emerson Electric(EMR), Steel Dynamics Inc(STLD), Apollo Global Management Inc(APO), Organon(OGN), Sonoco Products(SON), Nu Skin Enterprises Inc Class A(NUS), Kyndryl Holdings Inc(KD), B And G Foods Inc(BGS), Bancfirst Corp(BANF), Schweitzer Mauduit International I(SWM), Neenah Inc(NP), Ennis Inc(EBF), Cass Information Systems Inc(CASS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="71" t="n">
+        <v>44733</v>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C7" s="71" t="n">
+        <v>44729</v>
+      </c>
+      <c r="D7" s="71" t="n">
+        <v>44733</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="72" t="inlineStr"/>
+      <c r="I7" s="72" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="71" t="n">
+        <v>44823</v>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C8" s="71" t="n">
+        <v>44820</v>
+      </c>
+      <c r="D8" s="71" t="n">
+        <v>44823</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="H8" s="72" t="inlineStr"/>
+      <c r="I8" s="72" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="71" t="n">
+        <v>44914</v>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C9" s="71" t="n">
+        <v>44911</v>
+      </c>
+      <c r="D9" s="71" t="n">
+        <v>44914</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="H9" s="72" t="inlineStr"/>
+      <c r="I9" s="72" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="73" t="n">
+        <v>45005</v>
+      </c>
+      <c r="B10" s="74" t="inlineStr">
+        <is>
+          <t>정기 종목 교체</t>
+        </is>
+      </c>
+      <c r="C10" s="73" t="n">
+        <v>45002</v>
+      </c>
+      <c r="D10" s="73" t="n">
+        <v>45006</v>
+      </c>
+      <c r="E10" s="74" t="n">
+        <v>25</v>
+      </c>
+      <c r="F10" s="74" t="n">
+        <v>24</v>
+      </c>
+      <c r="G10" s="74" t="n">
+        <v>19</v>
+      </c>
+      <c r="H10" s="75" t="inlineStr">
+        <is>
+          <t>Abbvie Inc(ABBV), UPS(UPS), 셰브론(CVX), 블랙스톤(BX), Ford Motor(F), Coterra Energy Inc(CTRA), Darden Restaurants Inc(DRI), Packaging Corp Of America(PKG), Robert Half Inc(RHI), Williams Sonoma Inc(WSM), Advance Auto Parts Inc(AAP), Huntsman Corp(HUN), Wendys(WEN), Carters Inc(CRI), Cracker Barrel Old Country Store I(CBRL), Mdc Holdings Inc(MDC), Artisan Partners Asset Management(APAM), Ofg Bancorp(OFG), Kforce Inc(KFRC), Stewart Info Services Corp(STC), Clearway Energy Inc Class A(CWENA), Hanmi Financial Corp(HAFC), Guess Inc(GES), Ennis Inc(EBF), Central Pacific Financial Corp(CPF)</t>
+        </is>
+      </c>
+      <c r="I10" s="75" t="inlineStr">
+        <is>
+          <t>International Business Machines Co(IBM), Cummins Inc(CMI), Prudential Financial Inc(PRU), Genuine Parts(GPC), Hartford Financial Services Group(HIG), Omnicom Group Inc(OMC), Cincinnati Financial(CINF), Principal Financial Group Inc(PFG), First Horizon Corp(FHN), Franklin Resources Inc(BEN), Webster Financial Corp(WBS), Hasbro Inc(HAS), Jefferies Financial Group Inc(JEF), Flowers Foods Inc(FLO), Insperity(NSP), Evercore Inc Class A(EVR), Federated Hermes Inc Class B(FHI), Mcgrath Rent(MGRC), Stock Yards Bancorp Inc(SYBT), Employers Holdings Inc(EIG), Safety Insurance Group Inc(SAFT), Hni Corp(HNI), Mercury General Corp(MCY), Petmed Express Inc(PETS)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="71" t="n">
+        <v>45097</v>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C11" s="71" t="n">
+        <v>45093</v>
+      </c>
+      <c r="D11" s="71" t="n">
+        <v>45097</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H11" s="72" t="inlineStr"/>
+      <c r="I11" s="72" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="71" t="n">
+        <v>45187</v>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C12" s="71" t="n">
+        <v>45184</v>
+      </c>
+      <c r="D12" s="71" t="n">
+        <v>45187</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H12" s="72" t="inlineStr"/>
+      <c r="I12" s="72" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="71" t="n">
+        <v>45278</v>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C13" s="71" t="n">
+        <v>45275</v>
+      </c>
+      <c r="D13" s="71" t="n">
+        <v>45278</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="H13" s="72" t="inlineStr"/>
+      <c r="I13" s="72" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="73" t="n">
+        <v>45369</v>
+      </c>
+      <c r="B14" s="74" t="inlineStr">
+        <is>
+          <t>정기 종목 교체</t>
+        </is>
+      </c>
+      <c r="C14" s="73" t="n">
+        <v>45366</v>
+      </c>
+      <c r="D14" s="73" t="n">
+        <v>45370</v>
+      </c>
+      <c r="E14" s="74" t="n">
+        <v>23</v>
+      </c>
+      <c r="F14" s="74" t="n">
+        <v>23</v>
+      </c>
+      <c r="G14" s="74" t="n">
+        <v>23</v>
+      </c>
+      <c r="H14" s="75" t="inlineStr">
+        <is>
+          <t>브리스톨마이어스스퀴브(BMY), Hershey Foods(HSY), Cincinnati Financial(CINF), Skyworks Solutions(SWKS), Cf Industries Holdings Inc(CF), Dicks Sporting Inc(DKS), Tapestry Inc(TPR), East West Bancorp(EWBC), Apa(APA), Hf Sinclair(DINO), Ch Robinson Worldwide Inc(CHRW), Vail Resorts(MTN), Nexstar Media Group Inc(NXST), Columbia Banking System Inc(COLB), Insperity(NSP), Lakeland Financial Corp(LKFN), Virtus Investment Partners(VRTS), Oxford Industries Inc(OXM), Heartland Financial Usa Inc(HTLF), Amerisafe Inc(AMSF), German American Bancorp Inc(GABC), Preferred Bank(PFBC), First Bancshares Inc(FBMS)</t>
+        </is>
+      </c>
+      <c r="I14" s="75" t="inlineStr">
+        <is>
+          <t>Broadcom Inc(AVGO), 머크(MRK), ADP(ADP), 블랙스톤(BX), Illinois Tool Inc(ITW), 3M(MMM), Allstate Corp(ALL), Newmont(NEM), Williams Sonoma Inc(WSM), Northern Trust Corp(NTRS), Tyson Foods Inc Class A(TSN), Nrg Energy Inc(NRG), Kellanova(K), International Paper(IP), First American Financial Corp(FAF), Paramount Global Class B(PARA), Advance Auto Parts Inc(AAP), Lazard Inc(LAZ), Federal Agricultural Mortgage Non(AGM), Stewart Info Services Corp(STC), Sturm Ruger Inc(RGR), Ennis Inc(EBF), Hanmi Financial Corp(HAFC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="71" t="n">
+        <v>45467</v>
+      </c>
+      <c r="B15" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C15" s="71" t="n">
+        <v>45464</v>
+      </c>
+      <c r="D15" s="71" t="n">
+        <v>45467</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="H15" s="72" t="inlineStr"/>
+      <c r="I15" s="72" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="71" t="n">
+        <v>45558</v>
+      </c>
+      <c r="B16" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C16" s="71" t="n">
+        <v>45555</v>
+      </c>
+      <c r="D16" s="71" t="n">
+        <v>45558</v>
+      </c>
+      <c r="E16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="H16" s="72" t="inlineStr"/>
+      <c r="I16" s="72" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="71" t="n">
+        <v>45649</v>
+      </c>
+      <c r="B17" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C17" s="71" t="n">
+        <v>45646</v>
+      </c>
+      <c r="D17" s="71" t="n">
+        <v>45649</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="H17" s="72" t="inlineStr"/>
+      <c r="I17" s="72" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="73" t="n">
+        <v>45740</v>
+      </c>
+      <c r="B18" s="74" t="inlineStr">
+        <is>
+          <t>정기 종목 교체</t>
+        </is>
+      </c>
+      <c r="C18" s="73" t="n">
+        <v>45737</v>
+      </c>
+      <c r="D18" s="73" t="n">
+        <v>45741</v>
+      </c>
+      <c r="E18" s="74" t="n">
+        <v>20</v>
+      </c>
+      <c r="F18" s="74" t="n">
+        <v>17</v>
+      </c>
+      <c r="G18" s="74" t="n">
+        <v>29</v>
+      </c>
+      <c r="H18" s="75" t="inlineStr">
+        <is>
+          <t>코노코필립스(COP), 머크(MRK), SLB(SLB), 타깃(TGT), General Mills Inc(GIS), Halliburton(HAL), Archer Daniels Midland(ADM), Ovintiv Inc(OVV), American Financial Group(AFG), Autoliv(ALV), Fmc Corp(FMC), Moelis Class A(MC), Murphy Oil Corp(MUR), Flowers Foods Inc(FLO), Federated Hermes Inc Class B(FHI), Signet Jewelers Ltd(SIG), Interparfums Inc(IPAR), Cna Financial Corp(CNA), First Financial Corporation Corp(THFF), Ennis Inc(EBF)</t>
+        </is>
+      </c>
+      <c r="I18" s="75" t="inlineStr">
+        <is>
+          <t>Pfizer Inc(PFE), Blackrock Inc(BLK), Us Bancorp(USB), M&amp;T Bank Corp(MTB), Huntington Bancshares Inc(HBAN), Tapestry Inc(TPR), Keycorp(KEY), Ch Robinson Worldwide Inc(CHRW), Dicks Sporting Inc(DKS), Zions Bancorporation(ZION), H&amp;R Block Inc(HRB), Synovus Financial Corp(SNV), Bank Of Hawaii Corp(BOH), Leggett &amp; Platt Inc(LEG), Cracker Barrel Old Country Store I(CBRL), Heritage Financial Corp(HFWA), Guess Inc(GES)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="71" t="n">
+        <v>45831</v>
+      </c>
+      <c r="B19" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C19" s="71" t="n">
+        <v>45828</v>
+      </c>
+      <c r="D19" s="71" t="n">
+        <v>45831</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="H19" s="72" t="inlineStr"/>
+      <c r="I19" s="72" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="71" t="n">
+        <v>45922</v>
+      </c>
+      <c r="B20" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C20" s="71" t="n">
+        <v>45919</v>
+      </c>
+      <c r="D20" s="71" t="n">
+        <v>45922</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="H20" s="72" t="inlineStr"/>
+      <c r="I20" s="72" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="71" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B21" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C21" s="71" t="n">
+        <v>46010</v>
+      </c>
+      <c r="D21" s="71" t="n">
+        <v>46013</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="H21" s="72" t="inlineStr"/>
+      <c r="I21" s="72" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="73" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B22" s="74" t="inlineStr">
+        <is>
+          <t>정기 종목 교체</t>
+        </is>
+      </c>
+      <c r="C22" s="73" t="n">
+        <v>46101</v>
+      </c>
+      <c r="D22" s="73" t="n">
+        <v>46105</v>
+      </c>
+      <c r="E22" s="74" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="74" t="n">
+        <v>22</v>
+      </c>
+      <c r="G22" s="74" t="n">
+        <v>23</v>
+      </c>
+      <c r="H22" s="75" t="inlineStr">
+        <is>
+          <t>애보트(ABT), 유나이티드헬스(UNH), 프록터앤드갬블(PG), 퀄컴(QCOM), 액센츄어(ACN), 컴캐스트(CMCSA), ADP(ADP), 블랙스톤(BX), Devon Energy(DVN), Ares Management Class A(ARES), Broadridge Financial Solutions Inc(BR), Principal Financial Group Inc(PFG), Booz Allen Hamilton Holding Class(BAH), Old Republic International(ORI), Erie Indemnity Class A(ERIE), Macys Inc(M), Korn Ferry(KFY), Marzetti(MZTI), Penske Automotive Group Voting Inc(PAG), National Bank Holdings Corp Class(NBHC), Federal Agricultural Mortgage Non(AGM), Hanmi Financial Corp(HAFC), Orrstown Financial Services Inc(ORRF), Independent Bank Corp(IBCP), Capital City Bank Inc(CCBG)</t>
+        </is>
+      </c>
+      <c r="I22" s="75" t="inlineStr">
+        <is>
+          <t>Cisco Systems Inc(CSCO), Abbvie Inc(ABBV), Valero Energy Corp(VLO), Halliburton(HAL), Cf Industries Holdings Inc(CF), Lyondellbasell Industries Nv Class(LYB), Packaging Corp Of America(PKG), Amcor Plc(AMCR), Ovintiv Inc(OVV), Unum(UNM), Janus Henderson Group Plc(JHG), Radian Group Inc(RDN), Signet Jewelers Ltd(SIG), International Bancshares Corp(IBOC), Cathay General Bancorp(CATY), Whirlpool Corp(WHR), Huntsman Corp(HUN), Northwest Bancshares Inc(NWBI), First Commonwealth Financial Corp(FCF), Fmc Corp(FMC), Carters Inc(CRI), Kforce Inc(KFRC)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="71" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C23" s="71" t="n">
+        <v>46191</v>
+      </c>
+      <c r="D23" s="71" t="n">
+        <v>46195</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>48</v>
+      </c>
+      <c r="H23" s="72" t="inlineStr"/>
+      <c r="I23" s="72" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="71" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>분기 비중 재조정</t>
+        </is>
+      </c>
+      <c r="C24" s="71" t="n">
+        <v>46283</v>
+      </c>
+      <c r="D24" s="71" t="n">
+        <v>46286</v>
+      </c>
+      <c r="E24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="H24" s="72" t="inlineStr"/>
+      <c r="I24" s="72" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5153,10 +5831,10 @@
       <c r="B2" s="56" t="n">
         <v>40847</v>
       </c>
-      <c r="C2" s="71" t="n">
+      <c r="C2" s="76" t="n">
         <v>8.5</v>
       </c>
-      <c r="D2" s="72" t="n">
+      <c r="D2" s="77" t="n">
         <v>5.287</v>
       </c>
       <c r="E2" s="55" t="n"/>
@@ -5171,10 +5849,10 @@
       <c r="B3" s="56" t="n">
         <v>40877</v>
       </c>
-      <c r="C3" s="71" t="n">
+      <c r="C3" s="76" t="n">
         <v>8.640000000000001</v>
       </c>
-      <c r="D3" s="72" t="n">
+      <c r="D3" s="77" t="n">
         <v>5.3741</v>
       </c>
       <c r="E3" s="55" t="n"/>
@@ -5189,10 +5867,10 @@
       <c r="B4" s="56" t="n">
         <v>40907</v>
       </c>
-      <c r="C4" s="71" t="n">
+      <c r="C4" s="76" t="n">
         <v>8.726699999999999</v>
       </c>
-      <c r="D4" s="72" t="n">
+      <c r="D4" s="77" t="n">
         <v>5.4541</v>
       </c>
       <c r="E4" s="55" t="n"/>
@@ -5207,10 +5885,10 @@
       <c r="B5" s="56" t="n">
         <v>40939</v>
       </c>
-      <c r="C5" s="71" t="n">
+      <c r="C5" s="76" t="n">
         <v>8.869999999999999</v>
       </c>
-      <c r="D5" s="72" t="n">
+      <c r="D5" s="77" t="n">
         <v>5.5437</v>
       </c>
       <c r="E5" s="55" t="n"/>
@@ -5225,10 +5903,10 @@
       <c r="B6" s="56" t="n">
         <v>40968</v>
       </c>
-      <c r="C6" s="71" t="n">
+      <c r="C6" s="76" t="n">
         <v>9.1233</v>
       </c>
-      <c r="D6" s="72" t="n">
+      <c r="D6" s="77" t="n">
         <v>5.702</v>
       </c>
       <c r="E6" s="55" t="n"/>
@@ -5243,10 +5921,10 @@
       <c r="B7" s="56" t="n">
         <v>40998</v>
       </c>
-      <c r="C7" s="71" t="n">
+      <c r="C7" s="76" t="n">
         <v>9.2967</v>
       </c>
-      <c r="D7" s="72" t="n">
+      <c r="D7" s="77" t="n">
         <v>5.8393</v>
       </c>
       <c r="E7" s="55" t="n"/>
@@ -5261,10 +5939,10 @@
       <c r="B8" s="56" t="n">
         <v>41029</v>
       </c>
-      <c r="C8" s="71" t="n">
+      <c r="C8" s="76" t="n">
         <v>9.2867</v>
       </c>
-      <c r="D8" s="72" t="n">
+      <c r="D8" s="77" t="n">
         <v>5.833</v>
       </c>
       <c r="E8" s="55" t="n"/>
@@ -5279,10 +5957,10 @@
       <c r="B9" s="56" t="n">
         <v>41060</v>
       </c>
-      <c r="C9" s="71" t="n">
+      <c r="C9" s="76" t="n">
         <v>8.933299999999999</v>
       </c>
-      <c r="D9" s="72" t="n">
+      <c r="D9" s="77" t="n">
         <v>5.6111</v>
       </c>
       <c r="E9" s="55" t="n"/>
@@ -5297,10 +5975,10 @@
       <c r="B10" s="56" t="n">
         <v>41089</v>
       </c>
-      <c r="C10" s="71" t="n">
+      <c r="C10" s="76" t="n">
         <v>9.253299999999999</v>
       </c>
-      <c r="D10" s="72" t="n">
+      <c r="D10" s="77" t="n">
         <v>5.8558</v>
       </c>
       <c r="E10" s="55" t="n"/>
@@ -5315,10 +5993,10 @@
       <c r="B11" s="56" t="n">
         <v>41121</v>
       </c>
-      <c r="C11" s="71" t="n">
+      <c r="C11" s="76" t="n">
         <v>9.48</v>
       </c>
-      <c r="D11" s="72" t="n">
+      <c r="D11" s="77" t="n">
         <v>5.9992</v>
       </c>
       <c r="E11" s="55" t="n"/>
@@ -5333,10 +6011,10 @@
       <c r="B12" s="56" t="n">
         <v>41152</v>
       </c>
-      <c r="C12" s="71" t="n">
+      <c r="C12" s="76" t="n">
         <v>9.5367</v>
       </c>
-      <c r="D12" s="72" t="n">
+      <c r="D12" s="77" t="n">
         <v>6.0351</v>
       </c>
       <c r="E12" s="55" t="n"/>
@@ -5351,10 +6029,10 @@
       <c r="B13" s="56" t="n">
         <v>41180</v>
       </c>
-      <c r="C13" s="71" t="n">
+      <c r="C13" s="76" t="n">
         <v>9.583299999999999</v>
       </c>
-      <c r="D13" s="72" t="n">
+      <c r="D13" s="77" t="n">
         <v>6.1081</v>
       </c>
       <c r="E13" s="55" t="n"/>
@@ -5369,10 +6047,10 @@
       <c r="B14" s="56" t="n">
         <v>41213</v>
       </c>
-      <c r="C14" s="71" t="n">
+      <c r="C14" s="76" t="n">
         <v>9.4933</v>
       </c>
-      <c r="D14" s="72" t="n">
+      <c r="D14" s="77" t="n">
         <v>6.0508</v>
       </c>
       <c r="E14" s="58">
@@ -5393,10 +6071,10 @@
       <c r="B15" s="56" t="n">
         <v>41243</v>
       </c>
-      <c r="C15" s="71" t="n">
+      <c r="C15" s="76" t="n">
         <v>9.5367</v>
       </c>
-      <c r="D15" s="72" t="n">
+      <c r="D15" s="77" t="n">
         <v>6.0784</v>
       </c>
       <c r="E15" s="58">
@@ -5417,10 +6095,10 @@
       <c r="B16" s="56" t="n">
         <v>41274</v>
       </c>
-      <c r="C16" s="71" t="n">
+      <c r="C16" s="76" t="n">
         <v>9.4467</v>
       </c>
-      <c r="D16" s="72" t="n">
+      <c r="D16" s="77" t="n">
         <v>6.0754</v>
       </c>
       <c r="E16" s="58">
@@ -5441,10 +6119,10 @@
       <c r="B17" s="56" t="n">
         <v>41305</v>
       </c>
-      <c r="C17" s="71" t="n">
+      <c r="C17" s="76" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="D17" s="72" t="n">
+      <c r="D17" s="77" t="n">
         <v>6.412</v>
       </c>
       <c r="E17" s="58">
@@ -5465,10 +6143,10 @@
       <c r="B18" s="56" t="n">
         <v>41333</v>
       </c>
-      <c r="C18" s="71" t="n">
+      <c r="C18" s="76" t="n">
         <v>10.18</v>
       </c>
-      <c r="D18" s="72" t="n">
+      <c r="D18" s="77" t="n">
         <v>6.547</v>
       </c>
       <c r="E18" s="58">
@@ -5489,10 +6167,10 @@
       <c r="B19" s="56" t="n">
         <v>41361</v>
       </c>
-      <c r="C19" s="71" t="n">
+      <c r="C19" s="76" t="n">
         <v>10.5967</v>
       </c>
-      <c r="D19" s="72" t="n">
+      <c r="D19" s="77" t="n">
         <v>6.8585</v>
       </c>
       <c r="E19" s="58">
@@ -5513,10 +6191,10 @@
       <c r="B20" s="56" t="n">
         <v>41394</v>
       </c>
-      <c r="C20" s="71" t="n">
+      <c r="C20" s="76" t="n">
         <v>10.9133</v>
       </c>
-      <c r="D20" s="72" t="n">
+      <c r="D20" s="77" t="n">
         <v>7.0635</v>
       </c>
       <c r="E20" s="58">
@@ -5537,10 +6215,10 @@
       <c r="B21" s="56" t="n">
         <v>41425</v>
       </c>
-      <c r="C21" s="71" t="n">
+      <c r="C21" s="76" t="n">
         <v>11.0667</v>
       </c>
-      <c r="D21" s="72" t="n">
+      <c r="D21" s="77" t="n">
         <v>7.1627</v>
       </c>
       <c r="E21" s="58">
@@ -5561,10 +6239,10 @@
       <c r="B22" s="56" t="n">
         <v>41453</v>
       </c>
-      <c r="C22" s="71" t="n">
+      <c r="C22" s="76" t="n">
         <v>10.9</v>
       </c>
-      <c r="D22" s="72" t="n">
+      <c r="D22" s="77" t="n">
         <v>7.1037</v>
       </c>
       <c r="E22" s="58">
@@ -5585,10 +6263,10 @@
       <c r="B23" s="56" t="n">
         <v>41486</v>
       </c>
-      <c r="C23" s="71" t="n">
+      <c r="C23" s="76" t="n">
         <v>11.4</v>
       </c>
-      <c r="D23" s="72" t="n">
+      <c r="D23" s="77" t="n">
         <v>7.4296</v>
       </c>
       <c r="E23" s="58">
@@ -5609,10 +6287,10 @@
       <c r="B24" s="56" t="n">
         <v>41516</v>
       </c>
-      <c r="C24" s="71" t="n">
+      <c r="C24" s="76" t="n">
         <v>10.9967</v>
       </c>
-      <c r="D24" s="72" t="n">
+      <c r="D24" s="77" t="n">
         <v>7.1667</v>
       </c>
       <c r="E24" s="58">
@@ -5633,10 +6311,10 @@
       <c r="B25" s="56" t="n">
         <v>41547</v>
       </c>
-      <c r="C25" s="71" t="n">
+      <c r="C25" s="76" t="n">
         <v>11.2167</v>
       </c>
-      <c r="D25" s="72" t="n">
+      <c r="D25" s="77" t="n">
         <v>7.3593</v>
       </c>
       <c r="E25" s="58">
@@ -5657,10 +6335,10 @@
       <c r="B26" s="56" t="n">
         <v>41578</v>
       </c>
-      <c r="C26" s="71" t="n">
+      <c r="C26" s="76" t="n">
         <v>11.7767</v>
       </c>
-      <c r="D26" s="72" t="n">
+      <c r="D26" s="77" t="n">
         <v>7.7267</v>
       </c>
       <c r="E26" s="58">
@@ -5681,10 +6359,10 @@
       <c r="B27" s="56" t="n">
         <v>41607</v>
       </c>
-      <c r="C27" s="71" t="n">
+      <c r="C27" s="76" t="n">
         <v>12.0767</v>
       </c>
-      <c r="D27" s="72" t="n">
+      <c r="D27" s="77" t="n">
         <v>7.9236</v>
       </c>
       <c r="E27" s="58">
@@ -5705,10 +6383,10 @@
       <c r="B28" s="56" t="n">
         <v>41639</v>
       </c>
-      <c r="C28" s="71" t="n">
+      <c r="C28" s="76" t="n">
         <v>12.22</v>
       </c>
-      <c r="D28" s="72" t="n">
+      <c r="D28" s="77" t="n">
         <v>8.072900000000001</v>
       </c>
       <c r="E28" s="58">
@@ -5729,10 +6407,10 @@
       <c r="B29" s="56" t="n">
         <v>41670</v>
       </c>
-      <c r="C29" s="71" t="n">
+      <c r="C29" s="76" t="n">
         <v>11.6767</v>
       </c>
-      <c r="D29" s="72" t="n">
+      <c r="D29" s="77" t="n">
         <v>7.7139</v>
       </c>
       <c r="E29" s="58">
@@ -5753,10 +6431,10 @@
       <c r="B30" s="56" t="n">
         <v>41698</v>
       </c>
-      <c r="C30" s="71" t="n">
+      <c r="C30" s="76" t="n">
         <v>12.13</v>
       </c>
-      <c r="D30" s="72" t="n">
+      <c r="D30" s="77" t="n">
         <v>8.013400000000001</v>
       </c>
       <c r="E30" s="58">
@@ -5777,10 +6455,10 @@
       <c r="B31" s="56" t="n">
         <v>41729</v>
       </c>
-      <c r="C31" s="71" t="n">
+      <c r="C31" s="76" t="n">
         <v>12.2833</v>
       </c>
-      <c r="D31" s="72" t="n">
+      <c r="D31" s="77" t="n">
         <v>8.170199999999999</v>
       </c>
       <c r="E31" s="58">
@@ -5801,10 +6479,10 @@
       <c r="B32" s="56" t="n">
         <v>41759</v>
       </c>
-      <c r="C32" s="71" t="n">
+      <c r="C32" s="76" t="n">
         <v>12.5067</v>
       </c>
-      <c r="D32" s="72" t="n">
+      <c r="D32" s="77" t="n">
         <v>8.3187</v>
       </c>
       <c r="E32" s="58">
@@ -5825,10 +6503,10 @@
       <c r="B33" s="56" t="n">
         <v>41789</v>
       </c>
-      <c r="C33" s="71" t="n">
+      <c r="C33" s="76" t="n">
         <v>12.6733</v>
       </c>
-      <c r="D33" s="72" t="n">
+      <c r="D33" s="77" t="n">
         <v>8.429600000000001</v>
       </c>
       <c r="E33" s="58">
@@ -5849,10 +6527,10 @@
       <c r="B34" s="56" t="n">
         <v>41820</v>
       </c>
-      <c r="C34" s="71" t="n">
+      <c r="C34" s="76" t="n">
         <v>12.7567</v>
       </c>
-      <c r="D34" s="72" t="n">
+      <c r="D34" s="77" t="n">
         <v>8.5442</v>
       </c>
       <c r="E34" s="58">
@@ -5873,10 +6551,10 @@
       <c r="B35" s="56" t="n">
         <v>41851</v>
       </c>
-      <c r="C35" s="71" t="n">
+      <c r="C35" s="76" t="n">
         <v>12.5367</v>
       </c>
-      <c r="D35" s="72" t="n">
+      <c r="D35" s="77" t="n">
         <v>8.396800000000001</v>
       </c>
       <c r="E35" s="58">
@@ -5897,10 +6575,10 @@
       <c r="B36" s="56" t="n">
         <v>41880</v>
       </c>
-      <c r="C36" s="71" t="n">
+      <c r="C36" s="76" t="n">
         <v>12.9667</v>
       </c>
-      <c r="D36" s="72" t="n">
+      <c r="D36" s="77" t="n">
         <v>8.684799999999999</v>
       </c>
       <c r="E36" s="58">
@@ -5921,10 +6599,10 @@
       <c r="B37" s="56" t="n">
         <v>41912</v>
       </c>
-      <c r="C37" s="71" t="n">
+      <c r="C37" s="76" t="n">
         <v>12.8533</v>
       </c>
-      <c r="D37" s="72" t="n">
+      <c r="D37" s="77" t="n">
         <v>8.6648</v>
       </c>
       <c r="E37" s="58">
@@ -5945,10 +6623,10 @@
       <c r="B38" s="56" t="n">
         <v>41943</v>
       </c>
-      <c r="C38" s="71" t="n">
+      <c r="C38" s="76" t="n">
         <v>13.1067</v>
       </c>
-      <c r="D38" s="72" t="n">
+      <c r="D38" s="77" t="n">
         <v>8.8355</v>
       </c>
       <c r="E38" s="58">
@@ -5969,10 +6647,10 @@
       <c r="B39" s="56" t="n">
         <v>41971</v>
       </c>
-      <c r="C39" s="71" t="n">
+      <c r="C39" s="76" t="n">
         <v>13.4967</v>
       </c>
-      <c r="D39" s="72" t="n">
+      <c r="D39" s="77" t="n">
         <v>9.0985</v>
       </c>
       <c r="E39" s="58">
@@ -5993,10 +6671,10 @@
       <c r="B40" s="56" t="n">
         <v>42004</v>
       </c>
-      <c r="C40" s="71" t="n">
+      <c r="C40" s="76" t="n">
         <v>13.2833</v>
       </c>
-      <c r="D40" s="72" t="n">
+      <c r="D40" s="77" t="n">
         <v>9.0161</v>
       </c>
       <c r="E40" s="58">
@@ -6017,10 +6695,10 @@
       <c r="B41" s="56" t="n">
         <v>42034</v>
       </c>
-      <c r="C41" s="71" t="n">
+      <c r="C41" s="76" t="n">
         <v>12.87</v>
       </c>
-      <c r="D41" s="72" t="n">
+      <c r="D41" s="77" t="n">
         <v>8.7355</v>
       </c>
       <c r="E41" s="58">
@@ -6041,10 +6719,10 @@
       <c r="B42" s="56" t="n">
         <v>42062</v>
       </c>
-      <c r="C42" s="71" t="n">
+      <c r="C42" s="76" t="n">
         <v>13.5433</v>
       </c>
-      <c r="D42" s="72" t="n">
+      <c r="D42" s="77" t="n">
         <v>9.192600000000001</v>
       </c>
       <c r="E42" s="58">
@@ -6065,10 +6743,10 @@
       <c r="B43" s="56" t="n">
         <v>42094</v>
       </c>
-      <c r="C43" s="71" t="n">
+      <c r="C43" s="76" t="n">
         <v>13.1367</v>
       </c>
-      <c r="D43" s="72" t="n">
+      <c r="D43" s="77" t="n">
         <v>8.976900000000001</v>
       </c>
       <c r="E43" s="58">
@@ -6089,10 +6767,10 @@
       <c r="B44" s="56" t="n">
         <v>42124</v>
       </c>
-      <c r="C44" s="71" t="n">
+      <c r="C44" s="76" t="n">
         <v>13.2367</v>
       </c>
-      <c r="D44" s="72" t="n">
+      <c r="D44" s="77" t="n">
         <v>9.045199999999999</v>
       </c>
       <c r="E44" s="58">
@@ -6113,10 +6791,10 @@
       <c r="B45" s="56" t="n">
         <v>42153</v>
       </c>
-      <c r="C45" s="71" t="n">
+      <c r="C45" s="76" t="n">
         <v>13.3033</v>
       </c>
-      <c r="D45" s="72" t="n">
+      <c r="D45" s="77" t="n">
         <v>9.0908</v>
       </c>
       <c r="E45" s="58">
@@ -6137,10 +6815,10 @@
       <c r="B46" s="56" t="n">
         <v>42185</v>
       </c>
-      <c r="C46" s="71" t="n">
+      <c r="C46" s="76" t="n">
         <v>12.7633</v>
       </c>
-      <c r="D46" s="72" t="n">
+      <c r="D46" s="77" t="n">
         <v>8.7897</v>
       </c>
       <c r="E46" s="58">
@@ -6161,10 +6839,10 @@
       <c r="B47" s="56" t="n">
         <v>42216</v>
       </c>
-      <c r="C47" s="71" t="n">
+      <c r="C47" s="76" t="n">
         <v>12.8533</v>
       </c>
-      <c r="D47" s="72" t="n">
+      <c r="D47" s="77" t="n">
         <v>8.851699999999999</v>
       </c>
       <c r="E47" s="58">
@@ -6185,10 +6863,10 @@
       <c r="B48" s="56" t="n">
         <v>42247</v>
       </c>
-      <c r="C48" s="71" t="n">
+      <c r="C48" s="76" t="n">
         <v>12.17</v>
       </c>
-      <c r="D48" s="72" t="n">
+      <c r="D48" s="77" t="n">
         <v>8.3811</v>
       </c>
       <c r="E48" s="58">
@@ -6209,10 +6887,10 @@
       <c r="B49" s="56" t="n">
         <v>42277</v>
       </c>
-      <c r="C49" s="71" t="n">
+      <c r="C49" s="76" t="n">
         <v>11.9833</v>
       </c>
-      <c r="D49" s="72" t="n">
+      <c r="D49" s="77" t="n">
         <v>8.321099999999999</v>
       </c>
       <c r="E49" s="58">
@@ -6233,10 +6911,10 @@
       <c r="B50" s="56" t="n">
         <v>42307</v>
       </c>
-      <c r="C50" s="71" t="n">
+      <c r="C50" s="76" t="n">
         <v>13.0333</v>
       </c>
-      <c r="D50" s="72" t="n">
+      <c r="D50" s="77" t="n">
         <v>9.0502</v>
       </c>
       <c r="E50" s="58">
@@ -6257,10 +6935,10 @@
       <c r="B51" s="56" t="n">
         <v>42338</v>
       </c>
-      <c r="C51" s="71" t="n">
+      <c r="C51" s="76" t="n">
         <v>13.07</v>
       </c>
-      <c r="D51" s="72" t="n">
+      <c r="D51" s="77" t="n">
         <v>9.075699999999999</v>
       </c>
       <c r="E51" s="58">
@@ -6281,10 +6959,10 @@
       <c r="B52" s="56" t="n">
         <v>42369</v>
       </c>
-      <c r="C52" s="71" t="n">
+      <c r="C52" s="76" t="n">
         <v>12.8533</v>
       </c>
-      <c r="D52" s="72" t="n">
+      <c r="D52" s="77" t="n">
         <v>8.9894</v>
       </c>
       <c r="E52" s="58">
@@ -6305,10 +6983,10 @@
       <c r="B53" s="56" t="n">
         <v>42398</v>
       </c>
-      <c r="C53" s="71" t="n">
+      <c r="C53" s="76" t="n">
         <v>12.56</v>
       </c>
-      <c r="D53" s="72" t="n">
+      <c r="D53" s="77" t="n">
         <v>8.7842</v>
       </c>
       <c r="E53" s="58">
@@ -6329,10 +7007,10 @@
       <c r="B54" s="56" t="n">
         <v>42429</v>
       </c>
-      <c r="C54" s="71" t="n">
+      <c r="C54" s="76" t="n">
         <v>12.6533</v>
       </c>
-      <c r="D54" s="72" t="n">
+      <c r="D54" s="77" t="n">
         <v>8.849500000000001</v>
       </c>
       <c r="E54" s="58">
@@ -6353,10 +7031,10 @@
       <c r="B55" s="56" t="n">
         <v>42460</v>
       </c>
-      <c r="C55" s="71" t="n">
+      <c r="C55" s="76" t="n">
         <v>13.3633</v>
       </c>
-      <c r="D55" s="72" t="n">
+      <c r="D55" s="77" t="n">
         <v>9.415800000000001</v>
       </c>
       <c r="E55" s="58">
@@ -6377,10 +7055,10 @@
       <c r="B56" s="56" t="n">
         <v>42489</v>
       </c>
-      <c r="C56" s="71" t="n">
+      <c r="C56" s="76" t="n">
         <v>13.34</v>
       </c>
-      <c r="D56" s="72" t="n">
+      <c r="D56" s="77" t="n">
         <v>9.3993</v>
       </c>
       <c r="E56" s="58">
@@ -6401,10 +7079,10 @@
       <c r="B57" s="56" t="n">
         <v>42521</v>
       </c>
-      <c r="C57" s="71" t="n">
+      <c r="C57" s="76" t="n">
         <v>13.5267</v>
       </c>
-      <c r="D57" s="72" t="n">
+      <c r="D57" s="77" t="n">
         <v>9.530900000000001</v>
       </c>
       <c r="E57" s="58">
@@ -6425,10 +7103,10 @@
       <c r="B58" s="56" t="n">
         <v>42551</v>
       </c>
-      <c r="C58" s="71" t="n">
+      <c r="C58" s="76" t="n">
         <v>13.8133</v>
       </c>
-      <c r="D58" s="72" t="n">
+      <c r="D58" s="77" t="n">
         <v>9.8089</v>
       </c>
       <c r="E58" s="58">
@@ -6449,10 +7127,10 @@
       <c r="B59" s="56" t="n">
         <v>42580</v>
       </c>
-      <c r="C59" s="71" t="n">
+      <c r="C59" s="76" t="n">
         <v>14.2067</v>
       </c>
-      <c r="D59" s="72" t="n">
+      <c r="D59" s="77" t="n">
         <v>10.0882</v>
       </c>
       <c r="E59" s="58">
@@ -6473,10 +7151,10 @@
       <c r="B60" s="56" t="n">
         <v>42613</v>
       </c>
-      <c r="C60" s="71" t="n">
+      <c r="C60" s="76" t="n">
         <v>14.16</v>
       </c>
-      <c r="D60" s="72" t="n">
+      <c r="D60" s="77" t="n">
         <v>10.0551</v>
       </c>
       <c r="E60" s="58">
@@ -6497,10 +7175,10 @@
       <c r="B61" s="56" t="n">
         <v>42643</v>
       </c>
-      <c r="C61" s="71" t="n">
+      <c r="C61" s="76" t="n">
         <v>14.1033</v>
       </c>
-      <c r="D61" s="72" t="n">
+      <c r="D61" s="77" t="n">
         <v>10.0736</v>
       </c>
       <c r="E61" s="58">
@@ -6521,10 +7199,10 @@
       <c r="B62" s="56" t="n">
         <v>42674</v>
       </c>
-      <c r="C62" s="71" t="n">
+      <c r="C62" s="76" t="n">
         <v>13.8833</v>
       </c>
-      <c r="D62" s="72" t="n">
+      <c r="D62" s="77" t="n">
         <v>9.916399999999999</v>
       </c>
       <c r="E62" s="58">
@@ -6545,10 +7223,10 @@
       <c r="B63" s="56" t="n">
         <v>42704</v>
       </c>
-      <c r="C63" s="71" t="n">
+      <c r="C63" s="76" t="n">
         <v>14.3367</v>
       </c>
-      <c r="D63" s="72" t="n">
+      <c r="D63" s="77" t="n">
         <v>10.2402</v>
       </c>
       <c r="E63" s="58">
@@ -6569,10 +7247,10 @@
       <c r="B64" s="56" t="n">
         <v>42734</v>
       </c>
-      <c r="C64" s="71" t="n">
+      <c r="C64" s="76" t="n">
         <v>14.5233</v>
       </c>
-      <c r="D64" s="72" t="n">
+      <c r="D64" s="77" t="n">
         <v>10.468</v>
       </c>
       <c r="E64" s="58">
@@ -6593,10 +7271,10 @@
       <c r="B65" s="56" t="n">
         <v>42766</v>
       </c>
-      <c r="C65" s="71" t="n">
+      <c r="C65" s="76" t="n">
         <v>14.4533</v>
       </c>
-      <c r="D65" s="72" t="n">
+      <c r="D65" s="77" t="n">
         <v>10.4175</v>
       </c>
       <c r="E65" s="58">
@@ -6617,10 +7295,10 @@
       <c r="B66" s="56" t="n">
         <v>42794</v>
       </c>
-      <c r="C66" s="71" t="n">
+      <c r="C66" s="76" t="n">
         <v>14.9467</v>
       </c>
-      <c r="D66" s="72" t="n">
+      <c r="D66" s="77" t="n">
         <v>10.7731</v>
       </c>
       <c r="E66" s="58">
@@ -6641,10 +7319,10 @@
       <c r="B67" s="56" t="n">
         <v>42825</v>
       </c>
-      <c r="C67" s="71" t="n">
+      <c r="C67" s="76" t="n">
         <v>14.86</v>
       </c>
-      <c r="D67" s="72" t="n">
+      <c r="D67" s="77" t="n">
         <v>10.7884</v>
       </c>
       <c r="E67" s="58">
@@ -6665,10 +7343,10 @@
       <c r="B68" s="56" t="n">
         <v>42853</v>
       </c>
-      <c r="C68" s="71" t="n">
+      <c r="C68" s="76" t="n">
         <v>14.8967</v>
       </c>
-      <c r="D68" s="72" t="n">
+      <c r="D68" s="77" t="n">
         <v>10.815</v>
       </c>
       <c r="E68" s="58">
@@ -6689,10 +7367,10 @@
       <c r="B69" s="56" t="n">
         <v>42886</v>
       </c>
-      <c r="C69" s="71" t="n">
+      <c r="C69" s="76" t="n">
         <v>15.1567</v>
       </c>
-      <c r="D69" s="72" t="n">
+      <c r="D69" s="77" t="n">
         <v>11.0038</v>
       </c>
       <c r="E69" s="58">
@@ -6713,10 +7391,10 @@
       <c r="B70" s="56" t="n">
         <v>42916</v>
       </c>
-      <c r="C70" s="71" t="n">
+      <c r="C70" s="76" t="n">
         <v>15.0333</v>
       </c>
-      <c r="D70" s="72" t="n">
+      <c r="D70" s="77" t="n">
         <v>10.9933</v>
       </c>
       <c r="E70" s="58">
@@ -6737,10 +7415,10 @@
       <c r="B71" s="56" t="n">
         <v>42947</v>
       </c>
-      <c r="C71" s="71" t="n">
+      <c r="C71" s="76" t="n">
         <v>15.2833</v>
       </c>
-      <c r="D71" s="72" t="n">
+      <c r="D71" s="77" t="n">
         <v>11.1761</v>
       </c>
       <c r="E71" s="58">
@@ -6761,10 +7439,10 @@
       <c r="B72" s="56" t="n">
         <v>42978</v>
       </c>
-      <c r="C72" s="71" t="n">
+      <c r="C72" s="76" t="n">
         <v>15.28</v>
       </c>
-      <c r="D72" s="72" t="n">
+      <c r="D72" s="77" t="n">
         <v>11.1736</v>
       </c>
       <c r="E72" s="58">
@@ -6785,10 +7463,10 @@
       <c r="B73" s="56" t="n">
         <v>43007</v>
       </c>
-      <c r="C73" s="71" t="n">
+      <c r="C73" s="76" t="n">
         <v>15.6</v>
       </c>
-      <c r="D73" s="72" t="n">
+      <c r="D73" s="77" t="n">
         <v>11.4919</v>
       </c>
       <c r="E73" s="58">
@@ -6809,10 +7487,10 @@
       <c r="B74" s="56" t="n">
         <v>43039</v>
       </c>
-      <c r="C74" s="71" t="n">
+      <c r="C74" s="76" t="n">
         <v>16.1633</v>
       </c>
-      <c r="D74" s="72" t="n">
+      <c r="D74" s="77" t="n">
         <v>11.9069</v>
       </c>
       <c r="E74" s="58">
@@ -6833,10 +7511,10 @@
       <c r="B75" s="56" t="n">
         <v>43069</v>
       </c>
-      <c r="C75" s="71" t="n">
+      <c r="C75" s="76" t="n">
         <v>16.8433</v>
       </c>
-      <c r="D75" s="72" t="n">
+      <c r="D75" s="77" t="n">
         <v>12.4078</v>
       </c>
       <c r="E75" s="58">
@@ -6857,10 +7535,10 @@
       <c r="B76" s="56" t="n">
         <v>43098</v>
       </c>
-      <c r="C76" s="71" t="n">
+      <c r="C76" s="76" t="n">
         <v>17.0567</v>
       </c>
-      <c r="D76" s="72" t="n">
+      <c r="D76" s="77" t="n">
         <v>12.6502</v>
       </c>
       <c r="E76" s="58">
@@ -6881,10 +7559,10 @@
       <c r="B77" s="56" t="n">
         <v>43131</v>
       </c>
-      <c r="C77" s="71" t="n">
+      <c r="C77" s="76" t="n">
         <v>17.8333</v>
       </c>
-      <c r="D77" s="72" t="n">
+      <c r="D77" s="77" t="n">
         <v>13.2263</v>
       </c>
       <c r="E77" s="58">
@@ -6905,10 +7583,10 @@
       <c r="B78" s="56" t="n">
         <v>43159</v>
       </c>
-      <c r="C78" s="71" t="n">
+      <c r="C78" s="76" t="n">
         <v>16.83</v>
       </c>
-      <c r="D78" s="72" t="n">
+      <c r="D78" s="77" t="n">
         <v>12.4821</v>
       </c>
       <c r="E78" s="58">
@@ -6929,10 +7607,10 @@
       <c r="B79" s="56" t="n">
         <v>43188</v>
       </c>
-      <c r="C79" s="71" t="n">
+      <c r="C79" s="76" t="n">
         <v>16.3433</v>
       </c>
-      <c r="D79" s="72" t="n">
+      <c r="D79" s="77" t="n">
         <v>12.1845</v>
       </c>
       <c r="E79" s="58">
@@ -6953,10 +7631,10 @@
       <c r="B80" s="56" t="n">
         <v>43220</v>
       </c>
-      <c r="C80" s="71" t="n">
+      <c r="C80" s="76" t="n">
         <v>16.16</v>
       </c>
-      <c r="D80" s="72" t="n">
+      <c r="D80" s="77" t="n">
         <v>12.0478</v>
       </c>
       <c r="E80" s="58">
@@ -6977,10 +7655,10 @@
       <c r="B81" s="56" t="n">
         <v>43251</v>
       </c>
-      <c r="C81" s="71" t="n">
+      <c r="C81" s="76" t="n">
         <v>16.45</v>
       </c>
-      <c r="D81" s="72" t="n">
+      <c r="D81" s="77" t="n">
         <v>12.264</v>
       </c>
       <c r="E81" s="58">
@@ -7001,10 +7679,10 @@
       <c r="B82" s="56" t="n">
         <v>43280</v>
       </c>
-      <c r="C82" s="71" t="n">
+      <c r="C82" s="76" t="n">
         <v>16.43</v>
       </c>
-      <c r="D82" s="72" t="n">
+      <c r="D82" s="77" t="n">
         <v>12.3494</v>
       </c>
       <c r="E82" s="58">
@@ -7025,10 +7703,10 @@
       <c r="B83" s="56" t="n">
         <v>43312</v>
       </c>
-      <c r="C83" s="71" t="n">
+      <c r="C83" s="76" t="n">
         <v>17.1767</v>
       </c>
-      <c r="D83" s="72" t="n">
+      <c r="D83" s="77" t="n">
         <v>12.9106</v>
       </c>
       <c r="E83" s="58">
@@ -7049,10 +7727,10 @@
       <c r="B84" s="56" t="n">
         <v>43343</v>
       </c>
-      <c r="C84" s="71" t="n">
+      <c r="C84" s="76" t="n">
         <v>17.57</v>
       </c>
-      <c r="D84" s="72" t="n">
+      <c r="D84" s="77" t="n">
         <v>13.2063</v>
       </c>
       <c r="E84" s="58">
@@ -7073,10 +7751,10 @@
       <c r="B85" s="56" t="n">
         <v>43371</v>
       </c>
-      <c r="C85" s="71" t="n">
+      <c r="C85" s="76" t="n">
         <v>17.6667</v>
       </c>
-      <c r="D85" s="72" t="n">
+      <c r="D85" s="77" t="n">
         <v>13.3703</v>
       </c>
       <c r="E85" s="58">
@@ -7097,10 +7775,10 @@
       <c r="B86" s="56" t="n">
         <v>43404</v>
       </c>
-      <c r="C86" s="71" t="n">
+      <c r="C86" s="76" t="n">
         <v>16.6233</v>
       </c>
-      <c r="D86" s="72" t="n">
+      <c r="D86" s="77" t="n">
         <v>12.5807</v>
       </c>
       <c r="E86" s="58">
@@ -7121,10 +7799,10 @@
       <c r="B87" s="56" t="n">
         <v>43434</v>
       </c>
-      <c r="C87" s="71" t="n">
+      <c r="C87" s="76" t="n">
         <v>17.1833</v>
       </c>
-      <c r="D87" s="72" t="n">
+      <c r="D87" s="77" t="n">
         <v>13.0045</v>
       </c>
       <c r="E87" s="58">
@@ -7145,10 +7823,10 @@
       <c r="B88" s="56" t="n">
         <v>43465</v>
       </c>
-      <c r="C88" s="71" t="n">
+      <c r="C88" s="76" t="n">
         <v>15.6567</v>
       </c>
-      <c r="D88" s="72" t="n">
+      <c r="D88" s="77" t="n">
         <v>11.9471</v>
       </c>
       <c r="E88" s="58">
@@ -7169,10 +7847,10 @@
       <c r="B89" s="56" t="n">
         <v>43496</v>
       </c>
-      <c r="C89" s="71" t="n">
+      <c r="C89" s="76" t="n">
         <v>16.6033</v>
       </c>
-      <c r="D89" s="72" t="n">
+      <c r="D89" s="77" t="n">
         <v>12.6694</v>
       </c>
       <c r="E89" s="58">
@@ -7193,10 +7871,10 @@
       <c r="B90" s="56" t="n">
         <v>43524</v>
       </c>
-      <c r="C90" s="71" t="n">
+      <c r="C90" s="76" t="n">
         <v>17.2767</v>
       </c>
-      <c r="D90" s="72" t="n">
+      <c r="D90" s="77" t="n">
         <v>13.1832</v>
       </c>
       <c r="E90" s="58">
@@ -7217,10 +7895,10 @@
       <c r="B91" s="56" t="n">
         <v>43553</v>
       </c>
-      <c r="C91" s="71" t="n">
+      <c r="C91" s="76" t="n">
         <v>17.4267</v>
       </c>
-      <c r="D91" s="72" t="n">
+      <c r="D91" s="77" t="n">
         <v>13.3875</v>
       </c>
       <c r="E91" s="58">
@@ -7241,10 +7919,10 @@
       <c r="B92" s="56" t="n">
         <v>43585</v>
       </c>
-      <c r="C92" s="71" t="n">
+      <c r="C92" s="76" t="n">
         <v>17.9867</v>
       </c>
-      <c r="D92" s="72" t="n">
+      <c r="D92" s="77" t="n">
         <v>13.8177</v>
       </c>
       <c r="E92" s="58">
@@ -7265,10 +7943,10 @@
       <c r="B93" s="56" t="n">
         <v>43616</v>
       </c>
-      <c r="C93" s="71" t="n">
+      <c r="C93" s="76" t="n">
         <v>16.62</v>
       </c>
-      <c r="D93" s="72" t="n">
+      <c r="D93" s="77" t="n">
         <v>12.7678</v>
       </c>
       <c r="E93" s="58">
@@ -7289,10 +7967,10 @@
       <c r="B94" s="56" t="n">
         <v>43644</v>
       </c>
-      <c r="C94" s="71" t="n">
+      <c r="C94" s="76" t="n">
         <v>17.69</v>
       </c>
-      <c r="D94" s="72" t="n">
+      <c r="D94" s="77" t="n">
         <v>13.6983</v>
       </c>
       <c r="E94" s="58">
@@ -7313,10 +7991,10 @@
       <c r="B95" s="56" t="n">
         <v>43677</v>
       </c>
-      <c r="C95" s="71" t="n">
+      <c r="C95" s="76" t="n">
         <v>17.9833</v>
       </c>
-      <c r="D95" s="72" t="n">
+      <c r="D95" s="77" t="n">
         <v>13.9255</v>
       </c>
       <c r="E95" s="58">
@@ -7337,10 +8015,10 @@
       <c r="B96" s="56" t="n">
         <v>43707</v>
       </c>
-      <c r="C96" s="71" t="n">
+      <c r="C96" s="76" t="n">
         <v>17.75</v>
       </c>
-      <c r="D96" s="72" t="n">
+      <c r="D96" s="77" t="n">
         <v>13.7448</v>
       </c>
       <c r="E96" s="58">
@@ -7361,10 +8039,10 @@
       <c r="B97" s="56" t="n">
         <v>43738</v>
       </c>
-      <c r="C97" s="71" t="n">
+      <c r="C97" s="76" t="n">
         <v>18.26</v>
       </c>
-      <c r="D97" s="72" t="n">
+      <c r="D97" s="77" t="n">
         <v>14.2666</v>
       </c>
       <c r="E97" s="58">
@@ -7385,10 +8063,10 @@
       <c r="B98" s="56" t="n">
         <v>43769</v>
       </c>
-      <c r="C98" s="71" t="n">
+      <c r="C98" s="76" t="n">
         <v>18.5067</v>
       </c>
-      <c r="D98" s="72" t="n">
+      <c r="D98" s="77" t="n">
         <v>14.4594</v>
       </c>
       <c r="E98" s="58">
@@ -7409,10 +8087,10 @@
       <c r="B99" s="56" t="n">
         <v>43798</v>
       </c>
-      <c r="C99" s="71" t="n">
+      <c r="C99" s="76" t="n">
         <v>19.03</v>
       </c>
-      <c r="D99" s="72" t="n">
+      <c r="D99" s="77" t="n">
         <v>14.8682</v>
       </c>
       <c r="E99" s="58">
@@ -7433,10 +8111,10 @@
       <c r="B100" s="56" t="n">
         <v>43830</v>
       </c>
-      <c r="C100" s="71" t="n">
+      <c r="C100" s="76" t="n">
         <v>19.3067</v>
       </c>
-      <c r="D100" s="72" t="n">
+      <c r="D100" s="77" t="n">
         <v>15.2078</v>
       </c>
       <c r="E100" s="58">
@@ -7457,10 +8135,10 @@
       <c r="B101" s="56" t="n">
         <v>43861</v>
       </c>
-      <c r="C101" s="71" t="n">
+      <c r="C101" s="76" t="n">
         <v>18.9667</v>
       </c>
-      <c r="D101" s="72" t="n">
+      <c r="D101" s="77" t="n">
         <v>14.94</v>
       </c>
       <c r="E101" s="58">
@@ -7481,10 +8159,10 @@
       <c r="B102" s="56" t="n">
         <v>43889</v>
       </c>
-      <c r="C102" s="71" t="n">
+      <c r="C102" s="76" t="n">
         <v>17.1933</v>
       </c>
-      <c r="D102" s="72" t="n">
+      <c r="D102" s="77" t="n">
         <v>13.5432</v>
       </c>
       <c r="E102" s="58">
@@ -7505,10 +8183,10 @@
       <c r="B103" s="56" t="n">
         <v>43921</v>
       </c>
-      <c r="C103" s="71" t="n">
+      <c r="C103" s="76" t="n">
         <v>14.9933</v>
       </c>
-      <c r="D103" s="72" t="n">
+      <c r="D103" s="77" t="n">
         <v>11.9339</v>
       </c>
       <c r="E103" s="58">
@@ -7529,10 +8207,10 @@
       <c r="B104" s="56" t="n">
         <v>43951</v>
       </c>
-      <c r="C104" s="71" t="n">
+      <c r="C104" s="76" t="n">
         <v>16.8833</v>
       </c>
-      <c r="D104" s="72" t="n">
+      <c r="D104" s="77" t="n">
         <v>13.4382</v>
       </c>
       <c r="E104" s="58">
@@ -7553,10 +8231,10 @@
       <c r="B105" s="56" t="n">
         <v>43980</v>
       </c>
-      <c r="C105" s="71" t="n">
+      <c r="C105" s="76" t="n">
         <v>17.5067</v>
       </c>
-      <c r="D105" s="72" t="n">
+      <c r="D105" s="77" t="n">
         <v>13.9343</v>
       </c>
       <c r="E105" s="58">
@@ -7577,10 +8255,10 @@
       <c r="B106" s="56" t="n">
         <v>44012</v>
       </c>
-      <c r="C106" s="71" t="n">
+      <c r="C106" s="76" t="n">
         <v>17.25</v>
       </c>
-      <c r="D106" s="72" t="n">
+      <c r="D106" s="77" t="n">
         <v>13.846</v>
       </c>
       <c r="E106" s="58">
@@ -7601,10 +8279,10 @@
       <c r="B107" s="56" t="n">
         <v>44043</v>
       </c>
-      <c r="C107" s="71" t="n">
+      <c r="C107" s="76" t="n">
         <v>18.1633</v>
       </c>
-      <c r="D107" s="72" t="n">
+      <c r="D107" s="77" t="n">
         <v>14.5791</v>
       </c>
       <c r="E107" s="58">
@@ -7625,10 +8303,10 @@
       <c r="B108" s="56" t="n">
         <v>44074</v>
       </c>
-      <c r="C108" s="71" t="n">
+      <c r="C108" s="76" t="n">
         <v>19.0933</v>
       </c>
-      <c r="D108" s="72" t="n">
+      <c r="D108" s="77" t="n">
         <v>15.3255</v>
       </c>
       <c r="E108" s="58">
@@ -7649,10 +8327,10 @@
       <c r="B109" s="56" t="n">
         <v>44104</v>
       </c>
-      <c r="C109" s="71" t="n">
+      <c r="C109" s="76" t="n">
         <v>18.4333</v>
       </c>
-      <c r="D109" s="72" t="n">
+      <c r="D109" s="77" t="n">
         <v>14.9429</v>
       </c>
       <c r="E109" s="58">
@@ -7673,10 +8351,10 @@
       <c r="B110" s="56" t="n">
         <v>44134</v>
       </c>
-      <c r="C110" s="71" t="n">
+      <c r="C110" s="76" t="n">
         <v>18.5033</v>
       </c>
-      <c r="D110" s="72" t="n">
+      <c r="D110" s="77" t="n">
         <v>14.9997</v>
       </c>
       <c r="E110" s="58">
@@ -7697,10 +8375,10 @@
       <c r="B111" s="56" t="n">
         <v>44165</v>
       </c>
-      <c r="C111" s="71" t="n">
+      <c r="C111" s="76" t="n">
         <v>20.94</v>
       </c>
-      <c r="D111" s="72" t="n">
+      <c r="D111" s="77" t="n">
         <v>16.975</v>
       </c>
       <c r="E111" s="58">
@@ -7721,10 +8399,10 @@
       <c r="B112" s="56" t="n">
         <v>44196</v>
       </c>
-      <c r="C112" s="71" t="n">
+      <c r="C112" s="76" t="n">
         <v>21.38</v>
       </c>
-      <c r="D112" s="72" t="n">
+      <c r="D112" s="77" t="n">
         <v>17.4933</v>
       </c>
       <c r="E112" s="58">
@@ -7745,10 +8423,10 @@
       <c r="B113" s="56" t="n">
         <v>44225</v>
       </c>
-      <c r="C113" s="71" t="n">
+      <c r="C113" s="76" t="n">
         <v>21.1867</v>
       </c>
-      <c r="D113" s="72" t="n">
+      <c r="D113" s="77" t="n">
         <v>17.3351</v>
       </c>
       <c r="E113" s="58">
@@ -7769,10 +8447,10 @@
       <c r="B114" s="56" t="n">
         <v>44253</v>
       </c>
-      <c r="C114" s="71" t="n">
+      <c r="C114" s="76" t="n">
         <v>22.47</v>
       </c>
-      <c r="D114" s="72" t="n">
+      <c r="D114" s="77" t="n">
         <v>18.3851</v>
       </c>
       <c r="E114" s="58">
@@ -7793,10 +8471,10 @@
       <c r="B115" s="56" t="n">
         <v>44286</v>
       </c>
-      <c r="C115" s="71" t="n">
+      <c r="C115" s="76" t="n">
         <v>24.3067</v>
       </c>
-      <c r="D115" s="72" t="n">
+      <c r="D115" s="77" t="n">
         <v>20.0289</v>
       </c>
       <c r="E115" s="58">
@@ -7817,10 +8495,10 @@
       <c r="B116" s="56" t="n">
         <v>44316</v>
       </c>
-      <c r="C116" s="71" t="n">
+      <c r="C116" s="76" t="n">
         <v>24.8433</v>
       </c>
-      <c r="D116" s="72" t="n">
+      <c r="D116" s="77" t="n">
         <v>20.4711</v>
       </c>
       <c r="E116" s="58">
@@ -7841,10 +8519,10 @@
       <c r="B117" s="56" t="n">
         <v>44344</v>
       </c>
-      <c r="C117" s="71" t="n">
+      <c r="C117" s="76" t="n">
         <v>25.6433</v>
       </c>
-      <c r="D117" s="72" t="n">
+      <c r="D117" s="77" t="n">
         <v>21.1303</v>
       </c>
       <c r="E117" s="58">
@@ -7865,10 +8543,10 @@
       <c r="B118" s="56" t="n">
         <v>44377</v>
       </c>
-      <c r="C118" s="71" t="n">
+      <c r="C118" s="76" t="n">
         <v>25.2067</v>
       </c>
-      <c r="D118" s="72" t="n">
+      <c r="D118" s="77" t="n">
         <v>20.9203</v>
       </c>
       <c r="E118" s="58">
@@ -7889,10 +8567,10 @@
       <c r="B119" s="56" t="n">
         <v>44407</v>
       </c>
-      <c r="C119" s="71" t="n">
+      <c r="C119" s="76" t="n">
         <v>25.37</v>
       </c>
-      <c r="D119" s="72" t="n">
+      <c r="D119" s="77" t="n">
         <v>21.0559</v>
       </c>
       <c r="E119" s="58">
@@ -7913,10 +8591,10 @@
       <c r="B120" s="56" t="n">
         <v>44439</v>
       </c>
-      <c r="C120" s="71" t="n">
+      <c r="C120" s="76" t="n">
         <v>25.9</v>
       </c>
-      <c r="D120" s="72" t="n">
+      <c r="D120" s="77" t="n">
         <v>21.4958</v>
       </c>
       <c r="E120" s="58">
@@ -7937,10 +8615,10 @@
       <c r="B121" s="56" t="n">
         <v>44469</v>
       </c>
-      <c r="C121" s="71" t="n">
+      <c r="C121" s="76" t="n">
         <v>24.7467</v>
       </c>
-      <c r="D121" s="72" t="n">
+      <c r="D121" s="77" t="n">
         <v>20.7023</v>
       </c>
       <c r="E121" s="58">
@@ -7961,10 +8639,10 @@
       <c r="B122" s="56" t="n">
         <v>44498</v>
       </c>
-      <c r="C122" s="71" t="n">
+      <c r="C122" s="76" t="n">
         <v>25.8367</v>
       </c>
-      <c r="D122" s="72" t="n">
+      <c r="D122" s="77" t="n">
         <v>21.6141</v>
       </c>
       <c r="E122" s="58">
@@ -7985,10 +8663,10 @@
       <c r="B123" s="56" t="n">
         <v>44530</v>
       </c>
-      <c r="C123" s="71" t="n">
+      <c r="C123" s="76" t="n">
         <v>25.3067</v>
       </c>
-      <c r="D123" s="72" t="n">
+      <c r="D123" s="77" t="n">
         <v>21.1707</v>
       </c>
       <c r="E123" s="58">
@@ -8009,10 +8687,10 @@
       <c r="B124" s="56" t="n">
         <v>44561</v>
       </c>
-      <c r="C124" s="71" t="n">
+      <c r="C124" s="76" t="n">
         <v>26.9433</v>
       </c>
-      <c r="D124" s="72" t="n">
+      <c r="D124" s="77" t="n">
         <v>22.7195</v>
       </c>
       <c r="E124" s="58">
@@ -8033,10 +8711,10 @@
       <c r="B125" s="56" t="n">
         <v>44592</v>
       </c>
-      <c r="C125" s="71" t="n">
+      <c r="C125" s="76" t="n">
         <v>26.2067</v>
       </c>
-      <c r="D125" s="72" t="n">
+      <c r="D125" s="77" t="n">
         <v>22.0983</v>
       </c>
       <c r="E125" s="58">
@@ -8057,10 +8735,10 @@
       <c r="B126" s="56" t="n">
         <v>44620</v>
       </c>
-      <c r="C126" s="71" t="n">
+      <c r="C126" s="76" t="n">
         <v>25.7</v>
       </c>
-      <c r="D126" s="72" t="n">
+      <c r="D126" s="77" t="n">
         <v>21.6711</v>
       </c>
       <c r="E126" s="58">
@@ -8081,10 +8759,10 @@
       <c r="B127" s="56" t="n">
         <v>44651</v>
       </c>
-      <c r="C127" s="71" t="n">
+      <c r="C127" s="76" t="n">
         <v>26.2967</v>
       </c>
-      <c r="D127" s="72" t="n">
+      <c r="D127" s="77" t="n">
         <v>22.3198</v>
       </c>
       <c r="E127" s="58">
@@ -8105,10 +8783,10 @@
       <c r="B128" s="56" t="n">
         <v>44680</v>
       </c>
-      <c r="C128" s="71" t="n">
+      <c r="C128" s="76" t="n">
         <v>25.2133</v>
       </c>
-      <c r="D128" s="72" t="n">
+      <c r="D128" s="77" t="n">
         <v>21.4003</v>
       </c>
       <c r="E128" s="58">
@@ -8129,10 +8807,10 @@
       <c r="B129" s="56" t="n">
         <v>44712</v>
       </c>
-      <c r="C129" s="71" t="n">
+      <c r="C129" s="76" t="n">
         <v>26.1967</v>
       </c>
-      <c r="D129" s="72" t="n">
+      <c r="D129" s="77" t="n">
         <v>22.2349</v>
       </c>
       <c r="E129" s="58">
@@ -8153,10 +8831,10 @@
       <c r="B130" s="56" t="n">
         <v>44742</v>
       </c>
-      <c r="C130" s="71" t="n">
+      <c r="C130" s="76" t="n">
         <v>23.8767</v>
       </c>
-      <c r="D130" s="72" t="n">
+      <c r="D130" s="77" t="n">
         <v>20.4659</v>
       </c>
       <c r="E130" s="58">
@@ -8177,10 +8855,10 @@
       <c r="B131" s="56" t="n">
         <v>44771</v>
       </c>
-      <c r="C131" s="71" t="n">
+      <c r="C131" s="76" t="n">
         <v>24.81</v>
       </c>
-      <c r="D131" s="72" t="n">
+      <c r="D131" s="77" t="n">
         <v>21.266</v>
       </c>
       <c r="E131" s="58">
@@ -8201,10 +8879,10 @@
       <c r="B132" s="56" t="n">
         <v>44804</v>
       </c>
-      <c r="C132" s="71" t="n">
+      <c r="C132" s="76" t="n">
         <v>24.1333</v>
       </c>
-      <c r="D132" s="72" t="n">
+      <c r="D132" s="77" t="n">
         <v>20.6859</v>
       </c>
       <c r="E132" s="58">
@@ -8225,10 +8903,10 @@
       <c r="B133" s="56" t="n">
         <v>44834</v>
       </c>
-      <c r="C133" s="71" t="n">
+      <c r="C133" s="76" t="n">
         <v>22.1433</v>
       </c>
-      <c r="D133" s="72" t="n">
+      <c r="D133" s="77" t="n">
         <v>19.152</v>
       </c>
       <c r="E133" s="58">
@@ -8249,10 +8927,10 @@
       <c r="B134" s="56" t="n">
         <v>44865</v>
       </c>
-      <c r="C134" s="71" t="n">
+      <c r="C134" s="76" t="n">
         <v>24.6267</v>
       </c>
-      <c r="D134" s="72" t="n">
+      <c r="D134" s="77" t="n">
         <v>21.2999</v>
       </c>
       <c r="E134" s="58">
@@ -8273,10 +8951,10 @@
       <c r="B135" s="56" t="n">
         <v>44895</v>
       </c>
-      <c r="C135" s="71" t="n">
+      <c r="C135" s="76" t="n">
         <v>26.31</v>
       </c>
-      <c r="D135" s="72" t="n">
+      <c r="D135" s="77" t="n">
         <v>22.7558</v>
       </c>
       <c r="E135" s="58">
@@ -8297,10 +8975,10 @@
       <c r="B136" s="56" t="n">
         <v>44925</v>
       </c>
-      <c r="C136" s="71" t="n">
+      <c r="C136" s="76" t="n">
         <v>25.18</v>
       </c>
-      <c r="D136" s="72" t="n">
+      <c r="D136" s="77" t="n">
         <v>21.9799</v>
       </c>
       <c r="E136" s="58">
@@ -8321,10 +8999,10 @@
       <c r="B137" s="56" t="n">
         <v>44957</v>
       </c>
-      <c r="C137" s="71" t="n">
+      <c r="C137" s="76" t="n">
         <v>25.7033</v>
       </c>
-      <c r="D137" s="72" t="n">
+      <c r="D137" s="77" t="n">
         <v>22.4367</v>
       </c>
       <c r="E137" s="58">
@@ -8345,10 +9023,10 @@
       <c r="B138" s="56" t="n">
         <v>44985</v>
       </c>
-      <c r="C138" s="71" t="n">
+      <c r="C138" s="76" t="n">
         <v>24.85</v>
       </c>
-      <c r="D138" s="72" t="n">
+      <c r="D138" s="77" t="n">
         <v>21.6918</v>
       </c>
       <c r="E138" s="58">
@@ -8369,10 +9047,10 @@
       <c r="B139" s="56" t="n">
         <v>45016</v>
       </c>
-      <c r="C139" s="71" t="n">
+      <c r="C139" s="76" t="n">
         <v>24.3867</v>
       </c>
-      <c r="D139" s="72" t="n">
+      <c r="D139" s="77" t="n">
         <v>21.4645</v>
       </c>
       <c r="E139" s="58">
@@ -8393,10 +9071,10 @@
       <c r="B140" s="56" t="n">
         <v>45044</v>
       </c>
-      <c r="C140" s="71" t="n">
+      <c r="C140" s="76" t="n">
         <v>24.19</v>
       </c>
-      <c r="D140" s="72" t="n">
+      <c r="D140" s="77" t="n">
         <v>21.2914</v>
       </c>
       <c r="E140" s="58">
@@ -8417,10 +9095,10 @@
       <c r="B141" s="56" t="n">
         <v>45077</v>
       </c>
-      <c r="C141" s="71" t="n">
+      <c r="C141" s="76" t="n">
         <v>23.1967</v>
       </c>
-      <c r="D141" s="72" t="n">
+      <c r="D141" s="77" t="n">
         <v>20.4171</v>
       </c>
       <c r="E141" s="58">
@@ -8441,10 +9119,10 @@
       <c r="B142" s="56" t="n">
         <v>45107</v>
       </c>
-      <c r="C142" s="71" t="n">
+      <c r="C142" s="76" t="n">
         <v>24.2067</v>
       </c>
-      <c r="D142" s="72" t="n">
+      <c r="D142" s="77" t="n">
         <v>21.5029</v>
       </c>
       <c r="E142" s="58">
@@ -8465,10 +9143,10 @@
       <c r="B143" s="56" t="n">
         <v>45138</v>
       </c>
-      <c r="C143" s="71" t="n">
+      <c r="C143" s="76" t="n">
         <v>25.22</v>
       </c>
-      <c r="D143" s="72" t="n">
+      <c r="D143" s="77" t="n">
         <v>22.4031</v>
       </c>
       <c r="E143" s="58">
@@ -8489,10 +9167,10 @@
       <c r="B144" s="56" t="n">
         <v>45169</v>
       </c>
-      <c r="C144" s="71" t="n">
+      <c r="C144" s="76" t="n">
         <v>24.8433</v>
       </c>
-      <c r="D144" s="72" t="n">
+      <c r="D144" s="77" t="n">
         <v>22.0685</v>
       </c>
       <c r="E144" s="58">
@@ -8513,10 +9191,10 @@
       <c r="B145" s="56" t="n">
         <v>45198</v>
       </c>
-      <c r="C145" s="71" t="n">
+      <c r="C145" s="76" t="n">
         <v>23.5867</v>
       </c>
-      <c r="D145" s="72" t="n">
+      <c r="D145" s="77" t="n">
         <v>21.1408</v>
       </c>
       <c r="E145" s="58">
@@ -8537,10 +9215,10 @@
       <c r="B146" s="56" t="n">
         <v>45230</v>
       </c>
-      <c r="C146" s="71" t="n">
+      <c r="C146" s="76" t="n">
         <v>22.6867</v>
       </c>
-      <c r="D146" s="72" t="n">
+      <c r="D146" s="77" t="n">
         <v>20.3341</v>
       </c>
       <c r="E146" s="58">
@@ -8561,10 +9239,10 @@
       <c r="B147" s="56" t="n">
         <v>45260</v>
       </c>
-      <c r="C147" s="71" t="n">
+      <c r="C147" s="76" t="n">
         <v>24.1167</v>
       </c>
-      <c r="D147" s="72" t="n">
+      <c r="D147" s="77" t="n">
         <v>21.6158</v>
       </c>
       <c r="E147" s="58">
@@ -8585,10 +9263,10 @@
       <c r="B148" s="56" t="n">
         <v>45289</v>
       </c>
-      <c r="C148" s="71" t="n">
+      <c r="C148" s="76" t="n">
         <v>25.3767</v>
       </c>
-      <c r="D148" s="72" t="n">
+      <c r="D148" s="77" t="n">
         <v>22.9787</v>
       </c>
       <c r="E148" s="58">
@@ -8609,10 +9287,10 @@
       <c r="B149" s="56" t="n">
         <v>45322</v>
       </c>
-      <c r="C149" s="71" t="n">
+      <c r="C149" s="76" t="n">
         <v>25.4133</v>
       </c>
-      <c r="D149" s="72" t="n">
+      <c r="D149" s="77" t="n">
         <v>23.0119</v>
       </c>
       <c r="E149" s="58">
@@ -8633,10 +9311,10 @@
       <c r="B150" s="56" t="n">
         <v>45351</v>
       </c>
-      <c r="C150" s="71" t="n">
+      <c r="C150" s="76" t="n">
         <v>25.88</v>
       </c>
-      <c r="D150" s="72" t="n">
+      <c r="D150" s="77" t="n">
         <v>23.4345</v>
       </c>
       <c r="E150" s="58">
@@ -8657,10 +9335,10 @@
       <c r="B151" s="56" t="n">
         <v>45379</v>
       </c>
-      <c r="C151" s="71" t="n">
+      <c r="C151" s="76" t="n">
         <v>26.8767</v>
       </c>
-      <c r="D151" s="72" t="n">
+      <c r="D151" s="77" t="n">
         <v>24.5265</v>
       </c>
       <c r="E151" s="58">
@@ -8681,10 +9359,10 @@
       <c r="B152" s="56" t="n">
         <v>45412</v>
       </c>
-      <c r="C152" s="71" t="n">
+      <c r="C152" s="76" t="n">
         <v>25.6633</v>
       </c>
-      <c r="D152" s="72" t="n">
+      <c r="D152" s="77" t="n">
         <v>23.4192</v>
       </c>
       <c r="E152" s="58">
@@ -8705,10 +9383,10 @@
       <c r="B153" s="56" t="n">
         <v>45443</v>
       </c>
-      <c r="C153" s="71" t="n">
+      <c r="C153" s="76" t="n">
         <v>26.19</v>
       </c>
-      <c r="D153" s="72" t="n">
+      <c r="D153" s="77" t="n">
         <v>23.8998</v>
       </c>
       <c r="E153" s="58">
@@ -8729,10 +9407,10 @@
       <c r="B154" s="56" t="n">
         <v>45471</v>
       </c>
-      <c r="C154" s="71" t="n">
+      <c r="C154" s="76" t="n">
         <v>25.92</v>
       </c>
-      <c r="D154" s="72" t="n">
+      <c r="D154" s="77" t="n">
         <v>23.9041</v>
       </c>
       <c r="E154" s="58">
@@ -8753,10 +9431,10 @@
       <c r="B155" s="56" t="n">
         <v>45504</v>
       </c>
-      <c r="C155" s="71" t="n">
+      <c r="C155" s="76" t="n">
         <v>27.5267</v>
       </c>
-      <c r="D155" s="72" t="n">
+      <c r="D155" s="77" t="n">
         <v>25.3858</v>
       </c>
       <c r="E155" s="58">
@@ -8777,10 +9455,10 @@
       <c r="B156" s="56" t="n">
         <v>45534</v>
       </c>
-      <c r="C156" s="71" t="n">
+      <c r="C156" s="76" t="n">
         <v>28.1767</v>
       </c>
-      <c r="D156" s="72" t="n">
+      <c r="D156" s="77" t="n">
         <v>25.9853</v>
       </c>
       <c r="E156" s="58">
@@ -8801,10 +9479,10 @@
       <c r="B157" s="56" t="n">
         <v>45565</v>
       </c>
-      <c r="C157" s="71" t="n">
+      <c r="C157" s="76" t="n">
         <v>28.1767</v>
       </c>
-      <c r="D157" s="72" t="n">
+      <c r="D157" s="77" t="n">
         <v>26.218</v>
       </c>
       <c r="E157" s="58">
@@ -8825,10 +9503,10 @@
       <c r="B158" s="56" t="n">
         <v>45596</v>
       </c>
-      <c r="C158" s="71" t="n">
+      <c r="C158" s="76" t="n">
         <v>28.23</v>
       </c>
-      <c r="D158" s="72" t="n">
+      <c r="D158" s="77" t="n">
         <v>26.2676</v>
       </c>
       <c r="E158" s="58">
@@ -8849,10 +9527,10 @@
       <c r="B159" s="56" t="n">
         <v>45625</v>
       </c>
-      <c r="C159" s="71" t="n">
+      <c r="C159" s="76" t="n">
         <v>29.53</v>
       </c>
-      <c r="D159" s="72" t="n">
+      <c r="D159" s="77" t="n">
         <v>27.4772</v>
       </c>
       <c r="E159" s="58">
@@ -8873,10 +9551,10 @@
       <c r="B160" s="56" t="n">
         <v>45657</v>
       </c>
-      <c r="C160" s="71" t="n">
+      <c r="C160" s="76" t="n">
         <v>27.32</v>
       </c>
-      <c r="D160" s="72" t="n">
+      <c r="D160" s="77" t="n">
         <v>25.6579</v>
       </c>
       <c r="E160" s="58">
@@ -8897,10 +9575,10 @@
       <c r="B161" s="56" t="n">
         <v>45688</v>
       </c>
-      <c r="C161" s="71" t="n">
+      <c r="C161" s="76" t="n">
         <v>27.83</v>
       </c>
-      <c r="D161" s="72" t="n">
+      <c r="D161" s="77" t="n">
         <v>26.1369</v>
       </c>
       <c r="E161" s="58">
@@ -8921,10 +9599,10 @@
       <c r="B162" s="56" t="n">
         <v>45716</v>
       </c>
-      <c r="C162" s="71" t="n">
+      <c r="C162" s="76" t="n">
         <v>28.54</v>
       </c>
-      <c r="D162" s="72" t="n">
+      <c r="D162" s="77" t="n">
         <v>26.8037</v>
       </c>
       <c r="E162" s="58">
@@ -8945,10 +9623,10 @@
       <c r="B163" s="56" t="n">
         <v>45747</v>
       </c>
-      <c r="C163" s="71" t="n">
+      <c r="C163" s="76" t="n">
         <v>27.96</v>
       </c>
-      <c r="D163" s="72" t="n">
+      <c r="D163" s="77" t="n">
         <v>26.496</v>
       </c>
       <c r="E163" s="58">
@@ -8969,10 +9647,10 @@
       <c r="B164" s="56" t="n">
         <v>45777</v>
       </c>
-      <c r="C164" s="71" t="n">
+      <c r="C164" s="76" t="n">
         <v>25.82</v>
       </c>
-      <c r="D164" s="72" t="n">
+      <c r="D164" s="77" t="n">
         <v>24.468</v>
       </c>
       <c r="E164" s="58">
@@ -8993,10 +9671,10 @@
       <c r="B165" s="56" t="n">
         <v>45807</v>
       </c>
-      <c r="C165" s="71" t="n">
+      <c r="C165" s="76" t="n">
         <v>26.17</v>
       </c>
-      <c r="D165" s="72" t="n">
+      <c r="D165" s="77" t="n">
         <v>24.7997</v>
       </c>
       <c r="E165" s="58">
@@ -9017,10 +9695,10 @@
       <c r="B166" s="56" t="n">
         <v>45838</v>
       </c>
-      <c r="C166" s="71" t="n">
+      <c r="C166" s="76" t="n">
         <v>26.5</v>
       </c>
-      <c r="D166" s="72" t="n">
+      <c r="D166" s="77" t="n">
         <v>25.359</v>
       </c>
       <c r="E166" s="58">
@@ -9041,10 +9719,10 @@
       <c r="B167" s="56" t="n">
         <v>45869</v>
       </c>
-      <c r="C167" s="71" t="n">
+      <c r="C167" s="76" t="n">
         <v>26.5</v>
       </c>
-      <c r="D167" s="72" t="n">
+      <c r="D167" s="77" t="n">
         <v>25.359</v>
       </c>
       <c r="E167" s="58">
@@ -9065,10 +9743,10 @@
       <c r="B168" s="56" t="n">
         <v>45898</v>
       </c>
-      <c r="C168" s="71" t="n">
+      <c r="C168" s="76" t="n">
         <v>27.92</v>
       </c>
-      <c r="D168" s="72" t="n">
+      <c r="D168" s="77" t="n">
         <v>26.7179</v>
       </c>
       <c r="E168" s="58">
@@ -9089,10 +9767,10 @@
       <c r="B169" s="56" t="n">
         <v>45930</v>
       </c>
-      <c r="C169" s="71" t="n">
+      <c r="C169" s="76" t="n">
         <v>27.3</v>
       </c>
-      <c r="D169" s="72" t="n">
+      <c r="D169" s="77" t="n">
         <v>26.3748</v>
       </c>
       <c r="E169" s="58">
@@ -9113,10 +9791,10 @@
       <c r="B170" s="56" t="n">
         <v>45961</v>
       </c>
-      <c r="C170" s="71" t="n">
+      <c r="C170" s="76" t="n">
         <v>26.75</v>
       </c>
-      <c r="D170" s="72" t="n">
+      <c r="D170" s="77" t="n">
         <v>25.8435</v>
       </c>
       <c r="E170" s="58">
@@ -9137,10 +9815,10 @@
       <c r="B171" s="56" t="n">
         <v>45989</v>
       </c>
-      <c r="C171" s="71" t="n">
+      <c r="C171" s="76" t="n">
         <v>27.59</v>
       </c>
-      <c r="D171" s="72" t="n">
+      <c r="D171" s="77" t="n">
         <v>26.655</v>
       </c>
       <c r="E171" s="58">
@@ -9161,10 +9839,10 @@
       <c r="B172" s="56" t="n">
         <v>46022</v>
       </c>
-      <c r="C172" s="71" t="n">
+      <c r="C172" s="76" t="n">
         <v>27.43</v>
       </c>
-      <c r="D172" s="72" t="n">
+      <c r="D172" s="77" t="n">
         <v>26.7715</v>
       </c>
       <c r="E172" s="58">
@@ -9185,10 +9863,10 @@
       <c r="B173" s="56" t="n">
         <v>46052</v>
       </c>
-      <c r="C173" s="71" t="n">
+      <c r="C173" s="76" t="n">
         <v>29.82</v>
       </c>
-      <c r="D173" s="72" t="n">
+      <c r="D173" s="77" t="n">
         <v>29.1041</v>
       </c>
       <c r="E173" s="58">
@@ -9209,10 +9887,10 @@
       <c r="B174" s="56" t="n">
         <v>46080</v>
       </c>
-      <c r="C174" s="71" t="n">
+      <c r="C174" s="76" t="n">
         <v>31.77</v>
       </c>
-      <c r="D174" s="72" t="n">
+      <c r="D174" s="77" t="n">
         <v>31.0073</v>
       </c>
       <c r="E174" s="58">
@@ -9233,10 +9911,10 @@
       <c r="B175" s="56" t="n">
         <v>46112</v>
       </c>
-      <c r="C175" s="71" t="n">
+      <c r="C175" s="76" t="n">
         <v>30.68</v>
       </c>
-      <c r="D175" s="72" t="n">
+      <c r="D175" s="77" t="n">
         <v>30.1967</v>
       </c>
       <c r="E175" s="58">
@@ -9257,10 +9935,10 @@
       <c r="B176" s="56" t="n">
         <v>46142</v>
       </c>
-      <c r="C176" s="71" t="n">
+      <c r="C176" s="76" t="n">
         <v>32.07</v>
       </c>
-      <c r="D176" s="72" t="n">
+      <c r="D176" s="77" t="n">
         <v>31.5648</v>
       </c>
       <c r="E176" s="58">
@@ -9281,10 +9959,10 @@
       <c r="B177" s="56" t="n">
         <v>46171</v>
       </c>
-      <c r="C177" s="71" t="n">
+      <c r="C177" s="76" t="n">
         <v>32.5</v>
       </c>
-      <c r="D177" s="72" t="n">
+      <c r="D177" s="77" t="n">
         <v>31.9881</v>
       </c>
       <c r="E177" s="58">
@@ -9305,10 +9983,10 @@
       <c r="B178" s="56" t="n">
         <v>46203</v>
       </c>
-      <c r="C178" s="71" t="n">
+      <c r="C178" s="76" t="n">
         <v>31.71</v>
       </c>
-      <c r="D178" s="72" t="n">
+      <c r="D178" s="77" t="n">
         <v>31.4591</v>
       </c>
       <c r="E178" s="58">
@@ -9329,10 +10007,10 @@
       <c r="B179" s="56" t="n">
         <v>46234</v>
       </c>
-      <c r="C179" s="71" t="n">
+      <c r="C179" s="76" t="n">
         <v>33.47</v>
       </c>
-      <c r="D179" s="72" t="n">
+      <c r="D179" s="77" t="n">
         <v>33.2051</v>
       </c>
       <c r="E179" s="58">
@@ -9353,10 +10031,10 @@
       <c r="B180" s="56" t="n">
         <v>46265</v>
       </c>
-      <c r="C180" s="71" t="n">
+      <c r="C180" s="76" t="n">
         <v>34.89</v>
       </c>
-      <c r="D180" s="72" t="n">
+      <c r="D180" s="77" t="n">
         <v>34.6139</v>
       </c>
       <c r="E180" s="58">
@@ -9377,10 +10055,10 @@
       <c r="B181" s="56" t="n">
         <v>46295</v>
       </c>
-      <c r="C181" s="71" t="n">
+      <c r="C181" s="76" t="n">
         <v>32.53</v>
       </c>
-      <c r="D181" s="72" t="n">
+      <c r="D181" s="77" t="n">
         <v>32.53</v>
       </c>
       <c r="E181" s="58">
@@ -9401,10 +10079,10 @@
       <c r="B182" s="56" t="n">
         <v>46303</v>
       </c>
-      <c r="C182" s="71" t="n">
+      <c r="C182" s="76" t="n">
         <v>33.15</v>
       </c>
-      <c r="D182" s="72" t="n">
+      <c r="D182" s="77" t="n">
         <v>33.15</v>
       </c>
       <c r="E182" s="58">
@@ -9422,7 +10100,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9480,7 +10158,7 @@
       <c r="A2" s="45" t="n">
         <v>2012</v>
       </c>
-      <c r="B2" s="73" t="n">
+      <c r="B2" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="45" t="inlineStr">
@@ -9505,7 +10183,7 @@
       <c r="A3" s="45" t="n">
         <v>2012</v>
       </c>
-      <c r="B3" s="73" t="n">
+      <c r="B3" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C3" s="45" t="inlineStr">
@@ -9530,7 +10208,7 @@
       <c r="A4" s="45" t="n">
         <v>2012</v>
       </c>
-      <c r="B4" s="73" t="n">
+      <c r="B4" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C4" s="45" t="inlineStr">
@@ -9555,7 +10233,7 @@
       <c r="A5" s="45" t="n">
         <v>2012</v>
       </c>
-      <c r="B5" s="73" t="n">
+      <c r="B5" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="45" t="inlineStr">
@@ -9580,7 +10258,7 @@
       <c r="A6" s="45" t="n">
         <v>2013</v>
       </c>
-      <c r="B6" s="73" t="n">
+      <c r="B6" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C6" s="45" t="inlineStr">
@@ -9605,7 +10283,7 @@
       <c r="A7" s="45" t="n">
         <v>2013</v>
       </c>
-      <c r="B7" s="73" t="n">
+      <c r="B7" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C7" s="45" t="inlineStr">
@@ -9630,7 +10308,7 @@
       <c r="A8" s="45" t="n">
         <v>2013</v>
       </c>
-      <c r="B8" s="73" t="n">
+      <c r="B8" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C8" s="45" t="inlineStr">
@@ -9655,7 +10333,7 @@
       <c r="A9" s="45" t="n">
         <v>2013</v>
       </c>
-      <c r="B9" s="73" t="n">
+      <c r="B9" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="45" t="inlineStr">
@@ -9680,7 +10358,7 @@
       <c r="A10" s="45" t="n">
         <v>2014</v>
       </c>
-      <c r="B10" s="73" t="n">
+      <c r="B10" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="45" t="inlineStr">
@@ -9705,7 +10383,7 @@
       <c r="A11" s="45" t="n">
         <v>2014</v>
       </c>
-      <c r="B11" s="73" t="n">
+      <c r="B11" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C11" s="45" t="inlineStr">
@@ -9730,7 +10408,7 @@
       <c r="A12" s="45" t="n">
         <v>2014</v>
       </c>
-      <c r="B12" s="73" t="n">
+      <c r="B12" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C12" s="45" t="inlineStr">
@@ -9755,7 +10433,7 @@
       <c r="A13" s="45" t="n">
         <v>2014</v>
       </c>
-      <c r="B13" s="73" t="n">
+      <c r="B13" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C13" s="45" t="inlineStr">
@@ -9780,7 +10458,7 @@
       <c r="A14" s="45" t="n">
         <v>2015</v>
       </c>
-      <c r="B14" s="73" t="n">
+      <c r="B14" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C14" s="45" t="inlineStr">
@@ -9805,7 +10483,7 @@
       <c r="A15" s="45" t="n">
         <v>2015</v>
       </c>
-      <c r="B15" s="73" t="n">
+      <c r="B15" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C15" s="45" t="inlineStr">
@@ -9830,7 +10508,7 @@
       <c r="A16" s="45" t="n">
         <v>2015</v>
       </c>
-      <c r="B16" s="73" t="n">
+      <c r="B16" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C16" s="45" t="inlineStr">
@@ -9855,7 +10533,7 @@
       <c r="A17" s="45" t="n">
         <v>2015</v>
       </c>
-      <c r="B17" s="73" t="n">
+      <c r="B17" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C17" s="45" t="inlineStr">
@@ -9880,7 +10558,7 @@
       <c r="A18" s="45" t="n">
         <v>2016</v>
       </c>
-      <c r="B18" s="73" t="n">
+      <c r="B18" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C18" s="45" t="inlineStr">
@@ -9905,7 +10583,7 @@
       <c r="A19" s="45" t="n">
         <v>2016</v>
       </c>
-      <c r="B19" s="73" t="n">
+      <c r="B19" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C19" s="45" t="inlineStr">
@@ -9930,7 +10608,7 @@
       <c r="A20" s="45" t="n">
         <v>2016</v>
       </c>
-      <c r="B20" s="73" t="n">
+      <c r="B20" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C20" s="45" t="inlineStr">
@@ -9955,7 +10633,7 @@
       <c r="A21" s="45" t="n">
         <v>2016</v>
       </c>
-      <c r="B21" s="73" t="n">
+      <c r="B21" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C21" s="45" t="inlineStr">
@@ -9980,7 +10658,7 @@
       <c r="A22" s="45" t="n">
         <v>2017</v>
       </c>
-      <c r="B22" s="73" t="n">
+      <c r="B22" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C22" s="45" t="inlineStr">
@@ -10005,7 +10683,7 @@
       <c r="A23" s="45" t="n">
         <v>2017</v>
       </c>
-      <c r="B23" s="73" t="n">
+      <c r="B23" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C23" s="45" t="inlineStr">
@@ -10030,7 +10708,7 @@
       <c r="A24" s="45" t="n">
         <v>2017</v>
       </c>
-      <c r="B24" s="73" t="n">
+      <c r="B24" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C24" s="45" t="inlineStr">
@@ -10055,7 +10733,7 @@
       <c r="A25" s="45" t="n">
         <v>2017</v>
       </c>
-      <c r="B25" s="73" t="n">
+      <c r="B25" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C25" s="45" t="inlineStr">
@@ -10080,7 +10758,7 @@
       <c r="A26" s="45" t="n">
         <v>2018</v>
       </c>
-      <c r="B26" s="73" t="n">
+      <c r="B26" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C26" s="45" t="inlineStr">
@@ -10105,7 +10783,7 @@
       <c r="A27" s="45" t="n">
         <v>2018</v>
       </c>
-      <c r="B27" s="73" t="n">
+      <c r="B27" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C27" s="45" t="inlineStr">
@@ -10130,7 +10808,7 @@
       <c r="A28" s="45" t="n">
         <v>2018</v>
       </c>
-      <c r="B28" s="73" t="n">
+      <c r="B28" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C28" s="45" t="inlineStr">
@@ -10155,7 +10833,7 @@
       <c r="A29" s="45" t="n">
         <v>2018</v>
       </c>
-      <c r="B29" s="73" t="n">
+      <c r="B29" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C29" s="45" t="inlineStr">
@@ -10180,7 +10858,7 @@
       <c r="A30" s="45" t="n">
         <v>2019</v>
       </c>
-      <c r="B30" s="73" t="n">
+      <c r="B30" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C30" s="45" t="inlineStr">
@@ -10205,7 +10883,7 @@
       <c r="A31" s="45" t="n">
         <v>2019</v>
       </c>
-      <c r="B31" s="73" t="n">
+      <c r="B31" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C31" s="45" t="inlineStr">
@@ -10230,7 +10908,7 @@
       <c r="A32" s="45" t="n">
         <v>2019</v>
       </c>
-      <c r="B32" s="73" t="n">
+      <c r="B32" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C32" s="45" t="inlineStr">
@@ -10255,7 +10933,7 @@
       <c r="A33" s="45" t="n">
         <v>2019</v>
       </c>
-      <c r="B33" s="73" t="n">
+      <c r="B33" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C33" s="45" t="inlineStr">
@@ -10280,7 +10958,7 @@
       <c r="A34" s="45" t="n">
         <v>2020</v>
       </c>
-      <c r="B34" s="73" t="n">
+      <c r="B34" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C34" s="45" t="inlineStr">
@@ -10305,7 +10983,7 @@
       <c r="A35" s="45" t="n">
         <v>2020</v>
       </c>
-      <c r="B35" s="73" t="n">
+      <c r="B35" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C35" s="45" t="inlineStr">
@@ -10330,7 +11008,7 @@
       <c r="A36" s="45" t="n">
         <v>2020</v>
       </c>
-      <c r="B36" s="73" t="n">
+      <c r="B36" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C36" s="45" t="inlineStr">
@@ -10355,7 +11033,7 @@
       <c r="A37" s="45" t="n">
         <v>2020</v>
       </c>
-      <c r="B37" s="73" t="n">
+      <c r="B37" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C37" s="45" t="inlineStr">
@@ -10380,7 +11058,7 @@
       <c r="A38" s="45" t="n">
         <v>2021</v>
       </c>
-      <c r="B38" s="73" t="n">
+      <c r="B38" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="45" t="inlineStr">
@@ -10405,7 +11083,7 @@
       <c r="A39" s="45" t="n">
         <v>2021</v>
       </c>
-      <c r="B39" s="73" t="n">
+      <c r="B39" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C39" s="45" t="inlineStr">
@@ -10430,7 +11108,7 @@
       <c r="A40" s="45" t="n">
         <v>2021</v>
       </c>
-      <c r="B40" s="73" t="n">
+      <c r="B40" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C40" s="45" t="inlineStr">
@@ -10455,7 +11133,7 @@
       <c r="A41" s="45" t="n">
         <v>2021</v>
       </c>
-      <c r="B41" s="73" t="n">
+      <c r="B41" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C41" s="45" t="inlineStr">
@@ -10480,7 +11158,7 @@
       <c r="A42" s="45" t="n">
         <v>2022</v>
       </c>
-      <c r="B42" s="73" t="n">
+      <c r="B42" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="45" t="inlineStr">
@@ -10505,7 +11183,7 @@
       <c r="A43" s="45" t="n">
         <v>2022</v>
       </c>
-      <c r="B43" s="73" t="n">
+      <c r="B43" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C43" s="45" t="inlineStr">
@@ -10530,7 +11208,7 @@
       <c r="A44" s="45" t="n">
         <v>2022</v>
       </c>
-      <c r="B44" s="73" t="n">
+      <c r="B44" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C44" s="45" t="inlineStr">
@@ -10555,7 +11233,7 @@
       <c r="A45" s="45" t="n">
         <v>2022</v>
       </c>
-      <c r="B45" s="73" t="n">
+      <c r="B45" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C45" s="45" t="inlineStr">
@@ -10580,7 +11258,7 @@
       <c r="A46" s="45" t="n">
         <v>2023</v>
       </c>
-      <c r="B46" s="73" t="n">
+      <c r="B46" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C46" s="45" t="inlineStr">
@@ -10605,7 +11283,7 @@
       <c r="A47" s="45" t="n">
         <v>2023</v>
       </c>
-      <c r="B47" s="73" t="n">
+      <c r="B47" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C47" s="45" t="inlineStr">
@@ -10630,7 +11308,7 @@
       <c r="A48" s="45" t="n">
         <v>2023</v>
       </c>
-      <c r="B48" s="73" t="n">
+      <c r="B48" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C48" s="45" t="inlineStr">
@@ -10655,7 +11333,7 @@
       <c r="A49" s="45" t="n">
         <v>2023</v>
       </c>
-      <c r="B49" s="73" t="n">
+      <c r="B49" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C49" s="45" t="inlineStr">
@@ -10680,7 +11358,7 @@
       <c r="A50" s="45" t="n">
         <v>2024</v>
       </c>
-      <c r="B50" s="73" t="n">
+      <c r="B50" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C50" s="45" t="inlineStr">
@@ -10705,7 +11383,7 @@
       <c r="A51" s="45" t="n">
         <v>2024</v>
       </c>
-      <c r="B51" s="73" t="n">
+      <c r="B51" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C51" s="45" t="inlineStr">
@@ -10730,7 +11408,7 @@
       <c r="A52" s="45" t="n">
         <v>2024</v>
       </c>
-      <c r="B52" s="73" t="n">
+      <c r="B52" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C52" s="45" t="inlineStr">
@@ -10755,7 +11433,7 @@
       <c r="A53" s="45" t="n">
         <v>2024</v>
       </c>
-      <c r="B53" s="73" t="n">
+      <c r="B53" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C53" s="45" t="inlineStr">
@@ -10780,7 +11458,7 @@
       <c r="A54" s="45" t="n">
         <v>2025</v>
       </c>
-      <c r="B54" s="73" t="n">
+      <c r="B54" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C54" s="45" t="inlineStr">
@@ -10805,7 +11483,7 @@
       <c r="A55" s="45" t="n">
         <v>2025</v>
       </c>
-      <c r="B55" s="73" t="n">
+      <c r="B55" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C55" s="45" t="inlineStr">
@@ -10830,7 +11508,7 @@
       <c r="A56" s="45" t="n">
         <v>2025</v>
       </c>
-      <c r="B56" s="73" t="n">
+      <c r="B56" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C56" s="45" t="inlineStr">
@@ -10855,7 +11533,7 @@
       <c r="A57" s="45" t="n">
         <v>2025</v>
       </c>
-      <c r="B57" s="73" t="n">
+      <c r="B57" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C57" s="45" t="inlineStr">
@@ -10880,7 +11558,7 @@
       <c r="A58" s="45" t="n">
         <v>2026</v>
       </c>
-      <c r="B58" s="73" t="n">
+      <c r="B58" s="78" t="n">
         <v>1</v>
       </c>
       <c r="C58" s="45" t="inlineStr">
@@ -10905,7 +11583,7 @@
       <c r="A59" s="45" t="n">
         <v>2026</v>
       </c>
-      <c r="B59" s="73" t="n">
+      <c r="B59" s="78" t="n">
         <v>2</v>
       </c>
       <c r="C59" s="45" t="inlineStr">
@@ -10930,7 +11608,7 @@
       <c r="A60" s="45" t="n">
         <v>2026</v>
       </c>
-      <c r="B60" s="73" t="n">
+      <c r="B60" s="78" t="n">
         <v>3</v>
       </c>
       <c r="C60" s="45" t="inlineStr">
@@ -10955,7 +11633,7 @@
       <c r="A61" s="45" t="n">
         <v>2026</v>
       </c>
-      <c r="B61" s="73" t="n">
+      <c r="B61" s="78" t="n">
         <v>4</v>
       </c>
       <c r="C61" s="45" t="inlineStr">
@@ -29364,7 +30042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL200"/>
+  <dimension ref="A1:BL201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -54548,17 +55226,17 @@
     <row r="200">
       <c r="A200" s="66" t="inlineStr">
         <is>
-          <t>VTS</t>
+          <t>FG</t>
         </is>
       </c>
       <c r="B200" s="66" t="inlineStr">
         <is>
-          <t>Vitesse Energy Inc</t>
+          <t>F&amp;G Annuities And Life Inc</t>
         </is>
       </c>
       <c r="C200" s="66" t="inlineStr">
         <is>
-          <t>에너지</t>
+          <t>금융</t>
         </is>
       </c>
       <c r="D200" s="67" t="n"/>
@@ -54577,9 +55255,7 @@
       <c r="Q200" s="67" t="n"/>
       <c r="R200" s="67" t="n"/>
       <c r="S200" s="67" t="n"/>
-      <c r="T200" s="68" t="n">
-        <v>0</v>
-      </c>
+      <c r="T200" s="67" t="n"/>
       <c r="U200" s="67" t="n"/>
       <c r="V200" s="67" t="n"/>
       <c r="W200" s="67" t="n"/>
@@ -54625,6 +55301,26 @@
       <c r="BK200" s="67" t="n"/>
       <c r="BL200" s="67" t="n"/>
     </row>
+    <row r="201">
+      <c r="A201" s="4" t="inlineStr">
+        <is>
+          <t>VTS</t>
+        </is>
+      </c>
+      <c r="B201" s="4" t="inlineStr">
+        <is>
+          <t>Vitesse Energy Inc</t>
+        </is>
+      </c>
+      <c r="C201" s="4" t="inlineStr">
+        <is>
+          <t>에너지</t>
+        </is>
+      </c>
+      <c r="T201" s="65" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -25033,7 +25033,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>※ SCHD 행: 금액은 USD, 수익률은 최근 4회 배당 ÷ 배당락일 종가. 0.06%는 Schwab 공시 운용보수(매매비용 별도)라 국내 ETF 실부담비용과 기준이 다릅니다.</t>
+          <t>※ SCHD 행: 금액은 USD, 수익률은 최근 4회 배당 ÷ 배당락일 종가. 0.06%는 Schwab 공시 총보수(펀드 내부 매매비용 미포함)라 국내 ETF 실부담비용과 기준이 다릅니다. 투자자가 내는 증권사 수수료·환전 비용은 양쪽 모두 제외.</t>
         </is>
       </c>
     </row>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1265,22 +1265,22 @@
   <commentList>
     <comment ref="C6" authorId="0" shapeId="0">
       <text>
-        <t>총보수 0.01% + 기타비용 0.05% + 매매·중개수수료 0.0434% (KOFIA 2026-08-31)</t>
+        <t>총보수 0.01% + 기타비용 0.05% + 매매·중개수수료 0.0464% (KOFIA 2026-09-30)</t>
       </text>
     </comment>
     <comment ref="C7" authorId="0" shapeId="0">
       <text>
-        <t>총보수 0.01% + 기타비용 0.06% + 매매·중개수수료 0.0998% (KOFIA 2026-08-31)</t>
+        <t>총보수 0.01% + 기타비용 0.06% + 매매·중개수수료 0.1011% (KOFIA 2026-09-30)</t>
       </text>
     </comment>
     <comment ref="C8" authorId="0" shapeId="0">
       <text>
-        <t>총보수 0.01% + 기타비용 0.06% + 매매·중개수수료 0.0781% (KOFIA 2026-08-31)</t>
+        <t>총보수 0.01% + 기타비용 0.06% + 매매·중개수수료 0.0824% (KOFIA 2026-09-30)</t>
       </text>
     </comment>
     <comment ref="C9" authorId="0" shapeId="0">
       <text>
-        <t>총보수 0.0099% + 기타비용 0.08% + 매매·중개수수료 0.0934% (KOFIA 2026-08-31)</t>
+        <t>총보수 0.0099% + 기타비용 0.07% + 매매·중개수수료 0.0959% (KOFIA 2026-09-30)</t>
       </text>
     </comment>
   </commentList>
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-10 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-12 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -24842,7 +24842,7 @@
         </is>
       </c>
       <c r="C6" s="51" t="n">
-        <v>0.001034</v>
+        <v>0.001064</v>
       </c>
       <c r="D6" s="33" t="inlineStr">
         <is>
@@ -24882,7 +24882,7 @@
         </is>
       </c>
       <c r="C7" s="51" t="n">
-        <v>0.001698</v>
+        <v>0.001711</v>
       </c>
       <c r="D7" s="33" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         </is>
       </c>
       <c r="C8" s="51" t="n">
-        <v>0.001481</v>
+        <v>0.001524</v>
       </c>
       <c r="D8" s="33" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         </is>
       </c>
       <c r="C9" s="51" t="n">
-        <v>0.001834</v>
+        <v>0.001759</v>
       </c>
       <c r="D9" s="33" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>※ 국내 ETF 실부담비용 = 총보수 + 기타비용 + 매매·중개수수료(+판매수수료), 금융투자협회 공시 2026-08-31 기준. 셀 메모에 항목별 금액.</t>
+          <t>※ 국내 ETF 실부담비용 = 총보수 + 기타비용 + 매매·중개수수료(+판매수수료), 금융투자협회 공시 2026-09-30 기준. 셀 메모에 항목별 금액.</t>
         </is>
       </c>
     </row>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-12 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-13 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -26215,11 +26215,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-08)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-09)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26316,7 +26316,7 @@
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.04686291</v>
+        <v>0.04621969</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -26370,25 +26370,25 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04345508</v>
+        <v>0.04337427</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>QUALCOMM</t>
+          <t>PROCTER &amp; GAMBLE</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>퀄컴</t>
+          <t>프록터앤드갬블</t>
         </is>
       </c>
       <c r="M6" s="7">
@@ -26428,25 +26428,25 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04310645</v>
+        <v>0.04289955</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>PROCTER &amp; GAMBLE</t>
+          <t>QUALCOMM</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>프록터앤드갬블</t>
+          <t>퀄컴</t>
         </is>
       </c>
       <c r="M7" s="7">
@@ -26486,25 +26486,25 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04212293</v>
+        <v>0.04253438</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CHEVRON</t>
+          <t>COCA-COLA</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>코카콜라</t>
         </is>
       </c>
       <c r="M8" s="7">
@@ -26544,25 +26544,25 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.04199263</v>
+        <v>0.04243566999999999</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>COCA-COLA</t>
+          <t>CHEVRON</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>코카콜라</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="M9" s="7">
@@ -26606,7 +26606,7 @@
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.04107964</v>
+        <v>0.04185615</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
@@ -26664,7 +26664,7 @@
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04040699</v>
+        <v>0.04009386</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
@@ -26722,7 +26722,7 @@
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.03993899</v>
+        <v>0.03958902</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03942468</v>
+        <v>0.03941473</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -26834,25 +26834,25 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.03841367</v>
+        <v>0.0385271</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>HOME DEPOT</t>
+          <t>ABBOTT LABORATORIES</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>홈디포</t>
+          <t>애보트</t>
         </is>
       </c>
       <c r="M14" s="7">
@@ -26882,25 +26882,25 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.03794233</v>
+        <v>0.03813983</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>ABBOTT LABORATORIES</t>
+          <t>HOME DEPOT</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>애보트</t>
+          <t>홈디포</t>
         </is>
       </c>
       <c r="M15" s="7">
@@ -26934,7 +26934,7 @@
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.0377258</v>
+        <v>0.03768319</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -26972,7 +26972,7 @@
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03490183</v>
+        <v>0.03560754</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -27010,7 +27010,7 @@
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03262227</v>
+        <v>0.03330342</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -27035,25 +27035,25 @@
     <row r="19">
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03079479</v>
+        <v>0.03030605</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>BRISTOL MYERS SQUIBB</t>
+          <t>ALTRIA GROUP INC</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>브리스톨마이어스스퀴브</t>
+          <t>알트리아</t>
         </is>
       </c>
       <c r="M19" s="7">
@@ -27069,25 +27069,25 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.03051986</v>
+        <v>0.02979081</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>ALTRIA GROUP INC</t>
+          <t>BRISTOL MYERS SQUIBB</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>알트리아</t>
+          <t>브리스톨마이어스스퀴브</t>
         </is>
       </c>
       <c r="M20" s="7">
@@ -27112,7 +27112,7 @@
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02743966</v>
+        <v>0.02755036</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -27150,7 +27150,7 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02639063</v>
+        <v>0.02633119</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02187585</v>
+        <v>0.02182185</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.01981677</v>
+        <v>0.01999572</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
@@ -27264,7 +27264,7 @@
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01864535</v>
+        <v>0.01853778</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01852519</v>
+        <v>0.0183329</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.0180704</v>
+        <v>0.01809509</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.01779382</v>
+        <v>0.01767205</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01484986</v>
+        <v>0.01496504</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -27454,7 +27454,7 @@
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01443447</v>
+        <v>0.01469193</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -27488,7 +27488,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01353674</v>
+        <v>0.01364071</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27513,7 +27513,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01215489</v>
+        <v>0.01190445</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01171074</v>
+        <v>0.0116733</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27568,7 +27568,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.009818249999999999</v>
+        <v>0.00981695</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.00848757</v>
+        <v>0.00848407</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.00827607</v>
+        <v>0.00831993</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.00669426</v>
+        <v>0.006701970000000001</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -27668,7 +27668,7 @@
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.00639543</v>
+        <v>0.00643539</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.00607187</v>
+        <v>0.00607153</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -27718,7 +27718,7 @@
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.00587245</v>
+        <v>0.00590588</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
@@ -27743,7 +27743,7 @@
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.00572298</v>
+        <v>0.00574028</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.00572055</v>
+        <v>0.005618499999999999</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.00532826</v>
+        <v>0.00532189</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27814,20 +27814,20 @@
     <row r="44">
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>DINO</t>
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00481132</v>
+        <v>0.0048129</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>BROADRIDGE FINANCIAL SOLUTIONS INC</t>
+          <t>HF SINCLAIR</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr"/>
@@ -27839,20 +27839,20 @@
     <row r="45">
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00478645</v>
+        <v>0.00480721</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>HF SINCLAIR</t>
+          <t>BROADRIDGE FINANCIAL SOLUTIONS INC</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr"/>
@@ -27868,7 +27868,7 @@
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.00475361</v>
+        <v>0.00474319</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -27893,7 +27893,7 @@
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00440205</v>
+        <v>0.00442888</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.00439755</v>
+        <v>0.0043629</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
@@ -27943,7 +27943,7 @@
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.00438552</v>
+        <v>0.00435788</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
@@ -27968,7 +27968,7 @@
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00409683</v>
+        <v>0.00415646</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.00253814</v>
+        <v>0.00258126</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28018,7 +28018,7 @@
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00252111</v>
+        <v>0.00251795</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
@@ -28043,7 +28043,7 @@
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00247576</v>
+        <v>0.00250375</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
@@ -28068,7 +28068,7 @@
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00226879</v>
+        <v>0.00224197</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -28093,7 +28093,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00216306</v>
+        <v>0.00214089</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28118,7 +28118,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00204651</v>
+        <v>0.00204087</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28143,7 +28143,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.0018663</v>
+        <v>0.00186367</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28168,7 +28168,7 @@
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.00152055</v>
+        <v>0.00153021</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
@@ -28193,7 +28193,7 @@
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00151452</v>
+        <v>0.00149316</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00146504</v>
+        <v>0.00147345</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -28239,20 +28239,20 @@
     <row r="61">
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00132875</v>
+        <v>0.00134565</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>VAIL RESORTS</t>
+          <t>MURPHY OIL CORP</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr"/>
@@ -28264,20 +28264,20 @@
     <row r="62">
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.0013268</v>
+        <v>0.00132723</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>MURPHY OIL CORP</t>
+          <t>VAIL RESORTS</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr"/>
@@ -28293,7 +28293,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.0011899</v>
+        <v>0.00117918</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00114609</v>
+        <v>0.00116572</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28343,7 +28343,7 @@
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.00107629</v>
+        <v>0.0010776</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -28368,7 +28368,7 @@
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.00102357</v>
+        <v>0.00101182</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
@@ -28389,20 +28389,20 @@
     <row r="67">
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>KFY</t>
+          <t>CWEN</t>
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.0009363900000000001</v>
+        <v>0.00093153</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>KORN FERRY</t>
+          <t>CLEARWAY ENERGY INC CLASS C</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr"/>
@@ -28414,20 +28414,20 @@
     <row r="68">
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>CWEN</t>
+          <t>KFY</t>
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.0009310200000000001</v>
+        <v>0.00092506</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>CLEARWAY ENERGY INC CLASS C</t>
+          <t>KORN FERRY</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr"/>
@@ -28443,7 +28443,7 @@
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00091457</v>
+        <v>0.00091434</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -28468,7 +28468,7 @@
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.00088438</v>
+        <v>0.0008758</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.00086883</v>
+        <v>0.0008741300000000001</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
@@ -28514,18 +28514,22 @@
     <row r="72">
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>GVMXX</t>
+          <t>APAM</t>
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.00069814</v>
+        <v>0.0005806</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>SSC GOVERNMENT MM GVMXX</t>
-        </is>
-      </c>
-      <c r="K72" s="6" t="inlineStr"/>
+          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="L72" s="6" t="inlineStr"/>
       <c r="M72" s="7">
         <f>IF(H72="","",IFERROR(VLOOKUP(K72,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28535,15 +28539,15 @@
     <row r="73">
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>APAM</t>
+          <t>BANR</t>
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.0006036699999999999</v>
+        <v>0.00057219</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
+          <t>BANNER CORP</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -28560,15 +28564,15 @@
     <row r="74">
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>OFG</t>
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.00057333</v>
+        <v>0.00054473</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>BANNER CORP</t>
+          <t>OFG BANCORP</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
@@ -28585,20 +28589,20 @@
     <row r="75">
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>OFG</t>
+          <t>IPAR</t>
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.00054572</v>
+        <v>0.0005197999999999999</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>OFG BANCORP</t>
+          <t>INTERPARFUMS INC</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -28610,15 +28614,15 @@
     <row r="76">
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>IPAR</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.0005233</v>
+        <v>0.0004995900000000001</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>INTERPARFUMS INC</t>
+          <t>MARZETTI</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
@@ -28639,7 +28643,7 @@
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.0005022399999999999</v>
+        <v>0.00049819</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -28664,7 +28668,7 @@
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.0005004100000000001</v>
+        <v>0.0004946</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
@@ -28685,20 +28689,20 @@
     <row r="79">
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>WU</t>
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00049391</v>
+        <v>0.00048395</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>MARZETTI</t>
+          <t>WESTERN UNION</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -28710,15 +28714,15 @@
     <row r="80">
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>WU</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00048848</v>
+        <v>0.00048145</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>WESTERN UNION</t>
+          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
@@ -28735,15 +28739,15 @@
     <row r="81">
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>GABC</t>
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.00048224</v>
+        <v>0.00046591</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
+          <t>GERMAN AMERICAN BANCORP INC</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
@@ -28760,20 +28764,20 @@
     <row r="82">
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>GABC</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00046319</v>
+        <v>0.00044001</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>GERMAN AMERICAN BANCORP INC</t>
+          <t>INSPERITY</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr"/>
@@ -28785,20 +28789,20 @@
     <row r="83">
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>STBA</t>
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.00044532</v>
+        <v>0.0004335399999999999</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>INSPERITY</t>
+          <t>S AND T BANCORP INC</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -28810,15 +28814,15 @@
     <row r="84">
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>STBA</t>
+          <t>NBHC</t>
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.00043367</v>
+        <v>0.00042875</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>S AND T BANCORP INC</t>
+          <t>NATIONAL BANK HOLDINGS CORP CLASS</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
@@ -28835,15 +28839,15 @@
     <row r="85">
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>NBHC</t>
+          <t>SRCE</t>
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00043071</v>
+        <v>0.00038317</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>NATIONAL BANK HOLDINGS CORP CLASS</t>
+          <t>1ST SOURCE</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
@@ -28860,15 +28864,15 @@
     <row r="86">
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>SRCE</t>
+          <t>LKFN</t>
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.00038251</v>
+        <v>0.00036137</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>1ST SOURCE</t>
+          <t>LAKELAND FINANCIAL CORP</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
@@ -28885,20 +28889,20 @@
     <row r="87">
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>LKFN</t>
+          <t>BKE</t>
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.00036163</v>
+        <v>0.00034331</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>LAKELAND FINANCIAL CORP</t>
+          <t>BUCKLE</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -28910,20 +28914,20 @@
     <row r="88">
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>BKE</t>
+          <t>FLO</t>
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00034677</v>
+        <v>0.00032477</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>BUCKLE</t>
+          <t>FLOWERS FOODS INC</t>
         </is>
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr"/>
@@ -28935,20 +28939,20 @@
     <row r="89">
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>FLO</t>
+          <t>PFBC</t>
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.00031481</v>
+        <v>0.00028576</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>FLOWERS FOODS INC</t>
+          <t>PREFERRED BANK</t>
         </is>
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -28960,20 +28964,20 @@
     <row r="90">
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>PFBC</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00028586</v>
+        <v>0.00025686</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
-          <t>PREFERRED BANK</t>
+          <t>WENDYS</t>
         </is>
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr"/>
@@ -28989,7 +28993,7 @@
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00025597</v>
+        <v>0.0002567</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
@@ -29010,22 +29014,18 @@
     <row r="92">
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>WEN</t>
+          <t>GVMXX</t>
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.00025556</v>
+        <v>0.00024435</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>WENDYS</t>
-        </is>
-      </c>
-      <c r="K92" s="6" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
+          <t>SSC GOVERNMENT MM GVMXX</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr"/>
       <c r="L92" s="6" t="inlineStr"/>
       <c r="M92" s="7">
         <f>IF(H92="","",IFERROR(VLOOKUP(K92,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29039,7 +29039,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.00023346</v>
+        <v>0.00023328</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00023183</v>
+        <v>0.00023229</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00020811</v>
+        <v>0.00020862</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.00020509</v>
+        <v>0.00020236</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
@@ -29139,7 +29139,7 @@
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.00020096</v>
+        <v>0.0002006</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -29164,7 +29164,7 @@
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.00019848</v>
+        <v>0.00019921</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.00016827</v>
+        <v>0.00016796</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29210,18 +29210,22 @@
     <row r="100">
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EBF</t>
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00013909</v>
+        <v>0.00013436</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>US DOLLAR</t>
-        </is>
-      </c>
-      <c r="K100" s="6" t="inlineStr"/>
+          <t>ENNIS INC</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
       <c r="L100" s="6" t="inlineStr"/>
       <c r="M100" s="7">
         <f>IF(H100="","",IFERROR(VLOOKUP(K100,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29231,22 +29235,18 @@
     <row r="101">
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>EBF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00013509</v>
+        <v>0.00012374</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>ENNIS INC</t>
-        </is>
-      </c>
-      <c r="K101" s="6" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
+          <t>US DOLLAR</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr"/>
       <c r="L101" s="6" t="inlineStr"/>
       <c r="M101" s="7">
         <f>IF(H101="","",IFERROR(VLOOKUP(K101,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29260,7 +29260,7 @@
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>0.00011563</v>
+        <v>0.00011731</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -29285,7 +29285,7 @@
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>0.00010387</v>
+        <v>0.00010297</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
@@ -29310,7 +29310,7 @@
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>9.005000000000001e-05</v>
+        <v>8.899e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-13 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-14 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -20053,7 +20053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F355"/>
+  <dimension ref="A1:F357"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22808,22 +22808,22 @@
     <row r="131">
       <c r="A131" s="46" t="inlineStr">
         <is>
-          <t>489250</t>
+          <t>402970</t>
         </is>
       </c>
       <c r="B131" s="33" t="inlineStr">
         <is>
-          <t>KODEX 미국배당다우존스</t>
+          <t>ACE 미국배당다우존스</t>
         </is>
       </c>
       <c r="C131" s="26" t="n">
-        <v>45547</v>
+        <v>46309</v>
       </c>
       <c r="D131" s="47" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E131" s="48" t="n">
-        <v>0.002954</v>
+        <v>0.002624</v>
       </c>
     </row>
     <row r="132">
@@ -22838,13 +22838,13 @@
         </is>
       </c>
       <c r="C132" s="26" t="n">
-        <v>45579</v>
+        <v>45547</v>
       </c>
       <c r="D132" s="47" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E132" s="48" t="n">
-        <v>0.003148</v>
+        <v>0.002954</v>
       </c>
     </row>
     <row r="133">
@@ -22859,13 +22859,13 @@
         </is>
       </c>
       <c r="C133" s="26" t="n">
-        <v>45610</v>
+        <v>45579</v>
       </c>
       <c r="D133" s="47" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E133" s="48" t="n">
-        <v>0.002509</v>
+        <v>0.003148</v>
       </c>
     </row>
     <row r="134">
@@ -22880,13 +22880,13 @@
         </is>
       </c>
       <c r="C134" s="26" t="n">
-        <v>45638</v>
+        <v>45610</v>
       </c>
       <c r="D134" s="47" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="E134" s="48" t="n">
-        <v>0.003647</v>
+        <v>0.002509</v>
       </c>
     </row>
     <row r="135">
@@ -22901,13 +22901,13 @@
         </is>
       </c>
       <c r="C135" s="26" t="n">
-        <v>45671</v>
+        <v>45638</v>
       </c>
       <c r="D135" s="47" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E135" s="48" t="n">
-        <v>0.003659</v>
+        <v>0.003647</v>
       </c>
     </row>
     <row r="136">
@@ -22922,13 +22922,13 @@
         </is>
       </c>
       <c r="C136" s="26" t="n">
-        <v>45701</v>
+        <v>45671</v>
       </c>
       <c r="D136" s="47" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="E136" s="48" t="n">
-        <v>0.002909</v>
+        <v>0.003659</v>
       </c>
     </row>
     <row r="137">
@@ -22943,13 +22943,13 @@
         </is>
       </c>
       <c r="C137" s="26" t="n">
-        <v>45729</v>
+        <v>45701</v>
       </c>
       <c r="D137" s="47" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E137" s="48" t="n">
-        <v>0.002634</v>
+        <v>0.002909</v>
       </c>
     </row>
     <row r="138">
@@ -22964,13 +22964,13 @@
         </is>
       </c>
       <c r="C138" s="26" t="n">
-        <v>45761</v>
+        <v>45729</v>
       </c>
       <c r="D138" s="47" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E138" s="48" t="n">
-        <v>0.003378</v>
+        <v>0.002634</v>
       </c>
     </row>
     <row r="139">
@@ -22985,13 +22985,13 @@
         </is>
       </c>
       <c r="C139" s="26" t="n">
-        <v>45791</v>
+        <v>45761</v>
       </c>
       <c r="D139" s="47" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E139" s="48" t="n">
-        <v>0.002356</v>
+        <v>0.003378</v>
       </c>
     </row>
     <row r="140">
@@ -23006,13 +23006,13 @@
         </is>
       </c>
       <c r="C140" s="26" t="n">
-        <v>45820</v>
+        <v>45791</v>
       </c>
       <c r="D140" s="47" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E140" s="48" t="n">
-        <v>0.00299</v>
+        <v>0.002356</v>
       </c>
     </row>
     <row r="141">
@@ -23027,13 +23027,13 @@
         </is>
       </c>
       <c r="C141" s="26" t="n">
-        <v>45852</v>
+        <v>45820</v>
       </c>
       <c r="D141" s="47" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E141" s="48" t="n">
-        <v>0.003007</v>
+        <v>0.00299</v>
       </c>
     </row>
     <row r="142">
@@ -23048,13 +23048,13 @@
         </is>
       </c>
       <c r="C142" s="26" t="n">
-        <v>45882</v>
+        <v>45852</v>
       </c>
       <c r="D142" s="47" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E142" s="48" t="n">
-        <v>0.002165</v>
+        <v>0.003007</v>
       </c>
     </row>
     <row r="143">
@@ -23069,13 +23069,13 @@
         </is>
       </c>
       <c r="C143" s="26" t="n">
-        <v>45912</v>
+        <v>45882</v>
       </c>
       <c r="D143" s="47" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E143" s="48" t="n">
-        <v>0.002688</v>
+        <v>0.002165</v>
       </c>
     </row>
     <row r="144">
@@ -23090,13 +23090,13 @@
         </is>
       </c>
       <c r="C144" s="26" t="n">
-        <v>45944</v>
+        <v>45912</v>
       </c>
       <c r="D144" s="47" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E144" s="48" t="n">
-        <v>0.002989</v>
+        <v>0.002688</v>
       </c>
     </row>
     <row r="145">
@@ -23111,13 +23111,13 @@
         </is>
       </c>
       <c r="C145" s="26" t="n">
-        <v>45974</v>
+        <v>45944</v>
       </c>
       <c r="D145" s="47" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="E145" s="48" t="n">
-        <v>0.001939</v>
+        <v>0.002989</v>
       </c>
     </row>
     <row r="146">
@@ -23132,13 +23132,13 @@
         </is>
       </c>
       <c r="C146" s="26" t="n">
-        <v>46003</v>
+        <v>45974</v>
       </c>
       <c r="D146" s="47" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E146" s="48" t="n">
-        <v>0.002966</v>
+        <v>0.001939</v>
       </c>
     </row>
     <row r="147">
@@ -23153,13 +23153,13 @@
         </is>
       </c>
       <c r="C147" s="26" t="n">
-        <v>46036</v>
+        <v>46003</v>
       </c>
       <c r="D147" s="47" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E147" s="48" t="n">
-        <v>0.002964</v>
+        <v>0.002966</v>
       </c>
     </row>
     <row r="148">
@@ -23174,13 +23174,13 @@
         </is>
       </c>
       <c r="C148" s="26" t="n">
-        <v>46065</v>
+        <v>46036</v>
       </c>
       <c r="D148" s="47" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="E148" s="48" t="n">
-        <v>0.00224</v>
+        <v>0.002964</v>
       </c>
     </row>
     <row r="149">
@@ -23195,13 +23195,13 @@
         </is>
       </c>
       <c r="C149" s="26" t="n">
-        <v>46093</v>
+        <v>46065</v>
       </c>
       <c r="D149" s="47" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E149" s="48" t="n">
-        <v>0.002589</v>
+        <v>0.00224</v>
       </c>
     </row>
     <row r="150">
@@ -23216,13 +23216,13 @@
         </is>
       </c>
       <c r="C150" s="26" t="n">
-        <v>46126</v>
+        <v>46093</v>
       </c>
       <c r="D150" s="47" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E150" s="48" t="n">
-        <v>0.002645</v>
+        <v>0.002589</v>
       </c>
     </row>
     <row r="151">
@@ -23237,13 +23237,13 @@
         </is>
       </c>
       <c r="C151" s="26" t="n">
-        <v>46156</v>
+        <v>46126</v>
       </c>
       <c r="D151" s="47" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E151" s="48" t="n">
-        <v>0.002016</v>
+        <v>0.002645</v>
       </c>
     </row>
     <row r="152">
@@ -23258,13 +23258,13 @@
         </is>
       </c>
       <c r="C152" s="26" t="n">
-        <v>46185</v>
+        <v>46156</v>
       </c>
       <c r="D152" s="47" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E152" s="48" t="n">
-        <v>0.002161</v>
+        <v>0.002016</v>
       </c>
     </row>
     <row r="153">
@@ -23279,13 +23279,13 @@
         </is>
       </c>
       <c r="C153" s="26" t="n">
-        <v>46217</v>
+        <v>46185</v>
       </c>
       <c r="D153" s="47" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="E153" s="48" t="n">
-        <v>0.003001</v>
+        <v>0.002161</v>
       </c>
     </row>
     <row r="154">
@@ -23300,13 +23300,13 @@
         </is>
       </c>
       <c r="C154" s="26" t="n">
-        <v>46247</v>
+        <v>46217</v>
       </c>
       <c r="D154" s="47" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E154" s="48" t="n">
-        <v>0.0028</v>
+        <v>0.003001</v>
       </c>
     </row>
     <row r="155">
@@ -23321,28 +23321,56 @@
         </is>
       </c>
       <c r="C155" s="26" t="n">
+        <v>46247</v>
+      </c>
+      <c r="D155" s="47" t="n">
+        <v>37</v>
+      </c>
+      <c r="E155" s="48" t="n">
+        <v>0.0028</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="46" t="inlineStr">
+        <is>
+          <t>489250</t>
+        </is>
+      </c>
+      <c r="B156" s="33" t="inlineStr">
+        <is>
+          <t>KODEX 미국배당다우존스</t>
+        </is>
+      </c>
+      <c r="C156" s="26" t="n">
         <v>46279</v>
       </c>
-      <c r="D155" s="47" t="n">
+      <c r="D156" s="47" t="n">
         <v>24</v>
       </c>
-      <c r="E155" s="48" t="n">
+      <c r="E156" s="48" t="n">
         <v>0.001924</v>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="46" t="n"/>
-      <c r="B156" s="33" t="n"/>
-      <c r="C156" s="26" t="n"/>
-      <c r="D156" s="47" t="n"/>
-      <c r="E156" s="48" t="n"/>
-    </row>
     <row r="157">
-      <c r="A157" s="46" t="n"/>
-      <c r="B157" s="33" t="n"/>
-      <c r="C157" s="26" t="n"/>
-      <c r="D157" s="47" t="n"/>
-      <c r="E157" s="48" t="n"/>
+      <c r="A157" s="46" t="inlineStr">
+        <is>
+          <t>489250</t>
+        </is>
+      </c>
+      <c r="B157" s="33" t="inlineStr">
+        <is>
+          <t>KODEX 미국배당다우존스</t>
+        </is>
+      </c>
+      <c r="C157" s="26" t="n">
+        <v>46309</v>
+      </c>
+      <c r="D157" s="47" t="n">
+        <v>37</v>
+      </c>
+      <c r="E157" s="48" t="n">
+        <v>0.003019</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="46" t="n"/>
@@ -24729,6 +24757,20 @@
       <c r="C355" s="26" t="n"/>
       <c r="D355" s="47" t="n"/>
       <c r="E355" s="48" t="n"/>
+    </row>
+    <row r="356">
+      <c r="A356" s="46" t="n"/>
+      <c r="B356" s="33" t="n"/>
+      <c r="C356" s="26" t="n"/>
+      <c r="D356" s="47" t="n"/>
+      <c r="E356" s="48" t="n"/>
+    </row>
+    <row r="357">
+      <c r="A357" s="46" t="n"/>
+      <c r="B357" s="33" t="n"/>
+      <c r="C357" s="26" t="n"/>
+      <c r="D357" s="47" t="n"/>
+      <c r="E357" s="48" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24770,7 +24812,7 @@
         </is>
       </c>
       <c r="B3" s="49" t="n">
-        <v>46295</v>
+        <v>46326</v>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
@@ -24850,23 +24892,23 @@
         </is>
       </c>
       <c r="E6" s="52">
-        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$355,국내SCHD형_분배!$A$2:$A$355,$B6,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$357,국내SCHD형_분배!$A$2:$A$357,$B6,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="F6" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,$B6,국내SCHD형_분배!$C$2:$C$355,E6)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B6,국내SCHD형_분배!$C$2:$C$357,E6)</f>
         <v/>
       </c>
       <c r="G6" s="45">
-        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$355,$B6,국내SCHD형_분배!$C$2:$C$355,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$357,$B6,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="H6" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,$B6,국내SCHD형_분배!$C$2:$C$355,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B6,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="I6" s="29">
-        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$355,국내SCHD형_분배!$A$2:$A$355,$B6,국내SCHD형_분배!$C$2:$C$355,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$357,국내SCHD형_분배!$A$2:$A$357,$B6,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
     </row>
@@ -24890,23 +24932,23 @@
         </is>
       </c>
       <c r="E7" s="52">
-        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$355,국내SCHD형_분배!$A$2:$A$355,$B7,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$357,국내SCHD형_분배!$A$2:$A$357,$B7,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="F7" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,$B7,국내SCHD형_분배!$C$2:$C$355,E7)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B7,국내SCHD형_분배!$C$2:$C$357,E7)</f>
         <v/>
       </c>
       <c r="G7" s="45">
-        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$355,$B7,국내SCHD형_분배!$C$2:$C$355,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$357,$B7,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="H7" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,$B7,국내SCHD형_분배!$C$2:$C$355,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B7,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="I7" s="29">
-        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$355,국내SCHD형_분배!$A$2:$A$355,$B7,국내SCHD형_분배!$C$2:$C$355,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$357,국내SCHD형_분배!$A$2:$A$357,$B7,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
     </row>
@@ -24930,23 +24972,23 @@
         </is>
       </c>
       <c r="E8" s="52">
-        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$355,국내SCHD형_분배!$A$2:$A$355,$B8,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$357,국내SCHD형_분배!$A$2:$A$357,$B8,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="F8" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,$B8,국내SCHD형_분배!$C$2:$C$355,E8)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B8,국내SCHD형_분배!$C$2:$C$357,E8)</f>
         <v/>
       </c>
       <c r="G8" s="45">
-        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$355,$B8,국내SCHD형_분배!$C$2:$C$355,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$357,$B8,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="H8" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,$B8,국내SCHD형_분배!$C$2:$C$355,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B8,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="I8" s="29">
-        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$355,국내SCHD형_분배!$A$2:$A$355,$B8,국내SCHD형_분배!$C$2:$C$355,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$357,국내SCHD형_분배!$A$2:$A$357,$B8,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
     </row>
@@ -24970,23 +25012,23 @@
         </is>
       </c>
       <c r="E9" s="52">
-        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$355,국내SCHD형_분배!$A$2:$A$355,$B9,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$357,국내SCHD형_분배!$A$2:$A$357,$B9,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="F9" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,$B9,국내SCHD형_분배!$C$2:$C$355,E9)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B9,국내SCHD형_분배!$C$2:$C$357,E9)</f>
         <v/>
       </c>
       <c r="G9" s="45">
-        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$355,$B9,국내SCHD형_분배!$C$2:$C$355,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$357,$B9,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="H9" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,$B9,국내SCHD형_분배!$C$2:$C$355,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B9,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="I9" s="29">
-        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$355,국내SCHD형_분배!$A$2:$A$355,$B9,국내SCHD형_분배!$C$2:$C$355,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$357,국내SCHD형_분배!$A$2:$A$357,$B9,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
     </row>
@@ -25121,19 +25163,19 @@
         <v/>
       </c>
       <c r="D17" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C17))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17))</f>
         <v/>
       </c>
       <c r="E17" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C17))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17))</f>
         <v/>
       </c>
       <c r="F17" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C17))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17))</f>
         <v/>
       </c>
       <c r="G17" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C17))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17))</f>
         <v/>
       </c>
       <c r="H17" s="28">
@@ -25159,19 +25201,19 @@
         <v/>
       </c>
       <c r="D18" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C18))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18))</f>
         <v/>
       </c>
       <c r="E18" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C18))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18))</f>
         <v/>
       </c>
       <c r="F18" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C18))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18))</f>
         <v/>
       </c>
       <c r="G18" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C18))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18))</f>
         <v/>
       </c>
       <c r="H18" s="28">
@@ -25197,19 +25239,19 @@
         <v/>
       </c>
       <c r="D19" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C19))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19))</f>
         <v/>
       </c>
       <c r="E19" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C19))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19))</f>
         <v/>
       </c>
       <c r="F19" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C19))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19))</f>
         <v/>
       </c>
       <c r="G19" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C19))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19))</f>
         <v/>
       </c>
       <c r="H19" s="28">
@@ -25235,19 +25277,19 @@
         <v/>
       </c>
       <c r="D20" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C20))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20))</f>
         <v/>
       </c>
       <c r="E20" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C20))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20))</f>
         <v/>
       </c>
       <c r="F20" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C20))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20))</f>
         <v/>
       </c>
       <c r="G20" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C20))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20))</f>
         <v/>
       </c>
       <c r="H20" s="28">
@@ -25273,19 +25315,19 @@
         <v/>
       </c>
       <c r="D21" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C21))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21))</f>
         <v/>
       </c>
       <c r="E21" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C21))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21))</f>
         <v/>
       </c>
       <c r="F21" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C21))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21))</f>
         <v/>
       </c>
       <c r="G21" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C21))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21))</f>
         <v/>
       </c>
       <c r="H21" s="28">
@@ -25311,19 +25353,19 @@
         <v/>
       </c>
       <c r="D22" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C22))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22))</f>
         <v/>
       </c>
       <c r="E22" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C22))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22))</f>
         <v/>
       </c>
       <c r="F22" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C22))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22))</f>
         <v/>
       </c>
       <c r="G22" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C22))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22))</f>
         <v/>
       </c>
       <c r="H22" s="28">
@@ -25349,19 +25391,19 @@
         <v/>
       </c>
       <c r="D23" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C23))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23))</f>
         <v/>
       </c>
       <c r="E23" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C23))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23))</f>
         <v/>
       </c>
       <c r="F23" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C23))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23))</f>
         <v/>
       </c>
       <c r="G23" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C23))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23))</f>
         <v/>
       </c>
       <c r="H23" s="28">
@@ -25387,19 +25429,19 @@
         <v/>
       </c>
       <c r="D24" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C24))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24))</f>
         <v/>
       </c>
       <c r="E24" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C24))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24))</f>
         <v/>
       </c>
       <c r="F24" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C24))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24))</f>
         <v/>
       </c>
       <c r="G24" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C24))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24))</f>
         <v/>
       </c>
       <c r="H24" s="28">
@@ -25425,19 +25467,19 @@
         <v/>
       </c>
       <c r="D25" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C25))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25))</f>
         <v/>
       </c>
       <c r="E25" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C25))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25))</f>
         <v/>
       </c>
       <c r="F25" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C25))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25))</f>
         <v/>
       </c>
       <c r="G25" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C25))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25))</f>
         <v/>
       </c>
       <c r="H25" s="28">
@@ -25463,19 +25505,19 @@
         <v/>
       </c>
       <c r="D26" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C26))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26))</f>
         <v/>
       </c>
       <c r="E26" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C26))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26))</f>
         <v/>
       </c>
       <c r="F26" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C26))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26))</f>
         <v/>
       </c>
       <c r="G26" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C26))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26))</f>
         <v/>
       </c>
       <c r="H26" s="28">
@@ -25501,19 +25543,19 @@
         <v/>
       </c>
       <c r="D27" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C27))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27))</f>
         <v/>
       </c>
       <c r="E27" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C27))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27))</f>
         <v/>
       </c>
       <c r="F27" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C27))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27))</f>
         <v/>
       </c>
       <c r="G27" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C27))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27))</f>
         <v/>
       </c>
       <c r="H27" s="28">
@@ -25539,19 +25581,19 @@
         <v/>
       </c>
       <c r="D28" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C28))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28))</f>
         <v/>
       </c>
       <c r="E28" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C28))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28))</f>
         <v/>
       </c>
       <c r="F28" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C28))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28))</f>
         <v/>
       </c>
       <c r="G28" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C28))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28))</f>
         <v/>
       </c>
       <c r="H28" s="28">
@@ -25577,19 +25619,19 @@
         <v/>
       </c>
       <c r="D29" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C29))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29))</f>
         <v/>
       </c>
       <c r="E29" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C29))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29))</f>
         <v/>
       </c>
       <c r="F29" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C29))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29))</f>
         <v/>
       </c>
       <c r="G29" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C29))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29))</f>
         <v/>
       </c>
       <c r="H29" s="28">
@@ -25615,19 +25657,19 @@
         <v/>
       </c>
       <c r="D30" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C30))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30))</f>
         <v/>
       </c>
       <c r="E30" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C30))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30))</f>
         <v/>
       </c>
       <c r="F30" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C30))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30))</f>
         <v/>
       </c>
       <c r="G30" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C30))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30))</f>
         <v/>
       </c>
       <c r="H30" s="28">
@@ -25653,19 +25695,19 @@
         <v/>
       </c>
       <c r="D31" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C31))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31))</f>
         <v/>
       </c>
       <c r="E31" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C31))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31))</f>
         <v/>
       </c>
       <c r="F31" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C31))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31))</f>
         <v/>
       </c>
       <c r="G31" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C31))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31))</f>
         <v/>
       </c>
       <c r="H31" s="28">
@@ -25691,19 +25733,19 @@
         <v/>
       </c>
       <c r="D32" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C32))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32))</f>
         <v/>
       </c>
       <c r="E32" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C32))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32))</f>
         <v/>
       </c>
       <c r="F32" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C32))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32))</f>
         <v/>
       </c>
       <c r="G32" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C32))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32))</f>
         <v/>
       </c>
       <c r="H32" s="28">
@@ -25729,19 +25771,19 @@
         <v/>
       </c>
       <c r="D33" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C33))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33))</f>
         <v/>
       </c>
       <c r="E33" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C33))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33))</f>
         <v/>
       </c>
       <c r="F33" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C33))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33))</f>
         <v/>
       </c>
       <c r="G33" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C33))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33))</f>
         <v/>
       </c>
       <c r="H33" s="28">
@@ -25767,19 +25809,19 @@
         <v/>
       </c>
       <c r="D34" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C34))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34))</f>
         <v/>
       </c>
       <c r="E34" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C34))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34))</f>
         <v/>
       </c>
       <c r="F34" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C34))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34))</f>
         <v/>
       </c>
       <c r="G34" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C34))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34))</f>
         <v/>
       </c>
       <c r="H34" s="28">
@@ -25805,19 +25847,19 @@
         <v/>
       </c>
       <c r="D35" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C35))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35))</f>
         <v/>
       </c>
       <c r="E35" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C35))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35))</f>
         <v/>
       </c>
       <c r="F35" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C35))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35))</f>
         <v/>
       </c>
       <c r="G35" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C35))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35))</f>
         <v/>
       </c>
       <c r="H35" s="28">
@@ -25843,19 +25885,19 @@
         <v/>
       </c>
       <c r="D36" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C36))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36))</f>
         <v/>
       </c>
       <c r="E36" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C36))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36))</f>
         <v/>
       </c>
       <c r="F36" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C36))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36))</f>
         <v/>
       </c>
       <c r="G36" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C36))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36))</f>
         <v/>
       </c>
       <c r="H36" s="28">
@@ -25881,19 +25923,19 @@
         <v/>
       </c>
       <c r="D37" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C37))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37))</f>
         <v/>
       </c>
       <c r="E37" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C37))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37))</f>
         <v/>
       </c>
       <c r="F37" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C37))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37))</f>
         <v/>
       </c>
       <c r="G37" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C37))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37))</f>
         <v/>
       </c>
       <c r="H37" s="28">
@@ -25919,19 +25961,19 @@
         <v/>
       </c>
       <c r="D38" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C38))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38))</f>
         <v/>
       </c>
       <c r="E38" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C38))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38))</f>
         <v/>
       </c>
       <c r="F38" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C38))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38))</f>
         <v/>
       </c>
       <c r="G38" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C38))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38))</f>
         <v/>
       </c>
       <c r="H38" s="28">
@@ -25957,19 +25999,19 @@
         <v/>
       </c>
       <c r="D39" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C39))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39))</f>
         <v/>
       </c>
       <c r="E39" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C39))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39))</f>
         <v/>
       </c>
       <c r="F39" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C39))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39))</f>
         <v/>
       </c>
       <c r="G39" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C39))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39))</f>
         <v/>
       </c>
       <c r="H39" s="28">
@@ -25995,19 +26037,19 @@
         <v/>
       </c>
       <c r="D40" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C40))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40))</f>
         <v/>
       </c>
       <c r="E40" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C40))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40))</f>
         <v/>
       </c>
       <c r="F40" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C40))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40))</f>
         <v/>
       </c>
       <c r="G40" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C40))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40))</f>
         <v/>
       </c>
       <c r="H40" s="28">
@@ -26033,19 +26075,19 @@
         <v/>
       </c>
       <c r="D41" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C41))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41))</f>
         <v/>
       </c>
       <c r="E41" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C41))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41))</f>
         <v/>
       </c>
       <c r="F41" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C41))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41))</f>
         <v/>
       </c>
       <c r="G41" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C41))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41))</f>
         <v/>
       </c>
       <c r="H41" s="28">
@@ -26071,19 +26113,19 @@
         <v/>
       </c>
       <c r="D42" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C42))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42))</f>
         <v/>
       </c>
       <c r="E42" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C42))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42))</f>
         <v/>
       </c>
       <c r="F42" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C42))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42))</f>
         <v/>
       </c>
       <c r="G42" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C42))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42))</f>
         <v/>
       </c>
       <c r="H42" s="28">
@@ -26109,19 +26151,19 @@
         <v/>
       </c>
       <c r="D43" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C43))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43))</f>
         <v/>
       </c>
       <c r="E43" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C43))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43))</f>
         <v/>
       </c>
       <c r="F43" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C43))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43))</f>
         <v/>
       </c>
       <c r="G43" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C43))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43))</f>
         <v/>
       </c>
       <c r="H43" s="28">
@@ -26147,19 +26189,19 @@
         <v/>
       </c>
       <c r="D44" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"458730",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C44))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44))</f>
         <v/>
       </c>
       <c r="E44" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"446720",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C44))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44))</f>
         <v/>
       </c>
       <c r="F44" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"402970",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C44))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44))</f>
         <v/>
       </c>
       <c r="G44" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$355,국내SCHD형_분배!$A$2:$A$355,"489250",국내SCHD형_분배!$C$2:$C$355,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$355,"&lt;="&amp;$C44))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44))</f>
         <v/>
       </c>
       <c r="H44" s="28">
@@ -26215,11 +26257,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-09)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-12)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26316,7 +26358,7 @@
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.04621969</v>
+        <v>0.04708691</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -26370,25 +26412,25 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04337427</v>
+        <v>0.04337273</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>PROCTER &amp; GAMBLE</t>
+          <t>QUALCOMM</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>프록터앤드갬블</t>
+          <t>퀄컴</t>
         </is>
       </c>
       <c r="M6" s="7">
@@ -26428,25 +26470,25 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04289955</v>
+        <v>0.04320501</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>QUALCOMM</t>
+          <t>PROCTER &amp; GAMBLE</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>퀄컴</t>
+          <t>프록터앤드갬블</t>
         </is>
       </c>
       <c r="M7" s="7">
@@ -26486,25 +26528,25 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04253438</v>
+        <v>0.0428515</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>COCA-COLA</t>
+          <t>CHEVRON</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>코카콜라</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="M8" s="7">
@@ -26544,15 +26586,15 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.04243566999999999</v>
+        <v>0.04274977</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CHEVRON</t>
+          <t>CONOCOPHILLIPS</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -26562,7 +26604,7 @@
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>코노코필립스</t>
         </is>
       </c>
       <c r="M9" s="7">
@@ -26602,25 +26644,25 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.04185615</v>
+        <v>0.04256384</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CONOCOPHILLIPS</t>
+          <t>COCA-COLA</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>코노코필립스</t>
+          <t>코카콜라</t>
         </is>
       </c>
       <c r="M10" s="7">
@@ -26660,15 +26702,15 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04009386</v>
+        <v>0.0393964</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>MERCK &amp; CO INC</t>
+          <t>UNITEDHEALTH GROUP</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -26678,7 +26720,7 @@
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>머크</t>
+          <t>유나이티드헬스</t>
         </is>
       </c>
       <c r="M11" s="7">
@@ -26718,15 +26760,15 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.03958902</v>
+        <v>0.03902534</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>UNITEDHEALTH GROUP</t>
+          <t>MERCK &amp; CO INC</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -26736,7 +26778,7 @@
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>유나이티드헬스</t>
+          <t>머크</t>
         </is>
       </c>
       <c r="M12" s="7">
@@ -26780,7 +26822,7 @@
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03941473</v>
+        <v>0.03885666</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -26838,7 +26880,7 @@
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.0385271</v>
+        <v>0.03871495</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
@@ -26886,7 +26928,7 @@
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.03813983</v>
+        <v>0.03846246</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
@@ -26934,7 +26976,7 @@
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.03768319</v>
+        <v>0.03775924</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -26972,7 +27014,7 @@
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03560754</v>
+        <v>0.03612815</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -27010,7 +27052,7 @@
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03330342</v>
+        <v>0.03300566</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -27039,7 +27081,7 @@
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03030605</v>
+        <v>0.03017718</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -27073,7 +27115,7 @@
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.02979081</v>
+        <v>0.02923612</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
@@ -27112,7 +27154,7 @@
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02755036</v>
+        <v>0.02768124</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -27150,7 +27192,7 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02633119</v>
+        <v>0.02585262</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -27188,7 +27230,7 @@
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02182185</v>
+        <v>0.02084944</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -27226,7 +27268,7 @@
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.01999572</v>
+        <v>0.02029086</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
@@ -27264,7 +27306,7 @@
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01853778</v>
+        <v>0.01866352</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -27302,7 +27344,7 @@
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.0183329</v>
+        <v>0.01828045</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
@@ -27340,7 +27382,7 @@
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.01809509</v>
+        <v>0.01793923</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -27378,7 +27420,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.01767205</v>
+        <v>0.01743452</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27416,7 +27458,7 @@
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01496504</v>
+        <v>0.01490483</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -27454,7 +27496,7 @@
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01469193</v>
+        <v>0.01486642</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -27488,7 +27530,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01364071</v>
+        <v>0.01394894</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27513,7 +27555,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01190445</v>
+        <v>0.01196931</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27543,7 +27585,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.0116733</v>
+        <v>0.01150248</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27568,7 +27610,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.00981695</v>
+        <v>0.01012723</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27593,7 +27635,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.00848407</v>
+        <v>0.008589940000000001</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27618,7 +27660,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.00831993</v>
+        <v>0.008255780000000001</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27643,7 +27685,7 @@
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.006701970000000001</v>
+        <v>0.00653969</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -27668,7 +27710,7 @@
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.00643539</v>
+        <v>0.00642043</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
@@ -27693,7 +27735,7 @@
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.00607153</v>
+        <v>0.006024939999999999</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -27714,20 +27756,20 @@
     <row r="40">
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.00590588</v>
+        <v>0.005895559999999999</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>REGIONS FINANCIAL</t>
+          <t>DARDEN RESTAURANTS INC</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr"/>
@@ -27739,20 +27781,20 @@
     <row r="41">
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.00574028</v>
+        <v>0.00581152</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>DARDEN RESTAURANTS INC</t>
+          <t>REGIONS FINANCIAL</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr"/>
@@ -27768,7 +27810,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.005618499999999999</v>
+        <v>0.005462320000000001</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27793,7 +27835,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.00532189</v>
+        <v>0.00529678</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27818,7 +27860,7 @@
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.0048129</v>
+        <v>0.00500685</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -27843,7 +27885,7 @@
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00480721</v>
+        <v>0.00485186</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -27868,7 +27910,7 @@
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.00474319</v>
+        <v>0.00475145</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -27889,20 +27931,20 @@
     <row r="47">
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00442888</v>
+        <v>0.00439892</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>GENERAL MILLS INC</t>
+          <t>BEST BUY</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr"/>
@@ -27914,20 +27956,20 @@
     <row r="48">
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.0043629</v>
+        <v>0.00432773</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>BEST BUY</t>
+          <t>EAST WEST BANCORP</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
@@ -27939,20 +27981,20 @@
     <row r="49">
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.00435788</v>
+        <v>0.00429871</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>EAST WEST BANCORP</t>
+          <t>GENERAL MILLS INC</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
@@ -27968,7 +28010,7 @@
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00415646</v>
+        <v>0.00424809</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
@@ -27993,7 +28035,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.00258126</v>
+        <v>0.00262032</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28018,7 +28060,7 @@
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00251795</v>
+        <v>0.00252232</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
@@ -28043,7 +28085,7 @@
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00250375</v>
+        <v>0.00251094</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
@@ -28068,7 +28110,7 @@
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00224197</v>
+        <v>0.00219546</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -28093,7 +28135,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00214089</v>
+        <v>0.00213924</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28118,7 +28160,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00204087</v>
+        <v>0.00201503</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28143,7 +28185,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.00186367</v>
+        <v>0.00191453</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28164,20 +28206,20 @@
     <row r="58">
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.00153021</v>
+        <v>0.00152937</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>MACYS INC</t>
+          <t>MSC INDUSTRIAL CLASS A</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr"/>
@@ -28189,20 +28231,20 @@
     <row r="59">
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00149316</v>
+        <v>0.00150924</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>MSC INDUSTRIAL CLASS A</t>
+          <t>MACYS INC</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr"/>
@@ -28218,7 +28260,7 @@
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00147345</v>
+        <v>0.00150688</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -28239,20 +28281,20 @@
     <row r="61">
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00134565</v>
+        <v>0.00137352</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>MURPHY OIL CORP</t>
+          <t>VAIL RESORTS</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr"/>
@@ -28264,20 +28306,20 @@
     <row r="62">
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.00132723</v>
+        <v>0.0013302</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>VAIL RESORTS</t>
+          <t>MURPHY OIL CORP</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr"/>
@@ -28293,7 +28335,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.00117918</v>
+        <v>0.00117587</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28318,7 +28360,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00116572</v>
+        <v>0.00115621</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28343,7 +28385,7 @@
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.0010776</v>
+        <v>0.00105213</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -28368,7 +28410,7 @@
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.00101182</v>
+        <v>0.0009912600000000001</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
@@ -28389,20 +28431,20 @@
     <row r="67">
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>CWEN</t>
+          <t>KFY</t>
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.00093153</v>
+        <v>0.00093461</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>CLEARWAY ENERGY INC CLASS C</t>
+          <t>KORN FERRY</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr"/>
@@ -28414,20 +28456,20 @@
     <row r="68">
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>KFY</t>
+          <t>CWEN</t>
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.00092506</v>
+        <v>0.0009285499999999999</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>KORN FERRY</t>
+          <t>CLEARWAY ENERGY INC CLASS C</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr"/>
@@ -28443,7 +28485,7 @@
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00091434</v>
+        <v>0.00090456</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -28464,20 +28506,20 @@
     <row r="70">
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>PAG</t>
+          <t>RHI</t>
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.0008758</v>
+        <v>0.00088303</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
+          <t>ROBERT HALF INC</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr"/>
@@ -28489,20 +28531,20 @@
     <row r="71">
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>RHI</t>
+          <t>PAG</t>
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.0008741300000000001</v>
+        <v>0.00087774</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>ROBERT HALF INC</t>
+          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr"/>
@@ -28514,15 +28556,15 @@
     <row r="72">
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>APAM</t>
+          <t>BANR</t>
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.0005806</v>
+        <v>0.00056875</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
+          <t>BANNER CORP</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
@@ -28539,15 +28581,15 @@
     <row r="73">
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>APAM</t>
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.00057219</v>
+        <v>0.00055786</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>BANNER CORP</t>
+          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -28568,7 +28610,7 @@
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.00054473</v>
+        <v>0.0005433700000000001</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
@@ -28593,7 +28635,7 @@
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.0005197999999999999</v>
+        <v>0.00052626</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
@@ -28618,7 +28660,7 @@
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.0004995900000000001</v>
+        <v>0.00049683</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
@@ -28643,7 +28685,7 @@
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.00049819</v>
+        <v>0.0004948600000000001</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -28668,7 +28710,7 @@
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.0004946</v>
+        <v>0.0004922300000000001</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
@@ -28689,15 +28731,15 @@
     <row r="79">
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>WU</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00048395</v>
+        <v>0.00048252</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>WESTERN UNION</t>
+          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
@@ -28714,15 +28756,15 @@
     <row r="80">
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>WU</t>
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00048145</v>
+        <v>0.00048178</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
+          <t>WESTERN UNION</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
@@ -28743,7 +28785,7 @@
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.00046591</v>
+        <v>0.0004638</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
@@ -28768,7 +28810,7 @@
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00044001</v>
+        <v>0.00044671</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
@@ -28793,7 +28835,7 @@
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.0004335399999999999</v>
+        <v>0.00042943</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
@@ -28818,7 +28860,7 @@
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.00042875</v>
+        <v>0.000422</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
@@ -28843,7 +28885,7 @@
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00038317</v>
+        <v>0.00037917</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
@@ -28868,7 +28910,7 @@
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.00036137</v>
+        <v>0.000358</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
@@ -28893,7 +28935,7 @@
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.00034331</v>
+        <v>0.00034581</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
@@ -28918,7 +28960,7 @@
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00032477</v>
+        <v>0.00032008</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -28943,7 +28985,7 @@
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.00028576</v>
+        <v>0.00028273</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -28968,7 +29010,7 @@
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00025686</v>
+        <v>0.00025775</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
@@ -28993,7 +29035,7 @@
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.0002567</v>
+        <v>0.00025635</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
@@ -29018,7 +29060,7 @@
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.00024435</v>
+        <v>0.00024348</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -29039,7 +29081,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.00023328</v>
+        <v>0.00023104</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29064,7 +29106,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00023229</v>
+        <v>0.00023021</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29089,7 +29131,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00020862</v>
+        <v>0.00020731</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29110,15 +29152,15 @@
     <row r="96">
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>VRTS</t>
+          <t>THFF</t>
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.00020236</v>
+        <v>0.00019795</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>VIRTUS INVESTMENT PARTNERS</t>
+          <t>FIRST FINANCIAL CORPORATION CORP</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
@@ -29135,15 +29177,15 @@
     <row r="97">
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>IBCP</t>
+          <t>VRTS</t>
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.0002006</v>
+        <v>0.00019782</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>INDEPENDENT BANK CORP</t>
+          <t>VIRTUS INVESTMENT PARTNERS</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
@@ -29160,15 +29202,15 @@
     <row r="98">
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>THFF</t>
+          <t>IBCP</t>
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.00019921</v>
+        <v>0.00019772</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
-          <t>FIRST FINANCIAL CORPORATION CORP</t>
+          <t>INDEPENDENT BANK CORP</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr">
@@ -29189,7 +29231,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.00016796</v>
+        <v>0.0001667</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29214,7 +29256,7 @@
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00013436</v>
+        <v>0.00013458</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
@@ -29239,7 +29281,7 @@
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00012374</v>
+        <v>0.0001233</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
@@ -29260,7 +29302,7 @@
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>0.00011731</v>
+        <v>0.00011551</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -29285,7 +29327,7 @@
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>0.00010297</v>
+        <v>0.00010322</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
@@ -29310,7 +29352,7 @@
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>8.899e-05</v>
+        <v>9.028e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-14 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-15 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>출처: Yahoo Finance (종가: 주식분할 반영·배당 미조정 / adj: 배당 재투자 반영 수정주가) · 기준일 2026-10-08 · 3:1 분할(2024-10-11) 반영 가격</t>
+          <t>출처: Yahoo Finance (종가: 주식분할 반영·배당 미조정 / adj: 배당 재투자 반영 수정주가) · 기준일 2026-10-14 · 3:1 분할(2024-10-11) 반영 가격</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
         <v>10.9</v>
       </c>
       <c r="D22" s="77" t="n">
-        <v>7.1037</v>
+        <v>7.1038</v>
       </c>
       <c r="E22" s="58">
         <f>C22/C10-1</f>
@@ -7179,7 +7179,7 @@
         <v>14.1033</v>
       </c>
       <c r="D61" s="77" t="n">
-        <v>10.0736</v>
+        <v>10.0735</v>
       </c>
       <c r="E61" s="58">
         <f>C61/C49-1</f>
@@ -7995,7 +7995,7 @@
         <v>17.9833</v>
       </c>
       <c r="D95" s="77" t="n">
-        <v>13.9255</v>
+        <v>13.9254</v>
       </c>
       <c r="E95" s="58">
         <f>C95/C83-1</f>
@@ -8067,7 +8067,7 @@
         <v>18.5067</v>
       </c>
       <c r="D98" s="77" t="n">
-        <v>14.4594</v>
+        <v>14.4593</v>
       </c>
       <c r="E98" s="58">
         <f>C98/C86-1</f>
@@ -8187,7 +8187,7 @@
         <v>14.9933</v>
       </c>
       <c r="D103" s="77" t="n">
-        <v>11.9339</v>
+        <v>11.9338</v>
       </c>
       <c r="E103" s="58">
         <f>C103/C91-1</f>
@@ -10077,13 +10077,13 @@
         </is>
       </c>
       <c r="B182" s="56" t="n">
-        <v>46303</v>
+        <v>46309</v>
       </c>
       <c r="C182" s="76" t="n">
-        <v>33.15</v>
+        <v>33.71</v>
       </c>
       <c r="D182" s="77" t="n">
-        <v>33.15</v>
+        <v>33.71</v>
       </c>
       <c r="E182" s="58">
         <f>C182/C170-1</f>
@@ -11996,11 +11996,11 @@
         </is>
       </c>
       <c r="B34" s="19" t="n">
-        <v>0.0337</v>
+        <v>0.033</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-07 기준 · 최근 30일 순투자수익(보수 차감) 연 환산</t>
+          <t>2026-10-13 기준 · 최근 30일 순투자수익(보수 차감) 연 환산</t>
         </is>
       </c>
     </row>
@@ -12011,11 +12011,11 @@
         </is>
       </c>
       <c r="B35" s="19" t="n">
-        <v>0.03</v>
+        <v>0.0324</v>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2026-08-31 기준 · 최근 12개월 분배금 ÷ 기준일 NAV</t>
+          <t>2026-09-30 기준 · 최근 12개월 분배금 ÷ 기준일 NAV</t>
         </is>
       </c>
     </row>
@@ -26257,11 +26257,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-12)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-13)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26358,7 +26358,7 @@
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.04708691</v>
+        <v>0.04543222</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -26412,25 +26412,25 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04337273</v>
+        <v>0.04373126</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>QUALCOMM</t>
+          <t>PROCTER &amp; GAMBLE</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>퀄컴</t>
+          <t>프록터앤드갬블</t>
         </is>
       </c>
       <c r="M6" s="7">
@@ -26470,25 +26470,25 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04320501</v>
+        <v>0.04324578</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>PROCTER &amp; GAMBLE</t>
+          <t>CHEVRON</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>프록터앤드갬블</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="M7" s="7">
@@ -26528,25 +26528,25 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.0428515</v>
+        <v>0.04290234</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CHEVRON</t>
+          <t>COCA-COLA</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>코카콜라</t>
         </is>
       </c>
       <c r="M8" s="7">
@@ -26590,7 +26590,7 @@
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.04274977</v>
+        <v>0.04273807</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -26644,25 +26644,25 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.04256384</v>
+        <v>0.04189318</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>COCA-COLA</t>
+          <t>QUALCOMM</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>코카콜라</t>
+          <t>퀄컴</t>
         </is>
       </c>
       <c r="M10" s="7">
@@ -26706,7 +26706,7 @@
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.0393964</v>
+        <v>0.04083037</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.03902534</v>
+        <v>0.04008606999999999</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03885666</v>
+        <v>0.03968896</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.03871495</v>
+        <v>0.03844721</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.03846246</v>
+        <v>0.03826877</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.03775924</v>
+        <v>0.03794526</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03612815</v>
+        <v>0.03648387</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03300566</v>
+        <v>0.03287692</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03017718</v>
+        <v>0.03051891</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.02923612</v>
+        <v>0.03026495</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02768124</v>
+        <v>0.02783255</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02585262</v>
+        <v>0.02650835</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -27226,25 +27226,25 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02084944</v>
+        <v>0.02021378</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>BLACKSTONE</t>
+          <t>EOG RESOURCES</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>블랙스톤</t>
+          <t>EOG 리소시스</t>
         </is>
       </c>
       <c r="M23" s="7">
@@ -27264,25 +27264,25 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.02029086</v>
+        <v>0.01992557</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>EOG RESOURCES</t>
+          <t>BLACKSTONE</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>EOG 리소시스</t>
+          <t>블랙스톤</t>
         </is>
       </c>
       <c r="M24" s="7">
@@ -27306,7 +27306,7 @@
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01866352</v>
+        <v>0.01862003</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01828045</v>
+        <v>0.01799412</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.01793923</v>
+        <v>0.0179383</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.01743452</v>
+        <v>0.01763029</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01490483</v>
+        <v>0.01491347</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01486642</v>
+        <v>0.01448985</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01394894</v>
+        <v>0.01372431</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01196931</v>
+        <v>0.01179604</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01150248</v>
+        <v>0.01125153</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.01012723</v>
+        <v>0.01007502</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.008589940000000001</v>
+        <v>0.008670310000000001</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.008255780000000001</v>
+        <v>0.008263100000000001</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27681,15 +27681,15 @@
     <row r="37">
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>ARES</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.00653969</v>
+        <v>0.00639322</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>ARES MANAGEMENT CLASS A</t>
+          <t>CINCINNATI FINANCIAL</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -27706,15 +27706,15 @@
     <row r="38">
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>ARES</t>
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.00642043</v>
+        <v>0.00629656</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>CINCINNATI FINANCIAL</t>
+          <t>ARES MANAGEMENT CLASS A</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.006024939999999999</v>
+        <v>0.00600621</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.005895559999999999</v>
+        <v>0.00591714</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.00581152</v>
+        <v>0.0057256</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.005462320000000001</v>
+        <v>0.00531119</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.00529678</v>
+        <v>0.00522323</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00500685</v>
+        <v>0.00493398</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00485186</v>
+        <v>0.00479629</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.00475145</v>
+        <v>0.00469995</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00439892</v>
+        <v>0.00440964</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -27956,20 +27956,20 @@
     <row r="48">
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.00432773</v>
+        <v>0.00429147</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>EAST WEST BANCORP</t>
+          <t>GENERAL MILLS INC</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
@@ -27981,20 +27981,20 @@
     <row r="49">
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.00429871</v>
+        <v>0.00426734</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>GENERAL MILLS INC</t>
+          <t>EAST WEST BANCORP</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
@@ -28010,7 +28010,7 @@
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00424809</v>
+        <v>0.00414792</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.00262032</v>
+        <v>0.00262495</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28056,15 +28056,15 @@
     <row r="52">
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>FNF</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00252232</v>
+        <v>0.00250235</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>FIDELITY NATIONAL FINANCIAL INC</t>
+          <t>AMERICAN FINANCIAL GROUP</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
@@ -28081,15 +28081,15 @@
     <row r="53">
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>FNF</t>
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00251094</v>
+        <v>0.00249803</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>AMERICAN FINANCIAL GROUP</t>
+          <t>FIDELITY NATIONAL FINANCIAL INC</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
@@ -28110,7 +28110,7 @@
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00219546</v>
+        <v>0.00215943</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00213924</v>
+        <v>0.00213145</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00201503</v>
+        <v>0.00197997</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.00191453</v>
+        <v>0.00189248</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.00152937</v>
+        <v>0.00151817</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00150924</v>
+        <v>0.00148962</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00150688</v>
+        <v>0.00148646</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00137352</v>
+        <v>0.00133141</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
@@ -28310,11 +28310,11 @@
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.0013302</v>
+        <v>0.00132548</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>MURPHY OIL CORP</t>
+          <t>MURPHY OIL</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
@@ -28335,7 +28335,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.00117587</v>
+        <v>0.00116183</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00115621</v>
+        <v>0.00114039</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.00105213</v>
+        <v>0.00100205</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.0009912600000000001</v>
+        <v>0.0009784500000000001</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.00093461</v>
+        <v>0.00091228</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.0009285499999999999</v>
+        <v>0.00089414</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00090456</v>
+        <v>0.00088975</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.00088303</v>
+        <v>0.00087711</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.00087774</v>
+        <v>0.00086469</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.00056875</v>
+        <v>0.00056073</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.00055786</v>
+        <v>0.00056072</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.0005433700000000001</v>
+        <v>0.00053834</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.00052626</v>
+        <v>0.00052264</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.00049683</v>
+        <v>0.0004929299999999999</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.0004948600000000001</v>
+        <v>0.00049172</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -28706,15 +28706,15 @@
     <row r="78">
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>CNS</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.0004922300000000001</v>
+        <v>0.00047649</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>COHEN &amp; STEERS INC</t>
+          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr">
@@ -28731,15 +28731,15 @@
     <row r="79">
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>WU</t>
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00048252</v>
+        <v>0.00047286</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
+          <t>WESTERN UNION</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
@@ -28756,15 +28756,15 @@
     <row r="80">
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>WU</t>
+          <t>CNS</t>
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00048178</v>
+        <v>0.00046962</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>WESTERN UNION</t>
+          <t>COHEN &amp; STEERS INC</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
@@ -28785,7 +28785,7 @@
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.0004638</v>
+        <v>0.00045944</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00044671</v>
+        <v>0.00044368</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.00042943</v>
+        <v>0.00042389</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.000422</v>
+        <v>0.00041283</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00037917</v>
+        <v>0.00037643</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.000358</v>
+        <v>0.0003552</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.00034581</v>
+        <v>0.00034336</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00032008</v>
+        <v>0.00031676</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.00028273</v>
+        <v>0.00027823</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -29006,22 +29006,18 @@
     <row r="90">
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>WEN</t>
+          <t>GVMXX</t>
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00025775</v>
+        <v>0.00026386</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
-          <t>WENDYS</t>
-        </is>
-      </c>
-      <c r="K90" s="6" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
+          <t>SSC GOVERNMENT MM GVMXX</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr"/>
       <c r="L90" s="6" t="inlineStr"/>
       <c r="M90" s="7">
         <f>IF(H90="","",IFERROR(VLOOKUP(K90,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29031,20 +29027,20 @@
     <row r="91">
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>CNA</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00025635</v>
+        <v>0.00025869</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>CNA FINANCIAL CORP</t>
+          <t>WENDYS</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -29056,18 +29052,22 @@
     <row r="92">
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>GVMXX</t>
+          <t>CNA</t>
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.00024348</v>
+        <v>0.00025645</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>SSC GOVERNMENT MM GVMXX</t>
-        </is>
-      </c>
-      <c r="K92" s="6" t="inlineStr"/>
+          <t>CNA FINANCIAL CORP</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="L92" s="6" t="inlineStr"/>
       <c r="M92" s="7">
         <f>IF(H92="","",IFERROR(VLOOKUP(K92,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29081,7 +29081,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.00023104</v>
+        <v>0.00022735</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00023021</v>
+        <v>0.00022486</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00020731</v>
+        <v>0.00020461</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.00019795</v>
+        <v>0.0001949</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
@@ -29177,15 +29177,15 @@
     <row r="97">
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>VRTS</t>
+          <t>IBCP</t>
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.00019782</v>
+        <v>0.00019338</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>VIRTUS INVESTMENT PARTNERS</t>
+          <t>INDEPENDENT BANK CORP</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
@@ -29202,15 +29202,15 @@
     <row r="98">
       <c r="H98" s="6" t="inlineStr">
         <is>
-          <t>IBCP</t>
+          <t>VRTS</t>
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.00019772</v>
+        <v>0.00018735</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
-          <t>INDEPENDENT BANK CORP</t>
+          <t>VIRTUS INVESTMENT PARTNERS</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr">
@@ -29231,7 +29231,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.0001667</v>
+        <v>0.00016664</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00013458</v>
+        <v>0.00013372</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
@@ -29277,18 +29277,22 @@
     <row r="101">
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>AMSF</t>
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.0001233</v>
+        <v>0.00011426</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>US DOLLAR</t>
-        </is>
-      </c>
-      <c r="K101" s="6" t="inlineStr"/>
+          <t>AMERISAFE INC</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="L101" s="6" t="inlineStr"/>
       <c r="M101" s="7">
         <f>IF(H101="","",IFERROR(VLOOKUP(K101,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29298,22 +29302,18 @@
     <row r="102">
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>0.00011551</v>
+        <v>0.00010633</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>AMERISAFE INC</t>
-        </is>
-      </c>
-      <c r="K102" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+          <t>US DOLLAR</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr"/>
       <c r="L102" s="6" t="inlineStr"/>
       <c r="M102" s="7">
         <f>IF(H102="","",IFERROR(VLOOKUP(K102,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29327,7 +29327,7 @@
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>0.00010322</v>
+        <v>0.0001003</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>9.028e-05</v>
+        <v>9.043999999999999e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-15 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-16 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -26257,11 +26257,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-13)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-14)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26358,7 +26358,7 @@
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.04543222</v>
+        <v>0.04468937999999999</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04373126</v>
+        <v>0.04340403</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -26470,25 +26470,25 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04324578</v>
+        <v>0.04282148</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CHEVRON</t>
+          <t>QUALCOMM</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>퀄컴</t>
         </is>
       </c>
       <c r="M7" s="7">
@@ -26532,7 +26532,7 @@
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04290234</v>
+        <v>0.04253392</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
@@ -26586,15 +26586,15 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.04273807</v>
+        <v>0.0422479</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CONOCOPHILLIPS</t>
+          <t>CHEVRON</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>코노코필립스</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="M9" s="7">
@@ -26644,25 +26644,25 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.04189318</v>
+        <v>0.04208859</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>QUALCOMM</t>
+          <t>CONOCOPHILLIPS</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>퀄컴</t>
+          <t>코노코필립스</t>
         </is>
       </c>
       <c r="M10" s="7">
@@ -26706,7 +26706,7 @@
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04083037</v>
+        <v>0.04151081</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
@@ -26760,15 +26760,15 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.04008606999999999</v>
+        <v>0.03998357</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>MERCK &amp; CO INC</t>
+          <t>AMGEN INC</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -26778,7 +26778,7 @@
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>머크</t>
+          <t>암젠</t>
         </is>
       </c>
       <c r="M12" s="7">
@@ -26818,25 +26818,25 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03968896</v>
+        <v>0.03947982</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>AMGEN INC</t>
+          <t>HOME DEPOT</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>암젠</t>
+          <t>홈디포</t>
         </is>
       </c>
       <c r="M13" s="7">
@@ -26876,15 +26876,15 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.03844721</v>
+        <v>0.0390603</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>ABBOTT LABORATORIES</t>
+          <t>MERCK &amp; CO INC</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>애보트</t>
+          <t>머크</t>
         </is>
       </c>
       <c r="M14" s="7">
@@ -26924,25 +26924,25 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.03826877</v>
+        <v>0.03865739</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>HOME DEPOT</t>
+          <t>ABBOTT LABORATORIES</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>홈디포</t>
+          <t>애보트</t>
         </is>
       </c>
       <c r="M15" s="7">
@@ -26976,7 +26976,7 @@
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.03794526</v>
+        <v>0.03727104000000001</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03648387</v>
+        <v>0.03606784</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03287692</v>
+        <v>0.03402327</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -27077,25 +27077,25 @@
     <row r="19">
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03051891</v>
+        <v>0.03058469</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>ALTRIA GROUP INC</t>
+          <t>BRISTOL MYERS SQUIBB</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>알트리아</t>
+          <t>브리스톨마이어스스퀴브</t>
         </is>
       </c>
       <c r="M19" s="7">
@@ -27111,25 +27111,25 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.03026495</v>
+        <v>0.03047754</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>BRISTOL MYERS SQUIBB</t>
+          <t>ALTRIA GROUP INC</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>브리스톨마이어스스퀴브</t>
+          <t>알트리아</t>
         </is>
       </c>
       <c r="M20" s="7">
@@ -27154,7 +27154,7 @@
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02783255</v>
+        <v>0.02805097</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02650835</v>
+        <v>0.02674044</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -27226,25 +27226,25 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02021378</v>
+        <v>0.020262</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>EOG RESOURCES</t>
+          <t>BLACKSTONE</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>EOG 리소시스</t>
+          <t>블랙스톤</t>
         </is>
       </c>
       <c r="M23" s="7">
@@ -27264,25 +27264,25 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.01992557</v>
+        <v>0.01978869</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>BLACKSTONE</t>
+          <t>EOG RESOURCES</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>블랙스톤</t>
+          <t>EOG 리소시스</t>
         </is>
       </c>
       <c r="M24" s="7">
@@ -27306,7 +27306,7 @@
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01862003</v>
+        <v>0.01904589</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -27340,25 +27340,25 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01799412</v>
+        <v>0.01812146</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UNITED PARCEL SERVICE INC CLASS B</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="M26" s="7">
@@ -27378,25 +27378,25 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.0179383</v>
+        <v>0.01774558</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>UNITED PARCEL SERVICE INC CLASS B</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="M27" s="7">
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.01763029</v>
+        <v>0.0175853</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01491347</v>
+        <v>0.01429052</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01448985</v>
+        <v>0.01412538</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01372431</v>
+        <v>0.01338901</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01179604</v>
+        <v>0.01191851</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01125153</v>
+        <v>0.01128739</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.01007502</v>
+        <v>0.00988002</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.008670310000000001</v>
+        <v>0.00876598</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.008263100000000001</v>
+        <v>0.00855563</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.00639322</v>
+        <v>0.00634401</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.00629656</v>
+        <v>0.006312809999999999</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.00600621</v>
+        <v>0.00610059</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.00591714</v>
+        <v>0.00601476</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.0057256</v>
+        <v>0.005751309999999999</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.00531119</v>
+        <v>0.00534525</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.00522323</v>
+        <v>0.00524784</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27856,20 +27856,20 @@
     <row r="44">
       <c r="H44" s="6" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00493398</v>
+        <v>0.00490861</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>HF SINCLAIR</t>
+          <t>BROADRIDGE FINANCIAL SOLUTIONS INC</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr"/>
@@ -27881,20 +27881,20 @@
     <row r="45">
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>BR</t>
+          <t>DINO</t>
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00479629</v>
+        <v>0.00476564</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>BROADRIDGE FINANCIAL SOLUTIONS INC</t>
+          <t>HF SINCLAIR</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr"/>
@@ -27910,7 +27910,7 @@
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.00469995</v>
+        <v>0.00467906</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00440964</v>
+        <v>0.00460948</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.00429147</v>
+        <v>0.00434622</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.00426734</v>
+        <v>0.00427679</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00414792</v>
+        <v>0.00409034</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.00262495</v>
+        <v>0.00263491</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28056,15 +28056,15 @@
     <row r="52">
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>FNF</t>
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00250235</v>
+        <v>0.00249708</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>AMERICAN FINANCIAL GROUP</t>
+          <t>FIDELITY NATIONAL FINANCIAL INC</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
@@ -28081,15 +28081,15 @@
     <row r="53">
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>FNF</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00249803</v>
+        <v>0.00247659</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>FIDELITY NATIONAL FINANCIAL INC</t>
+          <t>AMERICAN FINANCIAL GROUP</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
@@ -28110,7 +28110,7 @@
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00215943</v>
+        <v>0.00221391</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00213145</v>
+        <v>0.00212235</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00197997</v>
+        <v>0.00200018</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.00189248</v>
+        <v>0.00190962</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28206,20 +28206,20 @@
     <row r="58">
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.00151817</v>
+        <v>0.00157333</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>MSC INDUSTRIAL CLASS A</t>
+          <t>MACYS INC</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr"/>
@@ -28231,20 +28231,20 @@
     <row r="59">
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00148962</v>
+        <v>0.00152493</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>MACYS INC</t>
+          <t>ERIE INDEMNITY CLASS A</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr"/>
@@ -28256,20 +28256,20 @@
     <row r="60">
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00148646</v>
+        <v>0.00148023</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>ERIE INDEMNITY CLASS A</t>
+          <t>MSC INDUSTRIAL CLASS A</t>
         </is>
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr"/>
@@ -28285,7 +28285,7 @@
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00133141</v>
+        <v>0.00134771</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.00132548</v>
+        <v>0.00132896</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.00116183</v>
+        <v>0.0011802</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00114039</v>
+        <v>0.00115072</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.00100205</v>
+        <v>0.00101025</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.0009784500000000001</v>
+        <v>0.0009951999999999999</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
@@ -28431,20 +28431,20 @@
     <row r="67">
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>KFY</t>
+          <t>PAG</t>
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.00091228</v>
+        <v>0.00093075</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>KORN FERRY</t>
+          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr"/>
@@ -28456,20 +28456,20 @@
     <row r="68">
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>CWEN</t>
+          <t>KFY</t>
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.00089414</v>
+        <v>0.00092899</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>CLEARWAY ENERGY INC CLASS C</t>
+          <t>KORN FERRY</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr"/>
@@ -28485,7 +28485,7 @@
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00088975</v>
+        <v>0.00089978</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -28506,20 +28506,20 @@
     <row r="70">
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>RHI</t>
+          <t>CWEN</t>
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.00087711</v>
+        <v>0.00089479</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>ROBERT HALF INC</t>
+          <t>CLEARWAY ENERGY INC CLASS C</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr"/>
@@ -28531,20 +28531,20 @@
     <row r="71">
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>PAG</t>
+          <t>RHI</t>
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.00086469</v>
+        <v>0.00085287</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
+          <t>ROBERT HALF INC</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr"/>
@@ -28556,15 +28556,15 @@
     <row r="72">
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>APAM</t>
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.00056073</v>
+        <v>0.00057239</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>BANNER CORP</t>
+          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
@@ -28581,15 +28581,15 @@
     <row r="73">
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>APAM</t>
+          <t>BANR</t>
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.00056072</v>
+        <v>0.00056285</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
+          <t>BANNER CORP</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -28610,7 +28610,7 @@
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.00053834</v>
+        <v>0.00054509</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.00052264</v>
+        <v>0.0005197800000000001</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.0004929299999999999</v>
+        <v>0.00049706</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.00049172</v>
+        <v>0.00048956</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -28706,15 +28706,15 @@
     <row r="78">
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>CNS</t>
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.00047649</v>
+        <v>0.00048258</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
+          <t>COHEN &amp; STEERS INC</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr">
@@ -28735,7 +28735,7 @@
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00047286</v>
+        <v>0.0004816</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
@@ -28756,15 +28756,15 @@
     <row r="80">
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>CNS</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00046962</v>
+        <v>0.0004767699999999999</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>COHEN &amp; STEERS INC</t>
+          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
@@ -28785,7 +28785,7 @@
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.00045944</v>
+        <v>0.0004612900000000001</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00044368</v>
+        <v>0.00044961</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.00042389</v>
+        <v>0.00042413</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.00041283</v>
+        <v>0.0004150100000000001</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00037643</v>
+        <v>0.00037781</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.0003552</v>
+        <v>0.00035679</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
@@ -28935,7 +28935,7 @@
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.00034336</v>
+        <v>0.00035411</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00031676</v>
+        <v>0.00032116</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -28985,7 +28985,7 @@
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.00027823</v>
+        <v>0.00027948</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -29006,18 +29006,22 @@
     <row r="90">
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>GVMXX</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00026386</v>
+        <v>0.00026618</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
-          <t>SSC GOVERNMENT MM GVMXX</t>
-        </is>
-      </c>
-      <c r="K90" s="6" t="inlineStr"/>
+          <t>WENDYS</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
       <c r="L90" s="6" t="inlineStr"/>
       <c r="M90" s="7">
         <f>IF(H90="","",IFERROR(VLOOKUP(K90,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29027,22 +29031,18 @@
     <row r="91">
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>WEN</t>
+          <t>GVMXX</t>
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00025869</v>
+        <v>0.00025601</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>WENDYS</t>
-        </is>
-      </c>
-      <c r="K91" s="6" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
+          <t>SSC GOVERNMENT MM GVMXX</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr"/>
       <c r="L91" s="6" t="inlineStr"/>
       <c r="M91" s="7">
         <f>IF(H91="","",IFERROR(VLOOKUP(K91,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.00025645</v>
+        <v>0.00025402</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.00022735</v>
+        <v>0.00022923</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00022486</v>
+        <v>0.00022568</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00020461</v>
+        <v>0.00020443</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.0001949</v>
+        <v>0.00019465</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.00019338</v>
+        <v>0.00019417</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.00018735</v>
+        <v>0.00018591</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.00016664</v>
+        <v>0.00016554</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00013372</v>
+        <v>0.00013261</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00011426</v>
+        <v>0.00011484</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>0.00010633</v>
+        <v>0.00011285</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>0.0001003</v>
+        <v>0.00010068</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>9.043999999999999e-05</v>
+        <v>9.577e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-16 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-17 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -26261,7 +26261,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-14)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← Schwab 공식 보유종목 CSV 기준일. 매일 자동으로 최신 파일을 받습니다.</t>
         </is>
       </c>
     </row>
@@ -26358,7 +26358,7 @@
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.04468937999999999</v>
+        <v>0.04468282000000001</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04340403</v>
+        <v>0.04339762999999999</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04282148</v>
+        <v>0.04281518</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04253392</v>
+        <v>0.04252766</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.0422479</v>
+        <v>0.0422417</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -26648,7 +26648,7 @@
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.04208859</v>
+        <v>0.0420824</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04151081</v>
+        <v>0.04150475</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.03998357</v>
+        <v>0.03997775</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03947982</v>
+        <v>0.03947407</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.0390603</v>
+        <v>0.03905457</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.03865739</v>
+        <v>0.0386517</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.03727104000000001</v>
+        <v>0.03726557</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03606784</v>
+        <v>0.03606252</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03402327</v>
+        <v>0.03401827</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03058469</v>
+        <v>0.03058018</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.03047754</v>
+        <v>0.03047305</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02805097</v>
+        <v>0.02804684</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02674044</v>
+        <v>0.02673655</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.020262</v>
+        <v>0.02025903</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.01978869</v>
+        <v>0.01978579</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01904589</v>
+        <v>0.01904309</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01812146</v>
+        <v>0.01811879</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.01774558</v>
+        <v>0.01774296</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.0175853</v>
+        <v>0.01758271</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01429052</v>
+        <v>0.01428842</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01412538</v>
+        <v>0.0141233</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01338901</v>
+        <v>0.01338705</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01191851</v>
+        <v>0.01191675</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01128739</v>
+        <v>0.01128573</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.00988002</v>
+        <v>0.00987858</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.00876598</v>
+        <v>0.0087647</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.00855563</v>
+        <v>0.00855439</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.00634401</v>
+        <v>0.00634309</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.006312809999999999</v>
+        <v>0.00631188</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.00610059</v>
+        <v>0.00609971</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.00601476</v>
+        <v>0.00601391</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.005751309999999999</v>
+        <v>0.00575046</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.00534525</v>
+        <v>0.00534448</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.00524784</v>
+        <v>0.005247089999999999</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00490861</v>
+        <v>0.00490793</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00476564</v>
+        <v>0.00476494</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.00467906</v>
+        <v>0.00467843</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00460948</v>
+        <v>0.00460881</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.00434622</v>
+        <v>0.00434558</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.00427679</v>
+        <v>0.00427618</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00409034</v>
+        <v>0.00408974</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.00263491</v>
+        <v>0.00263459</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00249708</v>
+        <v>0.00249672</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00247659</v>
+        <v>0.00247625</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00221391</v>
+        <v>0.00221359</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00212235</v>
+        <v>0.00212205</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00200018</v>
+        <v>0.00199989</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.00190962</v>
+        <v>0.00190934</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.00157333</v>
+        <v>0.0015731</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00152493</v>
+        <v>0.00152475</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00148023</v>
+        <v>0.00148002</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00134771</v>
+        <v>0.00134755</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.00132896</v>
+        <v>0.00132877</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.0011802</v>
+        <v>0.00118004</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00115072</v>
+        <v>0.00115056</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.00101025</v>
+        <v>0.0010101</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.0009951999999999999</v>
+        <v>0.00099507</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.00093075</v>
+        <v>0.0009306399999999999</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.00092899</v>
+        <v>0.00092886</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00089978</v>
+        <v>0.00089965</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.00089479</v>
+        <v>0.00089466</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.00085287</v>
+        <v>0.0008527400000000001</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.00057239</v>
+        <v>0.0005723099999999999</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.00056285</v>
+        <v>0.00056277</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.00054509</v>
+        <v>0.00054501</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.0005197800000000001</v>
+        <v>0.00051972</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.00049706</v>
+        <v>0.00049699</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.00048956</v>
+        <v>0.00048952</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.00048258</v>
+        <v>0.00048252</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.0004816</v>
+        <v>0.00048153</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.0004767699999999999</v>
+        <v>0.00047674</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.0004612900000000001</v>
+        <v>0.00046123</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00044961</v>
+        <v>0.00044955</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.00042413</v>
+        <v>0.00042408</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.0004150100000000001</v>
+        <v>0.00041495</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
@@ -28881,22 +28881,18 @@
     <row r="85">
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>SRCE</t>
+          <t>GVMXX</t>
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00037781</v>
+        <v>0.00039536</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>1ST SOURCE</t>
-        </is>
-      </c>
-      <c r="K85" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+          <t>SSC GOVERNMENT MM GVMXX</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr"/>
       <c r="L85" s="6" t="inlineStr"/>
       <c r="M85" s="7">
         <f>IF(H85="","",IFERROR(VLOOKUP(K85,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28906,15 +28902,15 @@
     <row r="86">
       <c r="H86" s="6" t="inlineStr">
         <is>
-          <t>LKFN</t>
+          <t>SRCE</t>
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.00035679</v>
+        <v>0.00037776</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>LAKELAND FINANCIAL CORP</t>
+          <t>1ST SOURCE</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
@@ -28931,20 +28927,20 @@
     <row r="87">
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>BKE</t>
+          <t>LKFN</t>
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.00035411</v>
+        <v>0.00035674</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>BUCKLE</t>
+          <t>LAKELAND FINANCIAL CORP</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -28956,20 +28952,20 @@
     <row r="88">
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>FLO</t>
+          <t>BKE</t>
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00032116</v>
+        <v>0.00035406</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>FLOWERS FOODS INC</t>
+          <t>BUCKLE</t>
         </is>
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr"/>
@@ -28981,20 +28977,20 @@
     <row r="89">
       <c r="H89" s="6" t="inlineStr">
         <is>
-          <t>PFBC</t>
+          <t>FLO</t>
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.00027948</v>
+        <v>0.00032111</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>PREFERRED BANK</t>
+          <t>FLOWERS FOODS INC</t>
         </is>
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -29006,20 +29002,20 @@
     <row r="90">
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>WEN</t>
+          <t>PFBC</t>
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00026618</v>
+        <v>0.00027945</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
-          <t>WENDYS</t>
+          <t>PREFERRED BANK</t>
         </is>
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr"/>
@@ -29031,18 +29027,22 @@
     <row r="91">
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>GVMXX</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00025601</v>
+        <v>0.00026614</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>SSC GOVERNMENT MM GVMXX</t>
-        </is>
-      </c>
-      <c r="K91" s="6" t="inlineStr"/>
+          <t>WENDYS</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
       <c r="L91" s="6" t="inlineStr"/>
       <c r="M91" s="7">
         <f>IF(H91="","",IFERROR(VLOOKUP(K91,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.00025402</v>
+        <v>0.00025398</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.00022923</v>
+        <v>0.0002292</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00022568</v>
+        <v>0.00022565</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00020443</v>
+        <v>0.00020441</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.00019465</v>
+        <v>0.00019463</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.00019417</v>
+        <v>0.00019415</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.00018591</v>
+        <v>0.0001859</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.00016554</v>
+        <v>0.00016553</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00013261</v>
+        <v>0.00013259</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
@@ -29277,22 +29277,18 @@
     <row r="101">
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00011484</v>
+        <v>0.00011947</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>AMERISAFE INC</t>
-        </is>
-      </c>
-      <c r="K101" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+          <t>US DOLLAR</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr"/>
       <c r="L101" s="6" t="inlineStr"/>
       <c r="M101" s="7">
         <f>IF(H101="","",IFERROR(VLOOKUP(K101,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29302,18 +29298,22 @@
     <row r="102">
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>AMSF</t>
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>0.00011285</v>
+        <v>0.00011483</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>US DOLLAR</t>
-        </is>
-      </c>
-      <c r="K102" s="6" t="inlineStr"/>
+          <t>AMERISAFE INC</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="L102" s="6" t="inlineStr"/>
       <c r="M102" s="7">
         <f>IF(H102="","",IFERROR(VLOOKUP(K102,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29327,7 +29327,7 @@
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>0.00010068</v>
+        <v>0.00010067</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>9.577e-05</v>
+        <v>9.575999999999999e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-17 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-18 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -26257,11 +26257,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← Schwab 공식 보유종목 CSV 기준일. 매일 자동으로 최신 파일을 받습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-15)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26358,7 +26358,7 @@
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.04468282000000001</v>
+        <v>0.04393346</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04339762999999999</v>
+        <v>0.04369979</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -26470,25 +26470,25 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04281518</v>
+        <v>0.04318054</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>QUALCOMM</t>
+          <t>CONOCOPHILLIPS</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>퀄컴</t>
+          <t>코노코필립스</t>
         </is>
       </c>
       <c r="M7" s="7">
@@ -26532,7 +26532,7 @@
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04252766</v>
+        <v>0.04308552</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.0422417</v>
+        <v>0.04301387</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -26644,25 +26644,25 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.0420824</v>
+        <v>0.04100069000000001</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CONOCOPHILLIPS</t>
+          <t>QUALCOMM</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>코노코필립스</t>
+          <t>퀄컴</t>
         </is>
       </c>
       <c r="M10" s="7">
@@ -26706,7 +26706,7 @@
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04150475</v>
+        <v>0.04066751</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.03997775</v>
+        <v>0.03954183</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03947407</v>
+        <v>0.03935936</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.03905457</v>
+        <v>0.03896919</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.0386517</v>
+        <v>0.03844334</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.03726557</v>
+        <v>0.03788657</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03606252</v>
+        <v>0.03611073</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03401827</v>
+        <v>0.03448176</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -27077,25 +27077,25 @@
     <row r="19">
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03058018</v>
+        <v>0.03076834</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>BRISTOL MYERS SQUIBB</t>
+          <t>ALTRIA GROUP INC</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>브리스톨마이어스스퀴브</t>
+          <t>알트리아</t>
         </is>
       </c>
       <c r="M19" s="7">
@@ -27111,25 +27111,25 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.03047305</v>
+        <v>0.0299435</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>ALTRIA GROUP INC</t>
+          <t>BRISTOL MYERS SQUIBB</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>알트리아</t>
+          <t>브리스톨마이어스스퀴브</t>
         </is>
       </c>
       <c r="M20" s="7">
@@ -27154,7 +27154,7 @@
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02804684</v>
+        <v>0.02815654</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02673655</v>
+        <v>0.02750829</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -27226,25 +27226,25 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02025903</v>
+        <v>0.02033334</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>BLACKSTONE</t>
+          <t>EOG RESOURCES</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>블랙스톤</t>
+          <t>EOG 리소시스</t>
         </is>
       </c>
       <c r="M23" s="7">
@@ -27264,25 +27264,25 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.01978579</v>
+        <v>0.01963252</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>EOG RESOURCES</t>
+          <t>BLACKSTONE</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>EOG 리소시스</t>
+          <t>블랙스톤</t>
         </is>
       </c>
       <c r="M24" s="7">
@@ -27306,7 +27306,7 @@
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01904309</v>
+        <v>0.01901539</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -27340,25 +27340,25 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01811879</v>
+        <v>0.01802343</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>UNITED PARCEL SERVICE INC CLASS B</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="M26" s="7">
@@ -27378,25 +27378,25 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.01774296</v>
+        <v>0.0179207</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UNITED PARCEL SERVICE INC CLASS B</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="M27" s="7">
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.01758271</v>
+        <v>0.01718883</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27454,27 +27454,23 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01428842</v>
+        <v>0.01443041</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>FASTENAL</t>
+          <t>ONEOK</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>패스널</t>
-        </is>
-      </c>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr"/>
       <c r="M29" s="7">
         <f>IF(H29="","",IFERROR(VLOOKUP(K29,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
         <v/>
@@ -27492,23 +27488,27 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.0141233</v>
+        <v>0.01436311</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>ONEOK</t>
+          <t>FASTENAL</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="L30" s="6" t="inlineStr"/>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>패스널</t>
+        </is>
+      </c>
       <c r="M30" s="7">
         <f>IF(H30="","",IFERROR(VLOOKUP(K30,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
         <v/>
@@ -27530,7 +27530,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01338705</v>
+        <v>0.01369032</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01191675</v>
+        <v>0.01194409</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01128573</v>
+        <v>0.01120687</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.00987858</v>
+        <v>0.00976781</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.0087647</v>
+        <v>0.00876676</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.00855439</v>
+        <v>0.008613619999999999</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.00634309</v>
+        <v>0.00644801</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.00631188</v>
+        <v>0.006168590000000001</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.00609971</v>
+        <v>0.00613186</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.00601391</v>
+        <v>0.00602634</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.00575046</v>
+        <v>0.00573727</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.00534448</v>
+        <v>0.005284100000000001</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.005247089999999999</v>
+        <v>0.00520119</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00490793</v>
+        <v>0.00489968</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00476494</v>
+        <v>0.00475214</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.00467843</v>
+        <v>0.0046609</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00460881</v>
+        <v>0.00449997</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.00434558</v>
+        <v>0.0043463</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
@@ -27985,7 +27985,7 @@
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.00427618</v>
+        <v>0.00426545</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
@@ -28010,7 +28010,7 @@
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00408974</v>
+        <v>0.00422458</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.00263459</v>
+        <v>0.00258379</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28056,15 +28056,15 @@
     <row r="52">
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>FNF</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00249672</v>
+        <v>0.00251532</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>FIDELITY NATIONAL FINANCIAL INC</t>
+          <t>AMERICAN FINANCIAL GROUP</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
@@ -28081,15 +28081,15 @@
     <row r="53">
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>FNF</t>
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00247625</v>
+        <v>0.0025014</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>AMERICAN FINANCIAL GROUP</t>
+          <t>FIDELITY NATIONAL FINANCIAL INC</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
@@ -28110,7 +28110,7 @@
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00221359</v>
+        <v>0.00219017</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00212205</v>
+        <v>0.00216031</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00199989</v>
+        <v>0.00197196</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.00190934</v>
+        <v>0.00189573</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.0015731</v>
+        <v>0.00154731</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00152475</v>
+        <v>0.00154533</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00148002</v>
+        <v>0.0014655</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -28281,20 +28281,20 @@
     <row r="61">
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00134755</v>
+        <v>0.00138152</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>VAIL RESORTS</t>
+          <t>MURPHY OIL</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr"/>
@@ -28306,20 +28306,20 @@
     <row r="62">
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.00132877</v>
+        <v>0.00132055</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>MURPHY OIL</t>
+          <t>VAIL RESORTS</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr"/>
@@ -28335,7 +28335,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.00118004</v>
+        <v>0.0011709</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00115056</v>
+        <v>0.00114904</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.0010101</v>
+        <v>0.00098869</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.00099507</v>
+        <v>0.00097828</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.0009306399999999999</v>
+        <v>0.0009256000000000001</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.00092886</v>
+        <v>0.0009221300000000001</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00089965</v>
+        <v>0.00089464</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.00089466</v>
+        <v>0.0008871700000000001</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.0008527400000000001</v>
+        <v>0.00081987</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
@@ -28556,15 +28556,15 @@
     <row r="72">
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>APAM</t>
+          <t>BANR</t>
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.0005723099999999999</v>
+        <v>0.0005605299999999999</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
+          <t>BANNER CORP</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
@@ -28581,15 +28581,15 @@
     <row r="73">
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>APAM</t>
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.00056277</v>
+        <v>0.00055993</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>BANNER CORP</t>
+          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -28610,7 +28610,7 @@
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.00054501</v>
+        <v>0.00054628</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.00051972</v>
+        <v>0.00051849</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.00049699</v>
+        <v>0.00049944</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.00048952</v>
+        <v>0.00048849</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.00048252</v>
+        <v>0.00048348</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00048153</v>
+        <v>0.00047337</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00047674</v>
+        <v>0.00046806</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.00046123</v>
+        <v>0.00046152</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00044955</v>
+        <v>0.00045132</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.00042408</v>
+        <v>0.00042364</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.00041495</v>
+        <v>0.00041385</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00039536</v>
+        <v>0.00039244</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.00037776</v>
+        <v>0.00037642</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.00035674</v>
+        <v>0.00035466</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00035406</v>
+        <v>0.00035092</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.00032111</v>
+        <v>0.00031822</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00027945</v>
+        <v>0.00027958</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00026614</v>
+        <v>0.00026418</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.00025398</v>
+        <v>0.00025525</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.0002292</v>
+        <v>0.0002299</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00022565</v>
+        <v>0.00022529</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00020441</v>
+        <v>0.00020373</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29152,15 +29152,15 @@
     <row r="96">
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>THFF</t>
+          <t>IBCP</t>
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.00019463</v>
+        <v>0.00019441</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>FIRST FINANCIAL CORPORATION CORP</t>
+          <t>INDEPENDENT BANK CORP</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
@@ -29177,15 +29177,15 @@
     <row r="97">
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>IBCP</t>
+          <t>THFF</t>
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.00019415</v>
+        <v>0.0001943</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>INDEPENDENT BANK CORP</t>
+          <t>FIRST FINANCIAL CORPORATION CORP</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
@@ -29206,7 +29206,7 @@
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.0001859</v>
+        <v>0.00018458</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.00016553</v>
+        <v>0.00016498</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00013259</v>
+        <v>0.00013126</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00011947</v>
+        <v>0.00011859</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
@@ -29302,7 +29302,7 @@
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>0.00011483</v>
+        <v>0.00011494</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>0.00010067</v>
+        <v>9.831e-05</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>9.575999999999999e-05</v>
+        <v>9.007e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-18 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-20 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -26257,11 +26257,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-15)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-16)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26358,7 +26358,7 @@
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.04393346</v>
+        <v>0.04404334000000001</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -26416,7 +26416,7 @@
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04369979</v>
+        <v>0.04340455000000001</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -26470,15 +26470,15 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04318054</v>
+        <v>0.04305399000000001</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CONOCOPHILLIPS</t>
+          <t>CHEVRON</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -26488,7 +26488,7 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>코노코필립스</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="M7" s="7">
@@ -26532,7 +26532,7 @@
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04308552</v>
+        <v>0.04302386</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
@@ -26586,15 +26586,15 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.04301387</v>
+        <v>0.04296461</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CHEVRON</t>
+          <t>CONOCOPHILLIPS</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -26604,7 +26604,7 @@
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>코노코필립스</t>
         </is>
       </c>
       <c r="M9" s="7">
@@ -26648,7 +26648,7 @@
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.04100069000000001</v>
+        <v>0.0414919</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04066751</v>
+        <v>0.04137204</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
@@ -26760,25 +26760,25 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.03954183</v>
+        <v>0.03953678</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>AMGEN INC</t>
+          <t>HOME DEPOT</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>암젠</t>
+          <t>홈디포</t>
         </is>
       </c>
       <c r="M12" s="7">
@@ -26818,25 +26818,25 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03935936</v>
+        <v>0.03899518</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>HOME DEPOT</t>
+          <t>AMGEN INC</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>홈디포</t>
+          <t>암젠</t>
         </is>
       </c>
       <c r="M13" s="7">
@@ -26876,25 +26876,25 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.03896919</v>
+        <v>0.03862823</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>MERCK &amp; CO INC</t>
+          <t>PEPSICO</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>머크</t>
+          <t>펩시코</t>
         </is>
       </c>
       <c r="M14" s="7">
@@ -26924,15 +26924,15 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.03844334</v>
+        <v>0.0384916</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>ABBOTT LABORATORIES</t>
+          <t>MERCK &amp; CO INC</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>애보트</t>
+          <t>머크</t>
         </is>
       </c>
       <c r="M15" s="7">
@@ -26972,25 +26972,25 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.03788657</v>
+        <v>0.03828023</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>PEPSICO</t>
+          <t>ABBOTT LABORATORIES</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>펩시코</t>
+          <t>애보트</t>
         </is>
       </c>
       <c r="M16" s="7">
@@ -27014,7 +27014,7 @@
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03611073</v>
+        <v>0.03572645</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03448176</v>
+        <v>0.03570178</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03076834</v>
+        <v>0.03046279</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.0299435</v>
+        <v>0.02959153</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02815654</v>
+        <v>0.02807779</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02750829</v>
+        <v>0.02741694</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02033334</v>
+        <v>0.02036204</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.01963252</v>
+        <v>0.01979386</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01901539</v>
+        <v>0.01908574</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -27340,25 +27340,25 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01802343</v>
+        <v>0.01798331</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UNITED PARCEL SERVICE INC CLASS B</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="M26" s="7">
@@ -27378,25 +27378,25 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.0179207</v>
+        <v>0.01794027</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>UNITED PARCEL SERVICE INC CLASS B</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="M27" s="7">
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.01718883</v>
+        <v>0.01714394</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27454,23 +27454,27 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01443041</v>
+        <v>0.01441625</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>ONEOK</t>
+          <t>FASTENAL</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr"/>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr">
+        <is>
+          <t>패스널</t>
+        </is>
+      </c>
       <c r="M29" s="7">
         <f>IF(H29="","",IFERROR(VLOOKUP(K29,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
         <v/>
@@ -27488,27 +27492,23 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01436311</v>
+        <v>0.01434565</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>FASTENAL</t>
+          <t>ONEOK</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="L30" s="6" t="inlineStr">
-        <is>
-          <t>패스널</t>
-        </is>
-      </c>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr"/>
       <c r="M30" s="7">
         <f>IF(H30="","",IFERROR(VLOOKUP(K30,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
         <v/>
@@ -27530,7 +27530,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01369032</v>
+        <v>0.01379243</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01194409</v>
+        <v>0.01174717</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01120687</v>
+        <v>0.01127959</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.00976781</v>
+        <v>0.009554709999999999</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.00876676</v>
+        <v>0.008729799999999999</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.008613619999999999</v>
+        <v>0.00863236</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.00644801</v>
+        <v>0.00642043</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.006168590000000001</v>
+        <v>0.00623166</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
@@ -27731,20 +27731,20 @@
     <row r="39">
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>HSY</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.00613186</v>
+        <v>0.006045500000000001</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>HERSHEY FOODS</t>
+          <t>DARDEN RESTAURANTS INC</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr"/>
@@ -27756,20 +27756,20 @@
     <row r="40">
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>HSY</t>
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.00602634</v>
+        <v>0.00601652</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>DARDEN RESTAURANTS INC</t>
+          <t>HERSHEY FOODS</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr"/>
@@ -27785,7 +27785,7 @@
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.00573727</v>
+        <v>0.005706050000000001</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.005284100000000001</v>
+        <v>0.00525792</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.00520119</v>
+        <v>0.005126840000000001</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00489968</v>
+        <v>0.00491802</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00475214</v>
+        <v>0.00473661</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.0046609</v>
+        <v>0.00464773</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00449997</v>
+        <v>0.00444347</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -27956,20 +27956,20 @@
     <row r="48">
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.0043463</v>
+        <v>0.00429283</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>GENERAL MILLS INC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
@@ -27981,20 +27981,20 @@
     <row r="49">
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.00426545</v>
+        <v>0.00428863</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>EAST WEST BANCORP</t>
+          <t>GENERAL MILLS INC</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
@@ -28006,20 +28006,20 @@
     <row r="50">
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00422458</v>
+        <v>0.00423464</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>EAST WEST BANCORP</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr"/>
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.00258379</v>
+        <v>0.0025765</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00251532</v>
+        <v>0.0025068</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.0025014</v>
+        <v>0.00249122</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00219017</v>
+        <v>0.00219234</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00216031</v>
+        <v>0.00214697</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00197196</v>
+        <v>0.00197159</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.00189573</v>
+        <v>0.00191095</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28206,20 +28206,20 @@
     <row r="58">
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.00154731</v>
+        <v>0.00154167</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>MACYS INC</t>
+          <t>ERIE INDEMNITY CLASS A</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr"/>
@@ -28231,20 +28231,20 @@
     <row r="59">
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00154533</v>
+        <v>0.00152714</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>ERIE INDEMNITY CLASS A</t>
+          <t>MACYS INC</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr"/>
@@ -28260,7 +28260,7 @@
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.0014655</v>
+        <v>0.00144688</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00138152</v>
+        <v>0.00141319</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.00132055</v>
+        <v>0.00132502</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.0011709</v>
+        <v>0.00118386</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00114904</v>
+        <v>0.00113003</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28381,15 +28381,15 @@
     <row r="65">
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>FHI</t>
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.00098869</v>
+        <v>0.00096994</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>MOELIS CLASS A</t>
+          <t>FEDERATED HERMES INC CLASS B</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
@@ -28406,15 +28406,15 @@
     <row r="66">
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>FHI</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.00097828</v>
+        <v>0.00096542</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>FEDERATED HERMES INC CLASS B</t>
+          <t>MOELIS CLASS A</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
@@ -28435,7 +28435,7 @@
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.0009256000000000001</v>
+        <v>0.0009271500000000001</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.0009221300000000001</v>
+        <v>0.00091108</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00089464</v>
+        <v>0.00089713</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.0008871700000000001</v>
+        <v>0.00087914</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.00081987</v>
+        <v>0.0008120299999999999</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.0005605299999999999</v>
+        <v>0.00055785</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.00055993</v>
+        <v>0.00055747</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.00054628</v>
+        <v>0.0005436</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.00051849</v>
+        <v>0.0005161500000000001</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.00049944</v>
+        <v>0.00050315</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.00048849</v>
+        <v>0.00048714</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.00048348</v>
+        <v>0.00047667</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00047337</v>
+        <v>0.00047435</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
@@ -28756,15 +28756,15 @@
     <row r="80">
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>GABC</t>
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00046806</v>
+        <v>0.00046024</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
+          <t>GERMAN AMERICAN BANCORP INC</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
@@ -28781,15 +28781,15 @@
     <row r="81">
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>GABC</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.00046152</v>
+        <v>0.00045899</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>GERMAN AMERICAN BANCORP INC</t>
+          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
@@ -28810,7 +28810,7 @@
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00045132</v>
+        <v>0.00043236</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.00042364</v>
+        <v>0.00042214</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.00041385</v>
+        <v>0.00041077</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00039244</v>
+        <v>0.00040583</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.00037642</v>
+        <v>0.00037481</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
@@ -28927,20 +28927,20 @@
     <row r="87">
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>LKFN</t>
+          <t>BKE</t>
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.00035466</v>
+        <v>0.00035561</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>LAKELAND FINANCIAL CORP</t>
+          <t>BUCKLE</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -28952,20 +28952,20 @@
     <row r="88">
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>BKE</t>
+          <t>LKFN</t>
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00035092</v>
+        <v>0.00035326</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>BUCKLE</t>
+          <t>LAKELAND FINANCIAL CORP</t>
         </is>
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr"/>
@@ -28981,7 +28981,7 @@
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.00031822</v>
+        <v>0.0003126</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00027958</v>
+        <v>0.00027839</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00026418</v>
+        <v>0.00026436</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.00025525</v>
+        <v>0.00025582</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.0002299</v>
+        <v>0.00022948</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00022529</v>
+        <v>0.0002251</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00020373</v>
+        <v>0.00020276</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.00019441</v>
+        <v>0.00019517</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.0001943</v>
+        <v>0.00019455</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.00018458</v>
+        <v>0.00017741</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.00016498</v>
+        <v>0.00016406</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00013126</v>
+        <v>0.00013139</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
@@ -29277,18 +29277,22 @@
     <row r="101">
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>AMSF</t>
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00011859</v>
+        <v>0.00011576</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>US DOLLAR</t>
-        </is>
-      </c>
-      <c r="K101" s="6" t="inlineStr"/>
+          <t>AMERISAFE INC</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="L101" s="6" t="inlineStr"/>
       <c r="M101" s="7">
         <f>IF(H101="","",IFERROR(VLOOKUP(K101,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29298,22 +29302,18 @@
     <row r="102">
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>0.00011494</v>
+        <v>0.00011066</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>AMERISAFE INC</t>
-        </is>
-      </c>
-      <c r="K102" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+          <t>US DOLLAR</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr"/>
       <c r="L102" s="6" t="inlineStr"/>
       <c r="M102" s="7">
         <f>IF(H102="","",IFERROR(VLOOKUP(K102,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29327,7 +29327,7 @@
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>9.831e-05</v>
+        <v>9.738999999999999e-05</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>9.007e-05</v>
+        <v>9.112000000000001e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-20 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-21 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>출처: Yahoo Finance (종가: 주식분할 반영·배당 미조정 / adj: 배당 재투자 반영 수정주가) · 기준일 2026-10-14 · 3:1 분할(2024-10-11) 반영 가격</t>
+          <t>출처: Yahoo Finance (종가: 주식분할 반영·배당 미조정 / adj: 배당 재투자 반영 수정주가) · 기준일 2026-10-20 · 3:1 분할(2024-10-11) 반영 가격</t>
         </is>
       </c>
     </row>
@@ -6243,7 +6243,7 @@
         <v>10.9</v>
       </c>
       <c r="D22" s="77" t="n">
-        <v>7.1038</v>
+        <v>7.1037</v>
       </c>
       <c r="E22" s="58">
         <f>C22/C10-1</f>
@@ -7491,7 +7491,7 @@
         <v>16.1633</v>
       </c>
       <c r="D74" s="77" t="n">
-        <v>11.9069</v>
+        <v>11.9068</v>
       </c>
       <c r="E74" s="58">
         <f>C74/C62-1</f>
@@ -7995,7 +7995,7 @@
         <v>17.9833</v>
       </c>
       <c r="D95" s="77" t="n">
-        <v>13.9254</v>
+        <v>13.9255</v>
       </c>
       <c r="E95" s="58">
         <f>C95/C83-1</f>
@@ -9555,7 +9555,7 @@
         <v>27.32</v>
       </c>
       <c r="D160" s="77" t="n">
-        <v>25.6579</v>
+        <v>25.658</v>
       </c>
       <c r="E160" s="58">
         <f>C160/C148-1</f>
@@ -10077,13 +10077,13 @@
         </is>
       </c>
       <c r="B182" s="56" t="n">
-        <v>46309</v>
+        <v>46315</v>
       </c>
       <c r="C182" s="76" t="n">
-        <v>33.71</v>
+        <v>34.69</v>
       </c>
       <c r="D182" s="77" t="n">
-        <v>33.71</v>
+        <v>34.69</v>
       </c>
       <c r="E182" s="58">
         <f>C182/C170-1</f>
@@ -26257,11 +26257,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-16)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-19)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26358,11 +26358,11 @@
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.04404334000000001</v>
+        <v>0.0437362</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>TEXAS INSTRUMENT INC</t>
+          <t>TEXAS INSTRUMENT</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
@@ -26416,7 +26416,7 @@
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04340455000000001</v>
+        <v>0.04329193</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04305399000000001</v>
+        <v>0.04275667</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
@@ -26528,25 +26528,25 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04302386</v>
+        <v>0.04262202</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>COCA-COLA</t>
+          <t>CONOCOPHILLIPS</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>코카콜라</t>
+          <t>코노코필립스</t>
         </is>
       </c>
       <c r="M8" s="7">
@@ -26586,25 +26586,25 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.04296461</v>
+        <v>0.04250498</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CONOCOPHILLIPS</t>
+          <t>COCA-COLA</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>코노코필립스</t>
+          <t>코카콜라</t>
         </is>
       </c>
       <c r="M9" s="7">
@@ -26644,25 +26644,25 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.0414919</v>
+        <v>0.04208503</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>QUALCOMM</t>
+          <t>UNITEDHEALTH GROUP</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>퀄컴</t>
+          <t>유나이티드헬스</t>
         </is>
       </c>
       <c r="M10" s="7">
@@ -26702,25 +26702,25 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04137204</v>
+        <v>0.04147538</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>UNITEDHEALTH GROUP</t>
+          <t>QUALCOMM</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>유나이티드헬스</t>
+          <t>퀄컴</t>
         </is>
       </c>
       <c r="M11" s="7">
@@ -26760,25 +26760,25 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.03953678</v>
+        <v>0.03976414</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>HOME DEPOT</t>
+          <t>AMGEN INC</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>홈디포</t>
+          <t>암젠</t>
         </is>
       </c>
       <c r="M12" s="7">
@@ -26818,25 +26818,25 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03899518</v>
+        <v>0.03968929</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>AMGEN INC</t>
+          <t>HOME DEPOT</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>암젠</t>
+          <t>홈디포</t>
         </is>
       </c>
       <c r="M13" s="7">
@@ -26876,25 +26876,25 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.03862823</v>
+        <v>0.03923437</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>PEPSICO</t>
+          <t>MERCK &amp; CO INC</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>펩시코</t>
+          <t>머크</t>
         </is>
       </c>
       <c r="M14" s="7">
@@ -26924,25 +26924,25 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.0384916</v>
+        <v>0.03826222</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>MERCK &amp; CO INC</t>
+          <t>PEPSICO</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>머크</t>
+          <t>펩시코</t>
         </is>
       </c>
       <c r="M15" s="7">
@@ -26976,7 +26976,7 @@
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.03828023</v>
+        <v>0.03720558</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -27014,7 +27014,7 @@
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03572645</v>
+        <v>0.03558074</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03570178</v>
+        <v>0.03557055</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -27077,25 +27077,25 @@
     <row r="19">
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03046279</v>
+        <v>0.03062798</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>ALTRIA GROUP INC</t>
+          <t>BRISTOL MYERS SQUIBB</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>알트리아</t>
+          <t>브리스톨마이어스스퀴브</t>
         </is>
       </c>
       <c r="M19" s="7">
@@ -27111,25 +27111,25 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.02959153</v>
+        <v>0.03029613</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>BRISTOL MYERS SQUIBB</t>
+          <t>ALTRIA GROUP INC</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>브리스톨마이어스스퀴브</t>
+          <t>알트리아</t>
         </is>
       </c>
       <c r="M20" s="7">
@@ -27154,7 +27154,7 @@
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02807779</v>
+        <v>0.02827079</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02741694</v>
+        <v>0.02708957</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02036204</v>
+        <v>0.02013451</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.01979386</v>
+        <v>0.02013349</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01908574</v>
+        <v>0.01923721</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -27340,25 +27340,25 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01798331</v>
+        <v>0.01803174</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>UNITED PARCEL SERVICE INC CLASS B</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="M26" s="7">
@@ -27378,25 +27378,25 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.01794027</v>
+        <v>0.01794622</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UNITED PARCEL SERVICE INC CLASS B</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="M27" s="7">
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.01714394</v>
+        <v>0.01700291</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01441625</v>
+        <v>0.01440745</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01434565</v>
+        <v>0.01422793</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01379243</v>
+        <v>0.01347148</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01174717</v>
+        <v>0.01156825</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01127959</v>
+        <v>0.01155408</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.009554709999999999</v>
+        <v>0.009426520000000001</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.008729799999999999</v>
+        <v>0.00876353</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.00863236</v>
+        <v>0.008757869999999999</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.00642043</v>
+        <v>0.00641953</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.00623166</v>
+        <v>0.006331</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
@@ -27731,20 +27731,20 @@
     <row r="39">
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>HSY</t>
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.006045500000000001</v>
+        <v>0.00603122</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>DARDEN RESTAURANTS INC</t>
+          <t>HERSHEY FOODS</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr"/>
@@ -27756,20 +27756,20 @@
     <row r="40">
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>HSY</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.00601652</v>
+        <v>0.0060163</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>HERSHEY FOODS</t>
+          <t>DARDEN RESTAURANTS INC</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr"/>
@@ -27785,7 +27785,7 @@
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.005706050000000001</v>
+        <v>0.00576763</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.00525792</v>
+        <v>0.00529584</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.005126840000000001</v>
+        <v>0.005112299999999999</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00491802</v>
+        <v>0.00498997</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00473661</v>
+        <v>0.00470943</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.00464773</v>
+        <v>0.00460754</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00444347</v>
+        <v>0.00451944</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -27956,20 +27956,20 @@
     <row r="48">
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.00429283</v>
+        <v>0.00434551</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GENERAL MILLS INC</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
@@ -27981,20 +27981,20 @@
     <row r="49">
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.00428863</v>
+        <v>0.00427266</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>GENERAL MILLS INC</t>
+          <t>EAST WEST BANCORP</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
@@ -28006,20 +28006,20 @@
     <row r="50">
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00423464</v>
+        <v>0.00424979</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>EAST WEST BANCORP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr"/>
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.0025765</v>
+        <v>0.00261124</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28056,15 +28056,15 @@
     <row r="52">
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>FNF</t>
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.0025068</v>
+        <v>0.00250636</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>AMERICAN FINANCIAL GROUP</t>
+          <t>FIDELITY NATIONAL FINANCIAL INC</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
@@ -28081,15 +28081,15 @@
     <row r="53">
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>FNF</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00249122</v>
+        <v>0.00249401</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>FIDELITY NATIONAL FINANCIAL INC</t>
+          <t>AMERICAN FINANCIAL GROUP</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
@@ -28110,7 +28110,7 @@
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00219234</v>
+        <v>0.00219085</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00214697</v>
+        <v>0.00214161</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00197159</v>
+        <v>0.00199168</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.00191095</v>
+        <v>0.00189993</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.00154167</v>
+        <v>0.00154497</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
@@ -28235,11 +28235,11 @@
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00152714</v>
+        <v>0.00149545</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>MACYS INC</t>
+          <t>MACYS</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
@@ -28260,7 +28260,7 @@
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00144688</v>
+        <v>0.00144259</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00141319</v>
+        <v>0.00141312</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.00132502</v>
+        <v>0.00131177</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.00118386</v>
+        <v>0.00119145</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00113003</v>
+        <v>0.00113949</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.00096994</v>
+        <v>0.00096997</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.00096542</v>
+        <v>0.00096707</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.0009271500000000001</v>
+        <v>0.0009162900000000001</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.00091108</v>
+        <v>0.0009137699999999999</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
@@ -28485,7 +28485,7 @@
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00089713</v>
+        <v>0.00089821</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.00087914</v>
+        <v>0.00088813</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
@@ -28535,7 +28535,7 @@
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.0008120299999999999</v>
+        <v>0.00082553</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
@@ -28556,15 +28556,15 @@
     <row r="72">
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>APAM</t>
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.00055785</v>
+        <v>0.0005663</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>BANNER CORP</t>
+          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
@@ -28581,15 +28581,15 @@
     <row r="73">
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>APAM</t>
+          <t>BANR</t>
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.00055747</v>
+        <v>0.00056032</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
+          <t>BANNER CORP</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -28610,7 +28610,7 @@
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.0005436</v>
+        <v>0.0005444299999999999</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.0005161500000000001</v>
+        <v>0.00051459</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.00050315</v>
+        <v>0.00050215</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
@@ -28681,15 +28681,15 @@
     <row r="77">
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>CHCO</t>
+          <t>CNS</t>
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.00048714</v>
+        <v>0.00049549</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>CITY HOLDING</t>
+          <t>COHEN &amp; STEERS INC</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
@@ -28706,15 +28706,15 @@
     <row r="78">
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>CNS</t>
+          <t>CHCO</t>
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.00047667</v>
+        <v>0.00048529</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>COHEN &amp; STEERS INC</t>
+          <t>CITY HOLDING</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr">
@@ -28735,7 +28735,7 @@
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00047435</v>
+        <v>0.00047208</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00046024</v>
+        <v>0.00046119</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.00045899</v>
+        <v>0.00045641</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00043236</v>
+        <v>0.00043535</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.00042214</v>
+        <v>0.00042315</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
@@ -28860,7 +28860,7 @@
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.00041077</v>
+        <v>0.00041123</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
@@ -28885,7 +28885,7 @@
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00040583</v>
+        <v>0.00038781</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.00037481</v>
+        <v>0.00037497</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
@@ -28927,20 +28927,20 @@
     <row r="87">
       <c r="H87" s="6" t="inlineStr">
         <is>
-          <t>BKE</t>
+          <t>LKFN</t>
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.00035561</v>
+        <v>0.00035496</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>BUCKLE</t>
+          <t>LAKELAND FINANCIAL CORP</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -28952,20 +28952,20 @@
     <row r="88">
       <c r="H88" s="6" t="inlineStr">
         <is>
-          <t>LKFN</t>
+          <t>BKE</t>
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00035326</v>
+        <v>0.00034819</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>LAKELAND FINANCIAL CORP</t>
+          <t>BUCKLE</t>
         </is>
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L88" s="6" t="inlineStr"/>
@@ -28981,7 +28981,7 @@
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.0003126</v>
+        <v>0.00030963</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00027839</v>
+        <v>0.00027876</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
@@ -29027,20 +29027,20 @@
     <row r="91">
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>WEN</t>
+          <t>CNA</t>
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00026436</v>
+        <v>0.00025555</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>WENDYS</t>
+          <t>CNA FINANCIAL CORP</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -29052,20 +29052,20 @@
     <row r="92">
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>CNA</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.00025582</v>
+        <v>0.00025473</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>CNA FINANCIAL CORP</t>
+          <t>WENDYS</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr"/>
@@ -29081,7 +29081,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.00022948</v>
+        <v>0.00022989</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.0002251</v>
+        <v>0.00022572</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00020276</v>
+        <v>0.00020398</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.00019517</v>
+        <v>0.00019656</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.00019455</v>
+        <v>0.00019476</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.00017741</v>
+        <v>0.00017857</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.00016406</v>
+        <v>0.00016453</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00013139</v>
+        <v>0.00013087</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
@@ -29277,22 +29277,18 @@
     <row r="101">
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00011576</v>
+        <v>0.00013085</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>AMERISAFE INC</t>
-        </is>
-      </c>
-      <c r="K101" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+          <t>US DOLLAR</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr"/>
       <c r="L101" s="6" t="inlineStr"/>
       <c r="M101" s="7">
         <f>IF(H101="","",IFERROR(VLOOKUP(K101,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29302,18 +29298,22 @@
     <row r="102">
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>AMSF</t>
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>0.00011066</v>
+        <v>0.00011431</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>US DOLLAR</t>
-        </is>
-      </c>
-      <c r="K102" s="6" t="inlineStr"/>
+          <t>AMERISAFE INC</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="L102" s="6" t="inlineStr"/>
       <c r="M102" s="7">
         <f>IF(H102="","",IFERROR(VLOOKUP(K102,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29327,7 +29327,7 @@
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>9.738999999999999e-05</v>
+        <v>9.802999999999999e-05</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>9.112000000000001e-05</v>
+        <v>9.091e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-21 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-22 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -11996,11 +11996,11 @@
         </is>
       </c>
       <c r="B34" s="19" t="n">
-        <v>0.033</v>
+        <v>0.0318</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-13 기준 · 최근 30일 순투자수익(보수 차감) 연 환산</t>
+          <t>2026-10-20 기준 · 최근 30일 순투자수익(보수 차감) 연 환산</t>
         </is>
       </c>
     </row>
@@ -26257,11 +26257,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-19)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-20)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26358,7 +26358,7 @@
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.0437362</v>
+        <v>0.04485776</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -26412,25 +26412,25 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04329193</v>
+        <v>0.04299757</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>PROCTER &amp; GAMBLE</t>
+          <t>CHEVRON</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>프록터앤드갬블</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="M6" s="7">
@@ -26470,25 +26470,25 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04275667</v>
+        <v>0.042656</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CHEVRON</t>
+          <t>PROCTER &amp; GAMBLE</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>프록터앤드갬블</t>
         </is>
       </c>
       <c r="M7" s="7">
@@ -26532,7 +26532,7 @@
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04262202</v>
+        <v>0.04257815</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
@@ -26590,7 +26590,7 @@
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.04250498</v>
+        <v>0.04217424</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -26644,25 +26644,25 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.04208503</v>
+        <v>0.04204388</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>UNITEDHEALTH GROUP</t>
+          <t>QUALCOMM</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>유나이티드헬스</t>
+          <t>퀄컴</t>
         </is>
       </c>
       <c r="M10" s="7">
@@ -26702,25 +26702,25 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04147538</v>
+        <v>0.04189536999999999</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>QUALCOMM</t>
+          <t>UNITEDHEALTH GROUP</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>퀄컴</t>
+          <t>유나이티드헬스</t>
         </is>
       </c>
       <c r="M11" s="7">
@@ -26764,7 +26764,7 @@
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.03976414</v>
+        <v>0.03974505</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
@@ -26818,25 +26818,25 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03968929</v>
+        <v>0.03968767</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>HOME DEPOT</t>
+          <t>MERCK &amp; CO INC</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>홈디포</t>
+          <t>머크</t>
         </is>
       </c>
       <c r="M13" s="7">
@@ -26876,25 +26876,25 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.03923437</v>
+        <v>0.03960226</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>MERCK &amp; CO INC</t>
+          <t>HOME DEPOT</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>머크</t>
+          <t>홈디포</t>
         </is>
       </c>
       <c r="M14" s="7">
@@ -26928,7 +26928,7 @@
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.03826222</v>
+        <v>0.03849057</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
@@ -26976,7 +26976,7 @@
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.03720558</v>
+        <v>0.03653357</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -27010,25 +27010,25 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03558074</v>
+        <v>0.03577195</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>VERIZON COMMUNICATIONS INC</t>
+          <t>ACCENTURE PLC CLASS A</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>버라이즌</t>
+          <t>액센츄어</t>
         </is>
       </c>
       <c r="M17" s="7">
@@ -27048,25 +27048,25 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03557055</v>
+        <v>0.03482887</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>ACCENTURE PLC CLASS A</t>
+          <t>VERIZON COMMUNICATIONS INC</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>액센츄어</t>
+          <t>버라이즌</t>
         </is>
       </c>
       <c r="M18" s="7">
@@ -27081,7 +27081,7 @@
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03062798</v>
+        <v>0.03037695</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.03029613</v>
+        <v>0.02999405</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02827079</v>
+        <v>0.02846511</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -27192,11 +27192,11 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02708957</v>
+        <v>0.02725198</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>LOCKHEED MARTIN CORP</t>
+          <t>LOCKHEED MARTIN</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02013451</v>
+        <v>0.02014859</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.02013349</v>
+        <v>0.02001077</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01923721</v>
+        <v>0.01901324</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01803174</v>
+        <v>0.01845224</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
@@ -27382,7 +27382,7 @@
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.01794622</v>
+        <v>0.01815364</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.01700291</v>
+        <v>0.01683904</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01440745</v>
+        <v>0.0146548</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01422793</v>
+        <v>0.01428201</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01347148</v>
+        <v>0.01334698</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27551,20 +27551,20 @@
     <row r="32">
       <c r="H32" s="6" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>FITB</t>
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01156825</v>
+        <v>0.01165263</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>FORD MOTOR</t>
+          <t>FIFTH THIRD BANCORP</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr"/>
@@ -27581,20 +27581,20 @@
       </c>
       <c r="H33" s="6" t="inlineStr">
         <is>
-          <t>FITB</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01155408</v>
+        <v>0.01134031</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>FIFTH THIRD BANCORP</t>
+          <t>FORD MOTOR</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
@@ -27610,7 +27610,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.009426520000000001</v>
+        <v>0.009305909999999999</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.00876353</v>
+        <v>0.008761970000000001</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.008757869999999999</v>
+        <v>0.00862889</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.00641953</v>
+        <v>0.00648346</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.006331</v>
+        <v>0.00637586</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.00603122</v>
+        <v>0.005973549999999999</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.0060163</v>
+        <v>0.00592575</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.00576763</v>
+        <v>0.00581422</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.00529584</v>
+        <v>0.00536073</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.005112299999999999</v>
+        <v>0.005140519999999999</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00498997</v>
+        <v>0.00494746</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00470943</v>
+        <v>0.0047234</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.00460754</v>
+        <v>0.004642879999999999</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00451944</v>
+        <v>0.00453454</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -27956,20 +27956,20 @@
     <row r="48">
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.00434551</v>
+        <v>0.00438045</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>GENERAL MILLS INC</t>
+          <t>EAST WEST BANCORP</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
@@ -27981,20 +27981,20 @@
     <row r="49">
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.00427266</v>
+        <v>0.00423748</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>EAST WEST BANCORP</t>
+          <t>GENERAL MILLS INC</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
@@ -28010,7 +28010,7 @@
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00424979</v>
+        <v>0.00423056</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.00261124</v>
+        <v>0.00264098</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00250636</v>
+        <v>0.00251603</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00249401</v>
+        <v>0.00250354</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00219085</v>
+        <v>0.00219483</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00214161</v>
+        <v>0.00216782</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00199168</v>
+        <v>0.00200789</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.00189993</v>
+        <v>0.00187926</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.00154497</v>
+        <v>0.00153483</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00149545</v>
+        <v>0.00149806</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00144259</v>
+        <v>0.00148054</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00141312</v>
+        <v>0.0014101</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.00131177</v>
+        <v>0.00127473</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
@@ -28331,20 +28331,20 @@
     <row r="63">
       <c r="H63" s="6" t="inlineStr">
         <is>
-          <t>NXST</t>
+          <t>OZK</t>
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.00119145</v>
+        <v>0.00118818</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>NEXSTAR MEDIA GROUP INC</t>
+          <t>BANK OZK</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L63" s="6" t="inlineStr"/>
@@ -28356,20 +28356,20 @@
     <row r="64">
       <c r="H64" s="6" t="inlineStr">
         <is>
-          <t>OZK</t>
+          <t>NXST</t>
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00113949</v>
+        <v>0.00116287</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>BANK OZK</t>
+          <t>NEXSTAR MEDIA GROUP INC</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="L64" s="6" t="inlineStr"/>
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.00096997</v>
+        <v>0.0009725399999999999</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.00096707</v>
+        <v>0.00095373</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
@@ -28431,20 +28431,20 @@
     <row r="67">
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>PAG</t>
+          <t>CWEN</t>
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.0009162900000000001</v>
+        <v>0.00092919</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
+          <t>CLEARWAY ENERGY INC CLASS C</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr"/>
@@ -28456,20 +28456,20 @@
     <row r="68">
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>KFY</t>
+          <t>PAG</t>
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.0009137699999999999</v>
+        <v>0.00091621</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>KORN FERRY</t>
+          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr"/>
@@ -28481,20 +28481,20 @@
     <row r="69">
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>CVBF</t>
+          <t>KFY</t>
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00089821</v>
+        <v>0.0009149500000000001</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>CVB FINANCIAL CORP</t>
+          <t>KORN FERRY</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr"/>
@@ -28506,20 +28506,20 @@
     <row r="70">
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>CWEN</t>
+          <t>CVBF</t>
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.00088813</v>
+        <v>0.00090226</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>CLEARWAY ENERGY INC CLASS C</t>
+          <t>CVB FINANCIAL CORP</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr"/>
@@ -28535,7 +28535,7 @@
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.00082553</v>
+        <v>0.00084555</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
@@ -28560,7 +28560,7 @@
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.0005663</v>
+        <v>0.00056972</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.00056032</v>
+        <v>0.0005598199999999999</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.0005444299999999999</v>
+        <v>0.0005196900000000001</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.00051459</v>
+        <v>0.00050302</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.00050215</v>
+        <v>0.00049936</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.00049549</v>
+        <v>0.00048373</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.00048529</v>
+        <v>0.0004815</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00047208</v>
+        <v>0.00047554</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00046119</v>
+        <v>0.00045774</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.00045641</v>
+        <v>0.00045368</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
@@ -28810,7 +28810,7 @@
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00043535</v>
+        <v>0.00043713</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.00042315</v>
+        <v>0.00042025</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
@@ -28856,22 +28856,18 @@
     <row r="84">
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>NBHC</t>
+          <t>GVMXX</t>
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.00041123</v>
+        <v>0.00041188</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>NATIONAL BANK HOLDINGS CORP CLASS</t>
-        </is>
-      </c>
-      <c r="K84" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+          <t>SSC GOVERNMENT MM GVMXX</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr"/>
       <c r="L84" s="6" t="inlineStr"/>
       <c r="M84" s="7">
         <f>IF(H84="","",IFERROR(VLOOKUP(K84,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28881,18 +28877,22 @@
     <row r="85">
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>GVMXX</t>
+          <t>NBHC</t>
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00038781</v>
+        <v>0.00041158</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>SSC GOVERNMENT MM GVMXX</t>
-        </is>
-      </c>
-      <c r="K85" s="6" t="inlineStr"/>
+          <t>NATIONAL BANK HOLDINGS CORP CLASS</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="L85" s="6" t="inlineStr"/>
       <c r="M85" s="7">
         <f>IF(H85="","",IFERROR(VLOOKUP(K85,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28906,7 +28906,7 @@
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.00037497</v>
+        <v>0.00037281</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.00035496</v>
+        <v>0.00035181</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00034819</v>
+        <v>0.00034437</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.00030963</v>
+        <v>0.00030009</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00027876</v>
+        <v>0.00027976</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00025555</v>
+        <v>0.00025535</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.00025473</v>
+        <v>0.00024557</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.00022989</v>
+        <v>0.00023034</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00022572</v>
+        <v>0.00022613</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00020398</v>
+        <v>0.00020799</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.00019656</v>
+        <v>0.00019489</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.00019476</v>
+        <v>0.00019378</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.00017857</v>
+        <v>0.00017768</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.00016453</v>
+        <v>0.00016509</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29252,22 +29252,18 @@
     <row r="100">
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>EBF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00013087</v>
+        <v>0.00013204</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>ENNIS INC</t>
-        </is>
-      </c>
-      <c r="K100" s="6" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
+          <t>US DOLLAR</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr"/>
       <c r="L100" s="6" t="inlineStr"/>
       <c r="M100" s="7">
         <f>IF(H100="","",IFERROR(VLOOKUP(K100,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29277,18 +29273,22 @@
     <row r="101">
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EBF</t>
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00013085</v>
+        <v>0.00013122</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>US DOLLAR</t>
-        </is>
-      </c>
-      <c r="K101" s="6" t="inlineStr"/>
+          <t>ENNIS INC</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
       <c r="L101" s="6" t="inlineStr"/>
       <c r="M101" s="7">
         <f>IF(H101="","",IFERROR(VLOOKUP(K101,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29302,7 +29302,7 @@
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>0.00011431</v>
+        <v>0.00011517</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>9.802999999999999e-05</v>
+        <v>9.625999999999999e-05</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>9.091e-05</v>
+        <v>8.805e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-22 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-23 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -26257,11 +26257,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-20)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-21)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26354,25 +26354,25 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.04485776</v>
+        <v>0.0440797</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>TEXAS INSTRUMENT</t>
+          <t>PROCTER &amp; GAMBLE</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>텍사스 인스트루먼트</t>
+          <t>프록터앤드갬블</t>
         </is>
       </c>
       <c r="M5" s="7">
@@ -26412,25 +26412,25 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04299757</v>
+        <v>0.04311106</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>CHEVRON</t>
+          <t>TEXAS INSTRUMENT</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>텍사스 인스트루먼트</t>
         </is>
       </c>
       <c r="M6" s="7">
@@ -26470,15 +26470,15 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.042656</v>
+        <v>0.04246364</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>PROCTER &amp; GAMBLE</t>
+          <t>COCA-COLA</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -26488,7 +26488,7 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>프록터앤드갬블</t>
+          <t>코카콜라</t>
         </is>
       </c>
       <c r="M7" s="7">
@@ -26528,15 +26528,15 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04257815</v>
+        <v>0.04206611</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CONOCOPHILLIPS</t>
+          <t>CHEVRON</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -26546,7 +26546,7 @@
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>코노코필립스</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="M8" s="7">
@@ -26586,25 +26586,25 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.04217424</v>
+        <v>0.04179048</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>COCA-COLA</t>
+          <t>UNITEDHEALTH GROUP</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>코카콜라</t>
+          <t>유나이티드헬스</t>
         </is>
       </c>
       <c r="M9" s="7">
@@ -26644,25 +26644,25 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.04204388</v>
+        <v>0.04166280000000001</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>QUALCOMM</t>
+          <t>CONOCOPHILLIPS</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>퀄컴</t>
+          <t>코노코필립스</t>
         </is>
       </c>
       <c r="M10" s="7">
@@ -26702,25 +26702,25 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04189536999999999</v>
+        <v>0.04043819</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>UNITEDHEALTH GROUP</t>
+          <t>HOME DEPOT</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>유나이티드헬스</t>
+          <t>홈디포</t>
         </is>
       </c>
       <c r="M11" s="7">
@@ -26760,25 +26760,25 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.03974505</v>
+        <v>0.03996504</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>AMGEN INC</t>
+          <t>QUALCOMM</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>암젠</t>
+          <t>퀄컴</t>
         </is>
       </c>
       <c r="M12" s="7">
@@ -26818,15 +26818,15 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03968767</v>
+        <v>0.03969446</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>MERCK &amp; CO INC</t>
+          <t>AMGEN INC</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -26836,7 +26836,7 @@
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>머크</t>
+          <t>암젠</t>
         </is>
       </c>
       <c r="M13" s="7">
@@ -26876,25 +26876,25 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.03960226</v>
+        <v>0.03882847</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>HOME DEPOT</t>
+          <t>PEPSICO</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>홈디포</t>
+          <t>펩시코</t>
         </is>
       </c>
       <c r="M14" s="7">
@@ -26924,25 +26924,25 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.03849057</v>
+        <v>0.03816085</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>PEPSICO</t>
+          <t>MERCK &amp; CO INC</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>펩시코</t>
+          <t>머크</t>
         </is>
       </c>
       <c r="M15" s="7">
@@ -26972,25 +26972,25 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.03653357</v>
+        <v>0.03770554</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>ABBOTT LABORATORIES</t>
+          <t>ACCENTURE PLC CLASS A</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>애보트</t>
+          <t>액센츄어</t>
         </is>
       </c>
       <c r="M16" s="7">
@@ -27010,25 +27010,25 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03577195</v>
+        <v>0.03646952000000001</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>ACCENTURE PLC CLASS A</t>
+          <t>ABBOTT LABORATORIES</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>액센츄어</t>
+          <t>애보트</t>
         </is>
       </c>
       <c r="M17" s="7">
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03482887</v>
+        <v>0.03537294</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03037695</v>
+        <v>0.03064662</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.02999405</v>
+        <v>0.03024801</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02846511</v>
+        <v>0.0291323</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02725198</v>
+        <v>0.02853046</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -27226,25 +27226,25 @@
       </c>
       <c r="H23" s="6" t="inlineStr">
         <is>
-          <t>EOG</t>
+          <t>BX</t>
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02014859</v>
+        <v>0.02122686</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>EOG RESOURCES</t>
+          <t>BLACKSTONE</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr">
         <is>
-          <t>EOG 리소시스</t>
+          <t>블랙스톤</t>
         </is>
       </c>
       <c r="M23" s="7">
@@ -27264,25 +27264,25 @@
       </c>
       <c r="H24" s="6" t="inlineStr">
         <is>
-          <t>BX</t>
+          <t>EOG</t>
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.02001077</v>
+        <v>0.01973078</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>BLACKSTONE</t>
+          <t>EOG RESOURCES</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr">
         <is>
-          <t>블랙스톤</t>
+          <t>EOG 리소시스</t>
         </is>
       </c>
       <c r="M24" s="7">
@@ -27306,7 +27306,7 @@
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01901324</v>
+        <v>0.01925016</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -27340,25 +27340,25 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01845224</v>
+        <v>0.01811623</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UNITED PARCEL SERVICE INC CLASS B</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="M26" s="7">
@@ -27378,25 +27378,25 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.01815364</v>
+        <v>0.01751269</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>UNITED PARCEL SERVICE INC CLASS B</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="M27" s="7">
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.01683904</v>
+        <v>0.01710133</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.0146548</v>
+        <v>0.01440925</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01428201</v>
+        <v>0.01409591</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01334698</v>
+        <v>0.01288287</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01165263</v>
+        <v>0.01149595</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01134031</v>
+        <v>0.01113688</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.009305909999999999</v>
+        <v>0.00916341</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.008761970000000001</v>
+        <v>0.009056920000000001</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.00862889</v>
+        <v>0.008895480000000001</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27681,15 +27681,15 @@
     <row r="37">
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>ARES</t>
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.00648346</v>
+        <v>0.00659729</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>CINCINNATI FINANCIAL</t>
+          <t>ARES MANAGEMENT CLASS A</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -27706,15 +27706,15 @@
     <row r="38">
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>ARES</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.00637586</v>
+        <v>0.00648337</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>ARES MANAGEMENT CLASS A</t>
+          <t>CINCINNATI FINANCIAL</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.005973549999999999</v>
+        <v>0.00611947</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.00592575</v>
+        <v>0.00588202</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.00581422</v>
+        <v>0.00576179</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.00536073</v>
+        <v>0.005254999999999999</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.005140519999999999</v>
+        <v>0.0051088</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00494746</v>
+        <v>0.00505467</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -27881,20 +27881,20 @@
     <row r="45">
       <c r="H45" s="6" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>BBY</t>
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.0047234</v>
+        <v>0.00470751</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>HF SINCLAIR</t>
+          <t>BEST BUY</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr"/>
@@ -27906,20 +27906,20 @@
     <row r="46">
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>DINO</t>
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.004642879999999999</v>
+        <v>0.004503480000000001</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>SNAP ON INC</t>
+          <t>HF SINCLAIR</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr"/>
@@ -27931,20 +27931,20 @@
     <row r="47">
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>BBY</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00453454</v>
+        <v>0.00447987</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>BEST BUY</t>
+          <t>GENERAL MILLS INC</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr"/>
@@ -27956,20 +27956,20 @@
     <row r="48">
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.00438045</v>
+        <v>0.004390740000000001</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>EAST WEST BANCORP</t>
+          <t>SNAP ON INC</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
@@ -27981,20 +27981,20 @@
     <row r="49">
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.00423748</v>
+        <v>0.00432851</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>GENERAL MILLS INC</t>
+          <t>EAST WEST BANCORP</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
@@ -28010,7 +28010,7 @@
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00423056</v>
+        <v>0.00412488</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.00264098</v>
+        <v>0.00277119</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28056,15 +28056,15 @@
     <row r="52">
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>FNF</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00251603</v>
+        <v>0.00251216</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>FIDELITY NATIONAL FINANCIAL INC</t>
+          <t>AMERICAN FINANCIAL GROUP</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
@@ -28081,15 +28081,15 @@
     <row r="53">
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>FNF</t>
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00250354</v>
+        <v>0.00250869</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>AMERICAN FINANCIAL GROUP</t>
+          <t>FIDELITY NATIONAL FINANCIAL INC</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
@@ -28110,7 +28110,7 @@
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00219483</v>
+        <v>0.00224926</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00216782</v>
+        <v>0.00211915</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00200789</v>
+        <v>0.00201168</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.00187926</v>
+        <v>0.001886</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.00153483</v>
+        <v>0.0015801</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00149806</v>
+        <v>0.00151255</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -28256,20 +28256,20 @@
     <row r="60">
       <c r="H60" s="6" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>MUR</t>
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00148054</v>
+        <v>0.00136119</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>MSC INDUSTRIAL CLASS A</t>
+          <t>MURPHY OIL</t>
         </is>
       </c>
       <c r="K60" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L60" s="6" t="inlineStr"/>
@@ -28281,20 +28281,20 @@
     <row r="61">
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>MUR</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.0014101</v>
+        <v>0.00125791</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>MURPHY OIL</t>
+          <t>VAIL RESORTS</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr"/>
@@ -28306,20 +28306,20 @@
     <row r="62">
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.00127473</v>
+        <v>0.00122662</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>VAIL RESORTS</t>
+          <t>MSC INDUSTRIAL CLASS A</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr"/>
@@ -28335,7 +28335,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.00118818</v>
+        <v>0.00120113</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00116287</v>
+        <v>0.0011653</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.0009725399999999999</v>
+        <v>0.0009790199999999999</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.00095373</v>
+        <v>0.00096866</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
@@ -28431,20 +28431,20 @@
     <row r="67">
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>CWEN</t>
+          <t>KFY</t>
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.00092919</v>
+        <v>0.0009356799999999999</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>CLEARWAY ENERGY INC CLASS C</t>
+          <t>KORN FERRY</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr"/>
@@ -28456,20 +28456,20 @@
     <row r="68">
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>PAG</t>
+          <t>CVBF</t>
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.00091621</v>
+        <v>0.00091526</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
+          <t>CVB FINANCIAL CORP</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr"/>
@@ -28481,20 +28481,20 @@
     <row r="69">
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>KFY</t>
+          <t>CWEN</t>
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.0009149500000000001</v>
+        <v>0.00090426</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>KORN FERRY</t>
+          <t>CLEARWAY ENERGY INC CLASS C</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr"/>
@@ -28506,20 +28506,20 @@
     <row r="70">
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>CVBF</t>
+          <t>RHI</t>
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.00090226</v>
+        <v>0.0009002200000000001</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>CVB FINANCIAL CORP</t>
+          <t>ROBERT HALF INC</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr"/>
@@ -28531,20 +28531,20 @@
     <row r="71">
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>RHI</t>
+          <t>PAG</t>
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.00084555</v>
+        <v>0.00089693</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>ROBERT HALF INC</t>
+          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr"/>
@@ -28560,7 +28560,7 @@
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.00056972</v>
+        <v>0.00057898</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.0005598199999999999</v>
+        <v>0.00056443</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
@@ -28606,20 +28606,20 @@
     <row r="74">
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>OFG</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.0005196900000000001</v>
+        <v>0.00052122</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>OFG BANCORP</t>
+          <t>MARZETTI</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr"/>
@@ -28631,20 +28631,20 @@
     <row r="75">
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>IPAR</t>
+          <t>OFG</t>
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.00050302</v>
+        <v>0.00051729</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>INTERPARFUMS INC</t>
+          <t>OFG BANCORP</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -28656,15 +28656,15 @@
     <row r="76">
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>IPAR</t>
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.00049936</v>
+        <v>0.00050476</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>MARZETTI</t>
+          <t>INTERPARFUMS INC</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
@@ -28685,7 +28685,7 @@
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.00048373</v>
+        <v>0.0004856</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.0004815</v>
+        <v>0.0004796099999999999</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00047554</v>
+        <v>0.00047885</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
@@ -28760,7 +28760,7 @@
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00045774</v>
+        <v>0.00045857</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
@@ -28781,20 +28781,20 @@
     <row r="81">
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.00045368</v>
+        <v>0.00045599</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
+          <t>INSPERITY</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -28806,20 +28806,20 @@
     <row r="82">
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00043713</v>
+        <v>0.00044824</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>INSPERITY</t>
+          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr"/>
@@ -28831,22 +28831,18 @@
     <row r="83">
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>STBA</t>
+          <t>GVMXX</t>
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.00042025</v>
+        <v>0.00043447</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>S AND T BANCORP INC</t>
-        </is>
-      </c>
-      <c r="K83" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+          <t>SSC GOVERNMENT MM GVMXX</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr"/>
       <c r="L83" s="6" t="inlineStr"/>
       <c r="M83" s="7">
         <f>IF(H83="","",IFERROR(VLOOKUP(K83,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28856,18 +28852,22 @@
     <row r="84">
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>GVMXX</t>
+          <t>STBA</t>
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.00041188</v>
+        <v>0.00042703</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>SSC GOVERNMENT MM GVMXX</t>
-        </is>
-      </c>
-      <c r="K84" s="6" t="inlineStr"/>
+          <t>S AND T BANCORP INC</t>
+        </is>
+      </c>
+      <c r="K84" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="L84" s="6" t="inlineStr"/>
       <c r="M84" s="7">
         <f>IF(H84="","",IFERROR(VLOOKUP(K84,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28881,7 +28881,7 @@
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00041158</v>
+        <v>0.00041268</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.00037281</v>
+        <v>0.00037069</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.00035181</v>
+        <v>0.00035239</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00034437</v>
+        <v>0.00034771</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.00030009</v>
+        <v>0.00032456</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00027976</v>
+        <v>0.00028219</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00025535</v>
+        <v>0.00025546</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.00024557</v>
+        <v>0.00025145</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.00023034</v>
+        <v>0.00023099</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00022613</v>
+        <v>0.00022652</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00020799</v>
+        <v>0.00021034</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.00019489</v>
+        <v>0.00019589</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.00019378</v>
+        <v>0.00019368</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.00017768</v>
+        <v>0.00017816</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.00016509</v>
+        <v>0.00016466</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29252,18 +29252,22 @@
     <row r="100">
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>EBF</t>
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00013204</v>
+        <v>0.0001306</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>US DOLLAR</t>
-        </is>
-      </c>
-      <c r="K100" s="6" t="inlineStr"/>
+          <t>ENNIS INC</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
       <c r="L100" s="6" t="inlineStr"/>
       <c r="M100" s="7">
         <f>IF(H100="","",IFERROR(VLOOKUP(K100,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29273,20 +29277,20 @@
     <row r="101">
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>EBF</t>
+          <t>AMSF</t>
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00013122</v>
+        <v>0.00011739</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>ENNIS INC</t>
+          <t>AMERISAFE INC</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -29298,22 +29302,18 @@
     <row r="102">
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>0.00011517</v>
+        <v>0.0001055</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>AMERISAFE INC</t>
-        </is>
-      </c>
-      <c r="K102" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+          <t>US DOLLAR</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr"/>
       <c r="L102" s="6" t="inlineStr"/>
       <c r="M102" s="7">
         <f>IF(H102="","",IFERROR(VLOOKUP(K102,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29327,7 +29327,7 @@
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>9.625999999999999e-05</v>
+        <v>9.903000000000001e-05</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
@@ -29352,7 +29352,7 @@
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>8.805e-05</v>
+        <v>9.377000000000001e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-23 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-24 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -26257,11 +26257,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-21)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-22)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26354,25 +26354,25 @@
       </c>
       <c r="H5" s="6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>TXN</t>
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.0440797</v>
+        <v>0.04408678</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
-          <t>PROCTER &amp; GAMBLE</t>
+          <t>TEXAS INSTRUMENT</t>
         </is>
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>프록터앤드갬블</t>
+          <t>텍사스 인스트루먼트</t>
         </is>
       </c>
       <c r="M5" s="7">
@@ -26412,25 +26412,25 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>TXN</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04311106</v>
+        <v>0.04345056999999999</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>TEXAS INSTRUMENT</t>
+          <t>CHEVRON</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>텍사스 인스트루먼트</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="M6" s="7">
@@ -26470,25 +26470,25 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04246364</v>
+        <v>0.04331401999999999</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>COCA-COLA</t>
+          <t>CONOCOPHILLIPS</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>코카콜라</t>
+          <t>코노코필립스</t>
         </is>
       </c>
       <c r="M7" s="7">
@@ -26528,25 +26528,25 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04206611</v>
+        <v>0.04303422</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CHEVRON</t>
+          <t>PROCTER &amp; GAMBLE</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>프록터앤드갬블</t>
         </is>
       </c>
       <c r="M8" s="7">
@@ -26586,25 +26586,25 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.04179048</v>
+        <v>0.04145703</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>UNITEDHEALTH GROUP</t>
+          <t>COCA-COLA</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>유나이티드헬스</t>
+          <t>코카콜라</t>
         </is>
       </c>
       <c r="M9" s="7">
@@ -26644,25 +26644,25 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.04166280000000001</v>
+        <v>0.04127694</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>CONOCOPHILLIPS</t>
+          <t>UNITEDHEALTH GROUP</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>코노코필립스</t>
+          <t>유나이티드헬스</t>
         </is>
       </c>
       <c r="M10" s="7">
@@ -26702,25 +26702,25 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04043819</v>
+        <v>0.04083957</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>HOME DEPOT</t>
+          <t>QUALCOMM</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>홈디포</t>
+          <t>퀄컴</t>
         </is>
       </c>
       <c r="M11" s="7">
@@ -26760,25 +26760,25 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.03996504</v>
+        <v>0.03962082</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>QUALCOMM</t>
+          <t>HOME DEPOT</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>퀄컴</t>
+          <t>홈디포</t>
         </is>
       </c>
       <c r="M12" s="7">
@@ -26822,7 +26822,7 @@
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03969446</v>
+        <v>0.03913819</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.03882847</v>
+        <v>0.03812414</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
@@ -26928,7 +26928,7 @@
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.03816085</v>
+        <v>0.0378005</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
@@ -26972,25 +26972,25 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.03770554</v>
+        <v>0.0370401</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>ACCENTURE PLC CLASS A</t>
+          <t>ABBOTT LABORATORIES</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>액센츄어</t>
+          <t>애보트</t>
         </is>
       </c>
       <c r="M16" s="7">
@@ -27010,25 +27010,25 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03646952000000001</v>
+        <v>0.03648506</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>ABBOTT LABORATORIES</t>
+          <t>ACCENTURE PLC CLASS A</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>애보트</t>
+          <t>액센츄어</t>
         </is>
       </c>
       <c r="M17" s="7">
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03537294</v>
+        <v>0.03508982</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03064662</v>
+        <v>0.03002656</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.03024801</v>
+        <v>0.02966608</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
@@ -27150,15 +27150,15 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.0291323</v>
+        <v>0.02933715</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>AUTOMATIC DATA PROCESSING INC</t>
+          <t>LOCKHEED MARTIN</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -27168,7 +27168,7 @@
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>ADP</t>
+          <t>록히드마틴</t>
         </is>
       </c>
       <c r="M21" s="7">
@@ -27188,15 +27188,15 @@
       </c>
       <c r="H22" s="6" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02853046</v>
+        <v>0.02888952</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>LOCKHEED MARTIN</t>
+          <t>AUTOMATIC DATA PROCESSING INC</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -27206,7 +27206,7 @@
       </c>
       <c r="L22" s="6" t="inlineStr">
         <is>
-          <t>록히드마틴</t>
+          <t>ADP</t>
         </is>
       </c>
       <c r="M22" s="7">
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02122686</v>
+        <v>0.02117156</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.01973078</v>
+        <v>0.02044531</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01925016</v>
+        <v>0.01920005</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -27340,25 +27340,25 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01811623</v>
+        <v>0.01882809</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>UNITED PARCEL SERVICE INC CLASS B</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="M26" s="7">
@@ -27378,25 +27378,25 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.01751269</v>
+        <v>0.01810611</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UNITED PARCEL SERVICE INC CLASS B</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="M27" s="7">
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.01710133</v>
+        <v>0.0165886</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27454,27 +27454,23 @@
       </c>
       <c r="H29" s="6" t="inlineStr">
         <is>
-          <t>FAST</t>
+          <t>OKE</t>
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01440925</v>
+        <v>0.01444304</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>FASTENAL</t>
+          <t>ONEOK</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="L29" s="6" t="inlineStr">
-        <is>
-          <t>패스널</t>
-        </is>
-      </c>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="L29" s="6" t="inlineStr"/>
       <c r="M29" s="7">
         <f>IF(H29="","",IFERROR(VLOOKUP(K29,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
         <v/>
@@ -27492,23 +27488,27 @@
       </c>
       <c r="H30" s="6" t="inlineStr">
         <is>
-          <t>OKE</t>
+          <t>FAST</t>
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01409591</v>
+        <v>0.01424178</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>ONEOK</t>
+          <t>FASTENAL</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="L30" s="6" t="inlineStr"/>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="L30" s="6" t="inlineStr">
+        <is>
+          <t>패스널</t>
+        </is>
+      </c>
       <c r="M30" s="7">
         <f>IF(H30="","",IFERROR(VLOOKUP(K30,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
         <v/>
@@ -27530,7 +27530,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01288287</v>
+        <v>0.0135155</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01149595</v>
+        <v>0.01148761</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01113688</v>
+        <v>0.01086293</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.00916341</v>
+        <v>0.009234529999999999</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.009056920000000001</v>
+        <v>0.00903411</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.008895480000000001</v>
+        <v>0.008758409999999999</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.00659729</v>
+        <v>0.00653687</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.00648337</v>
+        <v>0.00646902</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.00611947</v>
+        <v>0.00593399</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -27756,20 +27756,20 @@
     <row r="40">
       <c r="H40" s="6" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>RF</t>
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.00588202</v>
+        <v>0.00579904</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>DARDEN RESTAURANTS INC</t>
+          <t>REGIONS FINANCIAL</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr"/>
@@ -27781,20 +27781,20 @@
     <row r="41">
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>RF</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.00576179</v>
+        <v>0.00576538</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>REGIONS FINANCIAL</t>
+          <t>DARDEN RESTAURANTS INC</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr"/>
@@ -27810,7 +27810,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.005254999999999999</v>
+        <v>0.0053142</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.0051088</v>
+        <v>0.00505742</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00505467</v>
+        <v>0.00499736</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00470751</v>
+        <v>0.00472818</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.004503480000000001</v>
+        <v>0.00449705</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -27931,20 +27931,20 @@
     <row r="47">
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00447987</v>
+        <v>0.00441511</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>GENERAL MILLS INC</t>
+          <t>SNAP ON INC</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr"/>
@@ -27956,20 +27956,20 @@
     <row r="48">
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.004390740000000001</v>
+        <v>0.00439673</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>SNAP ON INC</t>
+          <t>GENERAL MILLS INC</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
@@ -27981,20 +27981,20 @@
     <row r="49">
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.00432851</v>
+        <v>0.0043474</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>EAST WEST BANCORP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
@@ -28006,20 +28006,20 @@
     <row r="50">
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00412488</v>
+        <v>0.00429793</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>EAST WEST BANCORP</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr"/>
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.00277119</v>
+        <v>0.00274762</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00251216</v>
+        <v>0.00247547</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00250869</v>
+        <v>0.00246148</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00224926</v>
+        <v>0.00225104</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -28131,15 +28131,15 @@
     <row r="55">
       <c r="H55" s="6" t="inlineStr">
         <is>
-          <t>ORI</t>
+          <t>COLB</t>
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00211915</v>
+        <v>0.00208524</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>OLD REPUBLIC INTERNATIONAL</t>
+          <t>COLUMBIA BANKING SYSTEM INC</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
@@ -28156,15 +28156,15 @@
     <row r="56">
       <c r="H56" s="6" t="inlineStr">
         <is>
-          <t>COLB</t>
+          <t>ORI</t>
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00201168</v>
+        <v>0.00206549</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>COLUMBIA BANKING SYSTEM INC</t>
+          <t>OLD REPUBLIC INTERNATIONAL</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
@@ -28185,7 +28185,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.001886</v>
+        <v>0.00182647</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.0015801</v>
+        <v>0.00156608</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00151255</v>
+        <v>0.00151419</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00136119</v>
+        <v>0.00143015</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00125791</v>
+        <v>0.00124874</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.00122662</v>
+        <v>0.00124717</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.00120113</v>
+        <v>0.00122874</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.0011653</v>
+        <v>0.00116009</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28381,20 +28381,20 @@
     <row r="65">
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>FHI</t>
+          <t>RHI</t>
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.0009790199999999999</v>
+        <v>0.00110026</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>FEDERATED HERMES INC CLASS B</t>
+          <t>ROBERT HALF INC</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr"/>
@@ -28406,15 +28406,15 @@
     <row r="66">
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>FHI</t>
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.00096866</v>
+        <v>0.0009682499999999999</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>MOELIS CLASS A</t>
+          <t>FEDERATED HERMES INC CLASS B</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
@@ -28435,7 +28435,7 @@
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.0009356799999999999</v>
+        <v>0.0009633899999999999</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -28456,15 +28456,15 @@
     <row r="68">
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>CVBF</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.00091526</v>
+        <v>0.00096317</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>CVB FINANCIAL CORP</t>
+          <t>MOELIS CLASS A</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
@@ -28481,20 +28481,20 @@
     <row r="69">
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>CWEN</t>
+          <t>CVBF</t>
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00090426</v>
+        <v>0.00091373</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>CLEARWAY ENERGY INC CLASS C</t>
+          <t>CVB FINANCIAL CORP</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr"/>
@@ -28506,20 +28506,20 @@
     <row r="70">
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>RHI</t>
+          <t>PAG</t>
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.0009002200000000001</v>
+        <v>0.00090142</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>ROBERT HALF INC</t>
+          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr"/>
@@ -28531,20 +28531,20 @@
     <row r="71">
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>PAG</t>
+          <t>CWEN</t>
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.00089693</v>
+        <v>0.0008986199999999999</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
+          <t>CLEARWAY ENERGY INC CLASS C</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr"/>
@@ -28556,15 +28556,15 @@
     <row r="72">
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>APAM</t>
+          <t>BANR</t>
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.00057898</v>
+        <v>0.0005681400000000001</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
+          <t>BANNER CORP</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
@@ -28581,15 +28581,15 @@
     <row r="73">
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>APAM</t>
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.00056443</v>
+        <v>0.00056726</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>BANNER CORP</t>
+          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -28606,20 +28606,20 @@
     <row r="74">
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>OFG</t>
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.00052122</v>
+        <v>0.00051843</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>MARZETTI</t>
+          <t>OFG BANCORP</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L74" s="6" t="inlineStr"/>
@@ -28631,20 +28631,20 @@
     <row r="75">
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>OFG</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.00051729</v>
+        <v>0.0005083900000000001</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>OFG BANCORP</t>
+          <t>MARZETTI</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -28660,7 +28660,7 @@
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.00050476</v>
+        <v>0.00050305</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.0004856</v>
+        <v>0.00048028</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.0004796099999999999</v>
+        <v>0.00047681</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
@@ -28735,7 +28735,7 @@
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00047885</v>
+        <v>0.00047403</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
@@ -28756,20 +28756,20 @@
     <row r="80">
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>GABC</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00045857</v>
+        <v>0.00046603</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>GERMAN AMERICAN BANCORP INC</t>
+          <t>INSPERITY</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr"/>
@@ -28781,20 +28781,20 @@
     <row r="81">
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>GABC</t>
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.00045599</v>
+        <v>0.00045787</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>INSPERITY</t>
+          <t>GERMAN AMERICAN BANCORP INC</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -28806,22 +28806,18 @@
     <row r="82">
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>GVMXX</t>
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00044824</v>
+        <v>0.00045314</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
-        </is>
-      </c>
-      <c r="K82" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+          <t>SSC GOVERNMENT MM GVMXX</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr"/>
       <c r="L82" s="6" t="inlineStr"/>
       <c r="M82" s="7">
         <f>IF(H82="","",IFERROR(VLOOKUP(K82,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28831,18 +28827,22 @@
     <row r="83">
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>GVMXX</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.00043447</v>
+        <v>0.000446</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>SSC GOVERNMENT MM GVMXX</t>
-        </is>
-      </c>
-      <c r="K83" s="6" t="inlineStr"/>
+          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="L83" s="6" t="inlineStr"/>
       <c r="M83" s="7">
         <f>IF(H83="","",IFERROR(VLOOKUP(K83,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28856,7 +28856,7 @@
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.00042703</v>
+        <v>0.0004269499999999999</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00041268</v>
+        <v>0.00041346</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.00037069</v>
+        <v>0.00037262</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.00035239</v>
+        <v>0.00034789</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00034771</v>
+        <v>0.00034218</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.00032456</v>
+        <v>0.00031215</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00028219</v>
+        <v>0.00027834</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00025546</v>
+        <v>0.00025134</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.00025145</v>
+        <v>0.000239</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.00023099</v>
+        <v>0.00023141</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00022652</v>
+        <v>0.00022679</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00021034</v>
+        <v>0.00021104</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.00019589</v>
+        <v>0.00019677</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.00019368</v>
+        <v>0.00019569</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.00017816</v>
+        <v>0.00017441</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.00016466</v>
+        <v>0.00016544</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.0001306</v>
+        <v>0.00012952</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00011739</v>
+        <v>0.00011666</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
@@ -29302,18 +29302,22 @@
     <row r="102">
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>ETD</t>
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>0.0001055</v>
+        <v>9.779e-05</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>US DOLLAR</t>
-        </is>
-      </c>
-      <c r="K102" s="6" t="inlineStr"/>
+          <t>ETHAN ALLEN INTERIORS</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
       <c r="L102" s="6" t="inlineStr"/>
       <c r="M102" s="7">
         <f>IF(H102="","",IFERROR(VLOOKUP(K102,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29323,15 +29327,15 @@
     <row r="103">
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>ETD</t>
+          <t>OXM</t>
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>9.903000000000001e-05</v>
+        <v>9.221e-05</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>ETHAN ALLEN INTERIORS</t>
+          <t>OXFORD INDUSTRIES INC</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
@@ -29348,22 +29352,18 @@
     <row r="104">
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>OXM</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>9.377000000000001e-05</v>
+        <v>9.174e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>OXFORD INDUSTRIES INC</t>
-        </is>
-      </c>
-      <c r="K104" s="6" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
+          <t>US DOLLAR</t>
+        </is>
+      </c>
+      <c r="K104" s="6" t="inlineStr"/>
       <c r="L104" s="6" t="inlineStr"/>
       <c r="M104" s="7">
         <f>IF(H104="","",IFERROR(VLOOKUP(K104,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-24 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-27 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>출처: Yahoo Finance (종가: 주식분할 반영·배당 미조정 / adj: 배당 재투자 반영 수정주가) · 기준일 2026-10-20 · 3:1 분할(2024-10-11) 반영 가격</t>
+          <t>출처: Yahoo Finance (종가: 주식분할 반영·배당 미조정 / adj: 배당 재투자 반영 수정주가) · 기준일 2026-10-26 · 3:1 분할(2024-10-11) 반영 가격</t>
         </is>
       </c>
     </row>
@@ -6627,7 +6627,7 @@
         <v>13.1067</v>
       </c>
       <c r="D38" s="77" t="n">
-        <v>8.8355</v>
+        <v>8.835599999999999</v>
       </c>
       <c r="E38" s="58">
         <f>C38/C26-1</f>
@@ -7995,7 +7995,7 @@
         <v>17.9833</v>
       </c>
       <c r="D95" s="77" t="n">
-        <v>13.9255</v>
+        <v>13.9254</v>
       </c>
       <c r="E95" s="58">
         <f>C95/C83-1</f>
@@ -9123,7 +9123,7 @@
         <v>24.2067</v>
       </c>
       <c r="D142" s="77" t="n">
-        <v>21.5029</v>
+        <v>21.503</v>
       </c>
       <c r="E142" s="58">
         <f>C142/C130-1</f>
@@ -9555,7 +9555,7 @@
         <v>27.32</v>
       </c>
       <c r="D160" s="77" t="n">
-        <v>25.658</v>
+        <v>25.6579</v>
       </c>
       <c r="E160" s="58">
         <f>C160/C148-1</f>
@@ -9651,7 +9651,7 @@
         <v>25.82</v>
       </c>
       <c r="D164" s="77" t="n">
-        <v>24.468</v>
+        <v>24.4681</v>
       </c>
       <c r="E164" s="58">
         <f>C164/C152-1</f>
@@ -10077,13 +10077,13 @@
         </is>
       </c>
       <c r="B182" s="56" t="n">
-        <v>46315</v>
+        <v>46321</v>
       </c>
       <c r="C182" s="76" t="n">
-        <v>34.69</v>
+        <v>35.3</v>
       </c>
       <c r="D182" s="77" t="n">
-        <v>34.69</v>
+        <v>35.3</v>
       </c>
       <c r="E182" s="58">
         <f>C182/C170-1</f>
@@ -26257,11 +26257,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46318</v>
+        <v>46321</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-22)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-23)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26358,7 +26358,7 @@
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.04408678</v>
+        <v>0.046169</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -26412,15 +26412,15 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04345056999999999</v>
+        <v>0.04348015</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>CHEVRON</t>
+          <t>CONOCOPHILLIPS</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -26430,7 +26430,7 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>코노코필립스</t>
         </is>
       </c>
       <c r="M6" s="7">
@@ -26470,15 +26470,15 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04331401999999999</v>
+        <v>0.04322924</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CONOCOPHILLIPS</t>
+          <t>CHEVRON</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -26488,7 +26488,7 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>코노코필립스</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="M7" s="7">
@@ -26532,7 +26532,7 @@
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04303422</v>
+        <v>0.04274261</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
@@ -26586,25 +26586,25 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.04145703</v>
+        <v>0.04169852</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>COCA-COLA</t>
+          <t>QUALCOMM</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>코카콜라</t>
+          <t>퀄컴</t>
         </is>
       </c>
       <c r="M9" s="7">
@@ -26644,25 +26644,25 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.04127694</v>
+        <v>0.04145483</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>UNITEDHEALTH GROUP</t>
+          <t>COCA-COLA</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>유나이티드헬스</t>
+          <t>코카콜라</t>
         </is>
       </c>
       <c r="M10" s="7">
@@ -26702,25 +26702,25 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04083957</v>
+        <v>0.04054933</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>QUALCOMM</t>
+          <t>UNITEDHEALTH GROUP</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>퀄컴</t>
+          <t>유나이티드헬스</t>
         </is>
       </c>
       <c r="M11" s="7">
@@ -26760,25 +26760,25 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.03962082</v>
+        <v>0.03961854</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>HOME DEPOT</t>
+          <t>AMGEN INC</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>홈디포</t>
+          <t>암젠</t>
         </is>
       </c>
       <c r="M12" s="7">
@@ -26818,25 +26818,25 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03913819</v>
+        <v>0.03956699</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>AMGEN INC</t>
+          <t>HOME DEPOT</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>암젠</t>
+          <t>홈디포</t>
         </is>
       </c>
       <c r="M13" s="7">
@@ -26880,7 +26880,7 @@
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.03812414</v>
+        <v>0.03803909</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
@@ -26924,15 +26924,15 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.0378005</v>
+        <v>0.03746365</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>MERCK &amp; CO INC</t>
+          <t>ABBOTT LABORATORIES</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>머크</t>
+          <t>애보트</t>
         </is>
       </c>
       <c r="M15" s="7">
@@ -26972,15 +26972,15 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.0370401</v>
+        <v>0.03658987</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>ABBOTT LABORATORIES</t>
+          <t>MERCK &amp; CO INC</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
@@ -26990,7 +26990,7 @@
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>애보트</t>
+          <t>머크</t>
         </is>
       </c>
       <c r="M16" s="7">
@@ -27014,7 +27014,7 @@
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03648506</v>
+        <v>0.0361739</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -27052,7 +27052,7 @@
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03508982</v>
+        <v>0.03386601</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -27077,25 +27077,25 @@
     <row r="19">
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03002656</v>
+        <v>0.03084485</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>BRISTOL MYERS SQUIBB</t>
+          <t>LOCKHEED MARTIN</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>브리스톨마이어스스퀴브</t>
+          <t>록히드마틴</t>
         </is>
       </c>
       <c r="M19" s="7">
@@ -27111,25 +27111,25 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.02966608</v>
+        <v>0.03009173</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>ALTRIA GROUP INC</t>
+          <t>BRISTOL MYERS SQUIBB</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>알트리아</t>
+          <t>브리스톨마이어스스퀴브</t>
         </is>
       </c>
       <c r="M20" s="7">
@@ -27150,25 +27150,25 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02933715</v>
+        <v>0.02939226</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>LOCKHEED MARTIN</t>
+          <t>ALTRIA GROUP INC</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>록히드마틴</t>
+          <t>알트리아</t>
         </is>
       </c>
       <c r="M21" s="7">
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02888952</v>
+        <v>0.02860236</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02117156</v>
+        <v>0.02136829</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.02044531</v>
+        <v>0.02052788</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
@@ -27302,25 +27302,25 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01920005</v>
+        <v>0.01883623</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>COMCAST CLASS A</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>컴캐스트</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="M25" s="7">
@@ -27340,25 +27340,25 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01882809</v>
+        <v>0.01865952</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>COMCAST CLASS A</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>컴캐스트</t>
         </is>
       </c>
       <c r="M26" s="7">
@@ -27382,7 +27382,7 @@
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.01810611</v>
+        <v>0.01797452</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.0165886</v>
+        <v>0.01613016</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01444304</v>
+        <v>0.01452372</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01424178</v>
+        <v>0.01439619</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.0135155</v>
+        <v>0.01358198</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01148761</v>
+        <v>0.01151425</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01086293</v>
+        <v>0.01084481</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.009234529999999999</v>
+        <v>0.00910477</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27635,7 +27635,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.00903411</v>
+        <v>0.008855439999999999</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27660,7 +27660,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.008758409999999999</v>
+        <v>0.00871745</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27685,7 +27685,7 @@
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.00653687</v>
+        <v>0.006526499999999999</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.00646902</v>
+        <v>0.00650634</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
@@ -27735,7 +27735,7 @@
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.00593399</v>
+        <v>0.005884899999999999</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -27760,7 +27760,7 @@
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.00579904</v>
+        <v>0.00582788</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.00576538</v>
+        <v>0.00578861</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -27810,7 +27810,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.0053142</v>
+        <v>0.00527821</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.00505742</v>
+        <v>0.00513027</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00499736</v>
+        <v>0.00493773</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00472818</v>
+        <v>0.00463751</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -27910,7 +27910,7 @@
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.00449705</v>
+        <v>0.00463001</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -27935,7 +27935,7 @@
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00441511</v>
+        <v>0.00442571</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -27956,20 +27956,20 @@
     <row r="48">
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.00439673</v>
+        <v>0.00432752</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>GENERAL MILLS INC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
@@ -27981,20 +27981,20 @@
     <row r="49">
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.0043474</v>
+        <v>0.00431709</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>EAST WEST BANCORP</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
@@ -28006,20 +28006,20 @@
     <row r="50">
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00429793</v>
+        <v>0.00430873</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>EAST WEST BANCORP</t>
+          <t>GENERAL MILLS INC</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr"/>
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.00274762</v>
+        <v>0.0025973</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00247547</v>
+        <v>0.00247497</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00246148</v>
+        <v>0.00243118</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00225104</v>
+        <v>0.00239598</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00208524</v>
+        <v>0.00209885</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00206549</v>
+        <v>0.00204011</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.00182647</v>
+        <v>0.00183693</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.00156608</v>
+        <v>0.00155222</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00151419</v>
+        <v>0.00148222</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00143015</v>
+        <v>0.00142633</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -28281,20 +28281,20 @@
     <row r="61">
       <c r="H61" s="6" t="inlineStr">
         <is>
-          <t>MTN</t>
+          <t>MSM</t>
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00124874</v>
+        <v>0.00130045</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>VAIL RESORTS</t>
+          <t>MSC INDUSTRIAL CLASS A</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L61" s="6" t="inlineStr"/>
@@ -28306,20 +28306,20 @@
     <row r="62">
       <c r="H62" s="6" t="inlineStr">
         <is>
-          <t>MSM</t>
+          <t>MTN</t>
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.00124717</v>
+        <v>0.00127277</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>MSC INDUSTRIAL CLASS A</t>
+          <t>VAIL RESORTS</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L62" s="6" t="inlineStr"/>
@@ -28335,7 +28335,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.00122874</v>
+        <v>0.0012227</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00116009</v>
+        <v>0.00114217</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.00110026</v>
+        <v>0.00107896</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -28406,15 +28406,15 @@
     <row r="66">
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>FHI</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.0009682499999999999</v>
+        <v>0.00097594</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>FEDERATED HERMES INC CLASS B</t>
+          <t>MOELIS CLASS A</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
@@ -28431,20 +28431,20 @@
     <row r="67">
       <c r="H67" s="6" t="inlineStr">
         <is>
-          <t>KFY</t>
+          <t>FHI</t>
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.0009633899999999999</v>
+        <v>0.0009702900000000001</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>KORN FERRY</t>
+          <t>FEDERATED HERMES INC CLASS B</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L67" s="6" t="inlineStr"/>
@@ -28456,20 +28456,20 @@
     <row r="68">
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>KFY</t>
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.00096317</v>
+        <v>0.0009701600000000001</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>MOELIS CLASS A</t>
+          <t>KORN FERRY</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr"/>
@@ -28485,7 +28485,7 @@
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00091373</v>
+        <v>0.00091338</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -28506,20 +28506,20 @@
     <row r="70">
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>PAG</t>
+          <t>CWEN</t>
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.00090142</v>
+        <v>0.00090731</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
+          <t>CLEARWAY ENERGY INC CLASS C</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr"/>
@@ -28531,20 +28531,20 @@
     <row r="71">
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>CWEN</t>
+          <t>PAG</t>
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.0008986199999999999</v>
+        <v>0.00090034</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>CLEARWAY ENERGY INC CLASS C</t>
+          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr"/>
@@ -28560,7 +28560,7 @@
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.0005681400000000001</v>
+        <v>0.00056977</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
@@ -28585,7 +28585,7 @@
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.00056726</v>
+        <v>0.00056338</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.00051843</v>
+        <v>0.00052084</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
@@ -28635,7 +28635,7 @@
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.0005083900000000001</v>
+        <v>0.00050793</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
@@ -28660,7 +28660,7 @@
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.00050305</v>
+        <v>0.0005036</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.00048028</v>
+        <v>0.00048119</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.00047681</v>
+        <v>0.00047939</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
@@ -28731,22 +28731,18 @@
     <row r="79">
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>WU</t>
+          <t>GVMXX</t>
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00047403</v>
+        <v>0.00047706</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>WESTERN UNION</t>
-        </is>
-      </c>
-      <c r="K79" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+          <t>SSC GOVERNMENT MM GVMXX</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr"/>
       <c r="L79" s="6" t="inlineStr"/>
       <c r="M79" s="7">
         <f>IF(H79="","",IFERROR(VLOOKUP(K79,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28756,20 +28752,20 @@
     <row r="80">
       <c r="H80" s="6" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>WU</t>
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00046603</v>
+        <v>0.00046433</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>INSPERITY</t>
+          <t>WESTERN UNION</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L80" s="6" t="inlineStr"/>
@@ -28781,20 +28777,20 @@
     <row r="81">
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>GABC</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.00045787</v>
+        <v>0.00046177</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>GERMAN AMERICAN BANCORP INC</t>
+          <t>INSPERITY</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -28806,18 +28802,22 @@
     <row r="82">
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>GVMXX</t>
+          <t>GABC</t>
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00045314</v>
+        <v>0.00046028</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>SSC GOVERNMENT MM GVMXX</t>
-        </is>
-      </c>
-      <c r="K82" s="6" t="inlineStr"/>
+          <t>GERMAN AMERICAN BANCORP INC</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="L82" s="6" t="inlineStr"/>
       <c r="M82" s="7">
         <f>IF(H82="","",IFERROR(VLOOKUP(K82,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28831,7 +28831,7 @@
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.000446</v>
+        <v>0.00044801</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.0004269499999999999</v>
+        <v>0.00043115</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00041346</v>
+        <v>0.00041527</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.00037262</v>
+        <v>0.00037503</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.00034789</v>
+        <v>0.0003644399999999999</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00034218</v>
+        <v>0.00034244</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.00031215</v>
+        <v>0.00031166</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00027834</v>
+        <v>0.00027665</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00025134</v>
+        <v>0.00025171</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.000239</v>
+        <v>0.00023786</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.00023141</v>
+        <v>0.00023164</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00022679</v>
+        <v>0.00022693</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00021104</v>
+        <v>0.00021275</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29156,7 +29156,7 @@
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.00019677</v>
+        <v>0.00019693</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
@@ -29181,7 +29181,7 @@
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.00019569</v>
+        <v>0.00019513</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -29206,7 +29206,7 @@
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.00017441</v>
+        <v>0.00017381</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.00016544</v>
+        <v>0.00016662</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29256,7 +29256,7 @@
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00012952</v>
+        <v>0.00012907</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
@@ -29281,7 +29281,7 @@
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00011666</v>
+        <v>0.00011629</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
@@ -29306,7 +29306,7 @@
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>9.779e-05</v>
+        <v>9.601999999999999e-05</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -29327,22 +29327,18 @@
     <row r="103">
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>OXM</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>9.221e-05</v>
+        <v>9.407999999999999e-05</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>OXFORD INDUSTRIES INC</t>
-        </is>
-      </c>
-      <c r="K103" s="6" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
+          <t>US DOLLAR</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr"/>
       <c r="L103" s="6" t="inlineStr"/>
       <c r="M103" s="7">
         <f>IF(H103="","",IFERROR(VLOOKUP(K103,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29352,18 +29348,22 @@
     <row r="104">
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>OXM</t>
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>9.174e-05</v>
+        <v>9.129e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>US DOLLAR</t>
-        </is>
-      </c>
-      <c r="K104" s="6" t="inlineStr"/>
+          <t>OXFORD INDUSTRIES INC</t>
+        </is>
+      </c>
+      <c r="K104" s="6" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
       <c r="L104" s="6" t="inlineStr"/>
       <c r="M104" s="7">
         <f>IF(H104="","",IFERROR(VLOOKUP(K104,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-27 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-28 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -26257,11 +26257,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-23)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-26)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26358,7 +26358,7 @@
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.046169</v>
+        <v>0.04804111</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -26412,25 +26412,25 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04348015</v>
+        <v>0.04293930999999999</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>CONOCOPHILLIPS</t>
+          <t>QUALCOMM</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>코노코필립스</t>
+          <t>퀄컴</t>
         </is>
       </c>
       <c r="M6" s="7">
@@ -26470,25 +26470,25 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04322924</v>
+        <v>0.04273715</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CHEVRON</t>
+          <t>PROCTER &amp; GAMBLE</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>프록터앤드갬블</t>
         </is>
       </c>
       <c r="M7" s="7">
@@ -26528,25 +26528,25 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04274261</v>
+        <v>0.04270364</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>PROCTER &amp; GAMBLE</t>
+          <t>CHEVRON</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>프록터앤드갬블</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="M8" s="7">
@@ -26586,25 +26586,25 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.04169852</v>
+        <v>0.04267935</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>QUALCOMM</t>
+          <t>CONOCOPHILLIPS</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>퀄컴</t>
+          <t>코노코필립스</t>
         </is>
       </c>
       <c r="M9" s="7">
@@ -26648,7 +26648,7 @@
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.04145483</v>
+        <v>0.04094653</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04054933</v>
+        <v>0.04068892</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.03961854</v>
+        <v>0.04008198</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
@@ -26822,7 +26822,7 @@
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03956699</v>
+        <v>0.03962369</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.03803909</v>
+        <v>0.03764625</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
@@ -26924,15 +26924,15 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>ABT</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.03746365</v>
+        <v>0.03705987</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>ABBOTT LABORATORIES</t>
+          <t>MERCK &amp; CO INC</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
@@ -26942,7 +26942,7 @@
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>애보트</t>
+          <t>머크</t>
         </is>
       </c>
       <c r="M15" s="7">
@@ -26972,15 +26972,15 @@
       </c>
       <c r="H16" s="6" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>ABT</t>
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.03658987</v>
+        <v>0.03698267</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>MERCK &amp; CO INC</t>
+          <t>ABBOTT LABORATORIES</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
@@ -26990,7 +26990,7 @@
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>머크</t>
+          <t>애보트</t>
         </is>
       </c>
       <c r="M16" s="7">
@@ -27010,25 +27010,25 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.0361739</v>
+        <v>0.03466334</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>ACCENTURE PLC CLASS A</t>
+          <t>VERIZON COMMUNICATIONS INC</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>액센츄어</t>
+          <t>버라이즌</t>
         </is>
       </c>
       <c r="M17" s="7">
@@ -27048,25 +27048,25 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03386601</v>
+        <v>0.03455249</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>VERIZON COMMUNICATIONS INC</t>
+          <t>ACCENTURE PLC CLASS A</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>버라이즌</t>
+          <t>액센츄어</t>
         </is>
       </c>
       <c r="M18" s="7">
@@ -27081,7 +27081,7 @@
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03084485</v>
+        <v>0.03037897</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.03009173</v>
+        <v>0.03018884</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02939226</v>
+        <v>0.02946372</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02860236</v>
+        <v>0.02795858</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02136829</v>
+        <v>0.02103275</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -27268,7 +27268,7 @@
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.02052788</v>
+        <v>0.0202892</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01883623</v>
+        <v>0.01927179</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -27340,25 +27340,25 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01865952</v>
+        <v>0.01908826</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>COMCAST CLASS A</t>
+          <t>UNITED PARCEL SERVICE INC CLASS B</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>컴캐스트</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="M26" s="7">
@@ -27378,25 +27378,25 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.01797452</v>
+        <v>0.01855952</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>UNITED PARCEL SERVICE INC CLASS B</t>
+          <t>COMCAST CLASS A</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>컴캐스트</t>
         </is>
       </c>
       <c r="M27" s="7">
@@ -27420,7 +27420,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.01613016</v>
+        <v>0.01614128</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01452372</v>
+        <v>0.01453181</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -27492,7 +27492,7 @@
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01439619</v>
+        <v>0.01420322</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01358198</v>
+        <v>0.01353078</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27555,7 +27555,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01151425</v>
+        <v>0.01166936</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01084481</v>
+        <v>0.01101267</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27610,7 +27610,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.00910477</v>
+        <v>0.00904929</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27631,20 +27631,20 @@
     <row r="35">
       <c r="H35" s="6" t="inlineStr">
         <is>
-          <t>PAYX</t>
+          <t>KMB</t>
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.008855439999999999</v>
+        <v>0.008711719999999999</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>PAYCHEX</t>
+          <t>KIMBERLY CLARK</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
@@ -27656,20 +27656,20 @@
     <row r="36">
       <c r="H36" s="6" t="inlineStr">
         <is>
-          <t>KMB</t>
+          <t>PAYX</t>
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.00871745</v>
+        <v>0.008397659999999999</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>KIMBERLY CLARK</t>
+          <t>PAYCHEX</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr"/>
@@ -27681,15 +27681,15 @@
     <row r="37">
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>ARES</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.006526499999999999</v>
+        <v>0.00668471</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>ARES MANAGEMENT CLASS A</t>
+          <t>CINCINNATI FINANCIAL</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -27706,15 +27706,15 @@
     <row r="38">
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>ARES</t>
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.00650634</v>
+        <v>0.006570599999999999</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>CINCINNATI FINANCIAL</t>
+          <t>ARES MANAGEMENT CLASS A</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -27731,20 +27731,20 @@
     <row r="39">
       <c r="H39" s="6" t="inlineStr">
         <is>
-          <t>HSY</t>
+          <t>DRI</t>
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.005884899999999999</v>
+        <v>0.00583219</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>HERSHEY FOODS</t>
+          <t>DARDEN RESTAURANTS INC</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr"/>
@@ -27760,7 +27760,7 @@
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.00582788</v>
+        <v>0.005829879999999999</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
@@ -27781,20 +27781,20 @@
     <row r="41">
       <c r="H41" s="6" t="inlineStr">
         <is>
-          <t>DRI</t>
+          <t>HSY</t>
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.00578861</v>
+        <v>0.005778910000000001</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>DARDEN RESTAURANTS INC</t>
+          <t>HERSHEY FOODS</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr"/>
@@ -27810,7 +27810,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.00527821</v>
+        <v>0.00530752</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.00513027</v>
+        <v>0.00523831</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27860,7 +27860,7 @@
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00493773</v>
+        <v>0.00484885</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -27885,7 +27885,7 @@
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00463751</v>
+        <v>0.00468315</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -27906,20 +27906,20 @@
     <row r="46">
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>DINO</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.00463001</v>
+        <v>0.00443953</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>HF SINCLAIR</t>
+          <t>SNAP ON INC</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr"/>
@@ -27931,20 +27931,20 @@
     <row r="47">
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00442571</v>
+        <v>0.00432334</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>SNAP ON INC</t>
+          <t>EAST WEST BANCORP</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr"/>
@@ -27956,20 +27956,20 @@
     <row r="48">
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.00432752</v>
+        <v>0.0042973</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GENERAL MILLS INC</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
@@ -27981,20 +27981,20 @@
     <row r="49">
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.00431709</v>
+        <v>0.00427252</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>EAST WEST BANCORP</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
@@ -28006,20 +28006,20 @@
     <row r="50">
       <c r="H50" s="6" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>DINO</t>
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00430873</v>
+        <v>0.00423965</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>GENERAL MILLS INC</t>
+          <t>HF SINCLAIR</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr"/>
@@ -28035,7 +28035,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.0025973</v>
+        <v>0.00257137</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00247497</v>
+        <v>0.00249799</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00243118</v>
+        <v>0.00241145</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
@@ -28110,7 +28110,7 @@
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00239598</v>
+        <v>0.00240717</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
@@ -28135,7 +28135,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00209885</v>
+        <v>0.0021063</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28160,7 +28160,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00204011</v>
+        <v>0.00203109</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28185,7 +28185,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.00183693</v>
+        <v>0.00185553</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28210,7 +28210,7 @@
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.00155222</v>
+        <v>0.00153118</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
@@ -28235,7 +28235,7 @@
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00148222</v>
+        <v>0.00150548</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00142633</v>
+        <v>0.00139764</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -28285,7 +28285,7 @@
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00130045</v>
+        <v>0.00130215</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.00127277</v>
+        <v>0.00129564</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
@@ -28335,7 +28335,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.0012227</v>
+        <v>0.00123781</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00114217</v>
+        <v>0.00115746</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.00107896</v>
+        <v>0.00101075</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -28410,7 +28410,7 @@
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.00097594</v>
+        <v>0.00099121</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
@@ -28435,7 +28435,7 @@
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.0009702900000000001</v>
+        <v>0.0009637199999999999</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -28456,20 +28456,20 @@
     <row r="68">
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>KFY</t>
+          <t>CWEN</t>
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.0009701600000000001</v>
+        <v>0.00094911</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>KORN FERRY</t>
+          <t>CLEARWAY ENERGY INC CLASS C</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr"/>
@@ -28481,20 +28481,20 @@
     <row r="69">
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>CVBF</t>
+          <t>KFY</t>
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00091338</v>
+        <v>0.00093986</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>CVB FINANCIAL CORP</t>
+          <t>KORN FERRY</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr"/>
@@ -28506,20 +28506,20 @@
     <row r="70">
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>CWEN</t>
+          <t>CVBF</t>
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.00090731</v>
+        <v>0.00091322</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>CLEARWAY ENERGY INC CLASS C</t>
+          <t>CVB FINANCIAL CORP</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr"/>
@@ -28535,7 +28535,7 @@
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.00090034</v>
+        <v>0.00090431</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
@@ -28556,15 +28556,15 @@
     <row r="72">
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>APAM</t>
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.00056977</v>
+        <v>0.00056335</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>BANNER CORP</t>
+          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
@@ -28581,15 +28581,15 @@
     <row r="73">
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>APAM</t>
+          <t>BANR</t>
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.00056338</v>
+        <v>0.0005627399999999999</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
+          <t>BANNER CORP</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -28610,7 +28610,7 @@
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.00052084</v>
+        <v>0.00051742</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
@@ -28631,15 +28631,15 @@
     <row r="75">
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>IPAR</t>
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.00050793</v>
+        <v>0.0005049200000000001</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>MARZETTI</t>
+          <t>INTERPARFUMS INC</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
@@ -28656,15 +28656,15 @@
     <row r="76">
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>IPAR</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.0005036</v>
+        <v>0.00050434</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>INTERPARFUMS INC</t>
+          <t>MARZETTI</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
@@ -28685,7 +28685,7 @@
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.00048119</v>
+        <v>0.00048079</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
@@ -28710,7 +28710,7 @@
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.00047939</v>
+        <v>0.00047747</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
@@ -28731,18 +28731,22 @@
     <row r="79">
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>GVMXX</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00047706</v>
+        <v>0.00045739</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>SSC GOVERNMENT MM GVMXX</t>
-        </is>
-      </c>
-      <c r="K79" s="6" t="inlineStr"/>
+          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="L79" s="6" t="inlineStr"/>
       <c r="M79" s="7">
         <f>IF(H79="","",IFERROR(VLOOKUP(K79,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28756,7 +28760,7 @@
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00046433</v>
+        <v>0.00044976</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
@@ -28781,7 +28785,7 @@
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.00046177</v>
+        <v>0.00044523</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
@@ -28806,7 +28810,7 @@
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00046028</v>
+        <v>0.00044491</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
@@ -28827,22 +28831,18 @@
     <row r="83">
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>GVMXX</t>
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.00044801</v>
+        <v>0.00043978</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
-        </is>
-      </c>
-      <c r="K83" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+          <t>SSC GOVERNMENT MM GVMXX</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr"/>
       <c r="L83" s="6" t="inlineStr"/>
       <c r="M83" s="7">
         <f>IF(H83="","",IFERROR(VLOOKUP(K83,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28856,7 +28856,7 @@
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.00043115</v>
+        <v>0.00042928</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
@@ -28881,7 +28881,7 @@
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00041527</v>
+        <v>0.00041625</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
@@ -28906,7 +28906,7 @@
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.00037503</v>
+        <v>0.00037696</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.0003644399999999999</v>
+        <v>0.0003632</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
@@ -28956,7 +28956,7 @@
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00034244</v>
+        <v>0.00034245</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -28981,7 +28981,7 @@
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.00031166</v>
+        <v>0.00031602</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00027665</v>
+        <v>0.00027826</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
@@ -29031,7 +29031,7 @@
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00025171</v>
+        <v>0.00025073</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.00023786</v>
+        <v>0.00023693</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -29081,7 +29081,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.00023164</v>
+        <v>0.00023314</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29106,7 +29106,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00022693</v>
+        <v>0.00022957</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00021275</v>
+        <v>0.00021191</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29152,15 +29152,15 @@
     <row r="96">
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>IBCP</t>
+          <t>THFF</t>
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.00019693</v>
+        <v>0.0001993</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>INDEPENDENT BANK CORP</t>
+          <t>FIRST FINANCIAL CORPORATION CORP</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
@@ -29177,15 +29177,15 @@
     <row r="97">
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>THFF</t>
+          <t>IBCP</t>
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.00019513</v>
+        <v>0.00019839</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>FIRST FINANCIAL CORPORATION CORP</t>
+          <t>INDEPENDENT BANK CORP</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
@@ -29206,7 +29206,7 @@
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.00017381</v>
+        <v>0.0001776</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -29231,7 +29231,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.00016662</v>
+        <v>0.00016834</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29252,22 +29252,18 @@
     <row r="100">
       <c r="H100" s="6" t="inlineStr">
         <is>
-          <t>EBF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00012907</v>
+        <v>0.00014105</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>ENNIS INC</t>
-        </is>
-      </c>
-      <c r="K100" s="6" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
+          <t>US DOLLAR</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr"/>
       <c r="L100" s="6" t="inlineStr"/>
       <c r="M100" s="7">
         <f>IF(H100="","",IFERROR(VLOOKUP(K100,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29277,20 +29273,20 @@
     <row r="101">
       <c r="H101" s="6" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>EBF</t>
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00011629</v>
+        <v>0.00012949</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>AMERISAFE INC</t>
+          <t>ENNIS INC</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -29302,20 +29298,20 @@
     <row r="102">
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>ETD</t>
+          <t>AMSF</t>
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>9.601999999999999e-05</v>
+        <v>0.00011334</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>ETHAN ALLEN INTERIORS</t>
+          <t>AMERISAFE INC</t>
         </is>
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr"/>
@@ -29327,18 +29323,22 @@
     <row r="103">
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>ETD</t>
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>9.407999999999999e-05</v>
+        <v>9.565000000000001e-05</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>US DOLLAR</t>
-        </is>
-      </c>
-      <c r="K103" s="6" t="inlineStr"/>
+          <t>ETHAN ALLEN INTERIORS</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
       <c r="L103" s="6" t="inlineStr"/>
       <c r="M103" s="7">
         <f>IF(H103="","",IFERROR(VLOOKUP(K103,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -29352,7 +29352,7 @@
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>9.129e-05</v>
+        <v>9.143e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-28 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-29 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -11996,11 +11996,11 @@
         </is>
       </c>
       <c r="B34" s="19" t="n">
-        <v>0.0318</v>
+        <v>0.0314</v>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2026-10-20 기준 · 최근 30일 순투자수익(보수 차감) 연 환산</t>
+          <t>2026-10-27 기준 · 최근 30일 순투자수익(보수 차감) 연 환산</t>
         </is>
       </c>
     </row>
@@ -20053,7 +20053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F357"/>
+  <dimension ref="A1:F359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -20918,22 +20918,22 @@
     <row r="41">
       <c r="A41" s="46" t="inlineStr">
         <is>
-          <t>446720</t>
+          <t>458730</t>
         </is>
       </c>
       <c r="B41" s="33" t="inlineStr">
         <is>
-          <t>SOL 미국배당다우존스</t>
+          <t>TIGER 미국배당다우존스</t>
         </is>
       </c>
       <c r="C41" s="26" t="n">
-        <v>44923</v>
+        <v>46324</v>
       </c>
       <c r="D41" s="47" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E41" s="48" t="n">
-        <v>0.003779</v>
+        <v>0.002362</v>
       </c>
     </row>
     <row r="42">
@@ -20948,13 +20948,13 @@
         </is>
       </c>
       <c r="C42" s="26" t="n">
-        <v>44956</v>
+        <v>44923</v>
       </c>
       <c r="D42" s="47" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="E42" s="48" t="n">
-        <v>0.001938</v>
+        <v>0.003779</v>
       </c>
     </row>
     <row r="43">
@@ -20969,13 +20969,13 @@
         </is>
       </c>
       <c r="C43" s="26" t="n">
-        <v>44984</v>
+        <v>44956</v>
       </c>
       <c r="D43" s="47" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="E43" s="48" t="n">
-        <v>0.003103</v>
+        <v>0.001938</v>
       </c>
     </row>
     <row r="44">
@@ -20990,13 +20990,13 @@
         </is>
       </c>
       <c r="C44" s="26" t="n">
-        <v>45015</v>
+        <v>44984</v>
       </c>
       <c r="D44" s="47" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E44" s="48" t="n">
-        <v>0.003162</v>
+        <v>0.003103</v>
       </c>
     </row>
     <row r="45">
@@ -21011,13 +21011,13 @@
         </is>
       </c>
       <c r="C45" s="26" t="n">
-        <v>45043</v>
+        <v>45015</v>
       </c>
       <c r="D45" s="47" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E45" s="48" t="n">
-        <v>0.002106</v>
+        <v>0.003162</v>
       </c>
     </row>
     <row r="46">
@@ -21032,13 +21032,13 @@
         </is>
       </c>
       <c r="C46" s="26" t="n">
-        <v>45076</v>
+        <v>45043</v>
       </c>
       <c r="D46" s="47" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E46" s="48" t="n">
-        <v>0.003642</v>
+        <v>0.002106</v>
       </c>
     </row>
     <row r="47">
@@ -21053,13 +21053,13 @@
         </is>
       </c>
       <c r="C47" s="26" t="n">
-        <v>45106</v>
+        <v>45076</v>
       </c>
       <c r="D47" s="47" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E47" s="48" t="n">
-        <v>0.003458</v>
+        <v>0.003642</v>
       </c>
     </row>
     <row r="48">
@@ -21074,13 +21074,13 @@
         </is>
       </c>
       <c r="C48" s="26" t="n">
-        <v>45135</v>
+        <v>45106</v>
       </c>
       <c r="D48" s="47" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E48" s="48" t="n">
-        <v>0.00274</v>
+        <v>0.003458</v>
       </c>
     </row>
     <row r="49">
@@ -21095,13 +21095,13 @@
         </is>
       </c>
       <c r="C49" s="26" t="n">
-        <v>45168</v>
+        <v>45135</v>
       </c>
       <c r="D49" s="47" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="E49" s="48" t="n">
-        <v>0.003346</v>
+        <v>0.00274</v>
       </c>
     </row>
     <row r="50">
@@ -21116,13 +21116,13 @@
         </is>
       </c>
       <c r="C50" s="26" t="n">
-        <v>45195</v>
+        <v>45168</v>
       </c>
       <c r="D50" s="47" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E50" s="48" t="n">
-        <v>0.002873</v>
+        <v>0.003346</v>
       </c>
     </row>
     <row r="51">
@@ -21137,13 +21137,13 @@
         </is>
       </c>
       <c r="C51" s="26" t="n">
-        <v>45229</v>
+        <v>45195</v>
       </c>
       <c r="D51" s="47" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E51" s="48" t="n">
-        <v>0.002864</v>
+        <v>0.002873</v>
       </c>
     </row>
     <row r="52">
@@ -21158,13 +21158,13 @@
         </is>
       </c>
       <c r="C52" s="26" t="n">
-        <v>45259</v>
+        <v>45229</v>
       </c>
       <c r="D52" s="47" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="E52" s="48" t="n">
-        <v>0.004202</v>
+        <v>0.002864</v>
       </c>
     </row>
     <row r="53">
@@ -21179,13 +21179,13 @@
         </is>
       </c>
       <c r="C53" s="26" t="n">
-        <v>45287</v>
+        <v>45259</v>
       </c>
       <c r="D53" s="47" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="E53" s="48" t="n">
-        <v>0.0031</v>
+        <v>0.004202</v>
       </c>
     </row>
     <row r="54">
@@ -21200,13 +21200,13 @@
         </is>
       </c>
       <c r="C54" s="26" t="n">
-        <v>45321</v>
+        <v>45287</v>
       </c>
       <c r="D54" s="47" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E54" s="48" t="n">
-        <v>0.00267</v>
+        <v>0.0031</v>
       </c>
     </row>
     <row r="55">
@@ -21221,13 +21221,13 @@
         </is>
       </c>
       <c r="C55" s="26" t="n">
-        <v>45350</v>
+        <v>45321</v>
       </c>
       <c r="D55" s="47" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E55" s="48" t="n">
-        <v>0.002969</v>
+        <v>0.00267</v>
       </c>
     </row>
     <row r="56">
@@ -21242,13 +21242,13 @@
         </is>
       </c>
       <c r="C56" s="26" t="n">
-        <v>45379</v>
+        <v>45350</v>
       </c>
       <c r="D56" s="47" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E56" s="48" t="n">
-        <v>0.002293</v>
+        <v>0.002969</v>
       </c>
     </row>
     <row r="57">
@@ -21263,13 +21263,13 @@
         </is>
       </c>
       <c r="C57" s="26" t="n">
-        <v>45411</v>
+        <v>45379</v>
       </c>
       <c r="D57" s="47" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E57" s="48" t="n">
-        <v>0.003152</v>
+        <v>0.002293</v>
       </c>
     </row>
     <row r="58">
@@ -21284,13 +21284,13 @@
         </is>
       </c>
       <c r="C58" s="26" t="n">
-        <v>45442</v>
+        <v>45411</v>
       </c>
       <c r="D58" s="47" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="E58" s="48" t="n">
-        <v>0.003771</v>
+        <v>0.003152</v>
       </c>
     </row>
     <row r="59">
@@ -21305,13 +21305,13 @@
         </is>
       </c>
       <c r="C59" s="26" t="n">
-        <v>45470</v>
+        <v>45442</v>
       </c>
       <c r="D59" s="47" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E59" s="48" t="n">
-        <v>0.003575</v>
+        <v>0.003771</v>
       </c>
     </row>
     <row r="60">
@@ -21326,13 +21326,13 @@
         </is>
       </c>
       <c r="C60" s="26" t="n">
-        <v>45503</v>
+        <v>45470</v>
       </c>
       <c r="D60" s="47" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E60" s="48" t="n">
-        <v>0.003132</v>
+        <v>0.003575</v>
       </c>
     </row>
     <row r="61">
@@ -21347,13 +21347,13 @@
         </is>
       </c>
       <c r="C61" s="26" t="n">
-        <v>45533</v>
+        <v>45503</v>
       </c>
       <c r="D61" s="47" t="n">
         <v>35</v>
       </c>
       <c r="E61" s="48" t="n">
-        <v>0.003204</v>
+        <v>0.003132</v>
       </c>
     </row>
     <row r="62">
@@ -21368,13 +21368,13 @@
         </is>
       </c>
       <c r="C62" s="26" t="n">
-        <v>45562</v>
+        <v>45533</v>
       </c>
       <c r="D62" s="47" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E62" s="48" t="n">
-        <v>0.002759</v>
+        <v>0.003204</v>
       </c>
     </row>
     <row r="63">
@@ -21389,13 +21389,13 @@
         </is>
       </c>
       <c r="C63" s="26" t="n">
-        <v>45595</v>
+        <v>45562</v>
       </c>
       <c r="D63" s="47" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E63" s="48" t="n">
-        <v>0.002775</v>
+        <v>0.002759</v>
       </c>
     </row>
     <row r="64">
@@ -21410,13 +21410,13 @@
         </is>
       </c>
       <c r="C64" s="26" t="n">
-        <v>45624</v>
+        <v>45595</v>
       </c>
       <c r="D64" s="47" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="E64" s="48" t="n">
-        <v>0.003817</v>
+        <v>0.002775</v>
       </c>
     </row>
     <row r="65">
@@ -21431,13 +21431,13 @@
         </is>
       </c>
       <c r="C65" s="26" t="n">
-        <v>45653</v>
+        <v>45624</v>
       </c>
       <c r="D65" s="47" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="E65" s="48" t="n">
-        <v>0.002942</v>
+        <v>0.003817</v>
       </c>
     </row>
     <row r="66">
@@ -21452,13 +21452,13 @@
         </is>
       </c>
       <c r="C66" s="26" t="n">
-        <v>45681</v>
+        <v>45653</v>
       </c>
       <c r="D66" s="47" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E66" s="48" t="n">
-        <v>0.003564</v>
+        <v>0.002942</v>
       </c>
     </row>
     <row r="67">
@@ -21473,13 +21473,13 @@
         </is>
       </c>
       <c r="C67" s="26" t="n">
-        <v>45715</v>
+        <v>45681</v>
       </c>
       <c r="D67" s="47" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="E67" s="48" t="n">
-        <v>0.002692</v>
+        <v>0.003564</v>
       </c>
     </row>
     <row r="68">
@@ -21494,13 +21494,13 @@
         </is>
       </c>
       <c r="C68" s="26" t="n">
-        <v>45744</v>
+        <v>45715</v>
       </c>
       <c r="D68" s="47" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E68" s="48" t="n">
-        <v>0.003181</v>
+        <v>0.002692</v>
       </c>
     </row>
     <row r="69">
@@ -21515,13 +21515,13 @@
         </is>
       </c>
       <c r="C69" s="26" t="n">
-        <v>45776</v>
+        <v>45744</v>
       </c>
       <c r="D69" s="47" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E69" s="48" t="n">
-        <v>0.002409</v>
+        <v>0.003181</v>
       </c>
     </row>
     <row r="70">
@@ -21536,13 +21536,13 @@
         </is>
       </c>
       <c r="C70" s="26" t="n">
-        <v>45806</v>
+        <v>45776</v>
       </c>
       <c r="D70" s="47" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E70" s="48" t="n">
-        <v>0.002857</v>
+        <v>0.002409</v>
       </c>
     </row>
     <row r="71">
@@ -21557,13 +21557,13 @@
         </is>
       </c>
       <c r="C71" s="26" t="n">
-        <v>45835</v>
+        <v>45806</v>
       </c>
       <c r="D71" s="47" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E71" s="48" t="n">
-        <v>0.00315</v>
+        <v>0.002857</v>
       </c>
     </row>
     <row r="72">
@@ -21578,13 +21578,13 @@
         </is>
       </c>
       <c r="C72" s="26" t="n">
-        <v>45868</v>
+        <v>45835</v>
       </c>
       <c r="D72" s="47" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E72" s="48" t="n">
-        <v>0.002532</v>
+        <v>0.00315</v>
       </c>
     </row>
     <row r="73">
@@ -21599,13 +21599,13 @@
         </is>
       </c>
       <c r="C73" s="26" t="n">
-        <v>45897</v>
+        <v>45868</v>
       </c>
       <c r="D73" s="47" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E73" s="48" t="n">
-        <v>0.002839</v>
+        <v>0.002532</v>
       </c>
     </row>
     <row r="74">
@@ -21620,13 +21620,13 @@
         </is>
       </c>
       <c r="C74" s="26" t="n">
-        <v>45929</v>
+        <v>45897</v>
       </c>
       <c r="D74" s="47" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E74" s="48" t="n">
-        <v>0.00314</v>
+        <v>0.002839</v>
       </c>
     </row>
     <row r="75">
@@ -21641,13 +21641,13 @@
         </is>
       </c>
       <c r="C75" s="26" t="n">
-        <v>45960</v>
+        <v>45929</v>
       </c>
       <c r="D75" s="47" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E75" s="48" t="n">
-        <v>0.003026</v>
+        <v>0.00314</v>
       </c>
     </row>
     <row r="76">
@@ -21662,13 +21662,13 @@
         </is>
       </c>
       <c r="C76" s="26" t="n">
-        <v>45988</v>
+        <v>45960</v>
       </c>
       <c r="D76" s="47" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E76" s="48" t="n">
-        <v>0.003017</v>
+        <v>0.003026</v>
       </c>
     </row>
     <row r="77">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="C77" s="26" t="n">
-        <v>46020</v>
+        <v>45988</v>
       </c>
       <c r="D77" s="47" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E77" s="48" t="n">
-        <v>0.003141</v>
+        <v>0.003017</v>
       </c>
     </row>
     <row r="78">
@@ -21704,13 +21704,13 @@
         </is>
       </c>
       <c r="C78" s="26" t="n">
-        <v>46051</v>
+        <v>46020</v>
       </c>
       <c r="D78" s="47" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E78" s="48" t="n">
-        <v>0.002463</v>
+        <v>0.003141</v>
       </c>
     </row>
     <row r="79">
@@ -21725,13 +21725,13 @@
         </is>
       </c>
       <c r="C79" s="26" t="n">
-        <v>46079</v>
+        <v>46051</v>
       </c>
       <c r="D79" s="47" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E79" s="48" t="n">
-        <v>0.00266</v>
+        <v>0.002463</v>
       </c>
     </row>
     <row r="80">
@@ -21746,13 +21746,13 @@
         </is>
       </c>
       <c r="C80" s="26" t="n">
-        <v>46111</v>
+        <v>46079</v>
       </c>
       <c r="D80" s="47" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E80" s="48" t="n">
-        <v>0.00244</v>
+        <v>0.00266</v>
       </c>
     </row>
     <row r="81">
@@ -21767,13 +21767,13 @@
         </is>
       </c>
       <c r="C81" s="26" t="n">
-        <v>46141</v>
+        <v>46111</v>
       </c>
       <c r="D81" s="47" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E81" s="48" t="n">
-        <v>0.002241</v>
+        <v>0.00244</v>
       </c>
     </row>
     <row r="82">
@@ -21788,13 +21788,13 @@
         </is>
       </c>
       <c r="C82" s="26" t="n">
-        <v>46170</v>
+        <v>46141</v>
       </c>
       <c r="D82" s="47" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E82" s="48" t="n">
-        <v>0.002313</v>
+        <v>0.002241</v>
       </c>
     </row>
     <row r="83">
@@ -21809,13 +21809,13 @@
         </is>
       </c>
       <c r="C83" s="26" t="n">
-        <v>46202</v>
+        <v>46170</v>
       </c>
       <c r="D83" s="47" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="E83" s="48" t="n">
-        <v>0.002932</v>
+        <v>0.002313</v>
       </c>
     </row>
     <row r="84">
@@ -21830,13 +21830,13 @@
         </is>
       </c>
       <c r="C84" s="26" t="n">
-        <v>46233</v>
+        <v>46202</v>
       </c>
       <c r="D84" s="47" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E84" s="48" t="n">
-        <v>0.00245</v>
+        <v>0.002932</v>
       </c>
     </row>
     <row r="85">
@@ -21851,13 +21851,13 @@
         </is>
       </c>
       <c r="C85" s="26" t="n">
-        <v>46262</v>
+        <v>46233</v>
       </c>
       <c r="D85" s="47" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="E85" s="48" t="n">
-        <v>0.001926</v>
+        <v>0.00245</v>
       </c>
     </row>
     <row r="86">
@@ -21872,55 +21872,55 @@
         </is>
       </c>
       <c r="C86" s="26" t="n">
-        <v>46294</v>
+        <v>46262</v>
       </c>
       <c r="D86" s="47" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E86" s="48" t="n">
-        <v>0.0028</v>
+        <v>0.001926</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="46" t="inlineStr">
         <is>
-          <t>402970</t>
+          <t>446720</t>
         </is>
       </c>
       <c r="B87" s="33" t="inlineStr">
         <is>
-          <t>ACE 미국배당다우존스</t>
+          <t>SOL 미국배당다우존스</t>
         </is>
       </c>
       <c r="C87" s="26" t="n">
-        <v>44588</v>
+        <v>46294</v>
       </c>
       <c r="D87" s="47" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="E87" s="48" t="n">
-        <v>0.005337</v>
+        <v>0.0028</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="46" t="inlineStr">
         <is>
-          <t>402970</t>
+          <t>446720</t>
         </is>
       </c>
       <c r="B88" s="33" t="inlineStr">
         <is>
-          <t>ACE 미국배당다우존스</t>
+          <t>SOL 미국배당다우존스</t>
         </is>
       </c>
       <c r="C88" s="26" t="n">
-        <v>44679</v>
+        <v>46324</v>
       </c>
       <c r="D88" s="47" t="n">
-        <v>65</v>
+        <v>32</v>
       </c>
       <c r="E88" s="48" t="n">
-        <v>0.006095000000000001</v>
+        <v>0.002357</v>
       </c>
     </row>
     <row r="89">
@@ -21935,13 +21935,13 @@
         </is>
       </c>
       <c r="C89" s="26" t="n">
-        <v>44770</v>
+        <v>44588</v>
       </c>
       <c r="D89" s="47" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E89" s="48" t="n">
-        <v>0.006222</v>
+        <v>0.005337</v>
       </c>
     </row>
     <row r="90">
@@ -21956,13 +21956,13 @@
         </is>
       </c>
       <c r="C90" s="26" t="n">
-        <v>44862</v>
+        <v>44679</v>
       </c>
       <c r="D90" s="47" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="E90" s="48" t="n">
-        <v>0.009284000000000001</v>
+        <v>0.006095000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -21977,13 +21977,13 @@
         </is>
       </c>
       <c r="C91" s="26" t="n">
-        <v>44956</v>
+        <v>44770</v>
       </c>
       <c r="D91" s="47" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E91" s="48" t="n">
-        <v>0.008215</v>
+        <v>0.006222</v>
       </c>
     </row>
     <row r="92">
@@ -21998,13 +21998,13 @@
         </is>
       </c>
       <c r="C92" s="26" t="n">
-        <v>45043</v>
+        <v>44862</v>
       </c>
       <c r="D92" s="47" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E92" s="48" t="n">
-        <v>0.009443</v>
+        <v>0.009284000000000001</v>
       </c>
     </row>
     <row r="93">
@@ -22019,13 +22019,13 @@
         </is>
       </c>
       <c r="C93" s="26" t="n">
-        <v>45135</v>
+        <v>44956</v>
       </c>
       <c r="D93" s="47" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="E93" s="48" t="n">
-        <v>0.007578000000000001</v>
+        <v>0.008215</v>
       </c>
     </row>
     <row r="94">
@@ -22040,13 +22040,13 @@
         </is>
       </c>
       <c r="C94" s="26" t="n">
-        <v>45168</v>
+        <v>45043</v>
       </c>
       <c r="D94" s="47" t="n">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="E94" s="48" t="n">
-        <v>0.003306</v>
+        <v>0.009443</v>
       </c>
     </row>
     <row r="95">
@@ -22061,13 +22061,13 @@
         </is>
       </c>
       <c r="C95" s="26" t="n">
-        <v>45195</v>
+        <v>45135</v>
       </c>
       <c r="D95" s="47" t="n">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="E95" s="48" t="n">
-        <v>0.004327</v>
+        <v>0.007578000000000001</v>
       </c>
     </row>
     <row r="96">
@@ -22082,13 +22082,13 @@
         </is>
       </c>
       <c r="C96" s="26" t="n">
-        <v>45229</v>
+        <v>45168</v>
       </c>
       <c r="D96" s="47" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E96" s="48" t="n">
-        <v>0.002493</v>
+        <v>0.003306</v>
       </c>
     </row>
     <row r="97">
@@ -22103,13 +22103,13 @@
         </is>
       </c>
       <c r="C97" s="26" t="n">
-        <v>45259</v>
+        <v>45195</v>
       </c>
       <c r="D97" s="47" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E97" s="48" t="n">
-        <v>0.0037</v>
+        <v>0.004327</v>
       </c>
     </row>
     <row r="98">
@@ -22124,13 +22124,13 @@
         </is>
       </c>
       <c r="C98" s="26" t="n">
-        <v>45287</v>
+        <v>45229</v>
       </c>
       <c r="D98" s="47" t="n">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="E98" s="48" t="n">
-        <v>0.004204</v>
+        <v>0.002493</v>
       </c>
     </row>
     <row r="99">
@@ -22145,13 +22145,13 @@
         </is>
       </c>
       <c r="C99" s="26" t="n">
-        <v>45321</v>
+        <v>45259</v>
       </c>
       <c r="D99" s="47" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E99" s="48" t="n">
-        <v>0.002685</v>
+        <v>0.0037</v>
       </c>
     </row>
     <row r="100">
@@ -22166,13 +22166,13 @@
         </is>
       </c>
       <c r="C100" s="26" t="n">
-        <v>45350</v>
+        <v>45287</v>
       </c>
       <c r="D100" s="47" t="n">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="E100" s="48" t="n">
-        <v>0.003045</v>
+        <v>0.004204</v>
       </c>
     </row>
     <row r="101">
@@ -22187,13 +22187,13 @@
         </is>
       </c>
       <c r="C101" s="26" t="n">
-        <v>45379</v>
+        <v>45321</v>
       </c>
       <c r="D101" s="47" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E101" s="48" t="n">
-        <v>0.003805</v>
+        <v>0.002685</v>
       </c>
     </row>
     <row r="102">
@@ -22208,13 +22208,13 @@
         </is>
       </c>
       <c r="C102" s="26" t="n">
-        <v>45411</v>
+        <v>45350</v>
       </c>
       <c r="D102" s="47" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E102" s="48" t="n">
-        <v>0.002771</v>
+        <v>0.003045</v>
       </c>
     </row>
     <row r="103">
@@ -22229,13 +22229,13 @@
         </is>
       </c>
       <c r="C103" s="26" t="n">
-        <v>45442</v>
+        <v>45379</v>
       </c>
       <c r="D103" s="47" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E103" s="48" t="n">
-        <v>0.003413</v>
+        <v>0.003805</v>
       </c>
     </row>
     <row r="104">
@@ -22250,13 +22250,13 @@
         </is>
       </c>
       <c r="C104" s="26" t="n">
-        <v>45470</v>
+        <v>45411</v>
       </c>
       <c r="D104" s="47" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="E104" s="48" t="n">
-        <v>0.003742</v>
+        <v>0.002771</v>
       </c>
     </row>
     <row r="105">
@@ -22271,13 +22271,13 @@
         </is>
       </c>
       <c r="C105" s="26" t="n">
-        <v>45503</v>
+        <v>45442</v>
       </c>
       <c r="D105" s="47" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E105" s="48" t="n">
-        <v>0.00356</v>
+        <v>0.003413</v>
       </c>
     </row>
     <row r="106">
@@ -22292,13 +22292,13 @@
         </is>
       </c>
       <c r="C106" s="26" t="n">
-        <v>45547</v>
+        <v>45470</v>
       </c>
       <c r="D106" s="47" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="E106" s="48" t="n">
-        <v>0.00466</v>
+        <v>0.003742</v>
       </c>
     </row>
     <row r="107">
@@ -22313,13 +22313,13 @@
         </is>
       </c>
       <c r="C107" s="26" t="n">
-        <v>45579</v>
+        <v>45503</v>
       </c>
       <c r="D107" s="47" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E107" s="48" t="n">
-        <v>0.003633</v>
+        <v>0.00356</v>
       </c>
     </row>
     <row r="108">
@@ -22334,13 +22334,13 @@
         </is>
       </c>
       <c r="C108" s="26" t="n">
-        <v>45610</v>
+        <v>45547</v>
       </c>
       <c r="D108" s="47" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="E108" s="48" t="n">
-        <v>0.002276</v>
+        <v>0.00466</v>
       </c>
     </row>
     <row r="109">
@@ -22355,13 +22355,13 @@
         </is>
       </c>
       <c r="C109" s="26" t="n">
-        <v>45638</v>
+        <v>45579</v>
       </c>
       <c r="D109" s="47" t="n">
-        <v>68</v>
+        <v>45</v>
       </c>
       <c r="E109" s="48" t="n">
-        <v>0.005121</v>
+        <v>0.003633</v>
       </c>
     </row>
     <row r="110">
@@ -22376,13 +22376,13 @@
         </is>
       </c>
       <c r="C110" s="26" t="n">
-        <v>45671</v>
+        <v>45610</v>
       </c>
       <c r="D110" s="47" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E110" s="48" t="n">
-        <v>0.003025</v>
+        <v>0.002276</v>
       </c>
     </row>
     <row r="111">
@@ -22397,13 +22397,13 @@
         </is>
       </c>
       <c r="C111" s="26" t="n">
-        <v>45701</v>
+        <v>45638</v>
       </c>
       <c r="D111" s="47" t="n">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="E111" s="48" t="n">
-        <v>0.002142</v>
+        <v>0.005121</v>
       </c>
     </row>
     <row r="112">
@@ -22418,13 +22418,13 @@
         </is>
       </c>
       <c r="C112" s="26" t="n">
-        <v>45729</v>
+        <v>45671</v>
       </c>
       <c r="D112" s="47" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E112" s="48" t="n">
-        <v>0.003543</v>
+        <v>0.003025</v>
       </c>
     </row>
     <row r="113">
@@ -22439,13 +22439,13 @@
         </is>
       </c>
       <c r="C113" s="26" t="n">
-        <v>45761</v>
+        <v>45701</v>
       </c>
       <c r="D113" s="47" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E113" s="48" t="n">
-        <v>0.002925</v>
+        <v>0.002142</v>
       </c>
     </row>
     <row r="114">
@@ -22460,13 +22460,13 @@
         </is>
       </c>
       <c r="C114" s="26" t="n">
-        <v>45791</v>
+        <v>45729</v>
       </c>
       <c r="D114" s="47" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="E114" s="48" t="n">
-        <v>0.001743</v>
+        <v>0.003543</v>
       </c>
     </row>
     <row r="115">
@@ -22481,13 +22481,13 @@
         </is>
       </c>
       <c r="C115" s="26" t="n">
-        <v>45820</v>
+        <v>45761</v>
       </c>
       <c r="D115" s="47" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E115" s="48" t="n">
-        <v>0.003794</v>
+        <v>0.002925</v>
       </c>
     </row>
     <row r="116">
@@ -22502,13 +22502,13 @@
         </is>
       </c>
       <c r="C116" s="26" t="n">
-        <v>45852</v>
+        <v>45791</v>
       </c>
       <c r="D116" s="47" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E116" s="48" t="n">
-        <v>0.003116</v>
+        <v>0.001743</v>
       </c>
     </row>
     <row r="117">
@@ -22523,13 +22523,13 @@
         </is>
       </c>
       <c r="C117" s="26" t="n">
-        <v>45882</v>
+        <v>45820</v>
       </c>
       <c r="D117" s="47" t="n">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="E117" s="48" t="n">
-        <v>0.001665</v>
+        <v>0.003794</v>
       </c>
     </row>
     <row r="118">
@@ -22544,13 +22544,13 @@
         </is>
       </c>
       <c r="C118" s="26" t="n">
-        <v>45912</v>
+        <v>45852</v>
       </c>
       <c r="D118" s="47" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E118" s="48" t="n">
-        <v>0.003577</v>
+        <v>0.003116</v>
       </c>
     </row>
     <row r="119">
@@ -22565,13 +22565,13 @@
         </is>
       </c>
       <c r="C119" s="26" t="n">
-        <v>45944</v>
+        <v>45882</v>
       </c>
       <c r="D119" s="47" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="E119" s="48" t="n">
-        <v>0.003019</v>
+        <v>0.001665</v>
       </c>
     </row>
     <row r="120">
@@ -22586,13 +22586,13 @@
         </is>
       </c>
       <c r="C120" s="26" t="n">
-        <v>45974</v>
+        <v>45912</v>
       </c>
       <c r="D120" s="47" t="n">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E120" s="48" t="n">
-        <v>0.001641</v>
+        <v>0.003577</v>
       </c>
     </row>
     <row r="121">
@@ -22607,13 +22607,13 @@
         </is>
       </c>
       <c r="C121" s="26" t="n">
-        <v>46003</v>
+        <v>45944</v>
       </c>
       <c r="D121" s="47" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E121" s="48" t="n">
-        <v>0.00404</v>
+        <v>0.003019</v>
       </c>
     </row>
     <row r="122">
@@ -22628,13 +22628,13 @@
         </is>
       </c>
       <c r="C122" s="26" t="n">
-        <v>46036</v>
+        <v>45974</v>
       </c>
       <c r="D122" s="47" t="n">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="E122" s="48" t="n">
-        <v>0.002885</v>
+        <v>0.001641</v>
       </c>
     </row>
     <row r="123">
@@ -22649,13 +22649,13 @@
         </is>
       </c>
       <c r="C123" s="26" t="n">
-        <v>46065</v>
+        <v>46003</v>
       </c>
       <c r="D123" s="47" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="E123" s="48" t="n">
-        <v>0.00163</v>
+        <v>0.00404</v>
       </c>
     </row>
     <row r="124">
@@ -22670,13 +22670,13 @@
         </is>
       </c>
       <c r="C124" s="26" t="n">
-        <v>46093</v>
+        <v>46036</v>
       </c>
       <c r="D124" s="47" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="E124" s="48" t="n">
-        <v>0.003151</v>
+        <v>0.002885</v>
       </c>
     </row>
     <row r="125">
@@ -22691,13 +22691,13 @@
         </is>
       </c>
       <c r="C125" s="26" t="n">
-        <v>46126</v>
+        <v>46065</v>
       </c>
       <c r="D125" s="47" t="n">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="E125" s="48" t="n">
-        <v>0.002994</v>
+        <v>0.00163</v>
       </c>
     </row>
     <row r="126">
@@ -22712,13 +22712,13 @@
         </is>
       </c>
       <c r="C126" s="26" t="n">
-        <v>46156</v>
+        <v>46093</v>
       </c>
       <c r="D126" s="47" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="E126" s="48" t="n">
-        <v>0.001774</v>
+        <v>0.003151</v>
       </c>
     </row>
     <row r="127">
@@ -22733,13 +22733,13 @@
         </is>
       </c>
       <c r="C127" s="26" t="n">
-        <v>46185</v>
+        <v>46126</v>
       </c>
       <c r="D127" s="47" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="E127" s="48" t="n">
-        <v>0.002525</v>
+        <v>0.002994</v>
       </c>
     </row>
     <row r="128">
@@ -22754,13 +22754,13 @@
         </is>
       </c>
       <c r="C128" s="26" t="n">
-        <v>46217</v>
+        <v>46156</v>
       </c>
       <c r="D128" s="47" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="E128" s="48" t="n">
-        <v>0.003178</v>
+        <v>0.001774</v>
       </c>
     </row>
     <row r="129">
@@ -22775,13 +22775,13 @@
         </is>
       </c>
       <c r="C129" s="26" t="n">
-        <v>46247</v>
+        <v>46185</v>
       </c>
       <c r="D129" s="47" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="E129" s="48" t="n">
-        <v>0.001604</v>
+        <v>0.002525</v>
       </c>
     </row>
     <row r="130">
@@ -22796,13 +22796,13 @@
         </is>
       </c>
       <c r="C130" s="26" t="n">
-        <v>46279</v>
+        <v>46217</v>
       </c>
       <c r="D130" s="47" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E130" s="48" t="n">
-        <v>0.002377</v>
+        <v>0.003178</v>
       </c>
     </row>
     <row r="131">
@@ -22817,55 +22817,55 @@
         </is>
       </c>
       <c r="C131" s="26" t="n">
-        <v>46309</v>
+        <v>46247</v>
       </c>
       <c r="D131" s="47" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="E131" s="48" t="n">
-        <v>0.002624</v>
+        <v>0.001604</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="46" t="inlineStr">
         <is>
-          <t>489250</t>
+          <t>402970</t>
         </is>
       </c>
       <c r="B132" s="33" t="inlineStr">
         <is>
-          <t>KODEX 미국배당다우존스</t>
+          <t>ACE 미국배당다우존스</t>
         </is>
       </c>
       <c r="C132" s="26" t="n">
-        <v>45547</v>
+        <v>46279</v>
       </c>
       <c r="D132" s="47" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E132" s="48" t="n">
-        <v>0.002954</v>
+        <v>0.002377</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="46" t="inlineStr">
         <is>
-          <t>489250</t>
+          <t>402970</t>
         </is>
       </c>
       <c r="B133" s="33" t="inlineStr">
         <is>
-          <t>KODEX 미국배당다우존스</t>
+          <t>ACE 미국배당다우존스</t>
         </is>
       </c>
       <c r="C133" s="26" t="n">
-        <v>45579</v>
+        <v>46309</v>
       </c>
       <c r="D133" s="47" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E133" s="48" t="n">
-        <v>0.003148</v>
+        <v>0.002624</v>
       </c>
     </row>
     <row r="134">
@@ -22880,13 +22880,13 @@
         </is>
       </c>
       <c r="C134" s="26" t="n">
-        <v>45610</v>
+        <v>45547</v>
       </c>
       <c r="D134" s="47" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E134" s="48" t="n">
-        <v>0.002509</v>
+        <v>0.002954</v>
       </c>
     </row>
     <row r="135">
@@ -22901,13 +22901,13 @@
         </is>
       </c>
       <c r="C135" s="26" t="n">
-        <v>45638</v>
+        <v>45579</v>
       </c>
       <c r="D135" s="47" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E135" s="48" t="n">
-        <v>0.003647</v>
+        <v>0.003148</v>
       </c>
     </row>
     <row r="136">
@@ -22922,13 +22922,13 @@
         </is>
       </c>
       <c r="C136" s="26" t="n">
-        <v>45671</v>
+        <v>45610</v>
       </c>
       <c r="D136" s="47" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="E136" s="48" t="n">
-        <v>0.003659</v>
+        <v>0.002509</v>
       </c>
     </row>
     <row r="137">
@@ -22943,13 +22943,13 @@
         </is>
       </c>
       <c r="C137" s="26" t="n">
-        <v>45701</v>
+        <v>45638</v>
       </c>
       <c r="D137" s="47" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="E137" s="48" t="n">
-        <v>0.002909</v>
+        <v>0.003647</v>
       </c>
     </row>
     <row r="138">
@@ -22964,13 +22964,13 @@
         </is>
       </c>
       <c r="C138" s="26" t="n">
-        <v>45729</v>
+        <v>45671</v>
       </c>
       <c r="D138" s="47" t="n">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="E138" s="48" t="n">
-        <v>0.002634</v>
+        <v>0.003659</v>
       </c>
     </row>
     <row r="139">
@@ -22985,13 +22985,13 @@
         </is>
       </c>
       <c r="C139" s="26" t="n">
-        <v>45761</v>
+        <v>45701</v>
       </c>
       <c r="D139" s="47" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E139" s="48" t="n">
-        <v>0.003378</v>
+        <v>0.002909</v>
       </c>
     </row>
     <row r="140">
@@ -23006,13 +23006,13 @@
         </is>
       </c>
       <c r="C140" s="26" t="n">
-        <v>45791</v>
+        <v>45729</v>
       </c>
       <c r="D140" s="47" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E140" s="48" t="n">
-        <v>0.002356</v>
+        <v>0.002634</v>
       </c>
     </row>
     <row r="141">
@@ -23027,13 +23027,13 @@
         </is>
       </c>
       <c r="C141" s="26" t="n">
-        <v>45820</v>
+        <v>45761</v>
       </c>
       <c r="D141" s="47" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="E141" s="48" t="n">
-        <v>0.00299</v>
+        <v>0.003378</v>
       </c>
     </row>
     <row r="142">
@@ -23048,13 +23048,13 @@
         </is>
       </c>
       <c r="C142" s="26" t="n">
-        <v>45852</v>
+        <v>45791</v>
       </c>
       <c r="D142" s="47" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E142" s="48" t="n">
-        <v>0.003007</v>
+        <v>0.002356</v>
       </c>
     </row>
     <row r="143">
@@ -23069,13 +23069,13 @@
         </is>
       </c>
       <c r="C143" s="26" t="n">
-        <v>45882</v>
+        <v>45820</v>
       </c>
       <c r="D143" s="47" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="E143" s="48" t="n">
-        <v>0.002165</v>
+        <v>0.00299</v>
       </c>
     </row>
     <row r="144">
@@ -23090,13 +23090,13 @@
         </is>
       </c>
       <c r="C144" s="26" t="n">
-        <v>45912</v>
+        <v>45852</v>
       </c>
       <c r="D144" s="47" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E144" s="48" t="n">
-        <v>0.002688</v>
+        <v>0.003007</v>
       </c>
     </row>
     <row r="145">
@@ -23111,13 +23111,13 @@
         </is>
       </c>
       <c r="C145" s="26" t="n">
-        <v>45944</v>
+        <v>45882</v>
       </c>
       <c r="D145" s="47" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E145" s="48" t="n">
-        <v>0.002989</v>
+        <v>0.002165</v>
       </c>
     </row>
     <row r="146">
@@ -23132,13 +23132,13 @@
         </is>
       </c>
       <c r="C146" s="26" t="n">
-        <v>45974</v>
+        <v>45912</v>
       </c>
       <c r="D146" s="47" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E146" s="48" t="n">
-        <v>0.001939</v>
+        <v>0.002688</v>
       </c>
     </row>
     <row r="147">
@@ -23153,13 +23153,13 @@
         </is>
       </c>
       <c r="C147" s="26" t="n">
-        <v>46003</v>
+        <v>45944</v>
       </c>
       <c r="D147" s="47" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E147" s="48" t="n">
-        <v>0.002966</v>
+        <v>0.002989</v>
       </c>
     </row>
     <row r="148">
@@ -23174,13 +23174,13 @@
         </is>
       </c>
       <c r="C148" s="26" t="n">
-        <v>46036</v>
+        <v>45974</v>
       </c>
       <c r="D148" s="47" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E148" s="48" t="n">
-        <v>0.002964</v>
+        <v>0.001939</v>
       </c>
     </row>
     <row r="149">
@@ -23195,13 +23195,13 @@
         </is>
       </c>
       <c r="C149" s="26" t="n">
-        <v>46065</v>
+        <v>46003</v>
       </c>
       <c r="D149" s="47" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="E149" s="48" t="n">
-        <v>0.00224</v>
+        <v>0.002966</v>
       </c>
     </row>
     <row r="150">
@@ -23216,13 +23216,13 @@
         </is>
       </c>
       <c r="C150" s="26" t="n">
-        <v>46093</v>
+        <v>46036</v>
       </c>
       <c r="D150" s="47" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E150" s="48" t="n">
-        <v>0.002589</v>
+        <v>0.002964</v>
       </c>
     </row>
     <row r="151">
@@ -23237,13 +23237,13 @@
         </is>
       </c>
       <c r="C151" s="26" t="n">
-        <v>46126</v>
+        <v>46065</v>
       </c>
       <c r="D151" s="47" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E151" s="48" t="n">
-        <v>0.002645</v>
+        <v>0.00224</v>
       </c>
     </row>
     <row r="152">
@@ -23258,13 +23258,13 @@
         </is>
       </c>
       <c r="C152" s="26" t="n">
-        <v>46156</v>
+        <v>46093</v>
       </c>
       <c r="D152" s="47" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E152" s="48" t="n">
-        <v>0.002016</v>
+        <v>0.002589</v>
       </c>
     </row>
     <row r="153">
@@ -23279,13 +23279,13 @@
         </is>
       </c>
       <c r="C153" s="26" t="n">
-        <v>46185</v>
+        <v>46126</v>
       </c>
       <c r="D153" s="47" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E153" s="48" t="n">
-        <v>0.002161</v>
+        <v>0.002645</v>
       </c>
     </row>
     <row r="154">
@@ -23300,13 +23300,13 @@
         </is>
       </c>
       <c r="C154" s="26" t="n">
-        <v>46217</v>
+        <v>46156</v>
       </c>
       <c r="D154" s="47" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="E154" s="48" t="n">
-        <v>0.003001</v>
+        <v>0.002016</v>
       </c>
     </row>
     <row r="155">
@@ -23321,13 +23321,13 @@
         </is>
       </c>
       <c r="C155" s="26" t="n">
-        <v>46247</v>
+        <v>46185</v>
       </c>
       <c r="D155" s="47" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E155" s="48" t="n">
-        <v>0.0028</v>
+        <v>0.002161</v>
       </c>
     </row>
     <row r="156">
@@ -23342,13 +23342,13 @@
         </is>
       </c>
       <c r="C156" s="26" t="n">
-        <v>46279</v>
+        <v>46217</v>
       </c>
       <c r="D156" s="47" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="E156" s="48" t="n">
-        <v>0.001924</v>
+        <v>0.003001</v>
       </c>
     </row>
     <row r="157">
@@ -23363,28 +23363,56 @@
         </is>
       </c>
       <c r="C157" s="26" t="n">
-        <v>46309</v>
+        <v>46247</v>
       </c>
       <c r="D157" s="47" t="n">
         <v>37</v>
       </c>
       <c r="E157" s="48" t="n">
+        <v>0.0028</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="46" t="inlineStr">
+        <is>
+          <t>489250</t>
+        </is>
+      </c>
+      <c r="B158" s="33" t="inlineStr">
+        <is>
+          <t>KODEX 미국배당다우존스</t>
+        </is>
+      </c>
+      <c r="C158" s="26" t="n">
+        <v>46279</v>
+      </c>
+      <c r="D158" s="47" t="n">
+        <v>24</v>
+      </c>
+      <c r="E158" s="48" t="n">
+        <v>0.001924</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="46" t="inlineStr">
+        <is>
+          <t>489250</t>
+        </is>
+      </c>
+      <c r="B159" s="33" t="inlineStr">
+        <is>
+          <t>KODEX 미국배당다우존스</t>
+        </is>
+      </c>
+      <c r="C159" s="26" t="n">
+        <v>46309</v>
+      </c>
+      <c r="D159" s="47" t="n">
+        <v>37</v>
+      </c>
+      <c r="E159" s="48" t="n">
         <v>0.003019</v>
       </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="46" t="n"/>
-      <c r="B158" s="33" t="n"/>
-      <c r="C158" s="26" t="n"/>
-      <c r="D158" s="47" t="n"/>
-      <c r="E158" s="48" t="n"/>
-    </row>
-    <row r="159">
-      <c r="A159" s="46" t="n"/>
-      <c r="B159" s="33" t="n"/>
-      <c r="C159" s="26" t="n"/>
-      <c r="D159" s="47" t="n"/>
-      <c r="E159" s="48" t="n"/>
     </row>
     <row r="160">
       <c r="A160" s="46" t="n"/>
@@ -24771,6 +24799,20 @@
       <c r="C357" s="26" t="n"/>
       <c r="D357" s="47" t="n"/>
       <c r="E357" s="48" t="n"/>
+    </row>
+    <row r="358">
+      <c r="A358" s="46" t="n"/>
+      <c r="B358" s="33" t="n"/>
+      <c r="C358" s="26" t="n"/>
+      <c r="D358" s="47" t="n"/>
+      <c r="E358" s="48" t="n"/>
+    </row>
+    <row r="359">
+      <c r="A359" s="46" t="n"/>
+      <c r="B359" s="33" t="n"/>
+      <c r="C359" s="26" t="n"/>
+      <c r="D359" s="47" t="n"/>
+      <c r="E359" s="48" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24892,23 +24934,23 @@
         </is>
       </c>
       <c r="E6" s="52">
-        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$357,국내SCHD형_분배!$A$2:$A$357,$B6,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$359,국내SCHD형_분배!$A$2:$A$359,$B6,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="F6" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B6,국내SCHD형_분배!$C$2:$C$357,E6)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,$B6,국내SCHD형_분배!$C$2:$C$359,E6)</f>
         <v/>
       </c>
       <c r="G6" s="45">
-        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$357,$B6,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$359,$B6,국내SCHD형_분배!$C$2:$C$359,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="H6" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B6,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,$B6,국내SCHD형_분배!$C$2:$C$359,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="I6" s="29">
-        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$357,국내SCHD형_분배!$A$2:$A$357,$B6,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$359,국내SCHD형_분배!$A$2:$A$359,$B6,국내SCHD형_분배!$C$2:$C$359,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
     </row>
@@ -24932,23 +24974,23 @@
         </is>
       </c>
       <c r="E7" s="52">
-        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$357,국내SCHD형_분배!$A$2:$A$357,$B7,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$359,국내SCHD형_분배!$A$2:$A$359,$B7,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="F7" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B7,국내SCHD형_분배!$C$2:$C$357,E7)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,$B7,국내SCHD형_분배!$C$2:$C$359,E7)</f>
         <v/>
       </c>
       <c r="G7" s="45">
-        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$357,$B7,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$359,$B7,국내SCHD형_분배!$C$2:$C$359,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="H7" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B7,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,$B7,국내SCHD형_분배!$C$2:$C$359,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="I7" s="29">
-        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$357,국내SCHD형_분배!$A$2:$A$357,$B7,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$359,국내SCHD형_분배!$A$2:$A$359,$B7,국내SCHD형_분배!$C$2:$C$359,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
     </row>
@@ -24972,23 +25014,23 @@
         </is>
       </c>
       <c r="E8" s="52">
-        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$357,국내SCHD형_분배!$A$2:$A$357,$B8,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$359,국내SCHD형_분배!$A$2:$A$359,$B8,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="F8" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B8,국내SCHD형_분배!$C$2:$C$357,E8)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,$B8,국내SCHD형_분배!$C$2:$C$359,E8)</f>
         <v/>
       </c>
       <c r="G8" s="45">
-        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$357,$B8,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$359,$B8,국내SCHD형_분배!$C$2:$C$359,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="H8" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B8,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,$B8,국내SCHD형_분배!$C$2:$C$359,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="I8" s="29">
-        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$357,국내SCHD형_분배!$A$2:$A$357,$B8,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$359,국내SCHD형_분배!$A$2:$A$359,$B8,국내SCHD형_분배!$C$2:$C$359,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
     </row>
@@ -25012,23 +25054,23 @@
         </is>
       </c>
       <c r="E9" s="52">
-        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$357,국내SCHD형_분배!$A$2:$A$357,$B9,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>_xlfn.MAXIFS(국내SCHD형_분배!$C$2:$C$359,국내SCHD형_분배!$A$2:$A$359,$B9,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="F9" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B9,국내SCHD형_분배!$C$2:$C$357,E9)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,$B9,국내SCHD형_분배!$C$2:$C$359,E9)</f>
         <v/>
       </c>
       <c r="G9" s="45">
-        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$357,$B9,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>COUNTIFS(국내SCHD형_분배!$A$2:$A$359,$B9,국내SCHD형_분배!$C$2:$C$359,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="H9" s="53">
-        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,$B9,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,$B9,국내SCHD형_분배!$C$2:$C$359,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
       <c r="I9" s="29">
-        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$357,국내SCHD형_분배!$A$2:$A$357,$B9,국내SCHD형_분배!$C$2:$C$357,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$B$3)</f>
+        <f>SUMIFS(국내SCHD형_분배!$E$2:$E$359,국내SCHD형_분배!$A$2:$A$359,$B9,국내SCHD형_분배!$C$2:$C$359,"&gt;"&amp;EDATE($B$3,-12),국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$B$3)</f>
         <v/>
       </c>
     </row>
@@ -25163,19 +25205,19 @@
         <v/>
       </c>
       <c r="D17" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C17))</f>
         <v/>
       </c>
       <c r="E17" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C17))</f>
         <v/>
       </c>
       <c r="F17" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C17))</f>
         <v/>
       </c>
       <c r="G17" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C17))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C17)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B17,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C17))</f>
         <v/>
       </c>
       <c r="H17" s="28">
@@ -25201,19 +25243,19 @@
         <v/>
       </c>
       <c r="D18" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C18))</f>
         <v/>
       </c>
       <c r="E18" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C18))</f>
         <v/>
       </c>
       <c r="F18" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C18))</f>
         <v/>
       </c>
       <c r="G18" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C18))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C18)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B18,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C18))</f>
         <v/>
       </c>
       <c r="H18" s="28">
@@ -25239,19 +25281,19 @@
         <v/>
       </c>
       <c r="D19" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C19))</f>
         <v/>
       </c>
       <c r="E19" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C19))</f>
         <v/>
       </c>
       <c r="F19" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C19))</f>
         <v/>
       </c>
       <c r="G19" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C19))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C19)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B19,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C19))</f>
         <v/>
       </c>
       <c r="H19" s="28">
@@ -25277,19 +25319,19 @@
         <v/>
       </c>
       <c r="D20" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C20))</f>
         <v/>
       </c>
       <c r="E20" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C20))</f>
         <v/>
       </c>
       <c r="F20" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C20))</f>
         <v/>
       </c>
       <c r="G20" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C20))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C20)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B20,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C20))</f>
         <v/>
       </c>
       <c r="H20" s="28">
@@ -25315,19 +25357,19 @@
         <v/>
       </c>
       <c r="D21" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C21))</f>
         <v/>
       </c>
       <c r="E21" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C21))</f>
         <v/>
       </c>
       <c r="F21" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C21))</f>
         <v/>
       </c>
       <c r="G21" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C21))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C21)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B21,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C21))</f>
         <v/>
       </c>
       <c r="H21" s="28">
@@ -25353,19 +25395,19 @@
         <v/>
       </c>
       <c r="D22" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C22))</f>
         <v/>
       </c>
       <c r="E22" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C22))</f>
         <v/>
       </c>
       <c r="F22" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C22))</f>
         <v/>
       </c>
       <c r="G22" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C22))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C22)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B22,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C22))</f>
         <v/>
       </c>
       <c r="H22" s="28">
@@ -25391,19 +25433,19 @@
         <v/>
       </c>
       <c r="D23" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C23))</f>
         <v/>
       </c>
       <c r="E23" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C23))</f>
         <v/>
       </c>
       <c r="F23" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C23))</f>
         <v/>
       </c>
       <c r="G23" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C23))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C23)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B23,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C23))</f>
         <v/>
       </c>
       <c r="H23" s="28">
@@ -25429,19 +25471,19 @@
         <v/>
       </c>
       <c r="D24" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C24))</f>
         <v/>
       </c>
       <c r="E24" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C24))</f>
         <v/>
       </c>
       <c r="F24" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C24))</f>
         <v/>
       </c>
       <c r="G24" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C24))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C24)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B24,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C24))</f>
         <v/>
       </c>
       <c r="H24" s="28">
@@ -25467,19 +25509,19 @@
         <v/>
       </c>
       <c r="D25" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C25))</f>
         <v/>
       </c>
       <c r="E25" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C25))</f>
         <v/>
       </c>
       <c r="F25" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C25))</f>
         <v/>
       </c>
       <c r="G25" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C25))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C25)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B25,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C25))</f>
         <v/>
       </c>
       <c r="H25" s="28">
@@ -25505,19 +25547,19 @@
         <v/>
       </c>
       <c r="D26" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C26))</f>
         <v/>
       </c>
       <c r="E26" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C26))</f>
         <v/>
       </c>
       <c r="F26" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C26))</f>
         <v/>
       </c>
       <c r="G26" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C26))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C26)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B26,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C26))</f>
         <v/>
       </c>
       <c r="H26" s="28">
@@ -25543,19 +25585,19 @@
         <v/>
       </c>
       <c r="D27" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C27))</f>
         <v/>
       </c>
       <c r="E27" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C27))</f>
         <v/>
       </c>
       <c r="F27" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C27))</f>
         <v/>
       </c>
       <c r="G27" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C27))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C27)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B27,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C27))</f>
         <v/>
       </c>
       <c r="H27" s="28">
@@ -25581,19 +25623,19 @@
         <v/>
       </c>
       <c r="D28" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C28))</f>
         <v/>
       </c>
       <c r="E28" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C28))</f>
         <v/>
       </c>
       <c r="F28" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C28))</f>
         <v/>
       </c>
       <c r="G28" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C28))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C28)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B28,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C28))</f>
         <v/>
       </c>
       <c r="H28" s="28">
@@ -25619,19 +25661,19 @@
         <v/>
       </c>
       <c r="D29" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C29))</f>
         <v/>
       </c>
       <c r="E29" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C29))</f>
         <v/>
       </c>
       <c r="F29" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C29))</f>
         <v/>
       </c>
       <c r="G29" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C29))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C29)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B29,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C29))</f>
         <v/>
       </c>
       <c r="H29" s="28">
@@ -25657,19 +25699,19 @@
         <v/>
       </c>
       <c r="D30" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C30))</f>
         <v/>
       </c>
       <c r="E30" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C30))</f>
         <v/>
       </c>
       <c r="F30" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C30))</f>
         <v/>
       </c>
       <c r="G30" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C30))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C30)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B30,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C30))</f>
         <v/>
       </c>
       <c r="H30" s="28">
@@ -25695,19 +25737,19 @@
         <v/>
       </c>
       <c r="D31" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C31))</f>
         <v/>
       </c>
       <c r="E31" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C31))</f>
         <v/>
       </c>
       <c r="F31" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C31))</f>
         <v/>
       </c>
       <c r="G31" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C31))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C31)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B31,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C31))</f>
         <v/>
       </c>
       <c r="H31" s="28">
@@ -25733,19 +25775,19 @@
         <v/>
       </c>
       <c r="D32" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C32))</f>
         <v/>
       </c>
       <c r="E32" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C32))</f>
         <v/>
       </c>
       <c r="F32" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C32))</f>
         <v/>
       </c>
       <c r="G32" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C32))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C32)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B32,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C32))</f>
         <v/>
       </c>
       <c r="H32" s="28">
@@ -25771,19 +25813,19 @@
         <v/>
       </c>
       <c r="D33" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C33))</f>
         <v/>
       </c>
       <c r="E33" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C33))</f>
         <v/>
       </c>
       <c r="F33" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C33))</f>
         <v/>
       </c>
       <c r="G33" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C33))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C33)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B33,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C33))</f>
         <v/>
       </c>
       <c r="H33" s="28">
@@ -25809,19 +25851,19 @@
         <v/>
       </c>
       <c r="D34" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C34))</f>
         <v/>
       </c>
       <c r="E34" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C34))</f>
         <v/>
       </c>
       <c r="F34" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C34))</f>
         <v/>
       </c>
       <c r="G34" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C34))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C34)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B34,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C34))</f>
         <v/>
       </c>
       <c r="H34" s="28">
@@ -25847,19 +25889,19 @@
         <v/>
       </c>
       <c r="D35" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C35))</f>
         <v/>
       </c>
       <c r="E35" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C35))</f>
         <v/>
       </c>
       <c r="F35" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C35))</f>
         <v/>
       </c>
       <c r="G35" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C35))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C35)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B35,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C35))</f>
         <v/>
       </c>
       <c r="H35" s="28">
@@ -25885,19 +25927,19 @@
         <v/>
       </c>
       <c r="D36" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C36))</f>
         <v/>
       </c>
       <c r="E36" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C36))</f>
         <v/>
       </c>
       <c r="F36" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C36))</f>
         <v/>
       </c>
       <c r="G36" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C36))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C36)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B36,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C36))</f>
         <v/>
       </c>
       <c r="H36" s="28">
@@ -25923,19 +25965,19 @@
         <v/>
       </c>
       <c r="D37" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C37))</f>
         <v/>
       </c>
       <c r="E37" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C37))</f>
         <v/>
       </c>
       <c r="F37" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C37))</f>
         <v/>
       </c>
       <c r="G37" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C37))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C37)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B37,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C37))</f>
         <v/>
       </c>
       <c r="H37" s="28">
@@ -25961,19 +26003,19 @@
         <v/>
       </c>
       <c r="D38" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C38))</f>
         <v/>
       </c>
       <c r="E38" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C38))</f>
         <v/>
       </c>
       <c r="F38" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C38))</f>
         <v/>
       </c>
       <c r="G38" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C38))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C38)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B38,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C38))</f>
         <v/>
       </c>
       <c r="H38" s="28">
@@ -25999,19 +26041,19 @@
         <v/>
       </c>
       <c r="D39" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C39))</f>
         <v/>
       </c>
       <c r="E39" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C39))</f>
         <v/>
       </c>
       <c r="F39" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C39))</f>
         <v/>
       </c>
       <c r="G39" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C39))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C39)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B39,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C39))</f>
         <v/>
       </c>
       <c r="H39" s="28">
@@ -26037,19 +26079,19 @@
         <v/>
       </c>
       <c r="D40" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C40))</f>
         <v/>
       </c>
       <c r="E40" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C40))</f>
         <v/>
       </c>
       <c r="F40" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C40))</f>
         <v/>
       </c>
       <c r="G40" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C40))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C40)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B40,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C40))</f>
         <v/>
       </c>
       <c r="H40" s="28">
@@ -26075,19 +26117,19 @@
         <v/>
       </c>
       <c r="D41" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C41))</f>
         <v/>
       </c>
       <c r="E41" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C41))</f>
         <v/>
       </c>
       <c r="F41" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C41))</f>
         <v/>
       </c>
       <c r="G41" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C41))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C41)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B41,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C41))</f>
         <v/>
       </c>
       <c r="H41" s="28">
@@ -26113,19 +26155,19 @@
         <v/>
       </c>
       <c r="D42" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C42))</f>
         <v/>
       </c>
       <c r="E42" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C42))</f>
         <v/>
       </c>
       <c r="F42" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C42))</f>
         <v/>
       </c>
       <c r="G42" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C42))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C42)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B42,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C42))</f>
         <v/>
       </c>
       <c r="H42" s="28">
@@ -26151,19 +26193,19 @@
         <v/>
       </c>
       <c r="D43" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C43))</f>
         <v/>
       </c>
       <c r="E43" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C43))</f>
         <v/>
       </c>
       <c r="F43" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C43))</f>
         <v/>
       </c>
       <c r="G43" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C43))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C43)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B43,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C43))</f>
         <v/>
       </c>
       <c r="H43" s="28">
@@ -26189,19 +26231,19 @@
         <v/>
       </c>
       <c r="D44" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"458730",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"458730",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C44))</f>
         <v/>
       </c>
       <c r="E44" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"446720",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"446720",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C44))</f>
         <v/>
       </c>
       <c r="F44" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"402970",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"402970",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C44))</f>
         <v/>
       </c>
       <c r="G44" s="53">
-        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$357,국내SCHD형_분배!$A$2:$A$357,"489250",국내SCHD형_분배!$C$2:$C$357,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$357,"&lt;="&amp;$C44))</f>
+        <f>IF(COUNTIFS(국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C44)=0,"",SUMIFS(국내SCHD형_분배!$D$2:$D$359,국내SCHD형_분배!$A$2:$A$359,"489250",국내SCHD형_분배!$C$2:$C$359,"&gt;="&amp;$B44,국내SCHD형_분배!$C$2:$C$359,"&lt;="&amp;$C44))</f>
         <v/>
       </c>
       <c r="H44" s="28">
@@ -26257,11 +26299,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-26)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-27)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26358,7 +26400,7 @@
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.04804111</v>
+        <v>0.048266</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -26412,25 +26454,25 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04293930999999999</v>
+        <v>0.04306968999999999</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>QUALCOMM</t>
+          <t>CONOCOPHILLIPS</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>퀄컴</t>
+          <t>코노코필립스</t>
         </is>
       </c>
       <c r="M6" s="7">
@@ -26470,25 +26512,25 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04273715</v>
+        <v>0.04295792</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>PROCTER &amp; GAMBLE</t>
+          <t>CHEVRON</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>프록터앤드갬블</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="M7" s="7">
@@ -26528,25 +26570,25 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04270364</v>
+        <v>0.04273199</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>CHEVRON</t>
+          <t>QUALCOMM</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>퀄컴</t>
         </is>
       </c>
       <c r="M8" s="7">
@@ -26586,25 +26628,25 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.04267935</v>
+        <v>0.04254898</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>CONOCOPHILLIPS</t>
+          <t>PROCTER &amp; GAMBLE</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>코노코필립스</t>
+          <t>프록터앤드갬블</t>
         </is>
       </c>
       <c r="M9" s="7">
@@ -26648,7 +26690,7 @@
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.04094653</v>
+        <v>0.0412635</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
@@ -26702,15 +26744,15 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04068892</v>
+        <v>0.04049768</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>UNITEDHEALTH GROUP</t>
+          <t>AMGEN INC</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -26720,7 +26762,7 @@
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>유나이티드헬스</t>
+          <t>암젠</t>
         </is>
       </c>
       <c r="M11" s="7">
@@ -26760,15 +26802,15 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.04008198</v>
+        <v>0.04043118</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>AMGEN INC</t>
+          <t>UNITEDHEALTH GROUP</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -26778,7 +26820,7 @@
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>암젠</t>
+          <t>유나이티드헬스</t>
         </is>
       </c>
       <c r="M12" s="7">
@@ -26822,7 +26864,7 @@
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03962369</v>
+        <v>0.03957373</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
@@ -26880,7 +26922,7 @@
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.03764625</v>
+        <v>0.03746441</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
@@ -26928,7 +26970,7 @@
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.03705987</v>
+        <v>0.03688982</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
@@ -26976,7 +27018,7 @@
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.03698267</v>
+        <v>0.03688022</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -27010,25 +27052,25 @@
       </c>
       <c r="H17" s="6" t="inlineStr">
         <is>
-          <t>VZ</t>
+          <t>ACN</t>
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03466334</v>
+        <v>0.03582394</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>VERIZON COMMUNICATIONS INC</t>
+          <t>ACCENTURE PLC CLASS A</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr">
         <is>
-          <t>버라이즌</t>
+          <t>액센츄어</t>
         </is>
       </c>
       <c r="M17" s="7">
@@ -27048,25 +27090,25 @@
       </c>
       <c r="H18" s="6" t="inlineStr">
         <is>
-          <t>ACN</t>
+          <t>VZ</t>
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03455249</v>
+        <v>0.03412945</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>ACCENTURE PLC CLASS A</t>
+          <t>VERIZON COMMUNICATIONS INC</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr">
         <is>
-          <t>액센츄어</t>
+          <t>버라이즌</t>
         </is>
       </c>
       <c r="M18" s="7">
@@ -27081,7 +27123,7 @@
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03037897</v>
+        <v>0.03076066</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -27115,7 +27157,7 @@
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.03018884</v>
+        <v>0.02975866</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
@@ -27154,7 +27196,7 @@
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02946372</v>
+        <v>0.02931298</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -27192,7 +27234,7 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02795858</v>
+        <v>0.02726654</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -27230,7 +27272,7 @@
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02103275</v>
+        <v>0.02113345</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -27268,7 +27310,7 @@
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.0202892</v>
+        <v>0.02030092</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
@@ -27306,7 +27348,7 @@
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01927179</v>
+        <v>0.01918674</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
@@ -27344,7 +27386,7 @@
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01908826</v>
+        <v>0.01903599</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
@@ -27382,7 +27424,7 @@
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.01855952</v>
+        <v>0.01836122</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -27420,7 +27462,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.01614128</v>
+        <v>0.01627249</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27458,7 +27500,7 @@
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01453181</v>
+        <v>0.01433363</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -27492,7 +27534,7 @@
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01420322</v>
+        <v>0.01419975</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -27530,7 +27572,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01353078</v>
+        <v>0.01356434</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27555,7 +27597,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01166936</v>
+        <v>0.011663</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27585,7 +27627,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01101267</v>
+        <v>0.01125747</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27610,7 +27652,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.00904929</v>
+        <v>0.0089522</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27635,7 +27677,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.008711719999999999</v>
+        <v>0.008670489999999999</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27660,7 +27702,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.008397659999999999</v>
+        <v>0.00833105</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27681,15 +27723,15 @@
     <row r="37">
       <c r="H37" s="6" t="inlineStr">
         <is>
-          <t>CINF</t>
+          <t>ARES</t>
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.00668471</v>
+        <v>0.00666956</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>CINCINNATI FINANCIAL</t>
+          <t>ARES MANAGEMENT CLASS A</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -27706,15 +27748,15 @@
     <row r="38">
       <c r="H38" s="6" t="inlineStr">
         <is>
-          <t>ARES</t>
+          <t>CINF</t>
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.006570599999999999</v>
+        <v>0.00662146</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>ARES MANAGEMENT CLASS A</t>
+          <t>CINCINNATI FINANCIAL</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -27735,7 +27777,7 @@
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.00583219</v>
+        <v>0.00591301</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -27760,7 +27802,7 @@
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.005829879999999999</v>
+        <v>0.00581724</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
@@ -27785,7 +27827,7 @@
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.005778910000000001</v>
+        <v>0.00576264</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -27810,7 +27852,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.00530752</v>
+        <v>0.005335490000000001</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27835,7 +27877,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.00523831</v>
+        <v>0.005240590000000001</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27860,7 +27902,7 @@
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00484885</v>
+        <v>0.00485371</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -27885,7 +27927,7 @@
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00468315</v>
+        <v>0.00461775</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -27910,7 +27952,7 @@
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.00443953</v>
+        <v>0.00442342</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -27935,7 +27977,7 @@
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00432334</v>
+        <v>0.00432635</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -27956,20 +27998,20 @@
     <row r="48">
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.0042973</v>
+        <v>0.00430674</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>GENERAL MILLS INC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
@@ -27981,20 +28023,20 @@
     <row r="49">
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.00427252</v>
+        <v>0.00425057</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GENERAL MILLS INC</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
@@ -28010,7 +28052,7 @@
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00423965</v>
+        <v>0.00416319</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
@@ -28035,7 +28077,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.00257137</v>
+        <v>0.00248823</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28060,7 +28102,7 @@
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00249799</v>
+        <v>0.00248447</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
@@ -28081,20 +28123,20 @@
     <row r="53">
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>FNF</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00241145</v>
+        <v>0.00241355</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>FIDELITY NATIONAL FINANCIAL INC</t>
+          <t>BOOZ ALLEN HAMILTON HOLDING CLASS</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr"/>
@@ -28106,20 +28148,20 @@
     <row r="54">
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>FNF</t>
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00240717</v>
+        <v>0.00240637</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>BOOZ ALLEN HAMILTON HOLDING CLASS</t>
+          <t>FIDELITY NATIONAL FINANCIAL INC</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr"/>
@@ -28135,7 +28177,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.0021063</v>
+        <v>0.00208811</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28160,7 +28202,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00203109</v>
+        <v>0.00201477</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28185,7 +28227,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.00185553</v>
+        <v>0.00185147</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28210,7 +28252,7 @@
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.00153118</v>
+        <v>0.00153062</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
@@ -28235,7 +28277,7 @@
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00150548</v>
+        <v>0.00150044</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
@@ -28260,7 +28302,7 @@
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00139764</v>
+        <v>0.00139481</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -28285,7 +28327,7 @@
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00130215</v>
+        <v>0.00135074</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
@@ -28310,7 +28352,7 @@
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.00129564</v>
+        <v>0.00130196</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
@@ -28335,7 +28377,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.00123781</v>
+        <v>0.00123355</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28360,7 +28402,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00115746</v>
+        <v>0.00114714</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28381,20 +28423,20 @@
     <row r="65">
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>RHI</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.00101075</v>
+        <v>0.00103589</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>ROBERT HALF INC</t>
+          <t>MOELIS CLASS A</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr"/>
@@ -28406,20 +28448,20 @@
     <row r="66">
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>RHI</t>
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.00099121</v>
+        <v>0.00101029</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>MOELIS CLASS A</t>
+          <t>ROBERT HALF INC</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr"/>
@@ -28435,7 +28477,7 @@
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.0009637199999999999</v>
+        <v>0.00097339</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -28460,7 +28502,7 @@
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.00094911</v>
+        <v>0.00095216</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
@@ -28485,7 +28527,7 @@
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00093986</v>
+        <v>0.00093041</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -28506,20 +28548,20 @@
     <row r="70">
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>CVBF</t>
+          <t>PAG</t>
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.00091322</v>
+        <v>0.00090494</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>CVB FINANCIAL CORP</t>
+          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr"/>
@@ -28531,20 +28573,20 @@
     <row r="71">
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>PAG</t>
+          <t>CVBF</t>
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.00090431</v>
+        <v>0.0009031400000000001</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
+          <t>CVB FINANCIAL CORP</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr"/>
@@ -28560,7 +28602,7 @@
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.00056335</v>
+        <v>0.0005903</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
@@ -28585,7 +28627,7 @@
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.0005627399999999999</v>
+        <v>0.00055848</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
@@ -28610,7 +28652,7 @@
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.00051742</v>
+        <v>0.00051614</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
@@ -28631,15 +28673,15 @@
     <row r="75">
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>IPAR</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.0005049200000000001</v>
+        <v>0.00050795</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>INTERPARFUMS INC</t>
+          <t>MARZETTI</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
@@ -28656,15 +28698,15 @@
     <row r="76">
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>IPAR</t>
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.00050434</v>
+        <v>0.00050156</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>MARZETTI</t>
+          <t>INTERPARFUMS INC</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
@@ -28681,15 +28723,15 @@
     <row r="77">
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>CNS</t>
+          <t>CHCO</t>
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.00048079</v>
+        <v>0.00048047</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>COHEN &amp; STEERS INC</t>
+          <t>CITY HOLDING</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
@@ -28706,15 +28748,15 @@
     <row r="78">
       <c r="H78" s="6" t="inlineStr">
         <is>
-          <t>CHCO</t>
+          <t>CNS</t>
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.00047747</v>
+        <v>0.00047654</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>CITY HOLDING</t>
+          <t>COHEN &amp; STEERS INC</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr">
@@ -28735,7 +28777,7 @@
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00045739</v>
+        <v>0.00045831</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
@@ -28760,7 +28802,7 @@
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00044976</v>
+        <v>0.00045805</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
@@ -28781,22 +28823,18 @@
     <row r="81">
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>GVMXX</t>
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.00044523</v>
+        <v>0.00045189</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>INSPERITY</t>
-        </is>
-      </c>
-      <c r="K81" s="6" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
+          <t>SSC GOVERNMENT MM GVMXX</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr"/>
       <c r="L81" s="6" t="inlineStr"/>
       <c r="M81" s="7">
         <f>IF(H81="","",IFERROR(VLOOKUP(K81,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28806,20 +28844,20 @@
     <row r="82">
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>GABC</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00044491</v>
+        <v>0.00044478</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>GERMAN AMERICAN BANCORP INC</t>
+          <t>INSPERITY</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr"/>
@@ -28831,18 +28869,22 @@
     <row r="83">
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>GVMXX</t>
+          <t>GABC</t>
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.00043978</v>
+        <v>0.00044338</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>SSC GOVERNMENT MM GVMXX</t>
-        </is>
-      </c>
-      <c r="K83" s="6" t="inlineStr"/>
+          <t>GERMAN AMERICAN BANCORP INC</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="L83" s="6" t="inlineStr"/>
       <c r="M83" s="7">
         <f>IF(H83="","",IFERROR(VLOOKUP(K83,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28856,7 +28898,7 @@
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.00042928</v>
+        <v>0.00042906</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
@@ -28881,7 +28923,7 @@
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00041625</v>
+        <v>0.00040089</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
@@ -28906,7 +28948,7 @@
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.00037696</v>
+        <v>0.00037513</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
@@ -28931,7 +28973,7 @@
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.0003632</v>
+        <v>0.00036194</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
@@ -28956,7 +28998,7 @@
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00034245</v>
+        <v>0.00033613</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -28981,7 +29023,7 @@
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.00031602</v>
+        <v>0.0003135</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -29006,7 +29048,7 @@
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00027826</v>
+        <v>0.0002808</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
@@ -29027,20 +29069,20 @@
     <row r="91">
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>CNA</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00025073</v>
+        <v>0.00027328</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>CNA FINANCIAL CORP</t>
+          <t>WENDYS</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -29052,20 +29094,20 @@
     <row r="92">
       <c r="H92" s="6" t="inlineStr">
         <is>
-          <t>WEN</t>
+          <t>CNA</t>
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.00023693</v>
+        <v>0.00025016</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>WENDYS</t>
+          <t>CNA FINANCIAL CORP</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L92" s="6" t="inlineStr"/>
@@ -29081,7 +29123,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.00023314</v>
+        <v>0.00023396</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29106,7 +29148,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00022957</v>
+        <v>0.00023201</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29131,7 +29173,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00021191</v>
+        <v>0.00021154</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29152,15 +29194,15 @@
     <row r="96">
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>THFF</t>
+          <t>IBCP</t>
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.0001993</v>
+        <v>0.00019759</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>FIRST FINANCIAL CORPORATION CORP</t>
+          <t>INDEPENDENT BANK CORP</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
@@ -29177,15 +29219,15 @@
     <row r="97">
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>IBCP</t>
+          <t>THFF</t>
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.00019839</v>
+        <v>0.00019718</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>INDEPENDENT BANK CORP</t>
+          <t>FIRST FINANCIAL CORPORATION CORP</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
@@ -29206,7 +29248,7 @@
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.0001776</v>
+        <v>0.00018082</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -29231,7 +29273,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.00016834</v>
+        <v>0.00016726</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29256,7 +29298,7 @@
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00014105</v>
+        <v>0.00013781</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
@@ -29277,7 +29319,7 @@
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00012949</v>
+        <v>0.00012793</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
@@ -29302,7 +29344,7 @@
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>0.00011334</v>
+        <v>0.0001128</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -29327,7 +29369,7 @@
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>9.565000000000001e-05</v>
+        <v>9.331000000000001e-05</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
@@ -29352,7 +29394,7 @@
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>9.143e-05</v>
+        <v>9.083000000000001e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-29 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-30 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -26299,11 +26299,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-27)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-28)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26400,7 +26400,7 @@
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.048266</v>
+        <v>0.04795357</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -26454,15 +26454,15 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04306968999999999</v>
+        <v>0.04267233</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>CONOCOPHILLIPS</t>
+          <t>CHEVRON</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -26472,7 +26472,7 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>코노코필립스</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="M6" s="7">
@@ -26512,15 +26512,15 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04295792</v>
+        <v>0.04264136</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CHEVRON</t>
+          <t>CONOCOPHILLIPS</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -26530,7 +26530,7 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>코노코필립스</t>
         </is>
       </c>
       <c r="M7" s="7">
@@ -26574,7 +26574,7 @@
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04273199</v>
+        <v>0.04259401</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
@@ -26632,7 +26632,7 @@
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.04254898</v>
+        <v>0.04246965999999999</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
@@ -26690,7 +26690,7 @@
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.0412635</v>
+        <v>0.0410713</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
@@ -26748,7 +26748,7 @@
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04049768</v>
+        <v>0.04062024</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
@@ -26802,25 +26802,25 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.04043118</v>
+        <v>0.04032661</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>UNITEDHEALTH GROUP</t>
+          <t>HOME DEPOT</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>유나이티드헬스</t>
+          <t>홈디포</t>
         </is>
       </c>
       <c r="M12" s="7">
@@ -26860,25 +26860,25 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.03957373</v>
+        <v>0.04014238</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>HOME DEPOT</t>
+          <t>UNITEDHEALTH GROUP</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>홈디포</t>
+          <t>유나이티드헬스</t>
         </is>
       </c>
       <c r="M13" s="7">
@@ -26918,25 +26918,25 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.03746441</v>
+        <v>0.03767718</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>PEPSICO</t>
+          <t>MERCK &amp; CO INC</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>펩시코</t>
+          <t>머크</t>
         </is>
       </c>
       <c r="M14" s="7">
@@ -26966,25 +26966,25 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.03688982</v>
+        <v>0.03717428</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>MERCK &amp; CO INC</t>
+          <t>PEPSICO</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>머크</t>
+          <t>펩시코</t>
         </is>
       </c>
       <c r="M15" s="7">
@@ -27018,7 +27018,7 @@
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.03688022</v>
+        <v>0.03695951</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03582394</v>
+        <v>0.03579137</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03412945</v>
+        <v>0.03394476</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03076066</v>
+        <v>0.03092271</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -27153,25 +27153,25 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.02975866</v>
+        <v>0.03031918</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>BRISTOL MYERS SQUIBB</t>
+          <t>ALTRIA GROUP INC</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>브리스톨마이어스스퀴브</t>
+          <t>알트리아</t>
         </is>
       </c>
       <c r="M20" s="7">
@@ -27192,25 +27192,25 @@
       </c>
       <c r="H21" s="6" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02931298</v>
+        <v>0.02966852</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>ALTRIA GROUP INC</t>
+          <t>BRISTOL MYERS SQUIBB</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L21" s="6" t="inlineStr">
         <is>
-          <t>알트리아</t>
+          <t>브리스톨마이어스스퀴브</t>
         </is>
       </c>
       <c r="M21" s="7">
@@ -27234,7 +27234,7 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02726654</v>
+        <v>0.02688757</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02113345</v>
+        <v>0.02141662</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.02030092</v>
+        <v>0.02013037</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
@@ -27344,25 +27344,25 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01918674</v>
+        <v>0.01902798</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UNITED PARCEL SERVICE INC CLASS B</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="M25" s="7">
@@ -27382,25 +27382,25 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01903599</v>
+        <v>0.01889418</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>UNITED PARCEL SERVICE INC CLASS B</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="M26" s="7">
@@ -27424,7 +27424,7 @@
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.01836122</v>
+        <v>0.01864722</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
@@ -27462,7 +27462,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.01627249</v>
+        <v>0.01631382</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01433363</v>
+        <v>0.01429022</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01419975</v>
+        <v>0.01426625</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01356434</v>
+        <v>0.01331659</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.011663</v>
+        <v>0.01168047</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01125747</v>
+        <v>0.01145338</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.0089522</v>
+        <v>0.008688399999999999</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.008670489999999999</v>
+        <v>0.008656179999999999</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.00833105</v>
+        <v>0.008282690000000001</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.00666956</v>
+        <v>0.00675392</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.00662146</v>
+        <v>0.00660323</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.00591301</v>
+        <v>0.00592157</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.00581724</v>
+        <v>0.00582091</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.00576264</v>
+        <v>0.00554762</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.005335490000000001</v>
+        <v>0.005380960000000001</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.005240590000000001</v>
+        <v>0.00523831</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00485371</v>
+        <v>0.00480586</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00461775</v>
+        <v>0.00470294</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.00442342</v>
+        <v>0.00438746</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00432635</v>
+        <v>0.00430974</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
@@ -28002,7 +28002,7 @@
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.00430674</v>
+        <v>0.00426949</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
@@ -28027,7 +28027,7 @@
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.00425057</v>
+        <v>0.004215229999999999</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00416319</v>
+        <v>0.00409258</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.00248823</v>
+        <v>0.00254985</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28102,7 +28102,7 @@
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00248447</v>
+        <v>0.00248949</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
@@ -28123,20 +28123,20 @@
     <row r="53">
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>FNF</t>
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00241355</v>
+        <v>0.00242606</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>BOOZ ALLEN HAMILTON HOLDING CLASS</t>
+          <t>FIDELITY NATIONAL FINANCIAL INC</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr"/>
@@ -28148,20 +28148,20 @@
     <row r="54">
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>FNF</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00240637</v>
+        <v>0.00239541</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>FIDELITY NATIONAL FINANCIAL INC</t>
+          <t>BOOZ ALLEN HAMILTON HOLDING CLASS</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr"/>
@@ -28177,7 +28177,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00208811</v>
+        <v>0.00207336</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00201477</v>
+        <v>0.00201913</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.00185147</v>
+        <v>0.00184327</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28248,20 +28248,20 @@
     <row r="58">
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.00153062</v>
+        <v>0.00153684</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>ERIE INDEMNITY CLASS A</t>
+          <t>MACYS</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr"/>
@@ -28273,20 +28273,20 @@
     <row r="59">
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.00150044</v>
+        <v>0.0015324</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>MACYS</t>
+          <t>ERIE INDEMNITY CLASS A</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr"/>
@@ -28302,7 +28302,7 @@
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00139481</v>
+        <v>0.00136721</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00135074</v>
+        <v>0.00133222</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.00130196</v>
+        <v>0.00130236</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.00123355</v>
+        <v>0.00123259</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00114714</v>
+        <v>0.00116678</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.00103589</v>
+        <v>0.00104832</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
@@ -28452,7 +28452,7 @@
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.00101029</v>
+        <v>0.00101585</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
@@ -28477,7 +28477,7 @@
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.00097339</v>
+        <v>0.0009781900000000001</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -28502,7 +28502,7 @@
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.00095216</v>
+        <v>0.0009397300000000001</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
@@ -28527,7 +28527,7 @@
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00093041</v>
+        <v>0.00092419</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
@@ -28548,20 +28548,20 @@
     <row r="70">
       <c r="H70" s="6" t="inlineStr">
         <is>
-          <t>PAG</t>
+          <t>CVBF</t>
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.00090494</v>
+        <v>0.00089745</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
+          <t>CVB FINANCIAL CORP</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L70" s="6" t="inlineStr"/>
@@ -28573,20 +28573,20 @@
     <row r="71">
       <c r="H71" s="6" t="inlineStr">
         <is>
-          <t>CVBF</t>
+          <t>PAG</t>
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.0009031400000000001</v>
+        <v>0.0008917500000000001</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>CVB FINANCIAL CORP</t>
+          <t>PENSKE AUTOMOTIVE GROUP VOTING INC</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L71" s="6" t="inlineStr"/>
@@ -28598,22 +28598,18 @@
     <row r="72">
       <c r="H72" s="6" t="inlineStr">
         <is>
-          <t>APAM</t>
+          <t>GVMXX</t>
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.0005903</v>
+        <v>0.0007404</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
-        </is>
-      </c>
-      <c r="K72" s="6" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
+          <t>SSC GOVERNMENT MM GVMXX</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr"/>
       <c r="L72" s="6" t="inlineStr"/>
       <c r="M72" s="7">
         <f>IF(H72="","",IFERROR(VLOOKUP(K72,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28623,15 +28619,15 @@
     <row r="73">
       <c r="H73" s="6" t="inlineStr">
         <is>
-          <t>BANR</t>
+          <t>APAM</t>
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.00055848</v>
+        <v>0.0006083999999999999</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>BANNER CORP</t>
+          <t>ARTISAN PARTNERS ASSET MANAGEMENT</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -28648,15 +28644,15 @@
     <row r="74">
       <c r="H74" s="6" t="inlineStr">
         <is>
-          <t>OFG</t>
+          <t>BANR</t>
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.00051614</v>
+        <v>0.00055446</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>OFG BANCORP</t>
+          <t>BANNER CORP</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
@@ -28673,20 +28669,20 @@
     <row r="75">
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>OFG</t>
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.00050795</v>
+        <v>0.00050899</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>MARZETTI</t>
+          <t>OFG BANCORP</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -28698,15 +28694,15 @@
     <row r="76">
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>IPAR</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.00050156</v>
+        <v>0.00050296</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>INTERPARFUMS INC</t>
+          <t>MARZETTI</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
@@ -28723,20 +28719,20 @@
     <row r="77">
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>CHCO</t>
+          <t>IPAR</t>
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.00048047</v>
+        <v>0.0004987699999999999</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>CITY HOLDING</t>
+          <t>INTERPARFUMS INC</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -28752,7 +28748,7 @@
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.00047654</v>
+        <v>0.00048786</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
@@ -28773,15 +28769,15 @@
     <row r="79">
       <c r="H79" s="6" t="inlineStr">
         <is>
-          <t>AGM</t>
+          <t>CHCO</t>
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00045831</v>
+        <v>0.00047741</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
+          <t>CITY HOLDING</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
@@ -28802,7 +28798,7 @@
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00045805</v>
+        <v>0.00045943</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
@@ -28823,18 +28819,22 @@
     <row r="81">
       <c r="H81" s="6" t="inlineStr">
         <is>
-          <t>GVMXX</t>
+          <t>AGM</t>
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.00045189</v>
+        <v>0.00045034</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>SSC GOVERNMENT MM GVMXX</t>
-        </is>
-      </c>
-      <c r="K81" s="6" t="inlineStr"/>
+          <t>FEDERAL AGRICULTURAL MORTGAGE NON</t>
+        </is>
+      </c>
+      <c r="K81" s="6" t="inlineStr">
+        <is>
+          <t>Financials</t>
+        </is>
+      </c>
       <c r="L81" s="6" t="inlineStr"/>
       <c r="M81" s="7">
         <f>IF(H81="","",IFERROR(VLOOKUP(K81,$P$5:$Q$15,2,FALSE),"현금·선물"))</f>
@@ -28844,20 +28844,20 @@
     <row r="82">
       <c r="H82" s="6" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>GABC</t>
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00044478</v>
+        <v>0.00044021</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>INSPERITY</t>
+          <t>GERMAN AMERICAN BANCORP INC</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L82" s="6" t="inlineStr"/>
@@ -28869,15 +28869,15 @@
     <row r="83">
       <c r="H83" s="6" t="inlineStr">
         <is>
-          <t>GABC</t>
+          <t>STBA</t>
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.00044338</v>
+        <v>0.00042712</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>GERMAN AMERICAN BANCORP INC</t>
+          <t>S AND T BANCORP INC</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
@@ -28894,15 +28894,15 @@
     <row r="84">
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>STBA</t>
+          <t>NBHC</t>
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.00042906</v>
+        <v>0.00039517</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>S AND T BANCORP INC</t>
+          <t>NATIONAL BANK HOLDINGS CORP CLASS</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
@@ -28919,20 +28919,20 @@
     <row r="85">
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>NBHC</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.00040089</v>
+        <v>0.0003921</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>NATIONAL BANK HOLDINGS CORP CLASS</t>
+          <t>INSPERITY</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -28948,7 +28948,7 @@
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.00037513</v>
+        <v>0.00037257</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.00036194</v>
+        <v>0.00035967</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.00033613</v>
+        <v>0.0003416</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.0003135</v>
+        <v>0.00031038</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -29048,7 +29048,7 @@
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.0002808</v>
+        <v>0.00027592</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00027328</v>
+        <v>0.00027261</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.00025016</v>
+        <v>0.0002511</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.00023396</v>
+        <v>0.00023498</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00023201</v>
+        <v>0.00023121</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00021154</v>
+        <v>0.00020949</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29194,15 +29194,15 @@
     <row r="96">
       <c r="H96" s="6" t="inlineStr">
         <is>
-          <t>IBCP</t>
+          <t>THFF</t>
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.00019759</v>
+        <v>0.00019564</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>INDEPENDENT BANK CORP</t>
+          <t>FIRST FINANCIAL CORPORATION CORP</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
@@ -29219,15 +29219,15 @@
     <row r="97">
       <c r="H97" s="6" t="inlineStr">
         <is>
-          <t>THFF</t>
+          <t>IBCP</t>
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.00019718</v>
+        <v>0.0001953</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>FIRST FINANCIAL CORPORATION CORP</t>
+          <t>INDEPENDENT BANK CORP</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
@@ -29248,7 +29248,7 @@
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.00018082</v>
+        <v>0.00018058</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.00016726</v>
+        <v>0.0001657</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00013781</v>
+        <v>0.00013253</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00012793</v>
+        <v>0.00012318</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
@@ -29344,7 +29344,7 @@
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>0.0001128</v>
+        <v>0.00010126</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>9.331000000000001e-05</v>
+        <v>9.547000000000001e-05</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
@@ -29394,7 +29394,7 @@
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>9.083000000000001e-05</v>
+        <v>9.400000000000001e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>

--- a/downloads/schd_dividend_tracker.xlsx
+++ b/downloads/schd_dividend_tracker.xlsx
@@ -1724,7 +1724,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>최종 갱신: 2026-10-30 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
+          <t>최종 갱신: 2026-10-31 · 반영 범위: 2012년 1분기 ~ 2026년 3분기 (배당락 2026-09-23) · GitHub Actions 자동 생성</t>
         </is>
       </c>
     </row>
@@ -26299,11 +26299,11 @@
         </is>
       </c>
       <c r="B2" s="49" t="n">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-28)의 보유 주식 수 × 종가로 계산했습니다.</t>
+          <t>← 이 날 종가로 계산한 비중. 그날 공식 파일을 못 받아 Schwab 공식 보유종목 CSV(2026-10-29)의 보유 주식 수 × 종가로 계산했습니다.</t>
         </is>
       </c>
     </row>
@@ -26400,7 +26400,7 @@
         </is>
       </c>
       <c r="I5" s="61" t="n">
-        <v>0.04795357</v>
+        <v>0.04591873</v>
       </c>
       <c r="J5" s="6" t="inlineStr">
         <is>
@@ -26454,15 +26454,15 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>CVX</t>
+          <t>COP</t>
         </is>
       </c>
       <c r="I6" s="61" t="n">
-        <v>0.04267233</v>
+        <v>0.04360672</v>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>CHEVRON</t>
+          <t>CONOCOPHILLIPS</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -26472,7 +26472,7 @@
       </c>
       <c r="L6" s="6" t="inlineStr">
         <is>
-          <t>셰브론</t>
+          <t>코노코필립스</t>
         </is>
       </c>
       <c r="M6" s="7">
@@ -26512,15 +26512,15 @@
       </c>
       <c r="H7" s="6" t="inlineStr">
         <is>
-          <t>COP</t>
+          <t>CVX</t>
         </is>
       </c>
       <c r="I7" s="61" t="n">
-        <v>0.04264136</v>
+        <v>0.04325059000000001</v>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>CONOCOPHILLIPS</t>
+          <t>CHEVRON</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -26530,7 +26530,7 @@
       </c>
       <c r="L7" s="6" t="inlineStr">
         <is>
-          <t>코노코필립스</t>
+          <t>셰브론</t>
         </is>
       </c>
       <c r="M7" s="7">
@@ -26570,25 +26570,25 @@
       </c>
       <c r="H8" s="6" t="inlineStr">
         <is>
-          <t>QCOM</t>
+          <t>PG</t>
         </is>
       </c>
       <c r="I8" s="61" t="n">
-        <v>0.04259401</v>
+        <v>0.04256144</v>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>QUALCOMM</t>
+          <t>PROCTER &amp; GAMBLE</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr">
         <is>
-          <t>퀄컴</t>
+          <t>프록터앤드갬블</t>
         </is>
       </c>
       <c r="M8" s="7">
@@ -26628,15 +26628,15 @@
       </c>
       <c r="H9" s="6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="I9" s="61" t="n">
-        <v>0.04246965999999999</v>
+        <v>0.04146571</v>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>PROCTER &amp; GAMBLE</t>
+          <t>COCA-COLA</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -26646,7 +26646,7 @@
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>프록터앤드갬블</t>
+          <t>코카콜라</t>
         </is>
       </c>
       <c r="M9" s="7">
@@ -26686,25 +26686,25 @@
       </c>
       <c r="H10" s="6" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>AMGN</t>
         </is>
       </c>
       <c r="I10" s="61" t="n">
-        <v>0.0410713</v>
+        <v>0.0409245</v>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>COCA-COLA</t>
+          <t>AMGEN INC</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>코카콜라</t>
+          <t>암젠</t>
         </is>
       </c>
       <c r="M10" s="7">
@@ -26744,25 +26744,25 @@
       </c>
       <c r="H11" s="6" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="I11" s="61" t="n">
-        <v>0.04062024</v>
+        <v>0.04019523999999999</v>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>AMGEN INC</t>
+          <t>HOME DEPOT</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>암젠</t>
+          <t>홈디포</t>
         </is>
       </c>
       <c r="M11" s="7">
@@ -26802,25 +26802,25 @@
       </c>
       <c r="H12" s="6" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>UNH</t>
         </is>
       </c>
       <c r="I12" s="61" t="n">
-        <v>0.04032661</v>
+        <v>0.0396015</v>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>HOME DEPOT</t>
+          <t>UNITEDHEALTH GROUP</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>홈디포</t>
+          <t>유나이티드헬스</t>
         </is>
       </c>
       <c r="M12" s="7">
@@ -26860,15 +26860,15 @@
       </c>
       <c r="H13" s="6" t="inlineStr">
         <is>
-          <t>UNH</t>
+          <t>MRK</t>
         </is>
       </c>
       <c r="I13" s="61" t="n">
-        <v>0.04014238</v>
+        <v>0.03834765</v>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>UNITEDHEALTH GROUP</t>
+          <t>MERCK &amp; CO INC</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -26878,7 +26878,7 @@
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>유나이티드헬스</t>
+          <t>머크</t>
         </is>
       </c>
       <c r="M13" s="7">
@@ -26918,25 +26918,25 @@
       </c>
       <c r="H14" s="6" t="inlineStr">
         <is>
-          <t>MRK</t>
+          <t>PEP</t>
         </is>
       </c>
       <c r="I14" s="61" t="n">
-        <v>0.03767718</v>
+        <v>0.03801107</v>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>MERCK &amp; CO INC</t>
+          <t>PEPSICO</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>머크</t>
+          <t>펩시코</t>
         </is>
       </c>
       <c r="M14" s="7">
@@ -26966,25 +26966,25 @@
       </c>
       <c r="H15" s="6" t="inlineStr">
         <is>
-          <t>PEP</t>
+          <t>QCOM</t>
         </is>
       </c>
       <c r="I15" s="61" t="n">
-        <v>0.03717428</v>
+        <v>0.03770865</v>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>PEPSICO</t>
+          <t>QUALCOMM</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>펩시코</t>
+          <t>퀄컴</t>
         </is>
       </c>
       <c r="M15" s="7">
@@ -27018,7 +27018,7 @@
         </is>
       </c>
       <c r="I16" s="61" t="n">
-        <v>0.03695951</v>
+        <v>0.03738856</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -27056,7 +27056,7 @@
         </is>
       </c>
       <c r="I17" s="61" t="n">
-        <v>0.03579137</v>
+        <v>0.03724026</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -27094,7 +27094,7 @@
         </is>
       </c>
       <c r="I18" s="61" t="n">
-        <v>0.03394476</v>
+        <v>0.03464044</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -27119,25 +27119,25 @@
     <row r="19">
       <c r="H19" s="6" t="inlineStr">
         <is>
-          <t>LMT</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="I19" s="61" t="n">
-        <v>0.03092271</v>
+        <v>0.03070406</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>LOCKHEED MARTIN</t>
+          <t>ALTRIA GROUP INC</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr">
         <is>
-          <t>록히드마틴</t>
+          <t>알트리아</t>
         </is>
       </c>
       <c r="M19" s="7">
@@ -27153,25 +27153,25 @@
       </c>
       <c r="H20" s="6" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>LMT</t>
         </is>
       </c>
       <c r="I20" s="61" t="n">
-        <v>0.03031918</v>
+        <v>0.03048356</v>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>ALTRIA GROUP INC</t>
+          <t>LOCKHEED MARTIN</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr">
         <is>
-          <t>알트리아</t>
+          <t>록히드마틴</t>
         </is>
       </c>
       <c r="M20" s="7">
@@ -27196,7 +27196,7 @@
         </is>
       </c>
       <c r="I21" s="61" t="n">
-        <v>0.02966852</v>
+        <v>0.03007701</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
@@ -27234,7 +27234,7 @@
         </is>
       </c>
       <c r="I22" s="61" t="n">
-        <v>0.02688757</v>
+        <v>0.0275087</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         </is>
       </c>
       <c r="I23" s="61" t="n">
-        <v>0.02141662</v>
+        <v>0.02096295</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         </is>
       </c>
       <c r="I24" s="61" t="n">
-        <v>0.02013037</v>
+        <v>0.0204618</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
@@ -27344,25 +27344,25 @@
       </c>
       <c r="H25" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>CMCSA</t>
         </is>
       </c>
       <c r="I25" s="61" t="n">
-        <v>0.01902798</v>
+        <v>0.01936651</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>UNITED PARCEL SERVICE INC CLASS B</t>
+          <t>COMCAST CLASS A</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Communication Services</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr">
         <is>
-          <t>UPS</t>
+          <t>컴캐스트</t>
         </is>
       </c>
       <c r="M25" s="7">
@@ -27382,25 +27382,25 @@
       </c>
       <c r="H26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="I26" s="61" t="n">
-        <v>0.01889418</v>
+        <v>0.01911589</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UNITED PARCEL SERVICE INC CLASS B</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>UPS</t>
         </is>
       </c>
       <c r="M26" s="7">
@@ -27420,25 +27420,25 @@
       </c>
       <c r="H27" s="6" t="inlineStr">
         <is>
-          <t>CMCSA</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="I27" s="61" t="n">
-        <v>0.01864722</v>
+        <v>0.01879568</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>COMCAST CLASS A</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>Communication Services</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr">
         <is>
-          <t>컴캐스트</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="M27" s="7">
@@ -27462,7 +27462,7 @@
         </is>
       </c>
       <c r="I28" s="61" t="n">
-        <v>0.01631382</v>
+        <v>0.01652392</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         </is>
       </c>
       <c r="I29" s="61" t="n">
-        <v>0.01429022</v>
+        <v>0.01441993</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         </is>
       </c>
       <c r="I30" s="61" t="n">
-        <v>0.01426625</v>
+        <v>0.01403728</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         </is>
       </c>
       <c r="I31" s="61" t="n">
-        <v>0.01331659</v>
+        <v>0.01351843</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         </is>
       </c>
       <c r="I32" s="61" t="n">
-        <v>0.01168047</v>
+        <v>0.01151288</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -27627,7 +27627,7 @@
         </is>
       </c>
       <c r="I33" s="61" t="n">
-        <v>0.01145338</v>
+        <v>0.01130699</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -27652,7 +27652,7 @@
         </is>
       </c>
       <c r="I34" s="61" t="n">
-        <v>0.008688399999999999</v>
+        <v>0.00873496</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -27677,7 +27677,7 @@
         </is>
       </c>
       <c r="I35" s="61" t="n">
-        <v>0.008656179999999999</v>
+        <v>0.00845918</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -27702,7 +27702,7 @@
         </is>
       </c>
       <c r="I36" s="61" t="n">
-        <v>0.008282690000000001</v>
+        <v>0.008457630000000001</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -27727,7 +27727,7 @@
         </is>
       </c>
       <c r="I37" s="61" t="n">
-        <v>0.00675392</v>
+        <v>0.00676333</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -27752,7 +27752,7 @@
         </is>
       </c>
       <c r="I38" s="61" t="n">
-        <v>0.00660323</v>
+        <v>0.00655268</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         </is>
       </c>
       <c r="I39" s="61" t="n">
-        <v>0.00592157</v>
+        <v>0.00588993</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -27802,7 +27802,7 @@
         </is>
       </c>
       <c r="I40" s="61" t="n">
-        <v>0.00582091</v>
+        <v>0.005735860000000001</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
@@ -27827,7 +27827,7 @@
         </is>
       </c>
       <c r="I41" s="61" t="n">
-        <v>0.00554762</v>
+        <v>0.00570956</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         </is>
       </c>
       <c r="I42" s="61" t="n">
-        <v>0.005380960000000001</v>
+        <v>0.00522259</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
@@ -27877,7 +27877,7 @@
         </is>
       </c>
       <c r="I43" s="61" t="n">
-        <v>0.00523831</v>
+        <v>0.005124950000000001</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
@@ -27902,7 +27902,7 @@
         </is>
       </c>
       <c r="I44" s="61" t="n">
-        <v>0.00480586</v>
+        <v>0.00480515</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         </is>
       </c>
       <c r="I45" s="61" t="n">
-        <v>0.00470294</v>
+        <v>0.00446331</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
@@ -27948,20 +27948,20 @@
     <row r="46">
       <c r="H46" s="6" t="inlineStr">
         <is>
-          <t>SNA</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="I46" s="61" t="n">
-        <v>0.00438746</v>
+        <v>0.0043609</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>SNAP ON INC</t>
+          <t>APA</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr"/>
@@ -27973,20 +27973,20 @@
     <row r="47">
       <c r="H47" s="6" t="inlineStr">
         <is>
-          <t>EWBC</t>
+          <t>SNA</t>
         </is>
       </c>
       <c r="I47" s="61" t="n">
-        <v>0.00430974</v>
+        <v>0.0043342</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>EAST WEST BANCORP</t>
+          <t>SNAP ON INC</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr"/>
@@ -27998,20 +27998,20 @@
     <row r="48">
       <c r="H48" s="6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GIS</t>
         </is>
       </c>
       <c r="I48" s="61" t="n">
-        <v>0.00426949</v>
+        <v>0.00432092</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>APA</t>
+          <t>GENERAL MILLS INC</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
@@ -28023,20 +28023,20 @@
     <row r="49">
       <c r="H49" s="6" t="inlineStr">
         <is>
-          <t>GIS</t>
+          <t>EWBC</t>
         </is>
       </c>
       <c r="I49" s="61" t="n">
-        <v>0.004215229999999999</v>
+        <v>0.00422368</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>GENERAL MILLS INC</t>
+          <t>EAST WEST BANCORP</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
@@ -28052,7 +28052,7 @@
         </is>
       </c>
       <c r="I50" s="61" t="n">
-        <v>0.00409258</v>
+        <v>0.00418986</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         </is>
       </c>
       <c r="I51" s="61" t="n">
-        <v>0.00254985</v>
+        <v>0.00254429</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -28098,20 +28098,20 @@
     <row r="52">
       <c r="H52" s="6" t="inlineStr">
         <is>
-          <t>AFG</t>
+          <t>BAH</t>
         </is>
       </c>
       <c r="I52" s="61" t="n">
-        <v>0.00248949</v>
+        <v>0.00250666</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>AMERICAN FINANCIAL GROUP</t>
+          <t>BOOZ ALLEN HAMILTON HOLDING CLASS</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr"/>
@@ -28123,15 +28123,15 @@
     <row r="53">
       <c r="H53" s="6" t="inlineStr">
         <is>
-          <t>FNF</t>
+          <t>AFG</t>
         </is>
       </c>
       <c r="I53" s="61" t="n">
-        <v>0.00242606</v>
+        <v>0.00249208</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>FIDELITY NATIONAL FINANCIAL INC</t>
+          <t>AMERICAN FINANCIAL GROUP</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
@@ -28148,20 +28148,20 @@
     <row r="54">
       <c r="H54" s="6" t="inlineStr">
         <is>
-          <t>BAH</t>
+          <t>FNF</t>
         </is>
       </c>
       <c r="I54" s="61" t="n">
-        <v>0.00239541</v>
+        <v>0.00243035</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>BOOZ ALLEN HAMILTON HOLDING CLASS</t>
+          <t>FIDELITY NATIONAL FINANCIAL INC</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr"/>
@@ -28177,7 +28177,7 @@
         </is>
       </c>
       <c r="I55" s="61" t="n">
-        <v>0.00207336</v>
+        <v>0.00204457</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="I56" s="61" t="n">
-        <v>0.00201913</v>
+        <v>0.00201539</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         </is>
       </c>
       <c r="I57" s="61" t="n">
-        <v>0.00184327</v>
+        <v>0.00184531</v>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
@@ -28248,20 +28248,20 @@
     <row r="58">
       <c r="H58" s="6" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>ERIE</t>
         </is>
       </c>
       <c r="I58" s="61" t="n">
-        <v>0.00153684</v>
+        <v>0.0015907</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>MACYS</t>
+          <t>ERIE INDEMNITY CLASS A</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L58" s="6" t="inlineStr"/>
@@ -28273,20 +28273,20 @@
     <row r="59">
       <c r="H59" s="6" t="inlineStr">
         <is>
-          <t>ERIE</t>
+          <t>M</t>
         </is>
       </c>
       <c r="I59" s="61" t="n">
-        <v>0.0015324</v>
+        <v>0.00149303</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>ERIE INDEMNITY CLASS A</t>
+          <t>MACYS</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L59" s="6" t="inlineStr"/>
@@ -28302,7 +28302,7 @@
         </is>
       </c>
       <c r="I60" s="61" t="n">
-        <v>0.00136721</v>
+        <v>0.00139711</v>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
@@ -28327,7 +28327,7 @@
         </is>
       </c>
       <c r="I61" s="61" t="n">
-        <v>0.00133222</v>
+        <v>0.00130646</v>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         </is>
       </c>
       <c r="I62" s="61" t="n">
-        <v>0.00130236</v>
+        <v>0.00127445</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
@@ -28377,7 +28377,7 @@
         </is>
       </c>
       <c r="I63" s="61" t="n">
-        <v>0.00123259</v>
+        <v>0.00123254</v>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         </is>
       </c>
       <c r="I64" s="61" t="n">
-        <v>0.00116678</v>
+        <v>0.00117134</v>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
@@ -28423,20 +28423,20 @@
     <row r="65">
       <c r="H65" s="6" t="inlineStr">
         <is>
-          <t>MC</t>
+          <t>RHI</t>
         </is>
       </c>
       <c r="I65" s="61" t="n">
-        <v>0.00104832</v>
+        <v>0.00103385</v>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>MOELIS CLASS A</t>
+          <t>ROBERT HALF INC</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L65" s="6" t="inlineStr"/>
@@ -28448,20 +28448,20 @@
     <row r="66">
       <c r="H66" s="6" t="inlineStr">
         <is>
-          <t>RHI</t>
+          <t>MC</t>
         </is>
       </c>
       <c r="I66" s="61" t="n">
-        <v>0.00101585</v>
+        <v>0.00102001</v>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>ROBERT HALF INC</t>
+          <t>MOELIS CLASS A</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L66" s="6" t="inlineStr"/>
@@ -28477,7 +28477,7 @@
         </is>
       </c>
       <c r="I67" s="61" t="n">
-        <v>0.0009781900000000001</v>
+        <v>0.0009821999999999999</v>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
@@ -28498,20 +28498,20 @@
     <row r="68">
       <c r="H68" s="6" t="inlineStr">
         <is>
-          <t>CWEN</t>
+          <t>KFY</t>
         </is>
       </c>
       <c r="I68" s="61" t="n">
-        <v>0.0009397300000000001</v>
+        <v>0.00092817</v>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>CLEARWAY ENERGY INC CLASS C</t>
+          <t>KORN FERRY</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L68" s="6" t="inlineStr"/>
@@ -28523,20 +28523,20 @@
     <row r="69">
       <c r="H69" s="6" t="inlineStr">
         <is>
-          <t>KFY</t>
+          <t>CWEN</t>
         </is>
       </c>
       <c r="I69" s="61" t="n">
-        <v>0.00092419</v>
+        <v>0.00091182</v>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>KORN FERRY</t>
+          <t>CLEARWAY ENERGY INC CLASS C</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="L69" s="6" t="inlineStr"/>
@@ -28552,7 +28552,7 @@
         </is>
       </c>
       <c r="I70" s="61" t="n">
-        <v>0.00089745</v>
+        <v>0.00088725</v>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
@@ -28577,7 +28577,7 @@
         </is>
       </c>
       <c r="I71" s="61" t="n">
-        <v>0.0008917500000000001</v>
+        <v>0.00088724</v>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
@@ -28602,7 +28602,7 @@
         </is>
       </c>
       <c r="I72" s="61" t="n">
-        <v>0.0007404</v>
+        <v>0.00074929</v>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
@@ -28623,7 +28623,7 @@
         </is>
       </c>
       <c r="I73" s="61" t="n">
-        <v>0.0006083999999999999</v>
+        <v>0.0006091499999999999</v>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
@@ -28648,7 +28648,7 @@
         </is>
       </c>
       <c r="I74" s="61" t="n">
-        <v>0.00055446</v>
+        <v>0.0005514000000000001</v>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
@@ -28669,20 +28669,20 @@
     <row r="75">
       <c r="H75" s="6" t="inlineStr">
         <is>
-          <t>OFG</t>
+          <t>MZTI</t>
         </is>
       </c>
       <c r="I75" s="61" t="n">
-        <v>0.00050899</v>
+        <v>0.00050382</v>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>OFG BANCORP</t>
+          <t>MARZETTI</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -28694,15 +28694,15 @@
     <row r="76">
       <c r="H76" s="6" t="inlineStr">
         <is>
-          <t>MZTI</t>
+          <t>IPAR</t>
         </is>
       </c>
       <c r="I76" s="61" t="n">
-        <v>0.00050296</v>
+        <v>0.00050049</v>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>MARZETTI</t>
+          <t>INTERPARFUMS INC</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
@@ -28719,20 +28719,20 @@
     <row r="77">
       <c r="H77" s="6" t="inlineStr">
         <is>
-          <t>IPAR</t>
+          <t>OFG</t>
         </is>
       </c>
       <c r="I77" s="61" t="n">
-        <v>0.0004987699999999999</v>
+        <v>0.00049829</v>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>INTERPARFUMS INC</t>
+          <t>OFG BANCORP</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -28748,7 +28748,7 @@
         </is>
       </c>
       <c r="I78" s="61" t="n">
-        <v>0.00048786</v>
+        <v>0.00048302</v>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         </is>
       </c>
       <c r="I79" s="61" t="n">
-        <v>0.00047741</v>
+        <v>0.00047175</v>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
@@ -28798,7 +28798,7 @@
         </is>
       </c>
       <c r="I80" s="61" t="n">
-        <v>0.00045943</v>
+        <v>0.00045395</v>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
@@ -28823,7 +28823,7 @@
         </is>
       </c>
       <c r="I81" s="61" t="n">
-        <v>0.00045034</v>
+        <v>0.00044446</v>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
@@ -28848,7 +28848,7 @@
         </is>
       </c>
       <c r="I82" s="61" t="n">
-        <v>0.00044021</v>
+        <v>0.0004343700000000001</v>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="I83" s="61" t="n">
-        <v>0.00042712</v>
+        <v>0.00042091</v>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
@@ -28894,20 +28894,20 @@
     <row r="84">
       <c r="H84" s="6" t="inlineStr">
         <is>
-          <t>NBHC</t>
+          <t>NSP</t>
         </is>
       </c>
       <c r="I84" s="61" t="n">
-        <v>0.00039517</v>
+        <v>0.00041073</v>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>NATIONAL BANK HOLDINGS CORP CLASS</t>
+          <t>INSPERITY</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="L84" s="6" t="inlineStr"/>
@@ -28919,20 +28919,20 @@
     <row r="85">
       <c r="H85" s="6" t="inlineStr">
         <is>
-          <t>NSP</t>
+          <t>NBHC</t>
         </is>
       </c>
       <c r="I85" s="61" t="n">
-        <v>0.0003921</v>
+        <v>0.00039224</v>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>INSPERITY</t>
+          <t>NATIONAL BANK HOLDINGS CORP CLASS</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -28948,7 +28948,7 @@
         </is>
       </c>
       <c r="I86" s="61" t="n">
-        <v>0.00037257</v>
+        <v>0.00036766</v>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         </is>
       </c>
       <c r="I87" s="61" t="n">
-        <v>0.00035967</v>
+        <v>0.00035277</v>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
@@ -28998,7 +28998,7 @@
         </is>
       </c>
       <c r="I88" s="61" t="n">
-        <v>0.0003416</v>
+        <v>0.00033595</v>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
@@ -29023,7 +29023,7 @@
         </is>
       </c>
       <c r="I89" s="61" t="n">
-        <v>0.00031038</v>
+        <v>0.00031367</v>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
@@ -29044,20 +29044,20 @@
     <row r="90">
       <c r="H90" s="6" t="inlineStr">
         <is>
-          <t>PFBC</t>
+          <t>WEN</t>
         </is>
       </c>
       <c r="I90" s="61" t="n">
-        <v>0.00027592</v>
+        <v>0.00027305</v>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
-          <t>PREFERRED BANK</t>
+          <t>WENDYS</t>
         </is>
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L90" s="6" t="inlineStr"/>
@@ -29069,20 +29069,20 @@
     <row r="91">
       <c r="H91" s="6" t="inlineStr">
         <is>
-          <t>WEN</t>
+          <t>PFBC</t>
         </is>
       </c>
       <c r="I91" s="61" t="n">
-        <v>0.00027261</v>
+        <v>0.00027137</v>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>WENDYS</t>
+          <t>PREFERRED BANK</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -29098,7 +29098,7 @@
         </is>
       </c>
       <c r="I92" s="61" t="n">
-        <v>0.0002511</v>
+        <v>0.00024914</v>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
@@ -29123,7 +29123,7 @@
         </is>
       </c>
       <c r="I93" s="61" t="n">
-        <v>0.00023498</v>
+        <v>0.00022973</v>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
@@ -29148,7 +29148,7 @@
         </is>
       </c>
       <c r="I94" s="61" t="n">
-        <v>0.00023121</v>
+        <v>0.00022626</v>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         </is>
       </c>
       <c r="I95" s="61" t="n">
-        <v>0.00020949</v>
+        <v>0.00020621</v>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         </is>
       </c>
       <c r="I96" s="61" t="n">
-        <v>0.00019564</v>
+        <v>0.00019245</v>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
@@ -29223,7 +29223,7 @@
         </is>
       </c>
       <c r="I97" s="61" t="n">
-        <v>0.0001953</v>
+        <v>0.00019175</v>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
@@ -29248,7 +29248,7 @@
         </is>
       </c>
       <c r="I98" s="61" t="n">
-        <v>0.00018058</v>
+        <v>0.00017011</v>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         </is>
       </c>
       <c r="I99" s="61" t="n">
-        <v>0.0001657</v>
+        <v>0.00016399</v>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
@@ -29298,7 +29298,7 @@
         </is>
       </c>
       <c r="I100" s="61" t="n">
-        <v>0.00013253</v>
+        <v>0.00013187</v>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         </is>
       </c>
       <c r="I101" s="61" t="n">
-        <v>0.00012318</v>
+        <v>0.00012055</v>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
@@ -29340,20 +29340,20 @@
     <row r="102">
       <c r="H102" s="6" t="inlineStr">
         <is>
-          <t>AMSF</t>
+          <t>ETD</t>
         </is>
       </c>
       <c r="I102" s="61" t="n">
-        <v>0.00010126</v>
+        <v>9.593000000000001e-05</v>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>AMERISAFE INC</t>
+          <t>ETHAN ALLEN INTERIORS</t>
         </is>
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="L102" s="6" t="inlineStr"/>
@@ -29365,15 +29365,15 @@
     <row r="103">
       <c r="H103" s="6" t="inlineStr">
         <is>
-          <t>ETD</t>
+          <t>OXM</t>
         </is>
       </c>
       <c r="I103" s="61" t="n">
-        <v>9.547000000000001e-05</v>
+        <v>9.221e-05</v>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>ETHAN ALLEN INTERIORS</t>
+          <t>OXFORD INDUSTRIES INC</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
@@ -29390,20 +29390,20 @@
     <row r="104">
       <c r="H104" s="6" t="inlineStr">
         <is>
-          <t>OXM</t>
+          <t>AMSF</t>
         </is>
       </c>
       <c r="I104" s="61" t="n">
-        <v>9.400000000000001e-05</v>
+        <v>9.132e-05</v>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>OXFORD INDUSTRIES INC</t>
+          <t>AMERISAFE INC</t>
         </is>
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="L104" s="6" t="inlineStr"/>
